--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E3CA0D5-3C34-4F5C-8CAB-440E563AAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79509454-72CB-414D-A1E6-182700FF99BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14176,8 +14176,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="11">
-      <filters blank="1"/>
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2026" month="2" dateTimeGrouping="month"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
@@ -38847,7 +38849,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13" hidden="1">
+    <row r="72" spans="1:13">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -40121,7 +40123,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13" hidden="1">
+    <row r="112" spans="1:13">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -40156,7 +40158,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13" hidden="1">
+    <row r="113" spans="1:13">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -40191,7 +40193,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13" hidden="1">
+    <row r="114" spans="1:13">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -40226,7 +40228,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13" hidden="1">
+    <row r="115" spans="1:13">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -40259,7 +40261,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13" hidden="1">
+    <row r="116" spans="1:13">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -40292,7 +40294,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13" hidden="1">
+    <row r="117" spans="1:13">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -40327,7 +40329,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13" hidden="1">
+    <row r="118" spans="1:13">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -40358,7 +40360,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13" hidden="1">
+    <row r="119" spans="1:13">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -40389,7 +40391,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13" hidden="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -40420,7 +40422,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13" hidden="1">
+    <row r="121" spans="1:13">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -40451,7 +40453,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13" hidden="1">
+    <row r="122" spans="1:13">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -40486,7 +40488,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13" hidden="1">
+    <row r="123" spans="1:13">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -40517,7 +40519,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13" hidden="1">
+    <row r="124" spans="1:13">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -40552,7 +40554,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13" hidden="1">
+    <row r="125" spans="1:13">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -40587,7 +40589,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13" hidden="1">
+    <row r="126" spans="1:13">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -40622,7 +40624,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13" hidden="1">
+    <row r="127" spans="1:13">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -40653,7 +40655,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13" hidden="1">
+    <row r="128" spans="1:13">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -40684,7 +40686,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13" hidden="1">
+    <row r="129" spans="1:13">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -40715,7 +40717,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13" hidden="1">
+    <row r="130" spans="1:13">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -40746,7 +40748,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13" hidden="1">
+    <row r="131" spans="1:13">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -40777,7 +40779,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13" hidden="1">
+    <row r="132" spans="1:13">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -40812,7 +40814,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13" hidden="1">
+    <row r="133" spans="1:13">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -40847,7 +40849,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13" hidden="1">
+    <row r="134" spans="1:13">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -40878,7 +40880,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13" hidden="1">
+    <row r="135" spans="1:13">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -40909,7 +40911,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13" hidden="1">
+    <row r="136" spans="1:13">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -40944,7 +40946,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13" hidden="1">
+    <row r="137" spans="1:13">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -40975,7 +40977,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13" hidden="1">
+    <row r="138" spans="1:13">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -41010,7 +41012,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13" hidden="1">
+    <row r="139" spans="1:13">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -41048,7 +41050,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1">
+    <row r="140" spans="1:13">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -41083,7 +41085,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13" hidden="1">
+    <row r="141" spans="1:13">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -41118,7 +41120,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13" hidden="1">
+    <row r="142" spans="1:13">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -41153,7 +41155,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13" hidden="1">
+    <row r="143" spans="1:13">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -41184,7 +41186,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13" hidden="1">
+    <row r="144" spans="1:13">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -41215,7 +41217,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13" hidden="1">
+    <row r="145" spans="1:13">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -41250,7 +41252,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13" hidden="1">
+    <row r="146" spans="1:13">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -41285,7 +41287,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13" hidden="1">
+    <row r="147" spans="1:13">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -41320,7 +41322,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13" hidden="1">
+    <row r="148" spans="1:13">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -41355,7 +41357,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13" hidden="1">
+    <row r="149" spans="1:13">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -41390,7 +41392,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13" hidden="1">
+    <row r="150" spans="1:13">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -41425,7 +41427,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13" hidden="1">
+    <row r="151" spans="1:13">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -41460,7 +41462,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13" hidden="1">
+    <row r="152" spans="1:13">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -41495,7 +41497,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13" hidden="1">
+    <row r="153" spans="1:13">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -41530,7 +41532,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13" hidden="1">
+    <row r="154" spans="1:13">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -41565,7 +41567,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13" hidden="1">
+    <row r="155" spans="1:13">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -41600,7 +41602,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13" hidden="1">
+    <row r="156" spans="1:13">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -41867,7 +41869,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -41900,7 +41902,7 @@
       <c r="L165" s="15"/>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -41933,7 +41935,7 @@
       <c r="L166" s="15"/>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -41966,7 +41968,7 @@
       <c r="L167" s="15"/>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -41999,7 +42001,7 @@
       <c r="L168" s="15"/>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -42032,7 +42034,7 @@
       <c r="L169" s="15"/>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -42065,7 +42067,7 @@
       <c r="L170" s="15"/>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -42098,7 +42100,7 @@
       <c r="L171" s="15"/>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -42131,7 +42133,7 @@
       <c r="L172" s="15"/>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -42164,7 +42166,7 @@
       <c r="L173" s="15"/>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -42263,7 +42265,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -42296,7 +42298,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -42329,7 +42331,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -42362,7 +42364,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -42395,7 +42397,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -42432,7 +42434,7 @@
       <c r="L181" s="15"/>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -42469,7 +42471,7 @@
       <c r="L182" s="15"/>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -42506,7 +42508,7 @@
       <c r="L183" s="15"/>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -42543,7 +42545,7 @@
       <c r="L184" s="15"/>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -42580,7 +42582,7 @@
       <c r="L185" s="15"/>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -42617,7 +42619,7 @@
       <c r="L186" s="15"/>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -42654,7 +42656,7 @@
       <c r="L187" s="15"/>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -42689,7 +42691,7 @@
       <c r="L188" s="15"/>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -42726,7 +42728,7 @@
       <c r="L189" s="15"/>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -42763,7 +42765,7 @@
       <c r="L190" s="15"/>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -42800,7 +42802,7 @@
       <c r="L191" s="15"/>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -42835,7 +42837,7 @@
       <c r="L192" s="15"/>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -42872,7 +42874,7 @@
       <c r="L193" s="15"/>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -42909,7 +42911,7 @@
       <c r="L194" s="15"/>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -42946,7 +42948,7 @@
       <c r="L195" s="15"/>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -42983,7 +42985,7 @@
       <c r="L196" s="15"/>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -43020,7 +43022,7 @@
       <c r="L197" s="15"/>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -43057,7 +43059,7 @@
       <c r="L198" s="15"/>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -43094,7 +43096,7 @@
       <c r="L199" s="15"/>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -43129,7 +43131,7 @@
       <c r="L200" s="15"/>
       <c r="M200" s="15"/>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" hidden="1">
       <c r="A201" s="14">
         <v>209</v>
       </c>
@@ -43162,7 +43164,7 @@
       <c r="L201" s="15"/>
       <c r="M201" s="15"/>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" hidden="1">
       <c r="A202" s="14">
         <v>210</v>
       </c>
@@ -43195,7 +43197,7 @@
       <c r="L202" s="15"/>
       <c r="M202" s="15"/>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" hidden="1">
       <c r="A203" s="14">
         <v>211</v>
       </c>
@@ -43228,7 +43230,7 @@
       <c r="L203" s="15"/>
       <c r="M203" s="15"/>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" hidden="1">
       <c r="A204" s="14">
         <v>212</v>
       </c>
@@ -43331,7 +43333,7 @@
       <c r="L206" s="15"/>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -43348,7 +43350,7 @@
       <c r="L207" s="15"/>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -43365,7 +43367,7 @@
       <c r="L208" s="15"/>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -43382,7 +43384,7 @@
       <c r="L209" s="15"/>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -43399,7 +43401,7 @@
       <c r="L210" s="15"/>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" hidden="1">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -43416,7 +43418,7 @@
       <c r="L211" s="15"/>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" hidden="1">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -43433,7 +43435,7 @@
       <c r="L212" s="15"/>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" hidden="1">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -43450,7 +43452,7 @@
       <c r="L213" s="15"/>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" hidden="1">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -43467,7 +43469,7 @@
       <c r="L214" s="15"/>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" hidden="1">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -43484,7 +43486,7 @@
       <c r="L215" s="15"/>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" hidden="1">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -43501,7 +43503,7 @@
       <c r="L216" s="15"/>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" hidden="1">
       <c r="A217" s="14">
         <v>225</v>
       </c>
@@ -43518,7 +43520,7 @@
       <c r="L217" s="15"/>
       <c r="M217" s="15"/>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" hidden="1">
       <c r="A218" s="14">
         <v>226</v>
       </c>
@@ -43535,7 +43537,7 @@
       <c r="L218" s="15"/>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" hidden="1">
       <c r="A219" s="14">
         <v>227</v>
       </c>
@@ -43552,7 +43554,7 @@
       <c r="L219" s="15"/>
       <c r="M219" s="15"/>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" hidden="1">
       <c r="A220" s="14">
         <v>228</v>
       </c>
@@ -43569,7 +43571,7 @@
       <c r="L220" s="15"/>
       <c r="M220" s="15"/>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" hidden="1">
       <c r="A221" s="14">
         <v>229</v>
       </c>
@@ -43586,7 +43588,7 @@
       <c r="L221" s="15"/>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" hidden="1">
       <c r="A222" s="14">
         <v>230</v>
       </c>
@@ -43603,7 +43605,7 @@
       <c r="L222" s="15"/>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" hidden="1">
       <c r="A223" s="14">
         <v>231</v>
       </c>
@@ -43620,7 +43622,7 @@
       <c r="L223" s="15"/>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" hidden="1">
       <c r="A224" s="14">
         <v>232</v>
       </c>
@@ -43637,7 +43639,7 @@
       <c r="L224" s="15"/>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" hidden="1">
       <c r="A225" s="14">
         <v>233</v>
       </c>
@@ -43654,7 +43656,7 @@
       <c r="L225" s="15"/>
       <c r="M225" s="15"/>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" hidden="1">
       <c r="A226" s="14">
         <v>234</v>
       </c>
@@ -43671,7 +43673,7 @@
       <c r="L226" s="15"/>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" ht="14.25">
+    <row r="227" spans="1:13" ht="14.25" hidden="1">
       <c r="A227" s="14">
         <v>235</v>
       </c>
@@ -43688,7 +43690,7 @@
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13" ht="14.25">
+    <row r="228" spans="1:13" ht="14.25" hidden="1">
       <c r="A228" s="14">
         <v>236</v>
       </c>
@@ -43705,7 +43707,7 @@
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13" ht="14.25">
+    <row r="229" spans="1:13" ht="14.25" hidden="1">
       <c r="A229" s="14">
         <v>237</v>
       </c>
@@ -43722,7 +43724,7 @@
       <c r="L229" s="15"/>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13" ht="14.25">
+    <row r="230" spans="1:13" ht="14.25" hidden="1">
       <c r="A230" s="14">
         <v>238</v>
       </c>
@@ -43739,7 +43741,7 @@
       <c r="L230" s="15"/>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13" ht="14.25">
+    <row r="231" spans="1:13" ht="14.25" hidden="1">
       <c r="A231" s="14">
         <v>239</v>
       </c>
@@ -43756,7 +43758,7 @@
       <c r="L231" s="15"/>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13" ht="14.25">
+    <row r="232" spans="1:13" ht="14.25" hidden="1">
       <c r="A232" s="14">
         <v>240</v>
       </c>
@@ -43773,7 +43775,7 @@
       <c r="L232" s="15"/>
       <c r="M232" s="15"/>
     </row>
-    <row r="233" spans="1:13" ht="14.25">
+    <row r="233" spans="1:13" ht="14.25" hidden="1">
       <c r="A233" s="14">
         <v>241</v>
       </c>
@@ -43790,7 +43792,7 @@
       <c r="L233" s="15"/>
       <c r="M233" s="15"/>
     </row>
-    <row r="234" spans="1:13" ht="14.25">
+    <row r="234" spans="1:13" ht="14.25" hidden="1">
       <c r="A234" s="14">
         <v>242</v>
       </c>
@@ -43807,7 +43809,7 @@
       <c r="L234" s="15"/>
       <c r="M234" s="15"/>
     </row>
-    <row r="235" spans="1:13" ht="14.25">
+    <row r="235" spans="1:13" ht="14.25" hidden="1">
       <c r="A235" s="14">
         <v>243</v>
       </c>
@@ -43824,7 +43826,7 @@
       <c r="L235" s="15"/>
       <c r="M235" s="15"/>
     </row>
-    <row r="236" spans="1:13" ht="14.25">
+    <row r="236" spans="1:13" ht="14.25" hidden="1">
       <c r="A236" s="14">
         <v>244</v>
       </c>
@@ -43841,7 +43843,7 @@
       <c r="L236" s="15"/>
       <c r="M236" s="15"/>
     </row>
-    <row r="237" spans="1:13" ht="14.25">
+    <row r="237" spans="1:13" ht="14.25" hidden="1">
       <c r="A237" s="14">
         <v>245</v>
       </c>
@@ -43858,7 +43860,7 @@
       <c r="L237" s="15"/>
       <c r="M237" s="15"/>
     </row>
-    <row r="238" spans="1:13" ht="14.25">
+    <row r="238" spans="1:13" ht="14.25" hidden="1">
       <c r="A238" s="14">
         <v>246</v>
       </c>
@@ -43875,7 +43877,7 @@
       <c r="L238" s="15"/>
       <c r="M238" s="15"/>
     </row>
-    <row r="239" spans="1:13" ht="14.25">
+    <row r="239" spans="1:13" ht="14.25" hidden="1">
       <c r="A239" s="14">
         <v>247</v>
       </c>
@@ -43892,7 +43894,7 @@
       <c r="L239" s="15"/>
       <c r="M239" s="15"/>
     </row>
-    <row r="240" spans="1:13" ht="14.25">
+    <row r="240" spans="1:13" ht="14.25" hidden="1">
       <c r="A240" s="14">
         <v>248</v>
       </c>
@@ -43909,7 +43911,7 @@
       <c r="L240" s="15"/>
       <c r="M240" s="15"/>
     </row>
-    <row r="241" spans="1:13" ht="14.25">
+    <row r="241" spans="1:13" ht="14.25" hidden="1">
       <c r="A241" s="14">
         <v>249</v>
       </c>
@@ -43926,7 +43928,7 @@
       <c r="L241" s="15"/>
       <c r="M241" s="15"/>
     </row>
-    <row r="242" spans="1:13" ht="14.25">
+    <row r="242" spans="1:13" ht="14.25" hidden="1">
       <c r="A242" s="14">
         <v>250</v>
       </c>
@@ -43943,7 +43945,7 @@
       <c r="L242" s="15"/>
       <c r="M242" s="15"/>
     </row>
-    <row r="243" spans="1:13" ht="14.25">
+    <row r="243" spans="1:13" ht="14.25" hidden="1">
       <c r="A243" s="14">
         <v>251</v>
       </c>
@@ -43960,7 +43962,7 @@
       <c r="L243" s="15"/>
       <c r="M243" s="15"/>
     </row>
-    <row r="244" spans="1:13" ht="14.25">
+    <row r="244" spans="1:13" ht="14.25" hidden="1">
       <c r="A244" s="14">
         <v>252</v>
       </c>
@@ -43977,7 +43979,7 @@
       <c r="L244" s="15"/>
       <c r="M244" s="15"/>
     </row>
-    <row r="245" spans="1:13" ht="14.25">
+    <row r="245" spans="1:13" ht="14.25" hidden="1">
       <c r="A245" s="14">
         <v>253</v>
       </c>
@@ -43994,7 +43996,7 @@
       <c r="L245" s="15"/>
       <c r="M245" s="15"/>
     </row>
-    <row r="246" spans="1:13" ht="14.25">
+    <row r="246" spans="1:13" ht="14.25" hidden="1">
       <c r="A246" s="14">
         <v>254</v>
       </c>
@@ -44011,7 +44013,7 @@
       <c r="L246" s="15"/>
       <c r="M246" s="15"/>
     </row>
-    <row r="247" spans="1:13" ht="14.25">
+    <row r="247" spans="1:13" ht="14.25" hidden="1">
       <c r="A247" s="14">
         <v>255</v>
       </c>
@@ -44028,7 +44030,7 @@
       <c r="L247" s="15"/>
       <c r="M247" s="15"/>
     </row>
-    <row r="248" spans="1:13" ht="14.25">
+    <row r="248" spans="1:13" ht="14.25" hidden="1">
       <c r="A248" s="14">
         <v>256</v>
       </c>
@@ -44045,7 +44047,7 @@
       <c r="L248" s="15"/>
       <c r="M248" s="15"/>
     </row>
-    <row r="249" spans="1:13" ht="14.25">
+    <row r="249" spans="1:13" ht="14.25" hidden="1">
       <c r="A249" s="14">
         <v>257</v>
       </c>
@@ -44062,7 +44064,7 @@
       <c r="L249" s="15"/>
       <c r="M249" s="15"/>
     </row>
-    <row r="250" spans="1:13" ht="14.25">
+    <row r="250" spans="1:13" ht="14.25" hidden="1">
       <c r="A250" s="14">
         <v>258</v>
       </c>
@@ -44079,7 +44081,7 @@
       <c r="L250" s="15"/>
       <c r="M250" s="15"/>
     </row>
-    <row r="251" spans="1:13" ht="14.25">
+    <row r="251" spans="1:13" ht="14.25" hidden="1">
       <c r="A251" s="14">
         <v>259</v>
       </c>
@@ -44096,7 +44098,7 @@
       <c r="L251" s="15"/>
       <c r="M251" s="15"/>
     </row>
-    <row r="252" spans="1:13" ht="14.25">
+    <row r="252" spans="1:13" ht="14.25" hidden="1">
       <c r="A252" s="14">
         <v>260</v>
       </c>
@@ -44113,7 +44115,7 @@
       <c r="L252" s="15"/>
       <c r="M252" s="15"/>
     </row>
-    <row r="253" spans="1:13" ht="14.25">
+    <row r="253" spans="1:13" ht="14.25" hidden="1">
       <c r="A253" s="14">
         <v>261</v>
       </c>
@@ -44130,7 +44132,7 @@
       <c r="L253" s="15"/>
       <c r="M253" s="15"/>
     </row>
-    <row r="254" spans="1:13" ht="14.25">
+    <row r="254" spans="1:13" ht="14.25" hidden="1">
       <c r="A254" s="14">
         <v>262</v>
       </c>
@@ -44147,7 +44149,7 @@
       <c r="L254" s="15"/>
       <c r="M254" s="15"/>
     </row>
-    <row r="255" spans="1:13" ht="14.25">
+    <row r="255" spans="1:13" ht="14.25" hidden="1">
       <c r="A255" s="14">
         <v>263</v>
       </c>
@@ -44164,7 +44166,7 @@
       <c r="L255" s="15"/>
       <c r="M255" s="15"/>
     </row>
-    <row r="256" spans="1:13" ht="14.25">
+    <row r="256" spans="1:13" ht="14.25" hidden="1">
       <c r="A256" s="14">
         <v>264</v>
       </c>
@@ -44181,7 +44183,7 @@
       <c r="L256" s="15"/>
       <c r="M256" s="15"/>
     </row>
-    <row r="257" spans="1:13" ht="14.25">
+    <row r="257" spans="1:13" ht="14.25" hidden="1">
       <c r="A257" s="14">
         <v>265</v>
       </c>
@@ -44198,7 +44200,7 @@
       <c r="L257" s="15"/>
       <c r="M257" s="15"/>
     </row>
-    <row r="258" spans="1:13" ht="14.25">
+    <row r="258" spans="1:13" ht="14.25" hidden="1">
       <c r="A258" s="14">
         <v>266</v>
       </c>
@@ -44215,7 +44217,7 @@
       <c r="L258" s="15"/>
       <c r="M258" s="15"/>
     </row>
-    <row r="259" spans="1:13" ht="14.25">
+    <row r="259" spans="1:13" ht="14.25" hidden="1">
       <c r="A259" s="14">
         <v>267</v>
       </c>
@@ -44232,7 +44234,7 @@
       <c r="L259" s="15"/>
       <c r="M259" s="15"/>
     </row>
-    <row r="260" spans="1:13" ht="14.25">
+    <row r="260" spans="1:13" ht="14.25" hidden="1">
       <c r="A260" s="14">
         <v>268</v>
       </c>
@@ -44249,7 +44251,7 @@
       <c r="L260" s="15"/>
       <c r="M260" s="15"/>
     </row>
-    <row r="261" spans="1:13" ht="14.25">
+    <row r="261" spans="1:13" ht="14.25" hidden="1">
       <c r="A261" s="14">
         <v>269</v>
       </c>
@@ -44266,7 +44268,7 @@
       <c r="L261" s="15"/>
       <c r="M261" s="15"/>
     </row>
-    <row r="262" spans="1:13" ht="14.25">
+    <row r="262" spans="1:13" ht="14.25" hidden="1">
       <c r="A262" s="14">
         <v>270</v>
       </c>
@@ -44283,7 +44285,7 @@
       <c r="L262" s="15"/>
       <c r="M262" s="15"/>
     </row>
-    <row r="263" spans="1:13" ht="14.25">
+    <row r="263" spans="1:13" ht="14.25" hidden="1">
       <c r="A263" s="14">
         <v>271</v>
       </c>
@@ -44300,7 +44302,7 @@
       <c r="L263" s="15"/>
       <c r="M263" s="15"/>
     </row>
-    <row r="264" spans="1:13" ht="14.25">
+    <row r="264" spans="1:13" ht="14.25" hidden="1">
       <c r="A264" s="14">
         <v>272</v>
       </c>
@@ -44317,7 +44319,7 @@
       <c r="L264" s="15"/>
       <c r="M264" s="15"/>
     </row>
-    <row r="265" spans="1:13" ht="14.25">
+    <row r="265" spans="1:13" ht="14.25" hidden="1">
       <c r="A265" s="14">
         <v>273</v>
       </c>
@@ -44334,7 +44336,7 @@
       <c r="L265" s="15"/>
       <c r="M265" s="15"/>
     </row>
-    <row r="266" spans="1:13" ht="14.25">
+    <row r="266" spans="1:13" ht="14.25" hidden="1">
       <c r="A266" s="14">
         <v>274</v>
       </c>
@@ -44351,7 +44353,7 @@
       <c r="L266" s="15"/>
       <c r="M266" s="15"/>
     </row>
-    <row r="267" spans="1:13" ht="14.25">
+    <row r="267" spans="1:13" ht="14.25" hidden="1">
       <c r="A267" s="14">
         <v>275</v>
       </c>
@@ -44368,7 +44370,7 @@
       <c r="L267" s="15"/>
       <c r="M267" s="15"/>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" hidden="1">
       <c r="A268" s="14">
         <v>276</v>
       </c>
@@ -44385,7 +44387,7 @@
       <c r="L268" s="15"/>
       <c r="M268" s="15"/>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" hidden="1">
       <c r="A269" s="14">
         <v>277</v>
       </c>
@@ -44402,7 +44404,7 @@
       <c r="L269" s="15"/>
       <c r="M269" s="15"/>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" hidden="1">
       <c r="A270" s="14">
         <v>278</v>
       </c>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66605EA2-E6B4-4069-844B-31CC9C3A25CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62D5EA01-5F5B-4BF3-8FBD-E7E1D50BF6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="324">
   <si>
     <t>日付</t>
   </si>
@@ -14180,9 +14180,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
     <filterColumn colId="1">
-      <filters blank="1">
-        <dateGroupItem year="2026" dateTimeGrouping="year"/>
+      <filters>
+        <dateGroupItem year="2026" month="2" dateTimeGrouping="month"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
@@ -32893,72 +32896,214 @@
     </row>
   </sheetData>
   <mergeCells count="302">
-    <mergeCell ref="B446:E446"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B472:E472"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B341:E341"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B346:E346"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B366:E366"/>
-    <mergeCell ref="B355:E355"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B326:E326"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B331:E331"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B470:E470"/>
+    <mergeCell ref="B471:E471"/>
+    <mergeCell ref="B440:E440"/>
+    <mergeCell ref="B424:E424"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B430:E430"/>
+    <mergeCell ref="B437:E437"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B441:E441"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B443:E443"/>
+    <mergeCell ref="B444:E444"/>
+    <mergeCell ref="B445:E445"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B394:E394"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B427:E427"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B414:E414"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B380:E380"/>
+    <mergeCell ref="B381:E381"/>
+    <mergeCell ref="B382:E382"/>
+    <mergeCell ref="B383:E383"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
     <mergeCell ref="B172:E172"/>
     <mergeCell ref="B174:E174"/>
     <mergeCell ref="B175:E175"/>
@@ -32983,218 +33128,76 @@
     <mergeCell ref="B195:E195"/>
     <mergeCell ref="B196:E196"/>
     <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B326:E326"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B331:E331"/>
+    <mergeCell ref="B446:E446"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B472:E472"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B341:E341"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B346:E346"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B366:E366"/>
+    <mergeCell ref="B355:E355"/>
     <mergeCell ref="B371:E371"/>
     <mergeCell ref="B372:E372"/>
     <mergeCell ref="B373:E373"/>
     <mergeCell ref="B384:E384"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B380:E380"/>
-    <mergeCell ref="B381:E381"/>
-    <mergeCell ref="B382:E382"/>
-    <mergeCell ref="B383:E383"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B394:E394"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B427:E427"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B414:E414"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B470:E470"/>
-    <mergeCell ref="B471:E471"/>
-    <mergeCell ref="B440:E440"/>
-    <mergeCell ref="B424:E424"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B430:E430"/>
-    <mergeCell ref="B437:E437"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B441:E441"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B443:E443"/>
-    <mergeCell ref="B444:E444"/>
-    <mergeCell ref="B445:E445"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -38864,7 +38867,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -38900,7 +38903,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" hidden="1">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -39051,7 +39054,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -39084,7 +39087,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -39117,7 +39120,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" hidden="1">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -39150,7 +39153,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" hidden="1">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -39183,7 +39186,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" hidden="1">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -39216,7 +39219,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" hidden="1">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -39249,7 +39252,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" hidden="1">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -39282,7 +39285,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" hidden="1">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -39315,7 +39318,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" hidden="1">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -39348,7 +39351,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" hidden="1">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -39381,7 +39384,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" hidden="1">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -39414,7 +39417,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" hidden="1">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -39447,7 +39450,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" hidden="1">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -39480,7 +39483,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" hidden="1">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -39513,7 +39516,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" hidden="1">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -39546,7 +39549,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" hidden="1">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -39579,7 +39582,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" hidden="1">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -39612,7 +39615,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" hidden="1">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -39645,7 +39648,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" hidden="1">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -39678,7 +39681,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" hidden="1">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -39711,7 +39714,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" hidden="1">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -39744,7 +39747,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" hidden="1">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -39777,7 +39780,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" hidden="1">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -39810,7 +39813,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" hidden="1">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -39843,7 +39846,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" hidden="1">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -39876,7 +39879,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" hidden="1">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -39909,7 +39912,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" hidden="1">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -40174,7 +40177,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" hidden="1">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -40209,7 +40212,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" hidden="1">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -40244,7 +40247,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" hidden="1">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -40279,7 +40282,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" hidden="1">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -40312,7 +40315,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" hidden="1">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -40345,7 +40348,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" hidden="1">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -40380,7 +40383,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" hidden="1">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -40411,7 +40414,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" hidden="1">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -40442,7 +40445,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" hidden="1">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -40473,7 +40476,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" hidden="1">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -40504,7 +40507,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" hidden="1">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -40539,7 +40542,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" hidden="1">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -40570,7 +40573,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" hidden="1">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -40605,7 +40608,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" hidden="1">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -40640,7 +40643,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" hidden="1">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -40675,7 +40678,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" hidden="1">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -40706,7 +40709,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" hidden="1">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -40737,7 +40740,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" hidden="1">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -40768,7 +40771,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" hidden="1">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -40799,7 +40802,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" hidden="1">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -40830,7 +40833,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" hidden="1">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -40865,7 +40868,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" hidden="1">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -40900,7 +40903,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" hidden="1">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -40931,7 +40934,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" hidden="1">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -40962,7 +40965,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" hidden="1">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -40997,7 +41000,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" hidden="1">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -41028,7 +41031,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" hidden="1">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -41063,7 +41066,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" hidden="1">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -41101,7 +41104,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" hidden="1">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -41136,7 +41139,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" hidden="1">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -41171,7 +41174,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" hidden="1">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -41206,7 +41209,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" hidden="1">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -41237,7 +41240,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" hidden="1">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -41268,7 +41271,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" hidden="1">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -41303,7 +41306,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" hidden="1">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -41338,7 +41341,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" hidden="1">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -41373,7 +41376,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" hidden="1">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -41408,7 +41411,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" hidden="1">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -41443,7 +41446,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" hidden="1">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -41478,7 +41481,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" hidden="1">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -41513,7 +41516,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" hidden="1">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -41548,7 +41551,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" hidden="1">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -41583,7 +41586,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" hidden="1">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -41618,7 +41621,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" hidden="1">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -41653,7 +41656,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" hidden="1">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -41804,7 +41807,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" hidden="1">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -41833,7 +41836,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" hidden="1">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -41862,7 +41865,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" hidden="1">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -41891,7 +41894,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" hidden="1">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -41920,7 +41923,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -41953,7 +41956,7 @@
       <c r="L165" s="15"/>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -41986,7 +41989,7 @@
       <c r="L166" s="15"/>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -42019,7 +42022,7 @@
       <c r="L167" s="15"/>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -42052,7 +42055,7 @@
       <c r="L168" s="15"/>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -42085,7 +42088,7 @@
       <c r="L169" s="15"/>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -42118,7 +42121,7 @@
       <c r="L170" s="15"/>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -42151,7 +42154,7 @@
       <c r="L171" s="15"/>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -42184,7 +42187,7 @@
       <c r="L172" s="15"/>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -42217,7 +42220,7 @@
       <c r="L173" s="15"/>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -42250,7 +42253,7 @@
       <c r="L174" s="15"/>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" hidden="1">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -42283,7 +42286,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" hidden="1">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -42316,7 +42319,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" hidden="1">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -42349,7 +42352,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" hidden="1">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -42382,7 +42385,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" hidden="1">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -42415,7 +42418,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" hidden="1">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -42448,7 +42451,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -42485,7 +42488,7 @@
       <c r="L181" s="15"/>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -42522,7 +42525,7 @@
       <c r="L182" s="15"/>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -42559,7 +42562,7 @@
       <c r="L183" s="15"/>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -42596,7 +42599,7 @@
       <c r="L184" s="15"/>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -42633,7 +42636,7 @@
       <c r="L185" s="15"/>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -42670,7 +42673,7 @@
       <c r="L186" s="15"/>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -42707,7 +42710,7 @@
       <c r="L187" s="15"/>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -42742,7 +42745,7 @@
       <c r="L188" s="15"/>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -42779,7 +42782,7 @@
       <c r="L189" s="15"/>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -42816,7 +42819,7 @@
       <c r="L190" s="15"/>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -42853,7 +42856,7 @@
       <c r="L191" s="15"/>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -42888,7 +42891,7 @@
       <c r="L192" s="15"/>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -42925,7 +42928,7 @@
       <c r="L193" s="15"/>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -42962,7 +42965,7 @@
       <c r="L194" s="15"/>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -42999,7 +43002,7 @@
       <c r="L195" s="15"/>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -43036,7 +43039,7 @@
       <c r="L196" s="15"/>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -43073,7 +43076,7 @@
       <c r="L197" s="15"/>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -43110,7 +43113,7 @@
       <c r="L198" s="15"/>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -43147,7 +43150,7 @@
       <c r="L199" s="15"/>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -43248,7 +43251,7 @@
       <c r="L202" s="15"/>
       <c r="M202" s="15"/>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" hidden="1">
       <c r="A203" s="14">
         <v>211</v>
       </c>
@@ -43281,7 +43284,7 @@
       <c r="L203" s="15"/>
       <c r="M203" s="15"/>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" hidden="1">
       <c r="A204" s="14">
         <v>212</v>
       </c>
@@ -43346,7 +43349,9 @@
       <c r="K205" s="22">
         <v>11000</v>
       </c>
-      <c r="L205" s="15"/>
+      <c r="L205" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="M205" s="15"/>
     </row>
     <row r="206" spans="1:13">
@@ -43381,10 +43386,12 @@
       <c r="K206" s="22">
         <v>11000</v>
       </c>
-      <c r="L206" s="15"/>
+      <c r="L206" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -43401,7 +43408,7 @@
       <c r="L207" s="15"/>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -43418,7 +43425,7 @@
       <c r="L208" s="15"/>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -43435,7 +43442,7 @@
       <c r="L209" s="15"/>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -43452,7 +43459,7 @@
       <c r="L210" s="15"/>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" hidden="1">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -43469,7 +43476,7 @@
       <c r="L211" s="15"/>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" hidden="1">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -43486,7 +43493,7 @@
       <c r="L212" s="15"/>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" hidden="1">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -43503,7 +43510,7 @@
       <c r="L213" s="15"/>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" hidden="1">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -43520,7 +43527,7 @@
       <c r="L214" s="15"/>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" hidden="1">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -43537,7 +43544,7 @@
       <c r="L215" s="15"/>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" hidden="1">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -43554,7 +43561,7 @@
       <c r="L216" s="15"/>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" hidden="1">
       <c r="A217" s="14">
         <v>225</v>
       </c>
@@ -43571,7 +43578,7 @@
       <c r="L217" s="15"/>
       <c r="M217" s="15"/>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" hidden="1">
       <c r="A218" s="14">
         <v>226</v>
       </c>
@@ -43588,7 +43595,7 @@
       <c r="L218" s="15"/>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" hidden="1">
       <c r="A219" s="14">
         <v>227</v>
       </c>
@@ -43605,7 +43612,7 @@
       <c r="L219" s="15"/>
       <c r="M219" s="15"/>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" hidden="1">
       <c r="A220" s="14">
         <v>228</v>
       </c>
@@ -43622,7 +43629,7 @@
       <c r="L220" s="15"/>
       <c r="M220" s="15"/>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" hidden="1">
       <c r="A221" s="14">
         <v>229</v>
       </c>
@@ -43639,7 +43646,7 @@
       <c r="L221" s="15"/>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" hidden="1">
       <c r="A222" s="14">
         <v>230</v>
       </c>
@@ -43656,7 +43663,7 @@
       <c r="L222" s="15"/>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" hidden="1">
       <c r="A223" s="14">
         <v>231</v>
       </c>
@@ -43673,7 +43680,7 @@
       <c r="L223" s="15"/>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" hidden="1">
       <c r="A224" s="14">
         <v>232</v>
       </c>
@@ -43690,7 +43697,7 @@
       <c r="L224" s="15"/>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" hidden="1">
       <c r="A225" s="14">
         <v>233</v>
       </c>
@@ -43707,7 +43714,7 @@
       <c r="L225" s="15"/>
       <c r="M225" s="15"/>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" hidden="1">
       <c r="A226" s="14">
         <v>234</v>
       </c>
@@ -43724,7 +43731,7 @@
       <c r="L226" s="15"/>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" ht="14.25">
+    <row r="227" spans="1:13" ht="14.25" hidden="1">
       <c r="A227" s="14">
         <v>235</v>
       </c>
@@ -43741,7 +43748,7 @@
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13" ht="14.25">
+    <row r="228" spans="1:13" ht="14.25" hidden="1">
       <c r="A228" s="14">
         <v>236</v>
       </c>
@@ -43758,7 +43765,7 @@
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13" ht="14.25">
+    <row r="229" spans="1:13" ht="14.25" hidden="1">
       <c r="A229" s="14">
         <v>237</v>
       </c>
@@ -43775,7 +43782,7 @@
       <c r="L229" s="15"/>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13" ht="14.25">
+    <row r="230" spans="1:13" ht="14.25" hidden="1">
       <c r="A230" s="14">
         <v>238</v>
       </c>
@@ -43792,7 +43799,7 @@
       <c r="L230" s="15"/>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13" ht="14.25">
+    <row r="231" spans="1:13" ht="14.25" hidden="1">
       <c r="A231" s="14">
         <v>239</v>
       </c>
@@ -43809,7 +43816,7 @@
       <c r="L231" s="15"/>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13" ht="14.25">
+    <row r="232" spans="1:13" ht="14.25" hidden="1">
       <c r="A232" s="14">
         <v>240</v>
       </c>
@@ -43826,7 +43833,7 @@
       <c r="L232" s="15"/>
       <c r="M232" s="15"/>
     </row>
-    <row r="233" spans="1:13" ht="14.25">
+    <row r="233" spans="1:13" ht="14.25" hidden="1">
       <c r="A233" s="14">
         <v>241</v>
       </c>
@@ -43843,7 +43850,7 @@
       <c r="L233" s="15"/>
       <c r="M233" s="15"/>
     </row>
-    <row r="234" spans="1:13" ht="14.25">
+    <row r="234" spans="1:13" ht="14.25" hidden="1">
       <c r="A234" s="14">
         <v>242</v>
       </c>
@@ -43860,7 +43867,7 @@
       <c r="L234" s="15"/>
       <c r="M234" s="15"/>
     </row>
-    <row r="235" spans="1:13" ht="14.25">
+    <row r="235" spans="1:13" ht="14.25" hidden="1">
       <c r="A235" s="14">
         <v>243</v>
       </c>
@@ -43877,7 +43884,7 @@
       <c r="L235" s="15"/>
       <c r="M235" s="15"/>
     </row>
-    <row r="236" spans="1:13" ht="14.25">
+    <row r="236" spans="1:13" ht="14.25" hidden="1">
       <c r="A236" s="14">
         <v>244</v>
       </c>
@@ -43894,7 +43901,7 @@
       <c r="L236" s="15"/>
       <c r="M236" s="15"/>
     </row>
-    <row r="237" spans="1:13" ht="14.25">
+    <row r="237" spans="1:13" ht="14.25" hidden="1">
       <c r="A237" s="14">
         <v>245</v>
       </c>
@@ -43911,7 +43918,7 @@
       <c r="L237" s="15"/>
       <c r="M237" s="15"/>
     </row>
-    <row r="238" spans="1:13" ht="14.25">
+    <row r="238" spans="1:13" ht="14.25" hidden="1">
       <c r="A238" s="14">
         <v>246</v>
       </c>
@@ -43928,7 +43935,7 @@
       <c r="L238" s="15"/>
       <c r="M238" s="15"/>
     </row>
-    <row r="239" spans="1:13" ht="14.25">
+    <row r="239" spans="1:13" ht="14.25" hidden="1">
       <c r="A239" s="14">
         <v>247</v>
       </c>
@@ -43945,7 +43952,7 @@
       <c r="L239" s="15"/>
       <c r="M239" s="15"/>
     </row>
-    <row r="240" spans="1:13" ht="14.25">
+    <row r="240" spans="1:13" ht="14.25" hidden="1">
       <c r="A240" s="14">
         <v>248</v>
       </c>
@@ -43962,7 +43969,7 @@
       <c r="L240" s="15"/>
       <c r="M240" s="15"/>
     </row>
-    <row r="241" spans="1:13" ht="14.25">
+    <row r="241" spans="1:13" ht="14.25" hidden="1">
       <c r="A241" s="14">
         <v>249</v>
       </c>
@@ -43979,7 +43986,7 @@
       <c r="L241" s="15"/>
       <c r="M241" s="15"/>
     </row>
-    <row r="242" spans="1:13" ht="14.25">
+    <row r="242" spans="1:13" ht="14.25" hidden="1">
       <c r="A242" s="14">
         <v>250</v>
       </c>
@@ -43996,7 +44003,7 @@
       <c r="L242" s="15"/>
       <c r="M242" s="15"/>
     </row>
-    <row r="243" spans="1:13" ht="14.25">
+    <row r="243" spans="1:13" ht="14.25" hidden="1">
       <c r="A243" s="14">
         <v>251</v>
       </c>
@@ -44013,7 +44020,7 @@
       <c r="L243" s="15"/>
       <c r="M243" s="15"/>
     </row>
-    <row r="244" spans="1:13" ht="14.25">
+    <row r="244" spans="1:13" ht="14.25" hidden="1">
       <c r="A244" s="14">
         <v>252</v>
       </c>
@@ -44030,7 +44037,7 @@
       <c r="L244" s="15"/>
       <c r="M244" s="15"/>
     </row>
-    <row r="245" spans="1:13" ht="14.25">
+    <row r="245" spans="1:13" ht="14.25" hidden="1">
       <c r="A245" s="14">
         <v>253</v>
       </c>
@@ -44047,7 +44054,7 @@
       <c r="L245" s="15"/>
       <c r="M245" s="15"/>
     </row>
-    <row r="246" spans="1:13" ht="14.25">
+    <row r="246" spans="1:13" ht="14.25" hidden="1">
       <c r="A246" s="14">
         <v>254</v>
       </c>
@@ -44064,7 +44071,7 @@
       <c r="L246" s="15"/>
       <c r="M246" s="15"/>
     </row>
-    <row r="247" spans="1:13" ht="14.25">
+    <row r="247" spans="1:13" ht="14.25" hidden="1">
       <c r="A247" s="14">
         <v>255</v>
       </c>
@@ -44081,7 +44088,7 @@
       <c r="L247" s="15"/>
       <c r="M247" s="15"/>
     </row>
-    <row r="248" spans="1:13" ht="14.25">
+    <row r="248" spans="1:13" ht="14.25" hidden="1">
       <c r="A248" s="14">
         <v>256</v>
       </c>
@@ -44098,7 +44105,7 @@
       <c r="L248" s="15"/>
       <c r="M248" s="15"/>
     </row>
-    <row r="249" spans="1:13" ht="14.25">
+    <row r="249" spans="1:13" ht="14.25" hidden="1">
       <c r="A249" s="14">
         <v>257</v>
       </c>
@@ -44115,7 +44122,7 @@
       <c r="L249" s="15"/>
       <c r="M249" s="15"/>
     </row>
-    <row r="250" spans="1:13" ht="14.25">
+    <row r="250" spans="1:13" ht="14.25" hidden="1">
       <c r="A250" s="14">
         <v>258</v>
       </c>
@@ -44132,7 +44139,7 @@
       <c r="L250" s="15"/>
       <c r="M250" s="15"/>
     </row>
-    <row r="251" spans="1:13" ht="14.25">
+    <row r="251" spans="1:13" ht="14.25" hidden="1">
       <c r="A251" s="14">
         <v>259</v>
       </c>
@@ -44149,7 +44156,7 @@
       <c r="L251" s="15"/>
       <c r="M251" s="15"/>
     </row>
-    <row r="252" spans="1:13" ht="14.25">
+    <row r="252" spans="1:13" ht="14.25" hidden="1">
       <c r="A252" s="14">
         <v>260</v>
       </c>
@@ -44166,7 +44173,7 @@
       <c r="L252" s="15"/>
       <c r="M252" s="15"/>
     </row>
-    <row r="253" spans="1:13" ht="14.25">
+    <row r="253" spans="1:13" ht="14.25" hidden="1">
       <c r="A253" s="14">
         <v>261</v>
       </c>
@@ -44183,7 +44190,7 @@
       <c r="L253" s="15"/>
       <c r="M253" s="15"/>
     </row>
-    <row r="254" spans="1:13" ht="14.25">
+    <row r="254" spans="1:13" ht="14.25" hidden="1">
       <c r="A254" s="14">
         <v>262</v>
       </c>
@@ -44200,7 +44207,7 @@
       <c r="L254" s="15"/>
       <c r="M254" s="15"/>
     </row>
-    <row r="255" spans="1:13" ht="14.25">
+    <row r="255" spans="1:13" ht="14.25" hidden="1">
       <c r="A255" s="14">
         <v>263</v>
       </c>
@@ -44217,7 +44224,7 @@
       <c r="L255" s="15"/>
       <c r="M255" s="15"/>
     </row>
-    <row r="256" spans="1:13" ht="14.25">
+    <row r="256" spans="1:13" ht="14.25" hidden="1">
       <c r="A256" s="14">
         <v>264</v>
       </c>
@@ -44234,7 +44241,7 @@
       <c r="L256" s="15"/>
       <c r="M256" s="15"/>
     </row>
-    <row r="257" spans="1:13" ht="14.25">
+    <row r="257" spans="1:13" ht="14.25" hidden="1">
       <c r="A257" s="14">
         <v>265</v>
       </c>
@@ -44251,7 +44258,7 @@
       <c r="L257" s="15"/>
       <c r="M257" s="15"/>
     </row>
-    <row r="258" spans="1:13" ht="14.25">
+    <row r="258" spans="1:13" ht="14.25" hidden="1">
       <c r="A258" s="14">
         <v>266</v>
       </c>
@@ -44268,7 +44275,7 @@
       <c r="L258" s="15"/>
       <c r="M258" s="15"/>
     </row>
-    <row r="259" spans="1:13" ht="14.25">
+    <row r="259" spans="1:13" ht="14.25" hidden="1">
       <c r="A259" s="14">
         <v>267</v>
       </c>
@@ -44285,7 +44292,7 @@
       <c r="L259" s="15"/>
       <c r="M259" s="15"/>
     </row>
-    <row r="260" spans="1:13" ht="14.25">
+    <row r="260" spans="1:13" ht="14.25" hidden="1">
       <c r="A260" s="14">
         <v>268</v>
       </c>
@@ -44302,7 +44309,7 @@
       <c r="L260" s="15"/>
       <c r="M260" s="15"/>
     </row>
-    <row r="261" spans="1:13" ht="14.25">
+    <row r="261" spans="1:13" ht="14.25" hidden="1">
       <c r="A261" s="14">
         <v>269</v>
       </c>
@@ -44319,7 +44326,7 @@
       <c r="L261" s="15"/>
       <c r="M261" s="15"/>
     </row>
-    <row r="262" spans="1:13" ht="14.25">
+    <row r="262" spans="1:13" ht="14.25" hidden="1">
       <c r="A262" s="14">
         <v>270</v>
       </c>
@@ -44336,7 +44343,7 @@
       <c r="L262" s="15"/>
       <c r="M262" s="15"/>
     </row>
-    <row r="263" spans="1:13" ht="14.25">
+    <row r="263" spans="1:13" ht="14.25" hidden="1">
       <c r="A263" s="14">
         <v>271</v>
       </c>
@@ -44353,7 +44360,7 @@
       <c r="L263" s="15"/>
       <c r="M263" s="15"/>
     </row>
-    <row r="264" spans="1:13" ht="14.25">
+    <row r="264" spans="1:13" ht="14.25" hidden="1">
       <c r="A264" s="14">
         <v>272</v>
       </c>
@@ -44370,7 +44377,7 @@
       <c r="L264" s="15"/>
       <c r="M264" s="15"/>
     </row>
-    <row r="265" spans="1:13" ht="14.25">
+    <row r="265" spans="1:13" ht="14.25" hidden="1">
       <c r="A265" s="14">
         <v>273</v>
       </c>
@@ -44387,7 +44394,7 @@
       <c r="L265" s="15"/>
       <c r="M265" s="15"/>
     </row>
-    <row r="266" spans="1:13" ht="14.25">
+    <row r="266" spans="1:13" ht="14.25" hidden="1">
       <c r="A266" s="14">
         <v>274</v>
       </c>
@@ -44404,7 +44411,7 @@
       <c r="L266" s="15"/>
       <c r="M266" s="15"/>
     </row>
-    <row r="267" spans="1:13" ht="14.25">
+    <row r="267" spans="1:13" ht="14.25" hidden="1">
       <c r="A267" s="14">
         <v>275</v>
       </c>
@@ -44421,7 +44428,7 @@
       <c r="L267" s="15"/>
       <c r="M267" s="15"/>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" hidden="1">
       <c r="A268" s="14">
         <v>276</v>
       </c>
@@ -44438,7 +44445,7 @@
       <c r="L268" s="15"/>
       <c r="M268" s="15"/>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" hidden="1">
       <c r="A269" s="14">
         <v>277</v>
       </c>
@@ -44455,7 +44462,7 @@
       <c r="L269" s="15"/>
       <c r="M269" s="15"/>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" hidden="1">
       <c r="A270" s="14">
         <v>278</v>
       </c>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81DC68D4-EA94-4ABB-800D-D4C7E2BCDD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17C0E637-E35C-47D9-BDFF-69930936088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="329">
   <si>
     <t>日付</t>
   </si>
@@ -790,7 +790,7 @@
     <t>JAL</t>
   </si>
   <si>
-    <t>東京（羽田）</t>
+    <t>東京(羽田)</t>
   </si>
   <si>
     <t>福岡</t>
@@ -823,7 +823,7 @@
     <t>JTA</t>
   </si>
   <si>
-    <t>沖縄（那覇）</t>
+    <t>沖縄(那覇)</t>
   </si>
   <si>
     <t>40分</t>
@@ -892,10 +892,10 @@
     <t>小松</t>
   </si>
   <si>
-    <t>大阪（関西）</t>
+    <t>大阪(関西)</t>
   </si>
   <si>
-    <t>大阪（伊丹）</t>
+    <t>大阪(伊丹)</t>
   </si>
   <si>
     <t>RAC873</t>
@@ -928,9 +928,6 @@
     <t>伊丹</t>
   </si>
   <si>
-    <t>沖縄 (那覇)</t>
-  </si>
-  <si>
     <t>鹿児島</t>
   </si>
   <si>
@@ -943,16 +940,7 @@
     <t>広島</t>
   </si>
   <si>
-    <t>東京(羽田)</t>
-  </si>
-  <si>
-    <t>沖縄(那覇)</t>
-  </si>
-  <si>
     <t>ダメ</t>
-  </si>
-  <si>
-    <t>沖縄</t>
   </si>
   <si>
     <t>小松空港</t>
@@ -1024,7 +1012,7 @@
     <t>東京(成田)</t>
   </si>
   <si>
-    <t>台湾（桃園）</t>
+    <t>台湾(桃園)</t>
   </si>
   <si>
     <t>総額</t>
@@ -3590,6 +3578,120 @@
                   <c:v>1113</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>1113</c:v>
                 </c:pt>
                 <c:pt idx="47">
@@ -8982,16 +9084,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="1">
-      <filters>
-        <dateGroupItem year="2026" month="2" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="11">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{E936A600-BB79-446A-9797-5E2C4AB43B97}" name="日付" dataDxfId="11"/>
@@ -29297,7 +29390,7 @@
       <c r="E11" s="45"/>
       <c r="F11" s="45"/>
       <c r="G11" s="34">
-        <f>G50+F11</f>
+        <f t="shared" si="0"/>
         <v>1113</v>
       </c>
       <c r="I11" s="31" t="s">
@@ -29314,7 +29407,10 @@
       <c r="D12" s="45"/>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
-      <c r="G12" s="34"/>
+      <c r="G12" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I12" s="31"/>
     </row>
     <row r="13" spans="2:10" ht="15">
@@ -29323,7 +29419,10 @@
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
       <c r="F13" s="45"/>
-      <c r="G13" s="34"/>
+      <c r="G13" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I13" s="31"/>
     </row>
     <row r="14" spans="2:10" ht="15">
@@ -29332,7 +29431,10 @@
       <c r="D14" s="45"/>
       <c r="E14" s="45"/>
       <c r="F14" s="45"/>
-      <c r="G14" s="34"/>
+      <c r="G14" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I14" s="31"/>
     </row>
     <row r="15" spans="2:10" ht="15">
@@ -29341,7 +29443,10 @@
       <c r="D15" s="45"/>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
-      <c r="G15" s="34"/>
+      <c r="G15" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I15" s="31"/>
     </row>
     <row r="16" spans="2:10" ht="15">
@@ -29350,7 +29455,10 @@
       <c r="D16" s="45"/>
       <c r="E16" s="45"/>
       <c r="F16" s="45"/>
-      <c r="G16" s="34"/>
+      <c r="G16" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="2:9" ht="15">
@@ -29359,7 +29467,10 @@
       <c r="D17" s="45"/>
       <c r="E17" s="45"/>
       <c r="F17" s="45"/>
-      <c r="G17" s="34"/>
+      <c r="G17" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I17" s="31"/>
     </row>
     <row r="18" spans="2:9" ht="15">
@@ -29368,7 +29479,10 @@
       <c r="D18" s="45"/>
       <c r="E18" s="45"/>
       <c r="F18" s="45"/>
-      <c r="G18" s="34"/>
+      <c r="G18" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I18" s="31"/>
     </row>
     <row r="19" spans="2:9" ht="15">
@@ -29377,7 +29491,10 @@
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
       <c r="F19" s="45"/>
-      <c r="G19" s="34"/>
+      <c r="G19" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I19" s="31"/>
     </row>
     <row r="20" spans="2:9" ht="15">
@@ -29386,7 +29503,10 @@
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
-      <c r="G20" s="34"/>
+      <c r="G20" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I20" s="31"/>
     </row>
     <row r="21" spans="2:9" ht="15">
@@ -29395,7 +29515,10 @@
       <c r="D21" s="45"/>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
-      <c r="G21" s="34"/>
+      <c r="G21" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I21" s="31"/>
     </row>
     <row r="22" spans="2:9" ht="15">
@@ -29404,7 +29527,10 @@
       <c r="D22" s="45"/>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
-      <c r="G22" s="34"/>
+      <c r="G22" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I22" s="31"/>
     </row>
     <row r="23" spans="2:9" ht="15">
@@ -29413,7 +29539,10 @@
       <c r="D23" s="45"/>
       <c r="E23" s="45"/>
       <c r="F23" s="45"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I23" s="31"/>
     </row>
     <row r="24" spans="2:9" ht="15">
@@ -29422,7 +29551,10 @@
       <c r="D24" s="45"/>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I24" s="31"/>
     </row>
     <row r="25" spans="2:9" ht="15">
@@ -29431,7 +29563,10 @@
       <c r="D25" s="45"/>
       <c r="E25" s="45"/>
       <c r="F25" s="45"/>
-      <c r="G25" s="34"/>
+      <c r="G25" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I25" s="31"/>
     </row>
     <row r="26" spans="2:9" ht="15">
@@ -29440,7 +29575,10 @@
       <c r="D26" s="45"/>
       <c r="E26" s="45"/>
       <c r="F26" s="45"/>
-      <c r="G26" s="34"/>
+      <c r="G26" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I26" s="31"/>
     </row>
     <row r="27" spans="2:9" ht="15">
@@ -29449,7 +29587,10 @@
       <c r="D27" s="45"/>
       <c r="E27" s="45"/>
       <c r="F27" s="45"/>
-      <c r="G27" s="34"/>
+      <c r="G27" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I27" s="31"/>
     </row>
     <row r="28" spans="2:9" ht="15">
@@ -29458,7 +29599,10 @@
       <c r="D28" s="45"/>
       <c r="E28" s="45"/>
       <c r="F28" s="45"/>
-      <c r="G28" s="34"/>
+      <c r="G28" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I28" s="31"/>
     </row>
     <row r="29" spans="2:9" ht="15">
@@ -29467,7 +29611,10 @@
       <c r="D29" s="45"/>
       <c r="E29" s="45"/>
       <c r="F29" s="45"/>
-      <c r="G29" s="34"/>
+      <c r="G29" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I29" s="31"/>
     </row>
     <row r="30" spans="2:9" ht="15">
@@ -29476,7 +29623,10 @@
       <c r="D30" s="45"/>
       <c r="E30" s="45"/>
       <c r="F30" s="45"/>
-      <c r="G30" s="34"/>
+      <c r="G30" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I30" s="31"/>
     </row>
     <row r="31" spans="2:9" ht="15">
@@ -29485,7 +29635,10 @@
       <c r="D31" s="45"/>
       <c r="E31" s="45"/>
       <c r="F31" s="45"/>
-      <c r="G31" s="34"/>
+      <c r="G31" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I31" s="31"/>
     </row>
     <row r="32" spans="2:9" ht="15">
@@ -29494,7 +29647,10 @@
       <c r="D32" s="45"/>
       <c r="E32" s="45"/>
       <c r="F32" s="45"/>
-      <c r="G32" s="34"/>
+      <c r="G32" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I32" s="31"/>
     </row>
     <row r="33" spans="2:9" ht="15">
@@ -29503,7 +29659,10 @@
       <c r="D33" s="45"/>
       <c r="E33" s="45"/>
       <c r="F33" s="45"/>
-      <c r="G33" s="34"/>
+      <c r="G33" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I33" s="31"/>
     </row>
     <row r="34" spans="2:9" ht="15">
@@ -29512,7 +29671,10 @@
       <c r="D34" s="45"/>
       <c r="E34" s="45"/>
       <c r="F34" s="45"/>
-      <c r="G34" s="34"/>
+      <c r="G34" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I34" s="31"/>
     </row>
     <row r="35" spans="2:9" ht="15">
@@ -29521,7 +29683,10 @@
       <c r="D35" s="45"/>
       <c r="E35" s="45"/>
       <c r="F35" s="45"/>
-      <c r="G35" s="34"/>
+      <c r="G35" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I35" s="31"/>
     </row>
     <row r="36" spans="2:9" ht="15">
@@ -29530,7 +29695,10 @@
       <c r="D36" s="45"/>
       <c r="E36" s="45"/>
       <c r="F36" s="45"/>
-      <c r="G36" s="34"/>
+      <c r="G36" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I36" s="31"/>
     </row>
     <row r="37" spans="2:9" ht="15">
@@ -29539,7 +29707,10 @@
       <c r="D37" s="45"/>
       <c r="E37" s="45"/>
       <c r="F37" s="45"/>
-      <c r="G37" s="34"/>
+      <c r="G37" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I37" s="31"/>
     </row>
     <row r="38" spans="2:9" ht="15">
@@ -29548,7 +29719,10 @@
       <c r="D38" s="45"/>
       <c r="E38" s="45"/>
       <c r="F38" s="45"/>
-      <c r="G38" s="34"/>
+      <c r="G38" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I38" s="31"/>
     </row>
     <row r="39" spans="2:9" ht="15">
@@ -29557,7 +29731,10 @@
       <c r="D39" s="45"/>
       <c r="E39" s="45"/>
       <c r="F39" s="45"/>
-      <c r="G39" s="34"/>
+      <c r="G39" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I39" s="31"/>
     </row>
     <row r="40" spans="2:9" ht="15">
@@ -29566,7 +29743,10 @@
       <c r="D40" s="45"/>
       <c r="E40" s="45"/>
       <c r="F40" s="45"/>
-      <c r="G40" s="34"/>
+      <c r="G40" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I40" s="31"/>
     </row>
     <row r="41" spans="2:9" ht="15">
@@ -29575,7 +29755,10 @@
       <c r="D41" s="45"/>
       <c r="E41" s="45"/>
       <c r="F41" s="45"/>
-      <c r="G41" s="34"/>
+      <c r="G41" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I41" s="31"/>
     </row>
     <row r="42" spans="2:9" ht="15">
@@ -29584,7 +29767,10 @@
       <c r="D42" s="45"/>
       <c r="E42" s="45"/>
       <c r="F42" s="45"/>
-      <c r="G42" s="34"/>
+      <c r="G42" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I42" s="31"/>
     </row>
     <row r="43" spans="2:9" ht="15">
@@ -29593,7 +29779,10 @@
       <c r="D43" s="45"/>
       <c r="E43" s="45"/>
       <c r="F43" s="45"/>
-      <c r="G43" s="34"/>
+      <c r="G43" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I43" s="31"/>
     </row>
     <row r="44" spans="2:9" ht="15">
@@ -29602,7 +29791,10 @@
       <c r="D44" s="45"/>
       <c r="E44" s="45"/>
       <c r="F44" s="45"/>
-      <c r="G44" s="34"/>
+      <c r="G44" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I44" s="31"/>
     </row>
     <row r="45" spans="2:9" ht="15">
@@ -29611,7 +29803,10 @@
       <c r="D45" s="45"/>
       <c r="E45" s="45"/>
       <c r="F45" s="45"/>
-      <c r="G45" s="34"/>
+      <c r="G45" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I45" s="31"/>
     </row>
     <row r="46" spans="2:9" ht="15">
@@ -29620,7 +29815,10 @@
       <c r="D46" s="45"/>
       <c r="E46" s="45"/>
       <c r="F46" s="45"/>
-      <c r="G46" s="34"/>
+      <c r="G46" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I46" s="31"/>
     </row>
     <row r="47" spans="2:9" ht="15">
@@ -29629,7 +29827,10 @@
       <c r="D47" s="45"/>
       <c r="E47" s="45"/>
       <c r="F47" s="45"/>
-      <c r="G47" s="34"/>
+      <c r="G47" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I47" s="31"/>
     </row>
     <row r="48" spans="2:9" ht="15">
@@ -29638,7 +29839,10 @@
       <c r="D48" s="45"/>
       <c r="E48" s="45"/>
       <c r="F48" s="45"/>
-      <c r="G48" s="34"/>
+      <c r="G48" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I48" s="31"/>
     </row>
     <row r="49" spans="2:9" ht="15">
@@ -29647,7 +29851,10 @@
       <c r="D49" s="45"/>
       <c r="E49" s="45"/>
       <c r="F49" s="45"/>
-      <c r="G49" s="34"/>
+      <c r="G49" s="34">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
       <c r="I49" s="31"/>
     </row>
     <row r="50" spans="2:9" ht="15">
@@ -32244,7 +32451,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:13">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -32281,7 +32488,7 @@
       </c>
       <c r="M2" s="63"/>
     </row>
-    <row r="3" spans="1:13" hidden="1">
+    <row r="3" spans="1:13">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -32318,7 +32525,7 @@
       </c>
       <c r="M3" s="15"/>
     </row>
-    <row r="4" spans="1:13" hidden="1">
+    <row r="4" spans="1:13">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -32355,7 +32562,7 @@
       </c>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13" hidden="1">
+    <row r="5" spans="1:13">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -32392,7 +32599,7 @@
       </c>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13" hidden="1">
+    <row r="6" spans="1:13">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -32429,7 +32636,7 @@
       </c>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" hidden="1">
+    <row r="7" spans="1:13">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -32466,7 +32673,7 @@
       </c>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" hidden="1">
+    <row r="8" spans="1:13">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -32503,7 +32710,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" hidden="1">
+    <row r="9" spans="1:13">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -32540,7 +32747,7 @@
       </c>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" hidden="1">
+    <row r="10" spans="1:13">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -32577,7 +32784,7 @@
       </c>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:13">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -32614,7 +32821,7 @@
       </c>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" hidden="1">
+    <row r="12" spans="1:13">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -32651,7 +32858,7 @@
       </c>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" hidden="1">
+    <row r="13" spans="1:13">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -32688,7 +32895,7 @@
       </c>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" hidden="1">
+    <row r="14" spans="1:13">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -32725,7 +32932,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" hidden="1">
+    <row r="15" spans="1:13">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -32762,7 +32969,7 @@
       </c>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13" hidden="1">
+    <row r="16" spans="1:13">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -32799,7 +33006,7 @@
       </c>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13" hidden="1">
+    <row r="17" spans="1:13">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -32836,7 +33043,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13" hidden="1">
+    <row r="18" spans="1:13">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -32873,7 +33080,7 @@
       </c>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" hidden="1">
+    <row r="19" spans="1:13">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -32910,7 +33117,7 @@
       </c>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13" hidden="1">
+    <row r="20" spans="1:13">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -32947,7 +33154,7 @@
       </c>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" hidden="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -32984,7 +33191,7 @@
       </c>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13" hidden="1">
+    <row r="22" spans="1:13">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -33021,7 +33228,7 @@
       </c>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13" hidden="1">
+    <row r="23" spans="1:13">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -33058,7 +33265,7 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="1:13" hidden="1">
+    <row r="24" spans="1:13">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -33095,7 +33302,7 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" hidden="1">
+    <row r="25" spans="1:13">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -33132,7 +33339,7 @@
       </c>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" hidden="1">
+    <row r="26" spans="1:13">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -33169,7 +33376,7 @@
       </c>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" hidden="1">
+    <row r="27" spans="1:13">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -33204,7 +33411,7 @@
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" hidden="1">
+    <row r="28" spans="1:13">
       <c r="A28" s="14">
         <v>27</v>
       </c>
@@ -33241,7 +33448,7 @@
       </c>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" hidden="1">
+    <row r="29" spans="1:13">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -33278,7 +33485,7 @@
       </c>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" hidden="1">
+    <row r="30" spans="1:13">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -33315,7 +33522,7 @@
       </c>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" hidden="1">
+    <row r="31" spans="1:13">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -33352,7 +33559,7 @@
       </c>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" hidden="1">
+    <row r="32" spans="1:13">
       <c r="A32" s="14">
         <v>31</v>
       </c>
@@ -33389,7 +33596,7 @@
       </c>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13" hidden="1">
+    <row r="33" spans="1:13">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -33426,7 +33633,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" hidden="1">
+    <row r="34" spans="1:13">
       <c r="A34" s="14">
         <v>33</v>
       </c>
@@ -33463,7 +33670,7 @@
       </c>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13" hidden="1">
+    <row r="35" spans="1:13">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -33498,7 +33705,7 @@
       </c>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:13" hidden="1">
+    <row r="36" spans="1:13">
       <c r="A36" s="14">
         <v>35</v>
       </c>
@@ -33533,7 +33740,7 @@
       </c>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13" hidden="1">
+    <row r="37" spans="1:13">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -33568,7 +33775,7 @@
       </c>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="1:13" hidden="1">
+    <row r="38" spans="1:13">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -33603,7 +33810,7 @@
       </c>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13" hidden="1">
+    <row r="39" spans="1:13">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -33638,7 +33845,7 @@
       </c>
       <c r="M39" s="15"/>
     </row>
-    <row r="40" spans="1:13" hidden="1">
+    <row r="40" spans="1:13">
       <c r="A40" s="14">
         <v>39</v>
       </c>
@@ -33673,7 +33880,7 @@
       </c>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13" hidden="1">
+    <row r="41" spans="1:13">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -33704,7 +33911,7 @@
       </c>
       <c r="M41" s="15"/>
     </row>
-    <row r="42" spans="1:13" hidden="1">
+    <row r="42" spans="1:13">
       <c r="A42" s="14">
         <v>41</v>
       </c>
@@ -33735,7 +33942,7 @@
       </c>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13" hidden="1">
+    <row r="43" spans="1:13">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -33766,7 +33973,7 @@
       </c>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="1:13" hidden="1">
+    <row r="44" spans="1:13">
       <c r="A44" s="14">
         <v>43</v>
       </c>
@@ -33797,7 +34004,7 @@
       </c>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13" hidden="1">
+    <row r="45" spans="1:13">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -33828,7 +34035,7 @@
       </c>
       <c r="M45" s="15"/>
     </row>
-    <row r="46" spans="1:13" hidden="1">
+    <row r="46" spans="1:13">
       <c r="A46" s="14">
         <v>45</v>
       </c>
@@ -33859,7 +34066,7 @@
       </c>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13" hidden="1">
+    <row r="47" spans="1:13">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -33890,7 +34097,7 @@
       </c>
       <c r="M47" s="15"/>
     </row>
-    <row r="48" spans="1:13" hidden="1">
+    <row r="48" spans="1:13">
       <c r="A48" s="14">
         <v>47</v>
       </c>
@@ -33921,7 +34128,7 @@
       </c>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13" hidden="1">
+    <row r="49" spans="1:13">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -33952,7 +34159,7 @@
       </c>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13" hidden="1">
+    <row r="50" spans="1:13">
       <c r="A50" s="14">
         <v>49</v>
       </c>
@@ -33983,7 +34190,7 @@
       </c>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13" hidden="1">
+    <row r="51" spans="1:13">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -34014,7 +34221,7 @@
       </c>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13" hidden="1">
+    <row r="52" spans="1:13">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -34045,7 +34252,7 @@
       </c>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13" hidden="1">
+    <row r="53" spans="1:13">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -34076,7 +34283,7 @@
       </c>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13" hidden="1">
+    <row r="54" spans="1:13">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -34107,7 +34314,7 @@
       </c>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13" hidden="1">
+    <row r="55" spans="1:13">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -34138,7 +34345,7 @@
       </c>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="1:13" hidden="1">
+    <row r="56" spans="1:13">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -34169,7 +34376,7 @@
       </c>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13" hidden="1">
+    <row r="57" spans="1:13">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -34200,7 +34407,7 @@
       </c>
       <c r="M57" s="15"/>
     </row>
-    <row r="58" spans="1:13" hidden="1">
+    <row r="58" spans="1:13">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -34231,7 +34438,7 @@
       </c>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13" hidden="1">
+    <row r="59" spans="1:13">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -34262,7 +34469,7 @@
       </c>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13" hidden="1">
+    <row r="60" spans="1:13">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -34297,7 +34504,7 @@
       </c>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13" hidden="1">
+    <row r="61" spans="1:13">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -34332,7 +34539,7 @@
       </c>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13" hidden="1">
+    <row r="62" spans="1:13">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -34367,7 +34574,7 @@
       </c>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13" hidden="1">
+    <row r="63" spans="1:13">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -34402,7 +34609,7 @@
       </c>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="1:13" hidden="1">
+    <row r="64" spans="1:13">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -34437,7 +34644,7 @@
       </c>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13" hidden="1">
+    <row r="65" spans="1:13">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -34472,7 +34679,7 @@
       </c>
       <c r="M65" s="15"/>
     </row>
-    <row r="66" spans="1:13" hidden="1">
+    <row r="66" spans="1:13">
       <c r="A66" s="14">
         <v>65</v>
       </c>
@@ -34507,7 +34714,7 @@
       </c>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13" hidden="1">
+    <row r="67" spans="1:13">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -34542,7 +34749,7 @@
       </c>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="1:13" hidden="1">
+    <row r="68" spans="1:13">
       <c r="A68" s="14">
         <v>67</v>
       </c>
@@ -34577,7 +34784,7 @@
       </c>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13" hidden="1">
+    <row r="69" spans="1:13">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -34608,7 +34815,7 @@
       </c>
       <c r="M69" s="15"/>
     </row>
-    <row r="70" spans="1:13" hidden="1">
+    <row r="70" spans="1:13">
       <c r="A70" s="14">
         <v>69</v>
       </c>
@@ -34639,7 +34846,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -34675,7 +34882,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13" hidden="1">
+    <row r="72" spans="1:13">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -34710,7 +34917,7 @@
       </c>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13" hidden="1">
+    <row r="73" spans="1:13">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -34739,7 +34946,7 @@
       </c>
       <c r="M73" s="15"/>
     </row>
-    <row r="74" spans="1:13" hidden="1">
+    <row r="74" spans="1:13">
       <c r="A74" s="14">
         <v>73</v>
       </c>
@@ -34768,7 +34975,7 @@
       </c>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13" hidden="1">
+    <row r="75" spans="1:13">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -34797,7 +35004,7 @@
       </c>
       <c r="M75" s="15"/>
     </row>
-    <row r="76" spans="1:13" hidden="1">
+    <row r="76" spans="1:13">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -34826,7 +35033,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13" hidden="1">
+    <row r="77" spans="1:13">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -34859,7 +35066,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13" hidden="1">
+    <row r="78" spans="1:13">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -34892,7 +35099,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13" hidden="1">
+    <row r="79" spans="1:13">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -34925,7 +35132,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13" hidden="1">
+    <row r="80" spans="1:13">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -34943,7 +35150,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H80" s="13">
         <v>0.52083333333333337</v>
@@ -34958,7 +35165,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -34970,7 +35177,7 @@
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F81" s="13">
         <v>0.58333333333333337</v>
@@ -34991,7 +35198,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -35009,7 +35216,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H82" s="13">
         <v>0.66319444444444442</v>
@@ -35024,7 +35231,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -35036,7 +35243,7 @@
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F83" s="13">
         <v>0.69444444444444442</v>
@@ -35057,7 +35264,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -35075,7 +35282,7 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H84" s="13">
         <v>0.79513888888888884</v>
@@ -35090,7 +35297,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -35102,7 +35309,7 @@
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F85" s="13">
         <v>0.82291666666666663</v>
@@ -35123,7 +35330,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -35156,7 +35363,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -35189,7 +35396,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -35207,7 +35414,7 @@
         <v>0.59722222222222221</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H88" s="13">
         <v>0.63541666666666663</v>
@@ -35222,7 +35429,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -35234,7 +35441,7 @@
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F89" s="13">
         <v>0.66319444444444442</v>
@@ -35255,7 +35462,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -35288,7 +35495,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -35321,7 +35528,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -35339,7 +35546,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H92" s="13">
         <v>0.52083333333333337</v>
@@ -35354,7 +35561,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -35366,13 +35573,13 @@
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F93" s="13">
         <v>0.55208333333333337</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H93" s="13">
         <v>0.57986111111111116</v>
@@ -35387,7 +35594,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -35399,13 +35606,13 @@
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F94" s="13">
         <v>0.60069444444444442</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H94" s="13">
         <v>0.625</v>
@@ -35420,7 +35627,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -35432,7 +35639,7 @@
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F95" s="13">
         <v>0.65277777777777779</v>
@@ -35453,7 +35660,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -35471,7 +35678,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H96" s="13">
         <v>0.72222222222222221</v>
@@ -35486,7 +35693,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13" hidden="1">
+    <row r="97" spans="1:13">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -35498,7 +35705,7 @@
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F97" s="13">
         <v>0.79166666666666663</v>
@@ -35519,7 +35726,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13" hidden="1">
+    <row r="98" spans="1:13">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -35537,7 +35744,7 @@
         <v>0.2638888888888889</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H98" s="13">
         <v>0.38541666666666669</v>
@@ -35552,7 +35759,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13" hidden="1">
+    <row r="99" spans="1:13">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -35564,7 +35771,7 @@
       </c>
       <c r="D99" s="12"/>
       <c r="E99" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F99" s="13">
         <v>0.4548611111111111</v>
@@ -35585,7 +35792,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13" hidden="1">
+    <row r="100" spans="1:13">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -35603,7 +35810,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H100" s="13">
         <v>0.55555555555555558</v>
@@ -35618,7 +35825,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13" hidden="1">
+    <row r="101" spans="1:13">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -35630,13 +35837,13 @@
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F101" s="13">
         <v>0.59375</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H101" s="13">
         <v>0.63541666666666663</v>
@@ -35651,7 +35858,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13" hidden="1">
+    <row r="102" spans="1:13">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -35663,13 +35870,13 @@
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F102" s="13">
         <v>0.65625</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="H102" s="13">
         <v>0.70138888888888884</v>
@@ -35684,7 +35891,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13" hidden="1">
+    <row r="103" spans="1:13">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -35696,7 +35903,7 @@
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F103" s="13">
         <v>0.87152777777777779</v>
@@ -35717,7 +35924,7 @@
       </c>
       <c r="M103" s="15"/>
     </row>
-    <row r="104" spans="1:13" hidden="1">
+    <row r="104" spans="1:13">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -35733,7 +35940,7 @@
       </c>
       <c r="F104" s="13"/>
       <c r="G104" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H104" s="13"/>
       <c r="I104" s="26"/>
@@ -35746,7 +35953,7 @@
       </c>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="1:13" hidden="1">
+    <row r="105" spans="1:13">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -35758,7 +35965,7 @@
       </c>
       <c r="D105" s="12"/>
       <c r="E105" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F105" s="13"/>
       <c r="G105" s="12" t="s">
@@ -35775,7 +35982,7 @@
       </c>
       <c r="M105" s="15"/>
     </row>
-    <row r="106" spans="1:13" hidden="1">
+    <row r="106" spans="1:13">
       <c r="A106" s="14">
         <v>105</v>
       </c>
@@ -35804,7 +36011,7 @@
       </c>
       <c r="M106" s="15"/>
     </row>
-    <row r="107" spans="1:13" hidden="1">
+    <row r="107" spans="1:13">
       <c r="A107" s="14">
         <v>106</v>
       </c>
@@ -35833,7 +36040,7 @@
       </c>
       <c r="M107" s="15"/>
     </row>
-    <row r="108" spans="1:13" hidden="1">
+    <row r="108" spans="1:13">
       <c r="A108" s="14">
         <v>107</v>
       </c>
@@ -35862,7 +36069,7 @@
       </c>
       <c r="M108" s="15"/>
     </row>
-    <row r="109" spans="1:13" hidden="1">
+    <row r="109" spans="1:13">
       <c r="A109" s="14">
         <v>108</v>
       </c>
@@ -35891,7 +36098,7 @@
       </c>
       <c r="M109" s="15"/>
     </row>
-    <row r="110" spans="1:13" hidden="1">
+    <row r="110" spans="1:13">
       <c r="A110" s="14">
         <v>109</v>
       </c>
@@ -35920,7 +36127,7 @@
       </c>
       <c r="M110" s="15"/>
     </row>
-    <row r="111" spans="1:13" hidden="1">
+    <row r="111" spans="1:13">
       <c r="A111" s="14">
         <v>110</v>
       </c>
@@ -35949,7 +36156,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13" hidden="1">
+    <row r="112" spans="1:13">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -35963,7 +36170,7 @@
         <v>303</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F112" s="13">
         <v>0.2673611111111111</v>
@@ -35984,7 +36191,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13" hidden="1">
+    <row r="113" spans="1:13">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -36019,7 +36226,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13" hidden="1">
+    <row r="114" spans="1:13">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -36054,7 +36261,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13" hidden="1">
+    <row r="115" spans="1:13">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -36087,7 +36294,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13" hidden="1">
+    <row r="116" spans="1:13">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -36120,7 +36327,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13" hidden="1">
+    <row r="117" spans="1:13">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -36140,7 +36347,7 @@
         <v>0.73263888888888884</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H117" s="13">
         <v>0.80902777777777779</v>
@@ -36155,7 +36362,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13" hidden="1">
+    <row r="118" spans="1:13">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -36165,7 +36372,7 @@
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
       <c r="E118" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F118" s="13">
         <v>0.60069444444444442</v>
@@ -36186,7 +36393,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13" hidden="1">
+    <row r="119" spans="1:13">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -36202,7 +36409,7 @@
         <v>0.67013888888888884</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H119" s="13">
         <v>0.70486111111111116</v>
@@ -36217,7 +36424,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13" hidden="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -36248,7 +36455,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13" hidden="1">
+    <row r="121" spans="1:13">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -36279,7 +36486,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13" hidden="1">
+    <row r="122" spans="1:13">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -36293,7 +36500,7 @@
         <v>62</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F122" s="13">
         <v>0.82291666666666663</v>
@@ -36314,7 +36521,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13" hidden="1">
+    <row r="123" spans="1:13">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -36330,7 +36537,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H123" s="13">
         <v>0.37847222222222221</v>
@@ -36345,7 +36552,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13" hidden="1">
+    <row r="124" spans="1:13">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -36359,7 +36566,7 @@
         <v>873</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F124" s="13">
         <v>0.41319444444444442</v>
@@ -36380,7 +36587,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13" hidden="1">
+    <row r="125" spans="1:13">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -36400,7 +36607,7 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H125" s="13">
         <v>0.4826388888888889</v>
@@ -36415,7 +36622,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13" hidden="1">
+    <row r="126" spans="1:13">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -36429,7 +36636,7 @@
         <v>559</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F126" s="13">
         <v>0.50694444444444442</v>
@@ -36450,7 +36657,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13" hidden="1">
+    <row r="127" spans="1:13">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -36466,7 +36673,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="G127" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H127" s="13">
         <v>0.60763888888888884</v>
@@ -36481,7 +36688,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13" hidden="1">
+    <row r="128" spans="1:13">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -36491,7 +36698,7 @@
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
       <c r="E128" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F128" s="13">
         <v>0.625</v>
@@ -36512,7 +36719,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13" hidden="1">
+    <row r="129" spans="1:13">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -36543,7 +36750,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13" hidden="1">
+    <row r="130" spans="1:13">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -36559,7 +36766,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H130" s="13">
         <v>0.83680555555555558</v>
@@ -36574,7 +36781,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13" hidden="1">
+    <row r="131" spans="1:13">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -36584,7 +36791,7 @@
       <c r="C131" s="12"/>
       <c r="D131" s="12"/>
       <c r="E131" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F131" s="13">
         <v>0.87152777777777779</v>
@@ -36605,7 +36812,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13" hidden="1">
+    <row r="132" spans="1:13">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -36619,7 +36826,7 @@
         <v>331</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F132" s="13">
         <v>0.77777777777777779</v>
@@ -36640,7 +36847,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13" hidden="1">
+    <row r="133" spans="1:13">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -36660,7 +36867,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H133" s="13">
         <v>0.37847222222222221</v>
@@ -36675,7 +36882,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13" hidden="1">
+    <row r="134" spans="1:13">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -36685,7 +36892,7 @@
       <c r="C134" s="12"/>
       <c r="D134" s="12"/>
       <c r="E134" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F134" s="13">
         <v>0.41319444444444442</v>
@@ -36706,7 +36913,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13" hidden="1">
+    <row r="135" spans="1:13">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -36722,7 +36929,7 @@
         <v>0.4826388888888889</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H135" s="13">
         <v>0.52430555555555558</v>
@@ -36737,7 +36944,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13" hidden="1">
+    <row r="136" spans="1:13">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -36751,7 +36958,7 @@
         <v>727</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F136" s="13">
         <v>0.61805555555555558</v>
@@ -36772,7 +36979,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13" hidden="1">
+    <row r="137" spans="1:13">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -36803,7 +37010,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13" hidden="1">
+    <row r="138" spans="1:13">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -36823,7 +37030,7 @@
         <v>0.80902777777777779</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H138" s="13">
         <v>0.91666666666666663</v>
@@ -36838,7 +37045,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13" hidden="1">
+    <row r="139" spans="1:13">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -36852,7 +37059,7 @@
         <v>325</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F139" s="13">
         <v>0.65972222222222221</v>
@@ -36873,10 +37080,10 @@
         <v>249</v>
       </c>
       <c r="M139" s="15" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" hidden="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -36911,7 +37118,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13" hidden="1">
+    <row r="141" spans="1:13">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -36946,7 +37153,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13" hidden="1">
+    <row r="142" spans="1:13">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -36966,7 +37173,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H142" s="13">
         <v>0.37847222222222221</v>
@@ -36981,7 +37188,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13" hidden="1">
+    <row r="143" spans="1:13">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -36991,7 +37198,7 @@
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
       <c r="E143" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F143" s="13">
         <v>0.44791666666666669</v>
@@ -37012,7 +37219,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13" hidden="1">
+    <row r="144" spans="1:13">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -37028,7 +37235,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G144" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H144" s="13">
         <v>0.5625</v>
@@ -37043,7 +37250,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13" hidden="1">
+    <row r="145" spans="1:13">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -37057,7 +37264,7 @@
         <v>563</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F145" s="13">
         <v>0.60069444444444442</v>
@@ -37078,7 +37285,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13" hidden="1">
+    <row r="146" spans="1:13">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -37113,7 +37320,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13" hidden="1">
+    <row r="147" spans="1:13">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -37148,7 +37355,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13" hidden="1">
+    <row r="148" spans="1:13">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -37183,7 +37390,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13" hidden="1">
+    <row r="149" spans="1:13">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -37203,7 +37410,7 @@
         <v>0.80902777777777779</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H149" s="13">
         <v>0.91666666666666663</v>
@@ -37218,7 +37425,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13" hidden="1">
+    <row r="150" spans="1:13">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -37232,7 +37439,7 @@
         <v>303</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F150" s="13">
         <v>0.2673611111111111</v>
@@ -37253,7 +37460,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13" hidden="1">
+    <row r="151" spans="1:13">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -37288,7 +37495,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13" hidden="1">
+    <row r="152" spans="1:13">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -37323,7 +37530,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13" hidden="1">
+    <row r="153" spans="1:13">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -37343,7 +37550,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H153" s="13">
         <v>0.625</v>
@@ -37358,7 +37565,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13" hidden="1">
+    <row r="154" spans="1:13">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -37372,7 +37579,7 @@
         <v>565</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F154" s="13">
         <v>0.65277777777777779</v>
@@ -37393,7 +37600,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13" hidden="1">
+    <row r="155" spans="1:13">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -37413,7 +37620,7 @@
         <v>0.71875</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H155" s="13">
         <v>0.75347222222222221</v>
@@ -37428,7 +37635,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13" hidden="1">
+    <row r="156" spans="1:13">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -37442,13 +37649,13 @@
         <v>920</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F156" s="13">
         <v>0.82986111111111116</v>
       </c>
       <c r="G156" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H156" s="13">
         <v>0.92013888888888884</v>
@@ -37463,7 +37670,7 @@
       </c>
       <c r="M156" s="15"/>
     </row>
-    <row r="157" spans="1:13" hidden="1">
+    <row r="157" spans="1:13">
       <c r="A157" s="14">
         <v>165</v>
       </c>
@@ -37492,7 +37699,7 @@
       </c>
       <c r="M157" s="15"/>
     </row>
-    <row r="158" spans="1:13" hidden="1">
+    <row r="158" spans="1:13">
       <c r="A158" s="14">
         <v>166</v>
       </c>
@@ -37521,7 +37728,7 @@
       </c>
       <c r="M158" s="15"/>
     </row>
-    <row r="159" spans="1:13" hidden="1">
+    <row r="159" spans="1:13">
       <c r="A159" s="14">
         <v>167</v>
       </c>
@@ -37537,7 +37744,7 @@
       </c>
       <c r="F159" s="13"/>
       <c r="G159" s="12" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="H159" s="13"/>
       <c r="I159" s="26"/>
@@ -37550,7 +37757,7 @@
       </c>
       <c r="M159" s="15"/>
     </row>
-    <row r="160" spans="1:13" hidden="1">
+    <row r="160" spans="1:13">
       <c r="A160" s="14">
         <v>168</v>
       </c>
@@ -37562,7 +37769,7 @@
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="12" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="F160" s="13"/>
       <c r="G160" s="12" t="s">
@@ -37579,7 +37786,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13" hidden="1">
+    <row r="161" spans="1:13">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -37608,7 +37815,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13" hidden="1">
+    <row r="162" spans="1:13">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -37620,7 +37827,7 @@
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F162" s="13"/>
       <c r="G162" s="12" t="s">
@@ -37637,7 +37844,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13" hidden="1">
+    <row r="163" spans="1:13">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -37653,7 +37860,7 @@
       </c>
       <c r="F163" s="13"/>
       <c r="G163" s="12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="H163" s="13"/>
       <c r="I163" s="26"/>
@@ -37666,7 +37873,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13" hidden="1">
+    <row r="164" spans="1:13">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -37678,7 +37885,7 @@
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F164" s="13"/>
       <c r="G164" s="12" t="s">
@@ -37695,7 +37902,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13" hidden="1">
+    <row r="165" spans="1:13">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -37706,16 +37913,16 @@
         <v>245</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F165" s="13">
         <v>0.2638888888888889</v>
       </c>
       <c r="G165" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H165" s="13">
         <v>0.38194444444444442</v>
@@ -37728,7 +37935,7 @@
       <c r="L165" s="15"/>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13" hidden="1">
+    <row r="166" spans="1:13">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -37739,10 +37946,10 @@
         <v>256</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F166" s="13">
         <v>0.40625</v>
@@ -37761,7 +37968,7 @@
       <c r="L166" s="15"/>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13" hidden="1">
+    <row r="167" spans="1:13">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -37772,7 +37979,7 @@
         <v>261</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E167" s="12" t="s">
         <v>260</v>
@@ -37794,7 +38001,7 @@
       <c r="L167" s="15"/>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13" hidden="1">
+    <row r="168" spans="1:13">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -37805,7 +38012,7 @@
         <v>261</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E168" s="12" t="s">
         <v>262</v>
@@ -37827,7 +38034,7 @@
       <c r="L168" s="15"/>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13" hidden="1">
+    <row r="169" spans="1:13">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -37838,7 +38045,7 @@
         <v>261</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E169" s="12" t="s">
         <v>260</v>
@@ -37860,7 +38067,7 @@
       <c r="L169" s="15"/>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13" hidden="1">
+    <row r="170" spans="1:13">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -37871,7 +38078,7 @@
         <v>261</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E170" s="12" t="s">
         <v>264</v>
@@ -37893,7 +38100,7 @@
       <c r="L170" s="15"/>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13" hidden="1">
+    <row r="171" spans="1:13">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -37904,7 +38111,7 @@
         <v>261</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E171" s="12" t="s">
         <v>265</v>
@@ -37926,7 +38133,7 @@
       <c r="L171" s="15"/>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13" hidden="1">
+    <row r="172" spans="1:13">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -37937,7 +38144,7 @@
         <v>261</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E172" s="12" t="s">
         <v>264</v>
@@ -37959,7 +38166,7 @@
       <c r="L172" s="15"/>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13" hidden="1">
+    <row r="173" spans="1:13">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -37970,7 +38177,7 @@
         <v>256</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E173" s="12" t="s">
         <v>260</v>
@@ -37979,7 +38186,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H173" s="13">
         <v>0.82638888888888884</v>
@@ -37992,7 +38199,7 @@
       <c r="L173" s="15"/>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13" hidden="1">
+    <row r="174" spans="1:13">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -38003,16 +38210,16 @@
         <v>245</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F174" s="13">
         <v>0.86805555555555558</v>
       </c>
       <c r="G174" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H174" s="13">
         <v>0.96180555555555558</v>
@@ -38025,7 +38232,7 @@
       <c r="L174" s="15"/>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13" hidden="1">
+    <row r="175" spans="1:13">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -38058,7 +38265,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13" hidden="1">
+    <row r="176" spans="1:13">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -38070,7 +38277,7 @@
       </c>
       <c r="D176" s="12"/>
       <c r="E176" s="12" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F176" s="13">
         <v>0.47569444444444442</v>
@@ -38091,7 +38298,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -38103,13 +38310,13 @@
       </c>
       <c r="D177" s="12"/>
       <c r="E177" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F177" s="13">
         <v>0.49652777777777779</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H177" s="13">
         <v>0.61805555555555558</v>
@@ -38124,7 +38331,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -38136,13 +38343,13 @@
       </c>
       <c r="D178" s="12"/>
       <c r="E178" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F178" s="13">
         <v>0.47569444444444442</v>
       </c>
       <c r="G178" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H178" s="13">
         <v>0.56597222222222221</v>
@@ -38157,7 +38364,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -38169,7 +38376,7 @@
       </c>
       <c r="D179" s="12"/>
       <c r="E179" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F179" s="13">
         <v>0.32291666666666669</v>
@@ -38190,7 +38397,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -38208,7 +38415,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H180" s="13">
         <v>0.35069444444444442</v>
@@ -38223,7 +38430,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13" hidden="1">
+    <row r="181" spans="1:13">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -38237,13 +38444,13 @@
         <v>585</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F181" s="13">
         <v>0.3125</v>
       </c>
       <c r="G181" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H181" s="13">
         <v>0.36805555555555558</v>
@@ -38252,7 +38459,7 @@
         <v>0.12152777777777778</v>
       </c>
       <c r="J181" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K181" s="22">
         <v>9800</v>
@@ -38260,7 +38467,7 @@
       <c r="L181" s="15"/>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13" hidden="1">
+    <row r="182" spans="1:13">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -38268,19 +38475,19 @@
         <v>46125</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D182" s="12">
         <v>2791</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F182" s="13">
         <v>0.48958333333333331</v>
       </c>
       <c r="G182" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H182" s="13">
         <v>0.51041666666666663</v>
@@ -38289,7 +38496,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="J182" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K182" s="22">
         <v>11912</v>
@@ -38297,7 +38504,7 @@
       <c r="L182" s="15"/>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13" hidden="1">
+    <row r="183" spans="1:13">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -38305,19 +38512,19 @@
         <v>46125</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D183" s="12">
         <v>2792</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F183" s="13">
         <v>0.53125</v>
       </c>
       <c r="G183" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H183" s="13">
         <v>0.55208333333333337</v>
@@ -38326,7 +38533,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="J183" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K183" s="22">
         <v>0</v>
@@ -38334,7 +38541,7 @@
       <c r="L183" s="15"/>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13" hidden="1">
+    <row r="184" spans="1:13">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -38342,19 +38549,19 @@
         <v>46125</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D184" s="12">
         <v>2748</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F184" s="13">
         <v>0.57291666666666663</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H184" s="13">
         <v>0.60069444444444442</v>
@@ -38363,7 +38570,7 @@
         <v>3.125E-2</v>
       </c>
       <c r="J184" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K184" s="22">
         <v>13584</v>
@@ -38371,7 +38578,7 @@
       <c r="L184" s="15"/>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13" hidden="1">
+    <row r="185" spans="1:13">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -38379,19 +38586,19 @@
         <v>46125</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D185" s="12">
         <v>2737</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F185" s="13">
         <v>0.63194444444444442</v>
       </c>
       <c r="G185" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H185" s="13">
         <v>0.66666666666666663</v>
@@ -38400,7 +38607,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="J185" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K185" s="22">
         <v>5940</v>
@@ -38408,7 +38615,7 @@
       <c r="L185" s="15"/>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13" hidden="1">
+    <row r="186" spans="1:13">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -38416,19 +38623,19 @@
         <v>46125</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D186" s="12">
         <v>2738</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F186" s="13">
         <v>0.6875</v>
       </c>
       <c r="G186" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H186" s="13">
         <v>0.72569444444444442</v>
@@ -38437,7 +38644,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="J186" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K186" s="22">
         <v>5940</v>
@@ -38445,7 +38652,7 @@
       <c r="L186" s="15"/>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13" hidden="1">
+    <row r="187" spans="1:13">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -38453,19 +38660,19 @@
         <v>46125</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D187" s="12">
         <v>2755</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F187" s="13">
         <v>0.75347222222222221</v>
       </c>
       <c r="G187" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H187" s="13">
         <v>0.78125</v>
@@ -38474,7 +38681,7 @@
         <v>3.125E-2</v>
       </c>
       <c r="J187" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K187" s="22">
         <v>0</v>
@@ -38482,7 +38689,7 @@
       <c r="L187" s="15"/>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13" hidden="1">
+    <row r="188" spans="1:13">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -38496,20 +38703,20 @@
         <v>588</v>
       </c>
       <c r="E188" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F188" s="13">
         <v>0.8125</v>
       </c>
       <c r="G188" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H188" s="13">
         <v>0.875</v>
       </c>
       <c r="I188" s="26"/>
       <c r="J188" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K188" s="22">
         <v>9800</v>
@@ -38517,7 +38724,7 @@
       <c r="L188" s="15"/>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13" hidden="1">
+    <row r="189" spans="1:13">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -38531,13 +38738,13 @@
         <v>553</v>
       </c>
       <c r="E189" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F189" s="13">
         <v>0.46527777777777779</v>
       </c>
       <c r="G189" s="12" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H189" s="13">
         <v>0.53125</v>
@@ -38546,7 +38753,7 @@
         <v>3.4722222222222224E-2</v>
       </c>
       <c r="J189" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K189" s="22">
         <v>9800</v>
@@ -38554,7 +38761,7 @@
       <c r="L189" s="15"/>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13" hidden="1">
+    <row r="190" spans="1:13">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -38568,13 +38775,13 @@
         <v>554</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F190" s="13">
         <v>0.56597222222222221</v>
       </c>
       <c r="G190" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H190" s="13">
         <v>0.64236111111111116</v>
@@ -38583,7 +38790,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="J190" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K190" s="22">
         <v>9800</v>
@@ -38591,7 +38798,7 @@
       <c r="L190" s="15"/>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13" hidden="1">
+    <row r="191" spans="1:13">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -38605,7 +38812,7 @@
         <v>695</v>
       </c>
       <c r="E191" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F191" s="13">
         <v>0.68402777777777779</v>
@@ -38620,7 +38827,7 @@
         <v>9.7222222222222224E-2</v>
       </c>
       <c r="J191" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K191" s="22">
         <v>10900</v>
@@ -38628,7 +38835,7 @@
       <c r="L191" s="15"/>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13" hidden="1">
+    <row r="192" spans="1:13">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -38655,7 +38862,7 @@
       </c>
       <c r="I192" s="26"/>
       <c r="J192" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K192" s="22">
         <v>5610</v>
@@ -38663,7 +38870,7 @@
       <c r="L192" s="15"/>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13" hidden="1">
+    <row r="193" spans="1:13">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -38683,7 +38890,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H193" s="13">
         <v>0.37847222222222221</v>
@@ -38692,7 +38899,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="J193" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K193" s="22">
         <v>10250</v>
@@ -38700,7 +38907,7 @@
       <c r="L193" s="15"/>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13" hidden="1">
+    <row r="194" spans="1:13">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -38714,7 +38921,7 @@
         <v>605</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F194" s="13">
         <v>0.40625</v>
@@ -38729,7 +38936,7 @@
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="J194" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K194" s="22">
         <v>4640</v>
@@ -38737,7 +38944,7 @@
       <c r="L194" s="15"/>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13" hidden="1">
+    <row r="195" spans="1:13">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -38757,7 +38964,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G195" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H195" s="13">
         <v>0.5625</v>
@@ -38766,7 +38973,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="J195" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K195" s="22">
         <v>5740</v>
@@ -38774,7 +38981,7 @@
       <c r="L195" s="15"/>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13" hidden="1">
+    <row r="196" spans="1:13">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -38788,7 +38995,7 @@
         <v>211</v>
       </c>
       <c r="E196" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F196" s="13">
         <v>0.59027777777777779</v>
@@ -38803,7 +39010,7 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="J196" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K196" s="22">
         <v>4640</v>
@@ -38811,7 +39018,7 @@
       <c r="L196" s="15"/>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13" hidden="1">
+    <row r="197" spans="1:13">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -38831,7 +39038,7 @@
         <v>0.625</v>
       </c>
       <c r="G197" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H197" s="13">
         <v>0.65277777777777779</v>
@@ -38840,7 +39047,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="J197" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K197" s="22">
         <v>5190</v>
@@ -38848,7 +39055,7 @@
       <c r="L197" s="15"/>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13" hidden="1">
+    <row r="198" spans="1:13">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -38862,7 +39069,7 @@
         <v>567</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F198" s="13">
         <v>0.68055555555555558</v>
@@ -38877,7 +39084,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="J198" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K198" s="22">
         <v>5190</v>
@@ -38885,7 +39092,7 @@
       <c r="L198" s="15"/>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13" hidden="1">
+    <row r="199" spans="1:13">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -38905,7 +39112,7 @@
         <v>0.74652777777777779</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H199" s="13">
         <v>0.78125</v>
@@ -38914,7 +39121,7 @@
         <v>7.9861111111111105E-2</v>
       </c>
       <c r="J199" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K199" s="22">
         <v>5190</v>
@@ -38922,7 +39129,7 @@
       <c r="L199" s="15"/>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13" hidden="1">
+    <row r="200" spans="1:13">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -38936,20 +39143,20 @@
         <v>922</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F200" s="13">
         <v>0.86111111111111116</v>
       </c>
       <c r="G200" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H200" s="13">
         <v>0.95833333333333337</v>
       </c>
       <c r="I200" s="26"/>
       <c r="J200" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K200" s="22">
         <v>10590</v>
@@ -38957,7 +39164,7 @@
       <c r="L200" s="15"/>
       <c r="M200" s="15"/>
     </row>
-    <row r="201" spans="1:13" hidden="1">
+    <row r="201" spans="1:13">
       <c r="A201" s="14">
         <v>209</v>
       </c>
@@ -38968,29 +39175,29 @@
         <v>245</v>
       </c>
       <c r="D201" s="23" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F201" s="13">
         <v>0.91319444444444442</v>
       </c>
       <c r="G201" s="12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H201" s="13">
         <v>0.40277777777777779</v>
       </c>
       <c r="I201" s="26"/>
       <c r="J201" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K201" s="22"/>
       <c r="L201" s="15"/>
       <c r="M201" s="15"/>
     </row>
-    <row r="202" spans="1:13" hidden="1">
+    <row r="202" spans="1:13">
       <c r="A202" s="14">
         <v>210</v>
       </c>
@@ -39001,29 +39208,29 @@
         <v>245</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F202" s="13">
         <v>0.4861111111111111</v>
       </c>
       <c r="G202" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H202" s="13">
         <v>0.67013888888888884</v>
       </c>
       <c r="I202" s="26"/>
       <c r="J202" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K202" s="22"/>
       <c r="L202" s="15"/>
       <c r="M202" s="15"/>
     </row>
-    <row r="203" spans="1:13" hidden="1">
+    <row r="203" spans="1:13">
       <c r="A203" s="14">
         <v>211</v>
       </c>
@@ -39037,26 +39244,26 @@
         <v>8663</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F203" s="13">
         <v>0.37152777777777779</v>
       </c>
       <c r="G203" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="H203" s="13">
         <v>0.4826388888888889</v>
       </c>
       <c r="I203" s="26"/>
       <c r="J203" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K203" s="22"/>
       <c r="L203" s="15"/>
       <c r="M203" s="15"/>
     </row>
-    <row r="204" spans="1:13" hidden="1">
+    <row r="204" spans="1:13">
       <c r="A204" s="14">
         <v>212</v>
       </c>
@@ -39070,20 +39277,20 @@
         <v>8664</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F204" s="13">
         <v>0.53125</v>
       </c>
       <c r="G204" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H204" s="13">
         <v>0.71875</v>
       </c>
       <c r="I204" s="26"/>
       <c r="J204" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K204" s="22"/>
       <c r="L204" s="15"/>
@@ -39103,7 +39310,7 @@
         <v>189</v>
       </c>
       <c r="E205" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="F205" s="13">
         <v>0.69097222222222221</v>
@@ -39116,7 +39323,7 @@
       </c>
       <c r="I205" s="26"/>
       <c r="J205" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K205" s="22">
         <v>11000</v>
@@ -39146,14 +39353,14 @@
         <v>0.76736111111111116</v>
       </c>
       <c r="G206" s="12" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="H206" s="13">
         <v>0.81597222222222221</v>
       </c>
       <c r="I206" s="26"/>
       <c r="J206" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K206" s="22">
         <v>11000</v>
@@ -39163,7 +39370,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13" hidden="1">
+    <row r="207" spans="1:13">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -39180,7 +39387,7 @@
       <c r="L207" s="15"/>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13" hidden="1">
+    <row r="208" spans="1:13">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -39197,7 +39404,7 @@
       <c r="L208" s="15"/>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13" hidden="1">
+    <row r="209" spans="1:13">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -39214,7 +39421,7 @@
       <c r="L209" s="15"/>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13" hidden="1">
+    <row r="210" spans="1:13">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -39231,7 +39438,7 @@
       <c r="L210" s="15"/>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13" hidden="1">
+    <row r="211" spans="1:13">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -39248,7 +39455,7 @@
       <c r="L211" s="15"/>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13" hidden="1">
+    <row r="212" spans="1:13">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -39265,7 +39472,7 @@
       <c r="L212" s="15"/>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13" hidden="1">
+    <row r="213" spans="1:13">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -39282,7 +39489,7 @@
       <c r="L213" s="15"/>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13" hidden="1">
+    <row r="214" spans="1:13">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -39299,7 +39506,7 @@
       <c r="L214" s="15"/>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13" hidden="1">
+    <row r="215" spans="1:13">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -39316,7 +39523,7 @@
       <c r="L215" s="15"/>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13" hidden="1">
+    <row r="216" spans="1:13">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -39333,7 +39540,7 @@
       <c r="L216" s="15"/>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13" hidden="1">
+    <row r="217" spans="1:13">
       <c r="A217" s="14">
         <v>225</v>
       </c>
@@ -39350,7 +39557,7 @@
       <c r="L217" s="15"/>
       <c r="M217" s="15"/>
     </row>
-    <row r="218" spans="1:13" hidden="1">
+    <row r="218" spans="1:13">
       <c r="A218" s="14">
         <v>226</v>
       </c>
@@ -39367,7 +39574,7 @@
       <c r="L218" s="15"/>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13" hidden="1">
+    <row r="219" spans="1:13">
       <c r="A219" s="14">
         <v>227</v>
       </c>
@@ -39384,7 +39591,7 @@
       <c r="L219" s="15"/>
       <c r="M219" s="15"/>
     </row>
-    <row r="220" spans="1:13" hidden="1">
+    <row r="220" spans="1:13">
       <c r="A220" s="14">
         <v>228</v>
       </c>
@@ -39401,7 +39608,7 @@
       <c r="L220" s="15"/>
       <c r="M220" s="15"/>
     </row>
-    <row r="221" spans="1:13" hidden="1">
+    <row r="221" spans="1:13">
       <c r="A221" s="14">
         <v>229</v>
       </c>
@@ -39418,7 +39625,7 @@
       <c r="L221" s="15"/>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13" hidden="1">
+    <row r="222" spans="1:13">
       <c r="A222" s="14">
         <v>230</v>
       </c>
@@ -39435,7 +39642,7 @@
       <c r="L222" s="15"/>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13" hidden="1">
+    <row r="223" spans="1:13">
       <c r="A223" s="14">
         <v>231</v>
       </c>
@@ -39452,7 +39659,7 @@
       <c r="L223" s="15"/>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13" hidden="1">
+    <row r="224" spans="1:13">
       <c r="A224" s="14">
         <v>232</v>
       </c>
@@ -39469,7 +39676,7 @@
       <c r="L224" s="15"/>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13" hidden="1">
+    <row r="225" spans="1:13">
       <c r="A225" s="14">
         <v>233</v>
       </c>
@@ -39486,7 +39693,7 @@
       <c r="L225" s="15"/>
       <c r="M225" s="15"/>
     </row>
-    <row r="226" spans="1:13" hidden="1">
+    <row r="226" spans="1:13">
       <c r="A226" s="14">
         <v>234</v>
       </c>
@@ -39503,7 +39710,7 @@
       <c r="L226" s="15"/>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" ht="14.25" hidden="1">
+    <row r="227" spans="1:13" ht="14.25">
       <c r="A227" s="14">
         <v>235</v>
       </c>
@@ -39520,7 +39727,7 @@
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13" ht="14.25" hidden="1">
+    <row r="228" spans="1:13" ht="14.25">
       <c r="A228" s="14">
         <v>236</v>
       </c>
@@ -39537,7 +39744,7 @@
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13" ht="14.25" hidden="1">
+    <row r="229" spans="1:13" ht="14.25">
       <c r="A229" s="14">
         <v>237</v>
       </c>
@@ -39554,7 +39761,7 @@
       <c r="L229" s="15"/>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13" ht="14.25" hidden="1">
+    <row r="230" spans="1:13" ht="14.25">
       <c r="A230" s="14">
         <v>238</v>
       </c>
@@ -39571,7 +39778,7 @@
       <c r="L230" s="15"/>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13" ht="14.25" hidden="1">
+    <row r="231" spans="1:13" ht="14.25">
       <c r="A231" s="14">
         <v>239</v>
       </c>
@@ -39588,7 +39795,7 @@
       <c r="L231" s="15"/>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13" ht="14.25" hidden="1">
+    <row r="232" spans="1:13" ht="14.25">
       <c r="A232" s="14">
         <v>240</v>
       </c>
@@ -39605,7 +39812,7 @@
       <c r="L232" s="15"/>
       <c r="M232" s="15"/>
     </row>
-    <row r="233" spans="1:13" ht="14.25" hidden="1">
+    <row r="233" spans="1:13" ht="14.25">
       <c r="A233" s="14">
         <v>241</v>
       </c>
@@ -39622,7 +39829,7 @@
       <c r="L233" s="15"/>
       <c r="M233" s="15"/>
     </row>
-    <row r="234" spans="1:13" ht="14.25" hidden="1">
+    <row r="234" spans="1:13" ht="14.25">
       <c r="A234" s="14">
         <v>242</v>
       </c>
@@ -39639,7 +39846,7 @@
       <c r="L234" s="15"/>
       <c r="M234" s="15"/>
     </row>
-    <row r="235" spans="1:13" ht="14.25" hidden="1">
+    <row r="235" spans="1:13" ht="14.25">
       <c r="A235" s="14">
         <v>243</v>
       </c>
@@ -39656,7 +39863,7 @@
       <c r="L235" s="15"/>
       <c r="M235" s="15"/>
     </row>
-    <row r="236" spans="1:13" ht="14.25" hidden="1">
+    <row r="236" spans="1:13" ht="14.25">
       <c r="A236" s="14">
         <v>244</v>
       </c>
@@ -39673,7 +39880,7 @@
       <c r="L236" s="15"/>
       <c r="M236" s="15"/>
     </row>
-    <row r="237" spans="1:13" ht="14.25" hidden="1">
+    <row r="237" spans="1:13" ht="14.25">
       <c r="A237" s="14">
         <v>245</v>
       </c>
@@ -39690,7 +39897,7 @@
       <c r="L237" s="15"/>
       <c r="M237" s="15"/>
     </row>
-    <row r="238" spans="1:13" ht="14.25" hidden="1">
+    <row r="238" spans="1:13" ht="14.25">
       <c r="A238" s="14">
         <v>246</v>
       </c>
@@ -39707,7 +39914,7 @@
       <c r="L238" s="15"/>
       <c r="M238" s="15"/>
     </row>
-    <row r="239" spans="1:13" ht="14.25" hidden="1">
+    <row r="239" spans="1:13" ht="14.25">
       <c r="A239" s="14">
         <v>247</v>
       </c>
@@ -39724,7 +39931,7 @@
       <c r="L239" s="15"/>
       <c r="M239" s="15"/>
     </row>
-    <row r="240" spans="1:13" ht="14.25" hidden="1">
+    <row r="240" spans="1:13" ht="14.25">
       <c r="A240" s="14">
         <v>248</v>
       </c>
@@ -39741,7 +39948,7 @@
       <c r="L240" s="15"/>
       <c r="M240" s="15"/>
     </row>
-    <row r="241" spans="1:13" ht="14.25" hidden="1">
+    <row r="241" spans="1:13" ht="14.25">
       <c r="A241" s="14">
         <v>249</v>
       </c>
@@ -39758,7 +39965,7 @@
       <c r="L241" s="15"/>
       <c r="M241" s="15"/>
     </row>
-    <row r="242" spans="1:13" ht="14.25" hidden="1">
+    <row r="242" spans="1:13" ht="14.25">
       <c r="A242" s="14">
         <v>250</v>
       </c>
@@ -39775,7 +39982,7 @@
       <c r="L242" s="15"/>
       <c r="M242" s="15"/>
     </row>
-    <row r="243" spans="1:13" ht="14.25" hidden="1">
+    <row r="243" spans="1:13" ht="14.25">
       <c r="A243" s="14">
         <v>251</v>
       </c>
@@ -39792,7 +39999,7 @@
       <c r="L243" s="15"/>
       <c r="M243" s="15"/>
     </row>
-    <row r="244" spans="1:13" ht="14.25" hidden="1">
+    <row r="244" spans="1:13" ht="14.25">
       <c r="A244" s="14">
         <v>252</v>
       </c>
@@ -39809,7 +40016,7 @@
       <c r="L244" s="15"/>
       <c r="M244" s="15"/>
     </row>
-    <row r="245" spans="1:13" ht="14.25" hidden="1">
+    <row r="245" spans="1:13" ht="14.25">
       <c r="A245" s="14">
         <v>253</v>
       </c>
@@ -39826,7 +40033,7 @@
       <c r="L245" s="15"/>
       <c r="M245" s="15"/>
     </row>
-    <row r="246" spans="1:13" ht="14.25" hidden="1">
+    <row r="246" spans="1:13" ht="14.25">
       <c r="A246" s="14">
         <v>254</v>
       </c>
@@ -39843,7 +40050,7 @@
       <c r="L246" s="15"/>
       <c r="M246" s="15"/>
     </row>
-    <row r="247" spans="1:13" ht="14.25" hidden="1">
+    <row r="247" spans="1:13" ht="14.25">
       <c r="A247" s="14">
         <v>255</v>
       </c>
@@ -39860,7 +40067,7 @@
       <c r="L247" s="15"/>
       <c r="M247" s="15"/>
     </row>
-    <row r="248" spans="1:13" ht="14.25" hidden="1">
+    <row r="248" spans="1:13" ht="14.25">
       <c r="A248" s="14">
         <v>256</v>
       </c>
@@ -39877,7 +40084,7 @@
       <c r="L248" s="15"/>
       <c r="M248" s="15"/>
     </row>
-    <row r="249" spans="1:13" ht="14.25" hidden="1">
+    <row r="249" spans="1:13" ht="14.25">
       <c r="A249" s="14">
         <v>257</v>
       </c>
@@ -39894,7 +40101,7 @@
       <c r="L249" s="15"/>
       <c r="M249" s="15"/>
     </row>
-    <row r="250" spans="1:13" ht="14.25" hidden="1">
+    <row r="250" spans="1:13" ht="14.25">
       <c r="A250" s="14">
         <v>258</v>
       </c>
@@ -39911,7 +40118,7 @@
       <c r="L250" s="15"/>
       <c r="M250" s="15"/>
     </row>
-    <row r="251" spans="1:13" ht="14.25" hidden="1">
+    <row r="251" spans="1:13" ht="14.25">
       <c r="A251" s="14">
         <v>259</v>
       </c>
@@ -39928,7 +40135,7 @@
       <c r="L251" s="15"/>
       <c r="M251" s="15"/>
     </row>
-    <row r="252" spans="1:13" ht="14.25" hidden="1">
+    <row r="252" spans="1:13" ht="14.25">
       <c r="A252" s="14">
         <v>260</v>
       </c>
@@ -39945,7 +40152,7 @@
       <c r="L252" s="15"/>
       <c r="M252" s="15"/>
     </row>
-    <row r="253" spans="1:13" ht="14.25" hidden="1">
+    <row r="253" spans="1:13" ht="14.25">
       <c r="A253" s="14">
         <v>261</v>
       </c>
@@ -39962,7 +40169,7 @@
       <c r="L253" s="15"/>
       <c r="M253" s="15"/>
     </row>
-    <row r="254" spans="1:13" ht="14.25" hidden="1">
+    <row r="254" spans="1:13" ht="14.25">
       <c r="A254" s="14">
         <v>262</v>
       </c>
@@ -39979,7 +40186,7 @@
       <c r="L254" s="15"/>
       <c r="M254" s="15"/>
     </row>
-    <row r="255" spans="1:13" ht="14.25" hidden="1">
+    <row r="255" spans="1:13" ht="14.25">
       <c r="A255" s="14">
         <v>263</v>
       </c>
@@ -39996,7 +40203,7 @@
       <c r="L255" s="15"/>
       <c r="M255" s="15"/>
     </row>
-    <row r="256" spans="1:13" ht="14.25" hidden="1">
+    <row r="256" spans="1:13" ht="14.25">
       <c r="A256" s="14">
         <v>264</v>
       </c>
@@ -40013,7 +40220,7 @@
       <c r="L256" s="15"/>
       <c r="M256" s="15"/>
     </row>
-    <row r="257" spans="1:13" ht="14.25" hidden="1">
+    <row r="257" spans="1:13" ht="14.25">
       <c r="A257" s="14">
         <v>265</v>
       </c>
@@ -40030,7 +40237,7 @@
       <c r="L257" s="15"/>
       <c r="M257" s="15"/>
     </row>
-    <row r="258" spans="1:13" ht="14.25" hidden="1">
+    <row r="258" spans="1:13" ht="14.25">
       <c r="A258" s="14">
         <v>266</v>
       </c>
@@ -40047,7 +40254,7 @@
       <c r="L258" s="15"/>
       <c r="M258" s="15"/>
     </row>
-    <row r="259" spans="1:13" ht="14.25" hidden="1">
+    <row r="259" spans="1:13" ht="14.25">
       <c r="A259" s="14">
         <v>267</v>
       </c>
@@ -40064,7 +40271,7 @@
       <c r="L259" s="15"/>
       <c r="M259" s="15"/>
     </row>
-    <row r="260" spans="1:13" ht="14.25" hidden="1">
+    <row r="260" spans="1:13" ht="14.25">
       <c r="A260" s="14">
         <v>268</v>
       </c>
@@ -40081,7 +40288,7 @@
       <c r="L260" s="15"/>
       <c r="M260" s="15"/>
     </row>
-    <row r="261" spans="1:13" ht="14.25" hidden="1">
+    <row r="261" spans="1:13" ht="14.25">
       <c r="A261" s="14">
         <v>269</v>
       </c>
@@ -40098,7 +40305,7 @@
       <c r="L261" s="15"/>
       <c r="M261" s="15"/>
     </row>
-    <row r="262" spans="1:13" ht="14.25" hidden="1">
+    <row r="262" spans="1:13" ht="14.25">
       <c r="A262" s="14">
         <v>270</v>
       </c>
@@ -40115,7 +40322,7 @@
       <c r="L262" s="15"/>
       <c r="M262" s="15"/>
     </row>
-    <row r="263" spans="1:13" ht="14.25" hidden="1">
+    <row r="263" spans="1:13" ht="14.25">
       <c r="A263" s="14">
         <v>271</v>
       </c>
@@ -40132,7 +40339,7 @@
       <c r="L263" s="15"/>
       <c r="M263" s="15"/>
     </row>
-    <row r="264" spans="1:13" ht="14.25" hidden="1">
+    <row r="264" spans="1:13" ht="14.25">
       <c r="A264" s="14">
         <v>272</v>
       </c>
@@ -40149,7 +40356,7 @@
       <c r="L264" s="15"/>
       <c r="M264" s="15"/>
     </row>
-    <row r="265" spans="1:13" ht="14.25" hidden="1">
+    <row r="265" spans="1:13" ht="14.25">
       <c r="A265" s="14">
         <v>273</v>
       </c>
@@ -40166,7 +40373,7 @@
       <c r="L265" s="15"/>
       <c r="M265" s="15"/>
     </row>
-    <row r="266" spans="1:13" ht="14.25" hidden="1">
+    <row r="266" spans="1:13" ht="14.25">
       <c r="A266" s="14">
         <v>274</v>
       </c>
@@ -40183,7 +40390,7 @@
       <c r="L266" s="15"/>
       <c r="M266" s="15"/>
     </row>
-    <row r="267" spans="1:13" ht="14.25" hidden="1">
+    <row r="267" spans="1:13" ht="14.25">
       <c r="A267" s="14">
         <v>275</v>
       </c>
@@ -40200,7 +40407,7 @@
       <c r="L267" s="15"/>
       <c r="M267" s="15"/>
     </row>
-    <row r="268" spans="1:13" hidden="1">
+    <row r="268" spans="1:13">
       <c r="A268" s="14">
         <v>276</v>
       </c>
@@ -40217,7 +40424,7 @@
       <c r="L268" s="15"/>
       <c r="M268" s="15"/>
     </row>
-    <row r="269" spans="1:13" hidden="1">
+    <row r="269" spans="1:13">
       <c r="A269" s="14">
         <v>277</v>
       </c>
@@ -40234,7 +40441,7 @@
       <c r="L269" s="15"/>
       <c r="M269" s="15"/>
     </row>
-    <row r="270" spans="1:13" hidden="1">
+    <row r="270" spans="1:13">
       <c r="A270" s="14">
         <v>278</v>
       </c>
@@ -40253,7 +40460,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -40262,7 +40469,7 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
@@ -40280,7 +40487,7 @@
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
@@ -40362,7 +40569,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -40414,7 +40621,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -40518,7 +40725,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -40740,19 +40947,19 @@
         <v>901</v>
       </c>
       <c r="D316" s="49" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="E316" s="50">
         <v>0.27083333333333331</v>
       </c>
       <c r="F316" s="49" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="G316" s="50">
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -40767,7 +40974,7 @@
         <v>605</v>
       </c>
       <c r="D317" s="54" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="E317" s="55">
         <v>0.39930555555555558</v>
@@ -40806,7 +41013,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -40935,13 +41142,13 @@
         <v>0.74652777777777779</v>
       </c>
       <c r="F323" s="54" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="G323" s="55">
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I323" s="56"/>
     </row>
@@ -40956,13 +41163,13 @@
         <v>920</v>
       </c>
       <c r="D324" s="58" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="E324" s="59">
         <v>0.8125</v>
       </c>
       <c r="F324" s="58" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="G324" s="59">
         <v>0.91666666666666663</v>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A6B045-EFE4-4CFE-9652-487AF7A52178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BCEC7EB-C585-4748-92C4-D623A4832A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="333">
   <si>
     <t>日付</t>
   </si>
@@ -1022,6 +1022,9 @@
   </si>
   <si>
     <t>JAL320</t>
+  </si>
+  <si>
+    <t>大阪 (伊丹)</t>
   </si>
   <si>
     <t>総額</t>
@@ -9408,7 +9411,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O506"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -9976,7 +9979,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>5028</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="17" spans="1:15" hidden="1">
@@ -10218,7 +10221,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>124774</v>
+        <v>124792</v>
       </c>
     </row>
     <row r="22" spans="1:15" hidden="1">
@@ -29016,31 +29019,31 @@
       </c>
     </row>
     <row r="504" spans="1:13">
-      <c r="A504" s="29">
+      <c r="A504" s="27">
         <v>46086</v>
       </c>
-      <c r="B504" s="75" t="s">
+      <c r="B504" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C504" s="75"/>
-      <c r="D504" s="75"/>
-      <c r="E504" s="76"/>
-      <c r="F504" s="72">
-        <v>0</v>
-      </c>
-      <c r="G504" s="72">
+      <c r="C504" s="73"/>
+      <c r="D504" s="73"/>
+      <c r="E504" s="74"/>
+      <c r="F504" s="71">
+        <v>0</v>
+      </c>
+      <c r="G504" s="71">
         <v>10</v>
       </c>
-      <c r="H504" s="72">
+      <c r="H504" s="71">
         <v>10</v>
       </c>
-      <c r="I504" s="30">
+      <c r="I504" s="4">
         <v>30060</v>
       </c>
-      <c r="J504" s="72">
-        <v>0</v>
-      </c>
-      <c r="K504" s="72">
+      <c r="J504" s="71">
+        <v>0</v>
+      </c>
+      <c r="K504" s="71">
         <v>0</v>
       </c>
       <c r="L504" s="71">
@@ -29051,6 +29054,47 @@
         <f t="shared" si="63"/>
         <v>157</v>
       </c>
+    </row>
+    <row r="505" spans="1:13">
+      <c r="A505" s="29">
+        <v>46087</v>
+      </c>
+      <c r="B505" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C505" s="75"/>
+      <c r="D505" s="75"/>
+      <c r="E505" s="76"/>
+      <c r="F505" s="72">
+        <v>0</v>
+      </c>
+      <c r="G505" s="72">
+        <v>18</v>
+      </c>
+      <c r="H505" s="72">
+        <v>18</v>
+      </c>
+      <c r="I505" s="30">
+        <v>30078</v>
+      </c>
+      <c r="J505" s="72">
+        <v>0</v>
+      </c>
+      <c r="K505" s="72">
+        <v>0</v>
+      </c>
+      <c r="L505" s="71">
+        <f t="shared" ref="L505:L506" si="64">J505+L504</f>
+        <v>135798</v>
+      </c>
+      <c r="M505" s="71">
+        <f t="shared" ref="M505:M506" si="65">K505+M504</f>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13">
+      <c r="L506" s="71"/>
+      <c r="M506" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O496" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
@@ -29060,7 +29104,308 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="324">
+  <mergeCells count="325">
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B489:E489"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
     <mergeCell ref="B497:E497"/>
     <mergeCell ref="B498:E498"/>
     <mergeCell ref="B499:E499"/>
@@ -29085,306 +29430,6 @@
     <mergeCell ref="B359:E359"/>
     <mergeCell ref="B367:E367"/>
     <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B489:E489"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -39782,16 +39827,32 @@
       <c r="A209" s="14">
         <v>217</v>
       </c>
-      <c r="B209" s="42"/>
-      <c r="C209" s="12"/>
-      <c r="D209" s="12"/>
-      <c r="E209" s="12"/>
-      <c r="F209" s="13"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="13"/>
+      <c r="B209" s="42">
+        <v>46122</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F209" s="13">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="G209" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="H209" s="13">
+        <v>0.39930555555555558</v>
+      </c>
       <c r="I209" s="26"/>
       <c r="J209" s="15"/>
-      <c r="K209" s="22"/>
+      <c r="K209" s="22">
+        <v>0</v>
+      </c>
       <c r="L209" s="15"/>
       <c r="M209" s="15"/>
     </row>
@@ -39799,16 +39860,32 @@
       <c r="A210" s="14">
         <v>218</v>
       </c>
-      <c r="B210" s="42"/>
-      <c r="C210" s="12"/>
-      <c r="D210" s="12"/>
-      <c r="E210" s="12"/>
-      <c r="F210" s="13"/>
-      <c r="G210" s="12"/>
-      <c r="H210" s="13"/>
+      <c r="B210" s="42">
+        <v>46122</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F210" s="13">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="G210" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H210" s="13">
+        <v>0.81944444444444442</v>
+      </c>
       <c r="I210" s="26"/>
       <c r="J210" s="15"/>
-      <c r="K210" s="22"/>
+      <c r="K210" s="22">
+        <v>0</v>
+      </c>
       <c r="L210" s="15"/>
       <c r="M210" s="15"/>
     </row>
@@ -40834,7 +40911,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -40843,11 +40920,11 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1015</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -40856,16 +40933,16 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1316.0433497536947</v>
+        <v>1303.2039024390244</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -40943,7 +41020,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -40995,7 +41072,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -41099,7 +41176,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -41333,7 +41410,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -41387,7 +41464,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -41522,7 +41599,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{651458DE-2F80-4614-A1BE-D236AFEE0DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D28BC05A-D4D5-4F68-A2C2-6B4B214749AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="334">
   <si>
     <t>日付</t>
   </si>
@@ -9106,8 +9106,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="11">
-      <filters blank="1"/>
+    <filterColumn colId="1">
+      <filters blank="1">
+        <dateGroupItem year="2026" month="1" dateTimeGrouping="month"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
@@ -21688,7 +21690,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" hidden="1">
       <c r="A320" s="27">
         <v>46023</v>
       </c>
@@ -21725,7 +21727,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" hidden="1">
       <c r="A321" s="27">
         <v>46024</v>
       </c>
@@ -21762,7 +21764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" hidden="1">
       <c r="A322" s="27">
         <v>46025</v>
       </c>
@@ -21799,7 +21801,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" hidden="1">
       <c r="A323" s="27">
         <v>46026</v>
       </c>
@@ -21836,7 +21838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" hidden="1">
       <c r="A324" s="27">
         <v>46027</v>
       </c>
@@ -21873,7 +21875,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" hidden="1">
       <c r="A325" s="27">
         <v>46027</v>
       </c>
@@ -21953,7 +21955,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" hidden="1">
       <c r="A327" s="27">
         <v>46028</v>
       </c>
@@ -21990,7 +21992,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" hidden="1">
       <c r="A328" s="27">
         <v>46028</v>
       </c>
@@ -22027,7 +22029,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" hidden="1">
       <c r="A329" s="27">
         <v>46029</v>
       </c>
@@ -22150,7 +22152,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" hidden="1">
       <c r="A332" s="27">
         <v>46030</v>
       </c>
@@ -22187,7 +22189,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" hidden="1">
       <c r="A333" s="27">
         <v>46030</v>
       </c>
@@ -22568,7 +22570,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" hidden="1">
       <c r="A342" s="27">
         <v>46031</v>
       </c>
@@ -22777,7 +22779,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" hidden="1">
       <c r="A347" s="27">
         <v>46032</v>
       </c>
@@ -23158,7 +23160,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" hidden="1">
       <c r="A356" s="27">
         <v>46033</v>
       </c>
@@ -23195,7 +23197,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" hidden="1">
       <c r="A357" s="27">
         <v>46033</v>
       </c>
@@ -23232,7 +23234,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" hidden="1">
       <c r="A358" s="27">
         <v>46034</v>
       </c>
@@ -23269,7 +23271,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" hidden="1">
       <c r="A359" s="27">
         <v>46035</v>
       </c>
@@ -23306,7 +23308,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" hidden="1">
       <c r="A360" s="27">
         <v>46035</v>
       </c>
@@ -23343,7 +23345,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" hidden="1">
       <c r="A361" s="27">
         <v>46036</v>
       </c>
@@ -23380,7 +23382,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" hidden="1">
       <c r="A362" s="27">
         <v>46036</v>
       </c>
@@ -23460,7 +23462,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" hidden="1">
       <c r="A364" s="27">
         <v>46037</v>
       </c>
@@ -23497,7 +23499,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" hidden="1">
       <c r="A365" s="27">
         <v>46037</v>
       </c>
@@ -23577,7 +23579,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" hidden="1">
       <c r="A367" s="27">
         <v>46038</v>
       </c>
@@ -23614,7 +23616,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" hidden="1">
       <c r="A368" s="27">
         <v>46039</v>
       </c>
@@ -23651,7 +23653,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" hidden="1">
       <c r="A369" s="27">
         <v>46040</v>
       </c>
@@ -23688,7 +23690,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" hidden="1">
       <c r="A370" s="27">
         <v>46041</v>
       </c>
@@ -23725,7 +23727,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" hidden="1">
       <c r="A371" s="27">
         <v>46041</v>
       </c>
@@ -23848,7 +23850,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" hidden="1">
       <c r="A374" s="27">
         <v>46042</v>
       </c>
@@ -23885,7 +23887,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" hidden="1">
       <c r="A375" s="27">
         <v>46043</v>
       </c>
@@ -23922,7 +23924,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" hidden="1">
       <c r="A376" s="27">
         <v>46044</v>
       </c>
@@ -23959,7 +23961,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" hidden="1">
       <c r="A377" s="27">
         <v>46045</v>
       </c>
@@ -23996,7 +23998,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" hidden="1">
       <c r="A378" s="27">
         <v>46045</v>
       </c>
@@ -24033,7 +24035,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" hidden="1">
       <c r="A379" s="27">
         <v>46045</v>
       </c>
@@ -24328,7 +24330,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" hidden="1">
       <c r="A386" s="27">
         <v>46046</v>
       </c>
@@ -24365,7 +24367,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" hidden="1">
       <c r="A387" s="27">
         <v>46047</v>
       </c>
@@ -24402,7 +24404,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" hidden="1">
       <c r="A388" s="27">
         <v>46047</v>
       </c>
@@ -24439,7 +24441,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" hidden="1">
       <c r="A389" s="27">
         <v>46048</v>
       </c>
@@ -24476,7 +24478,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" hidden="1">
       <c r="A390" s="27">
         <v>46048</v>
       </c>
@@ -24556,7 +24558,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" hidden="1">
       <c r="A392" s="27">
         <v>46049</v>
       </c>
@@ -24593,7 +24595,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" hidden="1">
       <c r="A393" s="27">
         <v>46049</v>
       </c>
@@ -24673,7 +24675,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" hidden="1">
       <c r="A395" s="27">
         <v>46050</v>
       </c>
@@ -24710,7 +24712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" hidden="1">
       <c r="A396" s="27">
         <v>46051</v>
       </c>
@@ -24790,7 +24792,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" hidden="1">
       <c r="A398" s="27">
         <v>46052</v>
       </c>
@@ -24827,7 +24829,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" hidden="1">
       <c r="A399" s="27">
         <v>46052</v>
       </c>
@@ -24864,7 +24866,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" hidden="1">
       <c r="A400" s="27">
         <v>46053</v>
       </c>
@@ -24901,7 +24903,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" hidden="1">
       <c r="A401" s="27">
         <v>46053</v>
       </c>
@@ -24938,7 +24940,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" hidden="1">
       <c r="A402" s="27">
         <v>46053</v>
       </c>
@@ -24975,7 +24977,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" hidden="1">
       <c r="A403" s="27">
         <v>46053</v>
       </c>
@@ -25012,7 +25014,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" hidden="1">
       <c r="A404" s="27">
         <v>46053</v>
       </c>
@@ -25049,7 +25051,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" hidden="1">
       <c r="A405" s="27">
         <v>46054</v>
       </c>
@@ -25092,7 +25094,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="406" spans="1:13" ht="22.5" customHeight="1">
+    <row r="406" spans="1:13" ht="22.5" hidden="1" customHeight="1">
       <c r="A406" s="27">
         <v>46054</v>
       </c>
@@ -25129,7 +25131,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" hidden="1">
       <c r="A407" s="27">
         <v>46055</v>
       </c>
@@ -25172,7 +25174,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" hidden="1">
       <c r="A408" s="27">
         <v>46055</v>
       </c>
@@ -25209,7 +25211,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" hidden="1">
       <c r="A409" s="27">
         <v>46056</v>
       </c>
@@ -25246,7 +25248,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" hidden="1">
       <c r="A410" s="27">
         <v>46056</v>
       </c>
@@ -25283,7 +25285,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" hidden="1">
       <c r="A411" s="27">
         <v>46057</v>
       </c>
@@ -25326,7 +25328,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" hidden="1">
       <c r="A412" s="27">
         <v>46058</v>
       </c>
@@ -25363,7 +25365,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" hidden="1">
       <c r="A413" s="27">
         <v>46059</v>
       </c>
@@ -25406,7 +25408,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" hidden="1">
       <c r="A414" s="27">
         <v>46059</v>
       </c>
@@ -25449,7 +25451,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" hidden="1">
       <c r="A415" s="27">
         <v>46059</v>
       </c>
@@ -25492,7 +25494,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" hidden="1">
       <c r="A416" s="27">
         <v>46059</v>
       </c>
@@ -25535,7 +25537,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" hidden="1">
       <c r="A417" s="27">
         <v>46059</v>
       </c>
@@ -25578,7 +25580,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" hidden="1">
       <c r="A418" s="27">
         <v>46059</v>
       </c>
@@ -25621,7 +25623,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" hidden="1">
       <c r="A419" s="27">
         <v>46059</v>
       </c>
@@ -25658,7 +25660,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" hidden="1">
       <c r="A420" s="27">
         <v>46060</v>
       </c>
@@ -25701,7 +25703,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" hidden="1">
       <c r="A421" s="27">
         <v>46060</v>
       </c>
@@ -25744,7 +25746,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" hidden="1">
       <c r="A422" s="27">
         <v>46060</v>
       </c>
@@ -25787,7 +25789,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" hidden="1">
       <c r="A423" s="27">
         <v>46060</v>
       </c>
@@ -25830,7 +25832,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" hidden="1">
       <c r="A424" s="27">
         <v>46060</v>
       </c>
@@ -25873,7 +25875,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" hidden="1">
       <c r="A425" s="27">
         <v>46060</v>
       </c>
@@ -25910,7 +25912,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" hidden="1">
       <c r="A426" s="27">
         <v>46060</v>
       </c>
@@ -25947,7 +25949,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" hidden="1">
       <c r="A427" s="27">
         <v>46061</v>
       </c>
@@ -25990,7 +25992,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" hidden="1">
       <c r="A428" s="27">
         <v>46061</v>
       </c>
@@ -26033,7 +26035,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" hidden="1">
       <c r="A429" s="27">
         <v>46061</v>
       </c>
@@ -26076,7 +26078,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" hidden="1">
       <c r="A430" s="27">
         <v>46061</v>
       </c>
@@ -26119,7 +26121,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" hidden="1">
       <c r="A431" s="27">
         <v>46061</v>
       </c>
@@ -26162,7 +26164,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" hidden="1">
       <c r="A432" s="27">
         <v>46061</v>
       </c>
@@ -26205,7 +26207,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" hidden="1">
       <c r="A433" s="27">
         <v>46061</v>
       </c>
@@ -26248,7 +26250,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" hidden="1">
       <c r="A434" s="27">
         <v>46061</v>
       </c>
@@ -26291,7 +26293,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" hidden="1">
       <c r="A435" s="27">
         <v>46061</v>
       </c>
@@ -26334,7 +26336,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" hidden="1">
       <c r="A436" s="27">
         <v>46061</v>
       </c>
@@ -26371,7 +26373,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" hidden="1">
       <c r="A437" s="27">
         <v>46062</v>
       </c>
@@ -26414,7 +26416,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" hidden="1">
       <c r="A438" s="27">
         <v>46062</v>
       </c>
@@ -26451,7 +26453,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" hidden="1">
       <c r="A439" s="27">
         <v>46063</v>
       </c>
@@ -26488,7 +26490,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" hidden="1">
       <c r="A440" s="27">
         <v>46063</v>
       </c>
@@ -26531,7 +26533,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" hidden="1">
       <c r="A441" s="27">
         <v>46063</v>
       </c>
@@ -26574,7 +26576,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" hidden="1">
       <c r="A442" s="27">
         <v>46063</v>
       </c>
@@ -26611,7 +26613,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" hidden="1">
       <c r="A443" s="27">
         <v>46064</v>
       </c>
@@ -26654,7 +26656,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" hidden="1">
       <c r="A444" s="27">
         <v>46064</v>
       </c>
@@ -26697,7 +26699,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" hidden="1">
       <c r="A445" s="27">
         <v>46064</v>
       </c>
@@ -26740,7 +26742,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" hidden="1">
       <c r="A446" s="27">
         <v>46064</v>
       </c>
@@ -26783,7 +26785,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" hidden="1">
       <c r="A447" s="27">
         <v>46064</v>
       </c>
@@ -26826,7 +26828,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" hidden="1">
       <c r="A448" s="27">
         <v>46064</v>
       </c>
@@ -26869,7 +26871,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" hidden="1">
       <c r="A449" s="27">
         <v>46064</v>
       </c>
@@ -26906,7 +26908,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" hidden="1">
       <c r="A450" s="27">
         <v>46065</v>
       </c>
@@ -26943,7 +26945,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" hidden="1">
       <c r="A451" s="27">
         <v>46065</v>
       </c>
@@ -26980,7 +26982,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" hidden="1">
       <c r="A452" s="27">
         <v>46066</v>
       </c>
@@ -27017,7 +27019,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" hidden="1">
       <c r="A453" s="27">
         <v>46067</v>
       </c>
@@ -27054,7 +27056,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" hidden="1">
       <c r="A454" s="27">
         <v>46068</v>
       </c>
@@ -27091,7 +27093,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" hidden="1">
       <c r="A455" s="27">
         <v>46069</v>
       </c>
@@ -27128,7 +27130,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" hidden="1">
       <c r="A456" s="27">
         <v>46069</v>
       </c>
@@ -27165,7 +27167,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" hidden="1">
       <c r="A457" s="27">
         <v>46070</v>
       </c>
@@ -27202,7 +27204,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" hidden="1">
       <c r="A458" s="27">
         <v>46071</v>
       </c>
@@ -27239,7 +27241,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" hidden="1">
       <c r="A459" s="27">
         <v>46072</v>
       </c>
@@ -27276,7 +27278,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" hidden="1">
       <c r="A460" s="27">
         <v>46073</v>
       </c>
@@ -27313,7 +27315,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" hidden="1">
       <c r="A461" s="27">
         <v>46073</v>
       </c>
@@ -27350,7 +27352,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" hidden="1">
       <c r="A462" s="27">
         <v>46074</v>
       </c>
@@ -27393,7 +27395,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" hidden="1">
       <c r="A463" s="27">
         <v>46074</v>
       </c>
@@ -27436,7 +27438,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" hidden="1">
       <c r="A464" s="27">
         <v>46074</v>
       </c>
@@ -27479,7 +27481,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="465" spans="1:13">
+    <row r="465" spans="1:13" hidden="1">
       <c r="A465" s="27">
         <v>46074</v>
       </c>
@@ -27516,7 +27518,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="466" spans="1:13">
+    <row r="466" spans="1:13" hidden="1">
       <c r="A466" s="27">
         <v>46074</v>
       </c>
@@ -27553,7 +27555,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="467" spans="1:13">
+    <row r="467" spans="1:13" hidden="1">
       <c r="A467" s="27">
         <v>46074</v>
       </c>
@@ -27590,7 +27592,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="468" spans="1:13">
+    <row r="468" spans="1:13" hidden="1">
       <c r="A468" s="27">
         <v>46074</v>
       </c>
@@ -27627,7 +27629,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="469" spans="1:13">
+    <row r="469" spans="1:13" hidden="1">
       <c r="A469" s="27">
         <v>46074</v>
       </c>
@@ -27664,7 +27666,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="470" spans="1:13">
+    <row r="470" spans="1:13" hidden="1">
       <c r="A470" s="27">
         <v>46075</v>
       </c>
@@ -27707,7 +27709,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="471" spans="1:13">
+    <row r="471" spans="1:13" hidden="1">
       <c r="A471" s="27">
         <v>46075</v>
       </c>
@@ -27750,7 +27752,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="472" spans="1:13">
+    <row r="472" spans="1:13" hidden="1">
       <c r="A472" s="27">
         <v>46075</v>
       </c>
@@ -27793,7 +27795,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="473" spans="1:13">
+    <row r="473" spans="1:13" hidden="1">
       <c r="A473" s="27">
         <v>46075</v>
       </c>
@@ -27836,7 +27838,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="474" spans="1:13">
+    <row r="474" spans="1:13" hidden="1">
       <c r="A474" s="27">
         <v>46075</v>
       </c>
@@ -27879,7 +27881,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" hidden="1">
       <c r="A475" s="27">
         <v>46075</v>
       </c>
@@ -27922,7 +27924,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="476" spans="1:13">
+    <row r="476" spans="1:13" hidden="1">
       <c r="A476" s="27">
         <v>46075</v>
       </c>
@@ -27965,7 +27967,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="477" spans="1:13">
+    <row r="477" spans="1:13" hidden="1">
       <c r="A477" s="27">
         <v>46075</v>
       </c>
@@ -28008,7 +28010,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="478" spans="1:13">
+    <row r="478" spans="1:13" hidden="1">
       <c r="A478" s="27">
         <v>46075</v>
       </c>
@@ -28045,7 +28047,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="479" spans="1:13">
+    <row r="479" spans="1:13" hidden="1">
       <c r="A479" s="27">
         <v>46075</v>
       </c>
@@ -28082,7 +28084,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="480" spans="1:13">
+    <row r="480" spans="1:13" hidden="1">
       <c r="A480" s="27">
         <v>46076</v>
       </c>
@@ -28119,7 +28121,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="481" spans="1:13">
+    <row r="481" spans="1:13" hidden="1">
       <c r="A481" s="27">
         <v>46077</v>
       </c>
@@ -28156,7 +28158,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="482" spans="1:13">
+    <row r="482" spans="1:13" hidden="1">
       <c r="A482" s="27">
         <v>46078</v>
       </c>
@@ -28199,7 +28201,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="483" spans="1:13">
+    <row r="483" spans="1:13" hidden="1">
       <c r="A483" s="27">
         <v>46078</v>
       </c>
@@ -28242,7 +28244,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="484" spans="1:13">
+    <row r="484" spans="1:13" hidden="1">
       <c r="A484" s="27">
         <v>46078</v>
       </c>
@@ -28285,7 +28287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="485" spans="1:13">
+    <row r="485" spans="1:13" hidden="1">
       <c r="A485" s="27">
         <v>46078</v>
       </c>
@@ -28328,7 +28330,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="486" spans="1:13">
+    <row r="486" spans="1:13" hidden="1">
       <c r="A486" s="27">
         <v>46078</v>
       </c>
@@ -28371,7 +28373,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="487" spans="1:13">
+    <row r="487" spans="1:13" hidden="1">
       <c r="A487" s="27">
         <v>46078</v>
       </c>
@@ -28414,7 +28416,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="488" spans="1:13">
+    <row r="488" spans="1:13" hidden="1">
       <c r="A488" s="27">
         <v>46078</v>
       </c>
@@ -28457,7 +28459,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="489" spans="1:13">
+    <row r="489" spans="1:13" hidden="1">
       <c r="A489" s="27">
         <v>46078</v>
       </c>
@@ -28494,7 +28496,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="490" spans="1:13">
+    <row r="490" spans="1:13" hidden="1">
       <c r="A490" s="27">
         <v>46079</v>
       </c>
@@ -28531,7 +28533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="491" spans="1:13">
+    <row r="491" spans="1:13" hidden="1">
       <c r="A491" s="27">
         <v>46080</v>
       </c>
@@ -28568,7 +28570,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="492" spans="1:13">
+    <row r="492" spans="1:13" hidden="1">
       <c r="A492" s="27">
         <v>46080</v>
       </c>
@@ -28605,7 +28607,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="493" spans="1:13">
+    <row r="493" spans="1:13" hidden="1">
       <c r="A493" s="27">
         <v>46080</v>
       </c>
@@ -28642,7 +28644,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="494" spans="1:13">
+    <row r="494" spans="1:13" hidden="1">
       <c r="A494" s="27">
         <v>46080</v>
       </c>
@@ -28679,7 +28681,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="495" spans="1:13">
+    <row r="495" spans="1:13" hidden="1">
       <c r="A495" s="27">
         <v>46081</v>
       </c>
@@ -28722,7 +28724,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="496" spans="1:13">
+    <row r="496" spans="1:13" hidden="1">
       <c r="A496" s="27">
         <v>46081</v>
       </c>
@@ -28765,7 +28767,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="497" spans="1:13">
+    <row r="497" spans="1:13" hidden="1">
       <c r="A497" s="27">
         <v>46081</v>
       </c>
@@ -28802,7 +28804,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="498" spans="1:13">
+    <row r="498" spans="1:13" hidden="1">
       <c r="A498" s="27">
         <v>46081</v>
       </c>
@@ -28839,7 +28841,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="499" spans="1:13">
+    <row r="499" spans="1:13" hidden="1">
       <c r="A499" s="27">
         <v>46082</v>
       </c>
@@ -28876,7 +28878,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="500" spans="1:13">
+    <row r="500" spans="1:13" hidden="1">
       <c r="A500" s="27">
         <v>46083</v>
       </c>
@@ -28913,7 +28915,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="501" spans="1:13">
+    <row r="501" spans="1:13" hidden="1">
       <c r="A501" s="27">
         <v>46084</v>
       </c>
@@ -28950,7 +28952,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="502" spans="1:13">
+    <row r="502" spans="1:13" hidden="1">
       <c r="A502" s="27">
         <v>46084</v>
       </c>
@@ -28987,7 +28989,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" hidden="1">
       <c r="A503" s="27">
         <v>46085</v>
       </c>
@@ -29024,7 +29026,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="504" spans="1:13">
+    <row r="504" spans="1:13" hidden="1">
       <c r="A504" s="27">
         <v>46086</v>
       </c>
@@ -29061,7 +29063,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="505" spans="1:13">
+    <row r="505" spans="1:13" hidden="1">
       <c r="A505" s="27">
         <v>46087</v>
       </c>
@@ -29098,7 +29100,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="506" spans="1:13">
+    <row r="506" spans="1:13" hidden="1">
       <c r="A506" s="27">
         <v>46088</v>
       </c>
@@ -29135,7 +29137,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="507" spans="1:13">
+    <row r="507" spans="1:13" hidden="1">
       <c r="A507" s="27">
         <v>46088</v>
       </c>
@@ -29172,7 +29174,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="508" spans="1:13">
+    <row r="508" spans="1:13" hidden="1">
       <c r="A508" s="27">
         <v>46089</v>
       </c>
@@ -29209,7 +29211,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="509" spans="1:13">
+    <row r="509" spans="1:13" hidden="1">
       <c r="A509" s="27">
         <v>46090</v>
       </c>
@@ -29246,7 +29248,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="510" spans="1:13">
+    <row r="510" spans="1:13" hidden="1">
       <c r="A510" s="27">
         <v>46091</v>
       </c>
@@ -29283,7 +29285,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="511" spans="1:13">
+    <row r="511" spans="1:13" hidden="1">
       <c r="A511" s="27">
         <v>46091</v>
       </c>
@@ -29326,7 +29328,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="512" spans="1:13">
+    <row r="512" spans="1:13" hidden="1">
       <c r="A512" s="27">
         <v>46091</v>
       </c>
@@ -29369,7 +29371,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="513" spans="1:13">
+    <row r="513" spans="1:13" hidden="1">
       <c r="A513" s="27">
         <v>46091</v>
       </c>
@@ -29412,7 +29414,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="514" spans="1:13">
+    <row r="514" spans="1:13" hidden="1">
       <c r="A514" s="27">
         <v>46091</v>
       </c>
@@ -29455,7 +29457,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="515" spans="1:13">
+    <row r="515" spans="1:13" hidden="1">
       <c r="A515" s="27">
         <v>46091</v>
       </c>
@@ -29498,7 +29500,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="516" spans="1:13">
+    <row r="516" spans="1:13" hidden="1">
       <c r="A516" s="27">
         <v>46091</v>
       </c>
@@ -29541,7 +29543,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="517" spans="1:13">
+    <row r="517" spans="1:13" hidden="1">
       <c r="A517" s="27">
         <v>46091</v>
       </c>
@@ -29584,7 +29586,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="518" spans="1:13">
+    <row r="518" spans="1:13" hidden="1">
       <c r="A518" s="27">
         <v>46091</v>
       </c>
@@ -29627,7 +29629,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="519" spans="1:13">
+    <row r="519" spans="1:13" hidden="1">
       <c r="A519" s="27">
         <v>46091</v>
       </c>
@@ -29670,7 +29672,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" hidden="1">
       <c r="A520" s="27">
         <v>46091</v>
       </c>
@@ -29713,7 +29715,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="521" spans="1:13">
+    <row r="521" spans="1:13" hidden="1">
       <c r="A521" s="27">
         <v>46091</v>
       </c>
@@ -29750,7 +29752,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="522" spans="1:13">
+    <row r="522" spans="1:13" hidden="1">
       <c r="A522" s="27">
         <v>46092</v>
       </c>
@@ -29787,7 +29789,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="523" spans="1:13">
+    <row r="523" spans="1:13" hidden="1">
       <c r="A523" s="29">
         <v>46093</v>
       </c>
@@ -29825,10 +29827,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O496" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
+  <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2026" dateTimeGrouping="year"/>
+        <dateGroupItem year="2026" month="1" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="1"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -35989,7 +35996,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -36176,7 +36183,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13" hidden="1">
+    <row r="77" spans="1:13">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -36209,7 +36216,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13" hidden="1">
+    <row r="78" spans="1:13">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -36242,7 +36249,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13" hidden="1">
+    <row r="79" spans="1:13">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -36275,7 +36282,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13" hidden="1">
+    <row r="80" spans="1:13">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -36308,7 +36315,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -36341,7 +36348,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -36374,7 +36381,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -36407,7 +36414,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -36440,7 +36447,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -36473,7 +36480,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -36506,7 +36513,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -36539,7 +36546,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -36572,7 +36579,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -36605,7 +36612,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -36638,7 +36645,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -36671,7 +36678,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -36704,7 +36711,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -36737,7 +36744,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -36770,7 +36777,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -36803,7 +36810,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -36836,7 +36843,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13" hidden="1">
+    <row r="97" spans="1:13">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -36869,7 +36876,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13" hidden="1">
+    <row r="98" spans="1:13">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -36902,7 +36909,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13" hidden="1">
+    <row r="99" spans="1:13">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -36935,7 +36942,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13" hidden="1">
+    <row r="100" spans="1:13">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -36968,7 +36975,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13" hidden="1">
+    <row r="101" spans="1:13">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -37001,7 +37008,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13" hidden="1">
+    <row r="102" spans="1:13">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -37034,7 +37041,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13" hidden="1">
+    <row r="103" spans="1:13">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -38929,7 +38936,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13" hidden="1">
+    <row r="161" spans="1:13">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -38958,7 +38965,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13" hidden="1">
+    <row r="162" spans="1:13">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -38987,7 +38994,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13" hidden="1">
+    <row r="163" spans="1:13">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -39016,7 +39023,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13" hidden="1">
+    <row r="164" spans="1:13">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -39395,7 +39402,7 @@
       </c>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13" hidden="1">
+    <row r="175" spans="1:13">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -39428,7 +39435,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13" hidden="1">
+    <row r="176" spans="1:13">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -39593,7 +39600,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -39630,7 +39637,7 @@
       <c r="L181" s="15"/>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -39667,7 +39674,7 @@
       <c r="L182" s="15"/>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -39704,7 +39711,7 @@
       <c r="L183" s="15"/>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -39741,7 +39748,7 @@
       <c r="L184" s="15"/>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -39778,7 +39785,7 @@
       <c r="L185" s="15"/>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -39815,7 +39822,7 @@
       <c r="L186" s="15"/>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -39852,7 +39859,7 @@
       <c r="L187" s="15"/>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -39887,7 +39894,7 @@
       <c r="L188" s="15"/>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -39924,7 +39931,7 @@
       <c r="L189" s="15"/>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -39961,7 +39968,7 @@
       <c r="L190" s="15"/>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -39998,7 +40005,7 @@
       <c r="L191" s="15"/>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -40033,7 +40040,7 @@
       <c r="L192" s="15"/>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -40070,7 +40077,7 @@
       <c r="L193" s="15"/>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -40107,7 +40114,7 @@
       <c r="L194" s="15"/>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -40144,7 +40151,7 @@
       <c r="L195" s="15"/>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -40181,7 +40188,7 @@
       <c r="L196" s="15"/>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -40218,7 +40225,7 @@
       <c r="L197" s="15"/>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -40255,7 +40262,7 @@
       <c r="L198" s="15"/>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -40292,7 +40299,7 @@
       <c r="L199" s="15"/>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -40327,7 +40334,7 @@
       <c r="L200" s="15"/>
       <c r="M200" s="15"/>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" hidden="1">
       <c r="A201" s="14">
         <v>209</v>
       </c>
@@ -40360,7 +40367,7 @@
       <c r="L201" s="15"/>
       <c r="M201" s="15"/>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" hidden="1">
       <c r="A202" s="14">
         <v>210</v>
       </c>
@@ -40393,7 +40400,7 @@
       <c r="L202" s="15"/>
       <c r="M202" s="15"/>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" hidden="1">
       <c r="A203" s="14">
         <v>211</v>
       </c>
@@ -40426,7 +40433,7 @@
       <c r="L203" s="15"/>
       <c r="M203" s="15"/>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" hidden="1">
       <c r="A204" s="14">
         <v>212</v>
       </c>
@@ -40533,7 +40540,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -40566,7 +40573,7 @@
       <c r="L207" s="15"/>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -40599,7 +40606,7 @@
       <c r="L208" s="15"/>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -40632,7 +40639,7 @@
       <c r="L209" s="15"/>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -40669,34 +40676,58 @@
       <c r="A211" s="14">
         <v>219</v>
       </c>
-      <c r="B211" s="42"/>
-      <c r="C211" s="12"/>
+      <c r="B211" s="42">
+        <v>46042</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="D211" s="12"/>
-      <c r="E211" s="12"/>
+      <c r="E211" s="12" t="s">
+        <v>248</v>
+      </c>
       <c r="F211" s="13"/>
-      <c r="G211" s="12"/>
+      <c r="G211" s="12" t="s">
+        <v>249</v>
+      </c>
       <c r="H211" s="13"/>
       <c r="I211" s="26"/>
       <c r="J211" s="15"/>
-      <c r="K211" s="22"/>
-      <c r="L211" s="15"/>
+      <c r="K211" s="22">
+        <v>0</v>
+      </c>
+      <c r="L211" s="15" t="s">
+        <v>251</v>
+      </c>
       <c r="M211" s="15"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="14">
         <v>220</v>
       </c>
-      <c r="B212" s="42"/>
-      <c r="C212" s="12"/>
+      <c r="B212" s="42">
+        <v>46042</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="D212" s="12"/>
-      <c r="E212" s="12"/>
+      <c r="E212" s="12" t="s">
+        <v>249</v>
+      </c>
       <c r="F212" s="13"/>
-      <c r="G212" s="12"/>
+      <c r="G212" s="12" t="s">
+        <v>248</v>
+      </c>
       <c r="H212" s="13"/>
       <c r="I212" s="26"/>
       <c r="J212" s="15"/>
-      <c r="K212" s="22"/>
-      <c r="L212" s="15"/>
+      <c r="K212" s="22">
+        <v>0</v>
+      </c>
+      <c r="L212" s="15" t="s">
+        <v>251</v>
+      </c>
       <c r="M212" s="15"/>
     </row>
     <row r="213" spans="1:13">
@@ -41700,7 +41731,7 @@
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1025</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -41709,7 +41740,7 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="284" spans="10:11">
@@ -41718,7 +41749,7 @@
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1303.2039024390244</v>
+        <v>1290.6125603864734</v>
       </c>
     </row>
     <row r="296" spans="1:8">

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC5EDCE5-EE17-4000-9339-4299C91D98CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DE9C1AA-67DD-4392-98D2-E2E9CF2A8658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="336">
   <si>
     <t>日付</t>
   </si>
@@ -724,22 +724,22 @@
     <t>合計</t>
   </si>
   <si>
+    <t>ライフスタイルサービス</t>
+  </si>
+  <si>
+    <t>JAL Wellness &amp; Travel利用</t>
+  </si>
+  <si>
     <t>航空</t>
   </si>
   <si>
     <t>JAL国内線利用</t>
   </si>
   <si>
-    <t>ライフスタイルサービス</t>
-  </si>
-  <si>
     <t>JALカード利用</t>
   </si>
   <si>
     <t>JALマイレージパーク利用</t>
-  </si>
-  <si>
-    <t>JAL Wellness &amp; Travel利用</t>
   </si>
   <si>
     <t>JAL ふるさと納税</t>
@@ -1030,6 +1030,12 @@
     <t>大阪 (伊丹)</t>
   </si>
   <si>
+    <t>JAL121</t>
+  </si>
+  <si>
+    <t>JAL128</t>
+  </si>
+  <si>
     <t>総額</t>
   </si>
   <si>
@@ -1063,7 +1069,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
     <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1129,6 +1135,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Yu Gothic"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1487,7 +1499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1645,12 +1657,21 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2202,10 +2223,10 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5186</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>84</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8456,6 +8477,12 @@
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="163"/>
+                <c:pt idx="48">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46096</c:v>
+                </c:pt>
                 <c:pt idx="50">
                   <c:v>46093</c:v>
                 </c:pt>
@@ -8799,154 +8826,154 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="163"/>
                 <c:pt idx="0">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1183</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1183</c:v>
+                  <c:v>1184</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>1183</c:v>
@@ -9748,10 +9775,10 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6</c:v>
@@ -14335,6 +14362,9 @@
         <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="11">
+      <filters blank="1"/>
+    </filterColumn>
   </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
@@ -14642,7 +14672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O525"/>
+  <dimension ref="A1:O532"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15210,7 +15240,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>5186</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15260,7 +15290,7 @@
       </c>
       <c r="O17">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＪＭＢアプリ*")</f>
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1">
@@ -15452,7 +15482,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>132256</v>
+        <v>132322</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -15760,12 +15790,12 @@
       <c r="A29" s="27">
         <v>45840</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="76"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="74"/>
       <c r="F29" s="72">
         <v>0</v>
       </c>
@@ -15797,12 +15827,12 @@
       <c r="A30" s="27">
         <v>45841</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="75"/>
-      <c r="D30" s="75"/>
-      <c r="E30" s="76"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="74"/>
       <c r="F30" s="72">
         <v>0</v>
       </c>
@@ -15834,12 +15864,12 @@
       <c r="A31" s="27">
         <v>45841</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="76"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="74"/>
       <c r="F31" s="72">
         <v>0</v>
       </c>
@@ -15871,12 +15901,12 @@
       <c r="A32" s="27">
         <v>45842</v>
       </c>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="76"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="74"/>
       <c r="F32" s="72">
         <v>0</v>
       </c>
@@ -15908,12 +15938,12 @@
       <c r="A33" s="27">
         <v>45843</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="76"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="74"/>
       <c r="F33" s="72">
         <v>0</v>
       </c>
@@ -15945,12 +15975,12 @@
       <c r="A34" s="27">
         <v>45844</v>
       </c>
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="76"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="74"/>
       <c r="F34" s="72">
         <v>0</v>
       </c>
@@ -15982,12 +16012,12 @@
       <c r="A35" s="27">
         <v>45845</v>
       </c>
-      <c r="B35" s="75" t="s">
+      <c r="B35" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="76"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="74"/>
       <c r="F35" s="72">
         <v>0</v>
       </c>
@@ -16019,12 +16049,12 @@
       <c r="A36" s="27">
         <v>45846</v>
       </c>
-      <c r="B36" s="75" t="s">
+      <c r="B36" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="76"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="74"/>
       <c r="F36" s="72">
         <v>0</v>
       </c>
@@ -16056,12 +16086,12 @@
       <c r="A37" s="27">
         <v>45846</v>
       </c>
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="75"/>
-      <c r="E37" s="76"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="74"/>
       <c r="F37" s="72">
         <v>0</v>
       </c>
@@ -16093,12 +16123,12 @@
       <c r="A38" s="27">
         <v>45847</v>
       </c>
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="76"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="74"/>
       <c r="F38" s="72">
         <v>0</v>
       </c>
@@ -16130,12 +16160,12 @@
       <c r="A39" s="27">
         <v>45848</v>
       </c>
-      <c r="B39" s="75" t="s">
+      <c r="B39" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="76"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="72">
         <v>0</v>
       </c>
@@ -16167,12 +16197,12 @@
       <c r="A40" s="27">
         <v>45848</v>
       </c>
-      <c r="B40" s="75" t="s">
+      <c r="B40" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="76"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="74"/>
       <c r="F40" s="72">
         <v>0</v>
       </c>
@@ -16204,12 +16234,12 @@
       <c r="A41" s="27">
         <v>45849</v>
       </c>
-      <c r="B41" s="75" t="s">
+      <c r="B41" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="76"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="74"/>
       <c r="F41" s="72">
         <v>0</v>
       </c>
@@ -16241,12 +16271,12 @@
       <c r="A42" s="27">
         <v>45849</v>
       </c>
-      <c r="B42" s="75" t="s">
+      <c r="B42" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="76"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="74"/>
       <c r="F42" s="72">
         <v>0</v>
       </c>
@@ -16278,12 +16308,12 @@
       <c r="A43" s="27">
         <v>45850</v>
       </c>
-      <c r="B43" s="75" t="s">
+      <c r="B43" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="76"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="74"/>
       <c r="F43" s="72">
         <v>0</v>
       </c>
@@ -16315,12 +16345,12 @@
       <c r="A44" s="27">
         <v>45850</v>
       </c>
-      <c r="B44" s="75" t="s">
+      <c r="B44" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="76"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="74"/>
       <c r="F44" s="72">
         <v>0</v>
       </c>
@@ -16352,12 +16382,12 @@
       <c r="A45" s="27">
         <v>45851</v>
       </c>
-      <c r="B45" s="75" t="s">
+      <c r="B45" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="76"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="74"/>
       <c r="F45" s="72">
         <v>0</v>
       </c>
@@ -16389,12 +16419,12 @@
       <c r="A46" s="27">
         <v>45851</v>
       </c>
-      <c r="B46" s="75" t="s">
+      <c r="B46" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="76"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="74"/>
       <c r="F46" s="72">
         <v>0</v>
       </c>
@@ -16426,12 +16456,12 @@
       <c r="A47" s="27">
         <v>45852</v>
       </c>
-      <c r="B47" s="75" t="s">
+      <c r="B47" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="76"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="74"/>
       <c r="F47" s="72">
         <v>0</v>
       </c>
@@ -16463,12 +16493,12 @@
       <c r="A48" s="27">
         <v>45853</v>
       </c>
-      <c r="B48" s="75" t="s">
+      <c r="B48" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="76"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="74"/>
       <c r="F48" s="72">
         <v>0</v>
       </c>
@@ -16500,12 +16530,12 @@
       <c r="A49" s="27">
         <v>45853</v>
       </c>
-      <c r="B49" s="75" t="s">
+      <c r="B49" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="76"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="74"/>
       <c r="F49" s="72">
         <v>0</v>
       </c>
@@ -16537,12 +16567,12 @@
       <c r="A50" s="27">
         <v>45854</v>
       </c>
-      <c r="B50" s="75" t="s">
+      <c r="B50" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="76"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="74"/>
       <c r="F50" s="72">
         <v>0</v>
       </c>
@@ -16574,12 +16604,12 @@
       <c r="A51" s="27">
         <v>45855</v>
       </c>
-      <c r="B51" s="75" t="s">
+      <c r="B51" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="76"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="74"/>
       <c r="F51" s="72">
         <v>0</v>
       </c>
@@ -16611,12 +16641,12 @@
       <c r="A52" s="27">
         <v>45856</v>
       </c>
-      <c r="B52" s="75" t="s">
+      <c r="B52" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="76"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="74"/>
       <c r="F52" s="72">
         <v>0</v>
       </c>
@@ -16648,12 +16678,12 @@
       <c r="A53" s="27">
         <v>45857</v>
       </c>
-      <c r="B53" s="75" t="s">
+      <c r="B53" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="76"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="74"/>
       <c r="F53" s="72">
         <v>0</v>
       </c>
@@ -16685,12 +16715,12 @@
       <c r="A54" s="27">
         <v>45858</v>
       </c>
-      <c r="B54" s="75" t="s">
+      <c r="B54" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="75"/>
-      <c r="D54" s="75"/>
-      <c r="E54" s="76"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="74"/>
       <c r="F54" s="72">
         <v>0</v>
       </c>
@@ -16722,12 +16752,12 @@
       <c r="A55" s="27">
         <v>45859</v>
       </c>
-      <c r="B55" s="75" t="s">
+      <c r="B55" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="76"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="74"/>
       <c r="F55" s="72">
         <v>0</v>
       </c>
@@ -16802,12 +16832,12 @@
       <c r="A57" s="27">
         <v>45860</v>
       </c>
-      <c r="B57" s="75" t="s">
+      <c r="B57" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="76"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="74"/>
       <c r="F57" s="72">
         <v>0</v>
       </c>
@@ -16839,12 +16869,12 @@
       <c r="A58" s="27">
         <v>45860</v>
       </c>
-      <c r="B58" s="75" t="s">
+      <c r="B58" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="75"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="76"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="74"/>
       <c r="F58" s="72">
         <v>0</v>
       </c>
@@ -16876,12 +16906,12 @@
       <c r="A59" s="27">
         <v>45861</v>
       </c>
-      <c r="B59" s="75" t="s">
+      <c r="B59" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="76"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="74"/>
       <c r="F59" s="72">
         <v>0</v>
       </c>
@@ -16913,12 +16943,12 @@
       <c r="A60" s="27">
         <v>45862</v>
       </c>
-      <c r="B60" s="75" t="s">
+      <c r="B60" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C60" s="75"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="76"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="74"/>
       <c r="F60" s="72">
         <v>0</v>
       </c>
@@ -16950,12 +16980,12 @@
       <c r="A61" s="27">
         <v>45863</v>
       </c>
-      <c r="B61" s="75" t="s">
+      <c r="B61" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="76"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="74"/>
       <c r="F61" s="72">
         <v>0</v>
       </c>
@@ -16987,12 +17017,12 @@
       <c r="A62" s="27">
         <v>45864</v>
       </c>
-      <c r="B62" s="75" t="s">
+      <c r="B62" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="75"/>
-      <c r="D62" s="75"/>
-      <c r="E62" s="76"/>
+      <c r="C62" s="73"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="74"/>
       <c r="F62" s="72">
         <v>0</v>
       </c>
@@ -17024,12 +17054,12 @@
       <c r="A63" s="27">
         <v>45864</v>
       </c>
-      <c r="B63" s="75" t="s">
+      <c r="B63" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C63" s="75"/>
-      <c r="D63" s="75"/>
-      <c r="E63" s="76"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74"/>
       <c r="F63" s="72">
         <v>0</v>
       </c>
@@ -17104,12 +17134,12 @@
       <c r="A65" s="27">
         <v>45865</v>
       </c>
-      <c r="B65" s="75" t="s">
+      <c r="B65" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C65" s="75"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="76"/>
+      <c r="C65" s="73"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="74"/>
       <c r="F65" s="72">
         <v>0</v>
       </c>
@@ -17141,12 +17171,12 @@
       <c r="A66" s="27">
         <v>45866</v>
       </c>
-      <c r="B66" s="75" t="s">
+      <c r="B66" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C66" s="75"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="76"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="74"/>
       <c r="F66" s="72">
         <v>0</v>
       </c>
@@ -17178,12 +17208,12 @@
       <c r="A67" s="27">
         <v>45867</v>
       </c>
-      <c r="B67" s="75" t="s">
+      <c r="B67" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C67" s="75"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="76"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="74"/>
       <c r="F67" s="72">
         <v>0</v>
       </c>
@@ -17215,12 +17245,12 @@
       <c r="A68" s="27">
         <v>45867</v>
       </c>
-      <c r="B68" s="75" t="s">
+      <c r="B68" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C68" s="75"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="76"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="74"/>
       <c r="F68" s="72">
         <v>0</v>
       </c>
@@ -17252,12 +17282,12 @@
       <c r="A69" s="27">
         <v>45868</v>
       </c>
-      <c r="B69" s="75" t="s">
+      <c r="B69" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C69" s="75"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="76"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="74"/>
       <c r="F69" s="72">
         <v>0</v>
       </c>
@@ -17289,12 +17319,12 @@
       <c r="A70" s="27">
         <v>45868</v>
       </c>
-      <c r="B70" s="75" t="s">
+      <c r="B70" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="76"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="74"/>
       <c r="F70" s="72">
         <v>0</v>
       </c>
@@ -17326,12 +17356,12 @@
       <c r="A71" s="27">
         <v>45869</v>
       </c>
-      <c r="B71" s="75" t="s">
+      <c r="B71" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C71" s="75"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="76"/>
+      <c r="C71" s="73"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="74"/>
       <c r="F71" s="72">
         <v>0</v>
       </c>
@@ -17363,12 +17393,12 @@
       <c r="A72" s="27">
         <v>45870</v>
       </c>
-      <c r="B72" s="75" t="s">
+      <c r="B72" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C72" s="75"/>
-      <c r="D72" s="75"/>
-      <c r="E72" s="76"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="72">
         <v>0</v>
       </c>
@@ -17443,12 +17473,12 @@
       <c r="A74" s="27">
         <v>45871</v>
       </c>
-      <c r="B74" s="75" t="s">
+      <c r="B74" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="76"/>
+      <c r="C74" s="73"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="74"/>
       <c r="F74" s="72">
         <v>0</v>
       </c>
@@ -17523,12 +17553,12 @@
       <c r="A76" s="27">
         <v>45872</v>
       </c>
-      <c r="B76" s="75" t="s">
+      <c r="B76" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="76"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="74"/>
       <c r="F76" s="72">
         <v>0</v>
       </c>
@@ -17560,12 +17590,12 @@
       <c r="A77" s="27">
         <v>45873</v>
       </c>
-      <c r="B77" s="75" t="s">
+      <c r="B77" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="75"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="76"/>
+      <c r="C77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="74"/>
       <c r="F77" s="72">
         <v>0</v>
       </c>
@@ -17597,12 +17627,12 @@
       <c r="A78" s="27">
         <v>45874</v>
       </c>
-      <c r="B78" s="75" t="s">
+      <c r="B78" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="75"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="76"/>
+      <c r="C78" s="73"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="74"/>
       <c r="F78" s="72">
         <v>0</v>
       </c>
@@ -17720,12 +17750,12 @@
       <c r="A81" s="27">
         <v>45875</v>
       </c>
-      <c r="B81" s="75" t="s">
+      <c r="B81" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
-      <c r="E81" s="76"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="74"/>
       <c r="F81" s="72">
         <v>0</v>
       </c>
@@ -17757,12 +17787,12 @@
       <c r="A82" s="27">
         <v>45876</v>
       </c>
-      <c r="B82" s="75" t="s">
+      <c r="B82" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="76"/>
+      <c r="C82" s="73"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="74"/>
       <c r="F82" s="72">
         <v>0</v>
       </c>
@@ -17794,12 +17824,12 @@
       <c r="A83" s="29">
         <v>45877</v>
       </c>
-      <c r="B83" s="73" t="s">
+      <c r="B83" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C83" s="73"/>
-      <c r="D83" s="73"/>
-      <c r="E83" s="74"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="76"/>
       <c r="F83" s="71">
         <v>0</v>
       </c>
@@ -17831,12 +17861,12 @@
       <c r="A84" s="27">
         <v>45878</v>
       </c>
-      <c r="B84" s="75" t="s">
+      <c r="B84" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C84" s="75"/>
-      <c r="D84" s="75"/>
-      <c r="E84" s="76"/>
+      <c r="C84" s="73"/>
+      <c r="D84" s="73"/>
+      <c r="E84" s="74"/>
       <c r="F84" s="72">
         <v>0</v>
       </c>
@@ -17868,12 +17898,12 @@
       <c r="A85" s="27">
         <v>45879</v>
       </c>
-      <c r="B85" s="75" t="s">
+      <c r="B85" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C85" s="75"/>
-      <c r="D85" s="75"/>
-      <c r="E85" s="76"/>
+      <c r="C85" s="73"/>
+      <c r="D85" s="73"/>
+      <c r="E85" s="74"/>
       <c r="F85" s="72">
         <v>0</v>
       </c>
@@ -17905,12 +17935,12 @@
       <c r="A86" s="27">
         <v>45879</v>
       </c>
-      <c r="B86" s="75" t="s">
+      <c r="B86" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C86" s="75"/>
-      <c r="D86" s="75"/>
-      <c r="E86" s="76"/>
+      <c r="C86" s="73"/>
+      <c r="D86" s="73"/>
+      <c r="E86" s="74"/>
       <c r="F86" s="72">
         <v>0</v>
       </c>
@@ -17942,12 +17972,12 @@
       <c r="A87" s="27">
         <v>45880</v>
       </c>
-      <c r="B87" s="75" t="s">
+      <c r="B87" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="76"/>
+      <c r="C87" s="73"/>
+      <c r="D87" s="73"/>
+      <c r="E87" s="74"/>
       <c r="F87" s="72">
         <v>0</v>
       </c>
@@ -17979,12 +18009,12 @@
       <c r="A88" s="27">
         <v>45881</v>
       </c>
-      <c r="B88" s="75" t="s">
+      <c r="B88" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C88" s="75"/>
-      <c r="D88" s="75"/>
-      <c r="E88" s="76"/>
+      <c r="C88" s="73"/>
+      <c r="D88" s="73"/>
+      <c r="E88" s="74"/>
       <c r="F88" s="72">
         <v>0</v>
       </c>
@@ -18016,12 +18046,12 @@
       <c r="A89" s="27">
         <v>45882</v>
       </c>
-      <c r="B89" s="75" t="s">
+      <c r="B89" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="76"/>
+      <c r="C89" s="73"/>
+      <c r="D89" s="73"/>
+      <c r="E89" s="74"/>
       <c r="F89" s="72">
         <v>0</v>
       </c>
@@ -18053,12 +18083,12 @@
       <c r="A90" s="27">
         <v>45883</v>
       </c>
-      <c r="B90" s="75" t="s">
+      <c r="B90" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="75"/>
-      <c r="E90" s="76"/>
+      <c r="C90" s="73"/>
+      <c r="D90" s="73"/>
+      <c r="E90" s="74"/>
       <c r="F90" s="72">
         <v>0</v>
       </c>
@@ -18090,12 +18120,12 @@
       <c r="A91" s="27">
         <v>45884</v>
       </c>
-      <c r="B91" s="75" t="s">
+      <c r="B91" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
-      <c r="E91" s="76"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="73"/>
+      <c r="E91" s="74"/>
       <c r="F91" s="72">
         <v>0</v>
       </c>
@@ -18127,12 +18157,12 @@
       <c r="A92" s="27">
         <v>45885</v>
       </c>
-      <c r="B92" s="75" t="s">
+      <c r="B92" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
-      <c r="E92" s="76"/>
+      <c r="C92" s="73"/>
+      <c r="D92" s="73"/>
+      <c r="E92" s="74"/>
       <c r="F92" s="72">
         <v>0</v>
       </c>
@@ -18164,12 +18194,12 @@
       <c r="A93" s="29">
         <v>45886</v>
       </c>
-      <c r="B93" s="73" t="s">
+      <c r="B93" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="73"/>
-      <c r="D93" s="73"/>
-      <c r="E93" s="74"/>
+      <c r="C93" s="75"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="76"/>
       <c r="F93" s="71">
         <v>0</v>
       </c>
@@ -18201,12 +18231,12 @@
       <c r="A94" s="27">
         <v>45887</v>
       </c>
-      <c r="B94" s="75" t="s">
+      <c r="B94" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C94" s="75"/>
-      <c r="D94" s="75"/>
-      <c r="E94" s="76"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="74"/>
       <c r="F94" s="72">
         <v>0</v>
       </c>
@@ -18238,12 +18268,12 @@
       <c r="A95" s="27">
         <v>45888</v>
       </c>
-      <c r="B95" s="75" t="s">
+      <c r="B95" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="76"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="74"/>
       <c r="F95" s="72">
         <v>0</v>
       </c>
@@ -18275,12 +18305,12 @@
       <c r="A96" s="27">
         <v>45889</v>
       </c>
-      <c r="B96" s="75" t="s">
+      <c r="B96" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C96" s="75"/>
-      <c r="D96" s="75"/>
-      <c r="E96" s="76"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="74"/>
       <c r="F96" s="72">
         <v>0</v>
       </c>
@@ -18355,12 +18385,12 @@
       <c r="A98" s="27">
         <v>45890</v>
       </c>
-      <c r="B98" s="75" t="s">
+      <c r="B98" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="76"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="73"/>
+      <c r="E98" s="74"/>
       <c r="F98" s="72">
         <v>0</v>
       </c>
@@ -18435,12 +18465,12 @@
       <c r="A100" s="27">
         <v>45891</v>
       </c>
-      <c r="B100" s="75" t="s">
+      <c r="B100" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C100" s="75"/>
-      <c r="D100" s="75"/>
-      <c r="E100" s="76"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="74"/>
       <c r="F100" s="72">
         <v>0</v>
       </c>
@@ -18472,12 +18502,12 @@
       <c r="A101" s="27">
         <v>45892</v>
       </c>
-      <c r="B101" s="75" t="s">
+      <c r="B101" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C101" s="75"/>
-      <c r="D101" s="75"/>
-      <c r="E101" s="76"/>
+      <c r="C101" s="73"/>
+      <c r="D101" s="73"/>
+      <c r="E101" s="74"/>
       <c r="F101" s="72">
         <v>0</v>
       </c>
@@ -18509,12 +18539,12 @@
       <c r="A102" s="29">
         <v>45893</v>
       </c>
-      <c r="B102" s="73" t="s">
+      <c r="B102" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C102" s="73"/>
-      <c r="D102" s="73"/>
-      <c r="E102" s="74"/>
+      <c r="C102" s="75"/>
+      <c r="D102" s="75"/>
+      <c r="E102" s="76"/>
       <c r="F102" s="71">
         <v>0</v>
       </c>
@@ -18546,12 +18576,12 @@
       <c r="A103" s="27">
         <v>45894</v>
       </c>
-      <c r="B103" s="75" t="s">
+      <c r="B103" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C103" s="75"/>
-      <c r="D103" s="75"/>
-      <c r="E103" s="76"/>
+      <c r="C103" s="73"/>
+      <c r="D103" s="73"/>
+      <c r="E103" s="74"/>
       <c r="F103" s="72">
         <v>0</v>
       </c>
@@ -18583,12 +18613,12 @@
       <c r="A104" s="27">
         <v>45895</v>
       </c>
-      <c r="B104" s="75" t="s">
+      <c r="B104" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C104" s="75"/>
-      <c r="D104" s="75"/>
-      <c r="E104" s="76"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="74"/>
       <c r="F104" s="72">
         <v>0</v>
       </c>
@@ -18620,12 +18650,12 @@
       <c r="A105" s="27">
         <v>45896</v>
       </c>
-      <c r="B105" s="75" t="s">
+      <c r="B105" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="76"/>
+      <c r="C105" s="73"/>
+      <c r="D105" s="73"/>
+      <c r="E105" s="74"/>
       <c r="F105" s="72">
         <v>0</v>
       </c>
@@ -18657,12 +18687,12 @@
       <c r="A106" s="27">
         <v>45896</v>
       </c>
-      <c r="B106" s="75" t="s">
+      <c r="B106" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="75"/>
-      <c r="D106" s="75"/>
-      <c r="E106" s="76"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="73"/>
+      <c r="E106" s="74"/>
       <c r="F106" s="72">
         <v>0</v>
       </c>
@@ -18694,12 +18724,12 @@
       <c r="A107" s="27">
         <v>45897</v>
       </c>
-      <c r="B107" s="75" t="s">
+      <c r="B107" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C107" s="75"/>
-      <c r="D107" s="75"/>
-      <c r="E107" s="76"/>
+      <c r="C107" s="73"/>
+      <c r="D107" s="73"/>
+      <c r="E107" s="74"/>
       <c r="F107" s="72">
         <v>0</v>
       </c>
@@ -18731,12 +18761,12 @@
       <c r="A108" s="27">
         <v>45897</v>
       </c>
-      <c r="B108" s="75" t="s">
+      <c r="B108" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C108" s="75"/>
-      <c r="D108" s="75"/>
-      <c r="E108" s="76"/>
+      <c r="C108" s="73"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="74"/>
       <c r="F108" s="72">
         <v>0</v>
       </c>
@@ -18768,12 +18798,12 @@
       <c r="A109" s="27">
         <v>45898</v>
       </c>
-      <c r="B109" s="75" t="s">
+      <c r="B109" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="75"/>
-      <c r="E109" s="76"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="73"/>
+      <c r="E109" s="74"/>
       <c r="F109" s="72">
         <v>0</v>
       </c>
@@ -18805,12 +18835,12 @@
       <c r="A110" s="27">
         <v>45899</v>
       </c>
-      <c r="B110" s="75" t="s">
+      <c r="B110" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C110" s="75"/>
-      <c r="D110" s="75"/>
-      <c r="E110" s="76"/>
+      <c r="C110" s="73"/>
+      <c r="D110" s="73"/>
+      <c r="E110" s="74"/>
       <c r="F110" s="72">
         <v>0</v>
       </c>
@@ -18842,12 +18872,12 @@
       <c r="A111" s="27">
         <v>45900</v>
       </c>
-      <c r="B111" s="75" t="s">
+      <c r="B111" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C111" s="75"/>
-      <c r="D111" s="75"/>
-      <c r="E111" s="76"/>
+      <c r="C111" s="73"/>
+      <c r="D111" s="73"/>
+      <c r="E111" s="74"/>
       <c r="F111" s="72">
         <v>0</v>
       </c>
@@ -18879,12 +18909,12 @@
       <c r="A112" s="27">
         <v>45900</v>
       </c>
-      <c r="B112" s="75" t="s">
+      <c r="B112" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C112" s="75"/>
-      <c r="D112" s="75"/>
-      <c r="E112" s="76"/>
+      <c r="C112" s="73"/>
+      <c r="D112" s="73"/>
+      <c r="E112" s="74"/>
       <c r="F112" s="72">
         <v>0</v>
       </c>
@@ -18959,12 +18989,12 @@
       <c r="A114" s="27">
         <v>45901</v>
       </c>
-      <c r="B114" s="75" t="s">
+      <c r="B114" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C114" s="75"/>
-      <c r="D114" s="75"/>
-      <c r="E114" s="76"/>
+      <c r="C114" s="73"/>
+      <c r="D114" s="73"/>
+      <c r="E114" s="74"/>
       <c r="F114" s="72">
         <v>0</v>
       </c>
@@ -18996,12 +19026,12 @@
       <c r="A115" s="27">
         <v>45902</v>
       </c>
-      <c r="B115" s="75" t="s">
+      <c r="B115" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C115" s="75"/>
-      <c r="D115" s="75"/>
-      <c r="E115" s="76"/>
+      <c r="C115" s="73"/>
+      <c r="D115" s="73"/>
+      <c r="E115" s="74"/>
       <c r="F115" s="72">
         <v>0</v>
       </c>
@@ -19076,12 +19106,12 @@
       <c r="A117" s="27">
         <v>45903</v>
       </c>
-      <c r="B117" s="75" t="s">
+      <c r="B117" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C117" s="75"/>
-      <c r="D117" s="75"/>
-      <c r="E117" s="76"/>
+      <c r="C117" s="73"/>
+      <c r="D117" s="73"/>
+      <c r="E117" s="74"/>
       <c r="F117" s="72">
         <v>0</v>
       </c>
@@ -19113,12 +19143,12 @@
       <c r="A118" s="27">
         <v>45904</v>
       </c>
-      <c r="B118" s="75" t="s">
+      <c r="B118" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C118" s="75"/>
-      <c r="D118" s="75"/>
-      <c r="E118" s="76"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="73"/>
+      <c r="E118" s="74"/>
       <c r="F118" s="72">
         <v>0</v>
       </c>
@@ -19150,12 +19180,12 @@
       <c r="A119" s="27">
         <v>45905</v>
       </c>
-      <c r="B119" s="75" t="s">
+      <c r="B119" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C119" s="75"/>
-      <c r="D119" s="75"/>
-      <c r="E119" s="76"/>
+      <c r="C119" s="73"/>
+      <c r="D119" s="73"/>
+      <c r="E119" s="74"/>
       <c r="F119" s="72">
         <v>0</v>
       </c>
@@ -19187,12 +19217,12 @@
       <c r="A120" s="27">
         <v>45906</v>
       </c>
-      <c r="B120" s="75" t="s">
+      <c r="B120" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C120" s="75"/>
-      <c r="D120" s="75"/>
-      <c r="E120" s="76"/>
+      <c r="C120" s="73"/>
+      <c r="D120" s="73"/>
+      <c r="E120" s="74"/>
       <c r="F120" s="72">
         <v>0</v>
       </c>
@@ -19224,12 +19254,12 @@
       <c r="A121" s="29">
         <v>45907</v>
       </c>
-      <c r="B121" s="73" t="s">
+      <c r="B121" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C121" s="73"/>
-      <c r="D121" s="73"/>
-      <c r="E121" s="74"/>
+      <c r="C121" s="75"/>
+      <c r="D121" s="75"/>
+      <c r="E121" s="76"/>
       <c r="F121" s="71">
         <v>0</v>
       </c>
@@ -19261,12 +19291,12 @@
       <c r="A122" s="27">
         <v>45908</v>
       </c>
-      <c r="B122" s="75" t="s">
+      <c r="B122" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C122" s="75"/>
-      <c r="D122" s="75"/>
-      <c r="E122" s="76"/>
+      <c r="C122" s="73"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="74"/>
       <c r="F122" s="72">
         <v>0</v>
       </c>
@@ -19298,12 +19328,12 @@
       <c r="A123" s="27">
         <v>45909</v>
       </c>
-      <c r="B123" s="75" t="s">
+      <c r="B123" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C123" s="75"/>
-      <c r="D123" s="75"/>
-      <c r="E123" s="76"/>
+      <c r="C123" s="73"/>
+      <c r="D123" s="73"/>
+      <c r="E123" s="74"/>
       <c r="F123" s="72">
         <v>0</v>
       </c>
@@ -19335,12 +19365,12 @@
       <c r="A124" s="27">
         <v>45910</v>
       </c>
-      <c r="B124" s="75" t="s">
+      <c r="B124" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C124" s="75"/>
-      <c r="D124" s="75"/>
-      <c r="E124" s="76"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="74"/>
       <c r="F124" s="4">
         <v>2207</v>
       </c>
@@ -19372,12 +19402,12 @@
       <c r="A125" s="27">
         <v>45910</v>
       </c>
-      <c r="B125" s="75" t="s">
+      <c r="B125" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C125" s="75"/>
-      <c r="D125" s="75"/>
-      <c r="E125" s="76"/>
+      <c r="C125" s="73"/>
+      <c r="D125" s="73"/>
+      <c r="E125" s="74"/>
       <c r="F125" s="72">
         <v>0</v>
       </c>
@@ -19409,12 +19439,12 @@
       <c r="A126" s="27">
         <v>45911</v>
       </c>
-      <c r="B126" s="75" t="s">
+      <c r="B126" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C126" s="75"/>
-      <c r="D126" s="75"/>
-      <c r="E126" s="76"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="73"/>
+      <c r="E126" s="74"/>
       <c r="F126" s="72">
         <v>12</v>
       </c>
@@ -19446,12 +19476,12 @@
       <c r="A127" s="27">
         <v>45911</v>
       </c>
-      <c r="B127" s="75" t="s">
+      <c r="B127" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C127" s="75"/>
-      <c r="D127" s="75"/>
-      <c r="E127" s="76"/>
+      <c r="C127" s="73"/>
+      <c r="D127" s="73"/>
+      <c r="E127" s="74"/>
       <c r="F127" s="72">
         <v>0</v>
       </c>
@@ -19483,12 +19513,12 @@
       <c r="A128" s="27">
         <v>45912</v>
       </c>
-      <c r="B128" s="75" t="s">
+      <c r="B128" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C128" s="75"/>
-      <c r="D128" s="75"/>
-      <c r="E128" s="76"/>
+      <c r="C128" s="73"/>
+      <c r="D128" s="73"/>
+      <c r="E128" s="74"/>
       <c r="F128" s="72">
         <v>0</v>
       </c>
@@ -19520,12 +19550,12 @@
       <c r="A129" s="29">
         <v>45913</v>
       </c>
-      <c r="B129" s="73" t="s">
+      <c r="B129" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C129" s="73"/>
-      <c r="D129" s="73"/>
-      <c r="E129" s="74"/>
+      <c r="C129" s="75"/>
+      <c r="D129" s="75"/>
+      <c r="E129" s="76"/>
       <c r="F129" s="71">
         <v>0</v>
       </c>
@@ -19557,12 +19587,12 @@
       <c r="A130" s="27">
         <v>45914</v>
       </c>
-      <c r="B130" s="75" t="s">
+      <c r="B130" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="75"/>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
+      <c r="C130" s="73"/>
+      <c r="D130" s="73"/>
+      <c r="E130" s="74"/>
       <c r="F130" s="72">
         <v>0</v>
       </c>
@@ -19594,12 +19624,12 @@
       <c r="A131" s="27">
         <v>45914</v>
       </c>
-      <c r="B131" s="75" t="s">
+      <c r="B131" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C131" s="75"/>
-      <c r="D131" s="75"/>
-      <c r="E131" s="76"/>
+      <c r="C131" s="73"/>
+      <c r="D131" s="73"/>
+      <c r="E131" s="74"/>
       <c r="F131" s="72">
         <v>0</v>
       </c>
@@ -19631,12 +19661,12 @@
       <c r="A132" s="29">
         <v>45914</v>
       </c>
-      <c r="B132" s="73" t="s">
+      <c r="B132" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="C132" s="73"/>
-      <c r="D132" s="73"/>
-      <c r="E132" s="74"/>
+      <c r="C132" s="75"/>
+      <c r="D132" s="75"/>
+      <c r="E132" s="76"/>
       <c r="F132" s="30">
         <v>-1500</v>
       </c>
@@ -19711,12 +19741,12 @@
       <c r="A134" s="27">
         <v>45915</v>
       </c>
-      <c r="B134" s="75" t="s">
+      <c r="B134" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C134" s="75"/>
-      <c r="D134" s="75"/>
-      <c r="E134" s="76"/>
+      <c r="C134" s="73"/>
+      <c r="D134" s="73"/>
+      <c r="E134" s="74"/>
       <c r="F134" s="72">
         <v>0</v>
       </c>
@@ -19748,12 +19778,12 @@
       <c r="A135" s="27">
         <v>45916</v>
       </c>
-      <c r="B135" s="75" t="s">
+      <c r="B135" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C135" s="75"/>
-      <c r="D135" s="75"/>
-      <c r="E135" s="76"/>
+      <c r="C135" s="73"/>
+      <c r="D135" s="73"/>
+      <c r="E135" s="74"/>
       <c r="F135" s="72">
         <v>0</v>
       </c>
@@ -19828,12 +19858,12 @@
       <c r="A137" s="27">
         <v>45917</v>
       </c>
-      <c r="B137" s="75" t="s">
+      <c r="B137" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C137" s="75"/>
-      <c r="D137" s="75"/>
-      <c r="E137" s="76"/>
+      <c r="C137" s="73"/>
+      <c r="D137" s="73"/>
+      <c r="E137" s="74"/>
       <c r="F137" s="72">
         <v>0</v>
       </c>
@@ -19865,12 +19895,12 @@
       <c r="A138" s="27">
         <v>45918</v>
       </c>
-      <c r="B138" s="75" t="s">
+      <c r="B138" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C138" s="75"/>
-      <c r="D138" s="75"/>
-      <c r="E138" s="76"/>
+      <c r="C138" s="73"/>
+      <c r="D138" s="73"/>
+      <c r="E138" s="74"/>
       <c r="F138" s="72">
         <v>0</v>
       </c>
@@ -19902,12 +19932,12 @@
       <c r="A139" s="27">
         <v>45919</v>
       </c>
-      <c r="B139" s="75" t="s">
+      <c r="B139" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C139" s="75"/>
-      <c r="D139" s="75"/>
-      <c r="E139" s="76"/>
+      <c r="C139" s="73"/>
+      <c r="D139" s="73"/>
+      <c r="E139" s="74"/>
       <c r="F139" s="72">
         <v>0</v>
       </c>
@@ -19939,12 +19969,12 @@
       <c r="A140" s="27">
         <v>45919</v>
       </c>
-      <c r="B140" s="75" t="s">
+      <c r="B140" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C140" s="75"/>
-      <c r="D140" s="75"/>
-      <c r="E140" s="76"/>
+      <c r="C140" s="73"/>
+      <c r="D140" s="73"/>
+      <c r="E140" s="74"/>
       <c r="F140" s="4">
         <v>-7000</v>
       </c>
@@ -19976,12 +20006,12 @@
       <c r="A141" s="27">
         <v>45919</v>
       </c>
-      <c r="B141" s="75" t="s">
+      <c r="B141" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C141" s="75"/>
-      <c r="D141" s="75"/>
-      <c r="E141" s="76"/>
+      <c r="C141" s="73"/>
+      <c r="D141" s="73"/>
+      <c r="E141" s="74"/>
       <c r="F141" s="4">
         <v>-7000</v>
       </c>
@@ -20013,12 +20043,12 @@
       <c r="A142" s="27">
         <v>45919</v>
       </c>
-      <c r="B142" s="75" t="s">
+      <c r="B142" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C142" s="75"/>
-      <c r="D142" s="75"/>
-      <c r="E142" s="76"/>
+      <c r="C142" s="73"/>
+      <c r="D142" s="73"/>
+      <c r="E142" s="74"/>
       <c r="F142" s="4">
         <v>-7000</v>
       </c>
@@ -20050,12 +20080,12 @@
       <c r="A143" s="27">
         <v>45919</v>
       </c>
-      <c r="B143" s="75" t="s">
+      <c r="B143" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C143" s="75"/>
-      <c r="D143" s="75"/>
-      <c r="E143" s="76"/>
+      <c r="C143" s="73"/>
+      <c r="D143" s="73"/>
+      <c r="E143" s="74"/>
       <c r="F143" s="4">
         <v>-7000</v>
       </c>
@@ -20087,12 +20117,12 @@
       <c r="A144" s="29">
         <v>45920</v>
       </c>
-      <c r="B144" s="73" t="s">
+      <c r="B144" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C144" s="73"/>
-      <c r="D144" s="73"/>
-      <c r="E144" s="74"/>
+      <c r="C144" s="75"/>
+      <c r="D144" s="75"/>
+      <c r="E144" s="76"/>
       <c r="F144" s="71">
         <v>0</v>
       </c>
@@ -20124,12 +20154,12 @@
       <c r="A145" s="27">
         <v>45921</v>
       </c>
-      <c r="B145" s="75" t="s">
+      <c r="B145" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C145" s="75"/>
-      <c r="D145" s="75"/>
-      <c r="E145" s="76"/>
+      <c r="C145" s="73"/>
+      <c r="D145" s="73"/>
+      <c r="E145" s="74"/>
       <c r="F145" s="72">
         <v>0</v>
       </c>
@@ -20161,12 +20191,12 @@
       <c r="A146" s="27">
         <v>45922</v>
       </c>
-      <c r="B146" s="75" t="s">
+      <c r="B146" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C146" s="75"/>
-      <c r="D146" s="75"/>
-      <c r="E146" s="76"/>
+      <c r="C146" s="73"/>
+      <c r="D146" s="73"/>
+      <c r="E146" s="74"/>
       <c r="F146" s="72">
         <v>0</v>
       </c>
@@ -20198,12 +20228,12 @@
       <c r="A147" s="27">
         <v>45923</v>
       </c>
-      <c r="B147" s="75" t="s">
+      <c r="B147" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C147" s="75"/>
-      <c r="D147" s="75"/>
-      <c r="E147" s="76"/>
+      <c r="C147" s="73"/>
+      <c r="D147" s="73"/>
+      <c r="E147" s="74"/>
       <c r="F147" s="72">
         <v>0</v>
       </c>
@@ -20235,12 +20265,12 @@
       <c r="A148" s="27">
         <v>45924</v>
       </c>
-      <c r="B148" s="75" t="s">
+      <c r="B148" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C148" s="75"/>
-      <c r="D148" s="75"/>
-      <c r="E148" s="76"/>
+      <c r="C148" s="73"/>
+      <c r="D148" s="73"/>
+      <c r="E148" s="74"/>
       <c r="F148" s="72">
         <v>0</v>
       </c>
@@ -20272,12 +20302,12 @@
       <c r="A149" s="27">
         <v>45925</v>
       </c>
-      <c r="B149" s="75" t="s">
+      <c r="B149" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="75"/>
-      <c r="D149" s="75"/>
-      <c r="E149" s="76"/>
+      <c r="C149" s="73"/>
+      <c r="D149" s="73"/>
+      <c r="E149" s="74"/>
       <c r="F149" s="72">
         <v>0</v>
       </c>
@@ -20610,12 +20640,12 @@
       <c r="A157" s="27">
         <v>45926</v>
       </c>
-      <c r="B157" s="75" t="s">
+      <c r="B157" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C157" s="75"/>
-      <c r="D157" s="75"/>
-      <c r="E157" s="76"/>
+      <c r="C157" s="73"/>
+      <c r="D157" s="73"/>
+      <c r="E157" s="74"/>
       <c r="F157" s="72">
         <v>0</v>
       </c>
@@ -21034,12 +21064,12 @@
       <c r="A167" s="27">
         <v>45927</v>
       </c>
-      <c r="B167" s="75" t="s">
+      <c r="B167" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C167" s="75"/>
-      <c r="D167" s="75"/>
-      <c r="E167" s="76"/>
+      <c r="C167" s="73"/>
+      <c r="D167" s="73"/>
+      <c r="E167" s="74"/>
       <c r="F167" s="72">
         <v>0</v>
       </c>
@@ -21071,12 +21101,12 @@
       <c r="A168" s="27">
         <v>45928</v>
       </c>
-      <c r="B168" s="75" t="s">
+      <c r="B168" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C168" s="75"/>
-      <c r="D168" s="75"/>
-      <c r="E168" s="76"/>
+      <c r="C168" s="73"/>
+      <c r="D168" s="73"/>
+      <c r="E168" s="74"/>
       <c r="F168" s="72">
         <v>0</v>
       </c>
@@ -21108,12 +21138,12 @@
       <c r="A169" s="29">
         <v>45929</v>
       </c>
-      <c r="B169" s="73" t="s">
+      <c r="B169" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C169" s="73"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="74"/>
+      <c r="C169" s="75"/>
+      <c r="D169" s="75"/>
+      <c r="E169" s="76"/>
       <c r="F169" s="71">
         <v>0</v>
       </c>
@@ -21145,12 +21175,12 @@
       <c r="A170" s="27">
         <v>45930</v>
       </c>
-      <c r="B170" s="75" t="s">
+      <c r="B170" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C170" s="75"/>
-      <c r="D170" s="75"/>
-      <c r="E170" s="76"/>
+      <c r="C170" s="73"/>
+      <c r="D170" s="73"/>
+      <c r="E170" s="74"/>
       <c r="F170" s="72">
         <v>0</v>
       </c>
@@ -21182,12 +21212,12 @@
       <c r="A171" s="27">
         <v>45930</v>
       </c>
-      <c r="B171" s="75" t="s">
+      <c r="B171" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C171" s="75"/>
-      <c r="D171" s="75"/>
-      <c r="E171" s="76"/>
+      <c r="C171" s="73"/>
+      <c r="D171" s="73"/>
+      <c r="E171" s="74"/>
       <c r="F171" s="72">
         <v>0</v>
       </c>
@@ -21219,12 +21249,12 @@
       <c r="A172" s="27">
         <v>45931</v>
       </c>
-      <c r="B172" s="75" t="s">
+      <c r="B172" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C172" s="75"/>
-      <c r="D172" s="75"/>
-      <c r="E172" s="76"/>
+      <c r="C172" s="73"/>
+      <c r="D172" s="73"/>
+      <c r="E172" s="74"/>
       <c r="F172" s="72">
         <v>0</v>
       </c>
@@ -21299,12 +21329,12 @@
       <c r="A174" s="27">
         <v>45932</v>
       </c>
-      <c r="B174" s="75" t="s">
+      <c r="B174" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C174" s="75"/>
-      <c r="D174" s="75"/>
-      <c r="E174" s="76"/>
+      <c r="C174" s="73"/>
+      <c r="D174" s="73"/>
+      <c r="E174" s="74"/>
       <c r="F174" s="72">
         <v>0</v>
       </c>
@@ -21336,12 +21366,12 @@
       <c r="A175" s="27">
         <v>45933</v>
       </c>
-      <c r="B175" s="75" t="s">
+      <c r="B175" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C175" s="75"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="76"/>
+      <c r="C175" s="73"/>
+      <c r="D175" s="73"/>
+      <c r="E175" s="74"/>
       <c r="F175" s="72">
         <v>0</v>
       </c>
@@ -21373,12 +21403,12 @@
       <c r="A176" s="27">
         <v>45933</v>
       </c>
-      <c r="B176" s="75" t="s">
+      <c r="B176" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C176" s="75"/>
-      <c r="D176" s="75"/>
-      <c r="E176" s="76"/>
+      <c r="C176" s="73"/>
+      <c r="D176" s="73"/>
+      <c r="E176" s="74"/>
       <c r="F176" s="72">
         <v>0</v>
       </c>
@@ -21453,12 +21483,12 @@
       <c r="A178" s="27">
         <v>45934</v>
       </c>
-      <c r="B178" s="75" t="s">
+      <c r="B178" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C178" s="75"/>
-      <c r="D178" s="75"/>
-      <c r="E178" s="76"/>
+      <c r="C178" s="73"/>
+      <c r="D178" s="73"/>
+      <c r="E178" s="74"/>
       <c r="F178" s="72">
         <v>0</v>
       </c>
@@ -21490,12 +21520,12 @@
       <c r="A179" s="27">
         <v>45934</v>
       </c>
-      <c r="B179" s="75" t="s">
+      <c r="B179" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C179" s="75"/>
-      <c r="D179" s="75"/>
-      <c r="E179" s="76"/>
+      <c r="C179" s="73"/>
+      <c r="D179" s="73"/>
+      <c r="E179" s="74"/>
       <c r="F179" s="72">
         <v>0</v>
       </c>
@@ -21828,12 +21858,12 @@
       <c r="A187" s="27">
         <v>45935</v>
       </c>
-      <c r="B187" s="75" t="s">
+      <c r="B187" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C187" s="75"/>
-      <c r="D187" s="75"/>
-      <c r="E187" s="76"/>
+      <c r="C187" s="73"/>
+      <c r="D187" s="73"/>
+      <c r="E187" s="74"/>
       <c r="F187" s="72">
         <v>0</v>
       </c>
@@ -21865,12 +21895,12 @@
       <c r="A188" s="27">
         <v>45935</v>
       </c>
-      <c r="B188" s="75" t="s">
+      <c r="B188" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C188" s="75"/>
-      <c r="D188" s="75"/>
-      <c r="E188" s="76"/>
+      <c r="C188" s="73"/>
+      <c r="D188" s="73"/>
+      <c r="E188" s="74"/>
       <c r="F188" s="72">
         <v>0</v>
       </c>
@@ -21902,12 +21932,12 @@
       <c r="A189" s="27">
         <v>45936</v>
       </c>
-      <c r="B189" s="75" t="s">
+      <c r="B189" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C189" s="75"/>
-      <c r="D189" s="75"/>
-      <c r="E189" s="76"/>
+      <c r="C189" s="73"/>
+      <c r="D189" s="73"/>
+      <c r="E189" s="74"/>
       <c r="F189" s="72">
         <v>0</v>
       </c>
@@ -21939,12 +21969,12 @@
       <c r="A190" s="27">
         <v>45937</v>
       </c>
-      <c r="B190" s="75" t="s">
+      <c r="B190" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C190" s="75"/>
-      <c r="D190" s="75"/>
-      <c r="E190" s="76"/>
+      <c r="C190" s="73"/>
+      <c r="D190" s="73"/>
+      <c r="E190" s="74"/>
       <c r="F190" s="72">
         <v>0</v>
       </c>
@@ -21976,12 +22006,12 @@
       <c r="A191" s="27">
         <v>45938</v>
       </c>
-      <c r="B191" s="75" t="s">
+      <c r="B191" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C191" s="75"/>
-      <c r="D191" s="75"/>
-      <c r="E191" s="76"/>
+      <c r="C191" s="73"/>
+      <c r="D191" s="73"/>
+      <c r="E191" s="74"/>
       <c r="F191" s="72">
         <v>0</v>
       </c>
@@ -22056,12 +22086,12 @@
       <c r="A193" s="27">
         <v>45939</v>
       </c>
-      <c r="B193" s="75" t="s">
+      <c r="B193" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C193" s="75"/>
-      <c r="D193" s="75"/>
-      <c r="E193" s="76"/>
+      <c r="C193" s="73"/>
+      <c r="D193" s="73"/>
+      <c r="E193" s="74"/>
       <c r="F193" s="72">
         <v>0</v>
       </c>
@@ -22093,12 +22123,12 @@
       <c r="A194" s="27">
         <v>45940</v>
       </c>
-      <c r="B194" s="75" t="s">
+      <c r="B194" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C194" s="75"/>
-      <c r="D194" s="75"/>
-      <c r="E194" s="76"/>
+      <c r="C194" s="73"/>
+      <c r="D194" s="73"/>
+      <c r="E194" s="74"/>
       <c r="F194" s="4">
         <v>7252</v>
       </c>
@@ -22130,12 +22160,12 @@
       <c r="A195" s="27">
         <v>45940</v>
       </c>
-      <c r="B195" s="75" t="s">
+      <c r="B195" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C195" s="75"/>
-      <c r="D195" s="75"/>
-      <c r="E195" s="76"/>
+      <c r="C195" s="73"/>
+      <c r="D195" s="73"/>
+      <c r="E195" s="74"/>
       <c r="F195" s="72">
         <v>0</v>
       </c>
@@ -22167,12 +22197,12 @@
       <c r="A196" s="27">
         <v>45941</v>
       </c>
-      <c r="B196" s="75" t="s">
+      <c r="B196" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C196" s="75"/>
-      <c r="D196" s="75"/>
-      <c r="E196" s="76"/>
+      <c r="C196" s="73"/>
+      <c r="D196" s="73"/>
+      <c r="E196" s="74"/>
       <c r="F196" s="72">
         <v>0</v>
       </c>
@@ -22204,12 +22234,12 @@
       <c r="A197" s="29">
         <v>45942</v>
       </c>
-      <c r="B197" s="73" t="s">
+      <c r="B197" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C197" s="73"/>
-      <c r="D197" s="73"/>
-      <c r="E197" s="74"/>
+      <c r="C197" s="75"/>
+      <c r="D197" s="75"/>
+      <c r="E197" s="76"/>
       <c r="F197" s="71">
         <v>0</v>
       </c>
@@ -22241,12 +22271,12 @@
       <c r="A198" s="27">
         <v>45943</v>
       </c>
-      <c r="B198" s="75" t="s">
+      <c r="B198" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C198" s="75"/>
-      <c r="D198" s="75"/>
-      <c r="E198" s="76"/>
+      <c r="C198" s="73"/>
+      <c r="D198" s="73"/>
+      <c r="E198" s="74"/>
       <c r="F198" s="72">
         <v>0</v>
       </c>
@@ -22364,12 +22394,12 @@
       <c r="A201" s="27">
         <v>45944</v>
       </c>
-      <c r="B201" s="75" t="s">
+      <c r="B201" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C201" s="75"/>
-      <c r="D201" s="75"/>
-      <c r="E201" s="76"/>
+      <c r="C201" s="73"/>
+      <c r="D201" s="73"/>
+      <c r="E201" s="74"/>
       <c r="F201" s="72">
         <v>0</v>
       </c>
@@ -22401,12 +22431,12 @@
       <c r="A202" s="27">
         <v>45945</v>
       </c>
-      <c r="B202" s="75" t="s">
+      <c r="B202" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C202" s="75"/>
-      <c r="D202" s="75"/>
-      <c r="E202" s="76"/>
+      <c r="C202" s="73"/>
+      <c r="D202" s="73"/>
+      <c r="E202" s="74"/>
       <c r="F202" s="72">
         <v>0</v>
       </c>
@@ -22438,12 +22468,12 @@
       <c r="A203" s="27">
         <v>45946</v>
       </c>
-      <c r="B203" s="75" t="s">
+      <c r="B203" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C203" s="75"/>
-      <c r="D203" s="75"/>
-      <c r="E203" s="76"/>
+      <c r="C203" s="73"/>
+      <c r="D203" s="73"/>
+      <c r="E203" s="74"/>
       <c r="F203" s="72">
         <v>0</v>
       </c>
@@ -22475,12 +22505,12 @@
       <c r="A204" s="27">
         <v>45947</v>
       </c>
-      <c r="B204" s="75" t="s">
+      <c r="B204" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C204" s="75"/>
-      <c r="D204" s="75"/>
-      <c r="E204" s="76"/>
+      <c r="C204" s="73"/>
+      <c r="D204" s="73"/>
+      <c r="E204" s="74"/>
       <c r="F204" s="72">
         <v>0</v>
       </c>
@@ -22512,12 +22542,12 @@
       <c r="A205" s="27">
         <v>45948</v>
       </c>
-      <c r="B205" s="75" t="s">
+      <c r="B205" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C205" s="75"/>
-      <c r="D205" s="75"/>
-      <c r="E205" s="76"/>
+      <c r="C205" s="73"/>
+      <c r="D205" s="73"/>
+      <c r="E205" s="74"/>
       <c r="F205" s="72">
         <v>0</v>
       </c>
@@ -22549,12 +22579,12 @@
       <c r="A206" s="29">
         <v>45949</v>
       </c>
-      <c r="B206" s="73" t="s">
+      <c r="B206" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C206" s="73"/>
-      <c r="D206" s="73"/>
-      <c r="E206" s="74"/>
+      <c r="C206" s="75"/>
+      <c r="D206" s="75"/>
+      <c r="E206" s="76"/>
       <c r="F206" s="71">
         <v>0</v>
       </c>
@@ -22586,12 +22616,12 @@
       <c r="A207" s="27">
         <v>45950</v>
       </c>
-      <c r="B207" s="75" t="s">
+      <c r="B207" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C207" s="75"/>
-      <c r="D207" s="75"/>
-      <c r="E207" s="76"/>
+      <c r="C207" s="73"/>
+      <c r="D207" s="73"/>
+      <c r="E207" s="74"/>
       <c r="F207" s="72">
         <v>0</v>
       </c>
@@ -22666,12 +22696,12 @@
       <c r="A209" s="27">
         <v>45951</v>
       </c>
-      <c r="B209" s="75" t="s">
+      <c r="B209" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C209" s="75"/>
-      <c r="D209" s="75"/>
-      <c r="E209" s="76"/>
+      <c r="C209" s="73"/>
+      <c r="D209" s="73"/>
+      <c r="E209" s="74"/>
       <c r="F209" s="72">
         <v>0</v>
       </c>
@@ -22703,12 +22733,12 @@
       <c r="A210" s="27">
         <v>45952</v>
       </c>
-      <c r="B210" s="75" t="s">
+      <c r="B210" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C210" s="75"/>
-      <c r="D210" s="75"/>
-      <c r="E210" s="76"/>
+      <c r="C210" s="73"/>
+      <c r="D210" s="73"/>
+      <c r="E210" s="74"/>
       <c r="F210" s="72">
         <v>0</v>
       </c>
@@ -22783,12 +22813,12 @@
       <c r="A212" s="27">
         <v>45953</v>
       </c>
-      <c r="B212" s="75" t="s">
+      <c r="B212" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C212" s="75"/>
-      <c r="D212" s="75"/>
-      <c r="E212" s="76"/>
+      <c r="C212" s="73"/>
+      <c r="D212" s="73"/>
+      <c r="E212" s="74"/>
       <c r="F212" s="72">
         <v>0</v>
       </c>
@@ -22863,12 +22893,12 @@
       <c r="A214" s="27">
         <v>45954</v>
       </c>
-      <c r="B214" s="75" t="s">
+      <c r="B214" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C214" s="75"/>
-      <c r="D214" s="75"/>
-      <c r="E214" s="76"/>
+      <c r="C214" s="73"/>
+      <c r="D214" s="73"/>
+      <c r="E214" s="74"/>
       <c r="F214" s="72">
         <v>0</v>
       </c>
@@ -22900,12 +22930,12 @@
       <c r="A215" s="27">
         <v>45955</v>
       </c>
-      <c r="B215" s="75" t="s">
+      <c r="B215" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C215" s="75"/>
-      <c r="D215" s="75"/>
-      <c r="E215" s="76"/>
+      <c r="C215" s="73"/>
+      <c r="D215" s="73"/>
+      <c r="E215" s="74"/>
       <c r="F215" s="72">
         <v>0</v>
       </c>
@@ -22937,12 +22967,12 @@
       <c r="A216" s="29">
         <v>45956</v>
       </c>
-      <c r="B216" s="73" t="s">
+      <c r="B216" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C216" s="73"/>
-      <c r="D216" s="73"/>
-      <c r="E216" s="74"/>
+      <c r="C216" s="75"/>
+      <c r="D216" s="75"/>
+      <c r="E216" s="76"/>
       <c r="F216" s="71">
         <v>0</v>
       </c>
@@ -22974,12 +23004,12 @@
       <c r="A217" s="27">
         <v>45957</v>
       </c>
-      <c r="B217" s="75" t="s">
+      <c r="B217" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C217" s="75"/>
-      <c r="D217" s="75"/>
-      <c r="E217" s="76"/>
+      <c r="C217" s="73"/>
+      <c r="D217" s="73"/>
+      <c r="E217" s="74"/>
       <c r="F217" s="72">
         <v>0</v>
       </c>
@@ -23011,12 +23041,12 @@
       <c r="A218" s="27">
         <v>45958</v>
       </c>
-      <c r="B218" s="75" t="s">
+      <c r="B218" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C218" s="75"/>
-      <c r="D218" s="75"/>
-      <c r="E218" s="76"/>
+      <c r="C218" s="73"/>
+      <c r="D218" s="73"/>
+      <c r="E218" s="74"/>
       <c r="F218" s="72">
         <v>0</v>
       </c>
@@ -23048,12 +23078,12 @@
       <c r="A219" s="27">
         <v>45959</v>
       </c>
-      <c r="B219" s="75" t="s">
+      <c r="B219" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C219" s="75"/>
-      <c r="D219" s="75"/>
-      <c r="E219" s="76"/>
+      <c r="C219" s="73"/>
+      <c r="D219" s="73"/>
+      <c r="E219" s="74"/>
       <c r="F219" s="72">
         <v>0</v>
       </c>
@@ -23085,12 +23115,12 @@
       <c r="A220" s="27">
         <v>45960</v>
       </c>
-      <c r="B220" s="75" t="s">
+      <c r="B220" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C220" s="75"/>
-      <c r="D220" s="75"/>
-      <c r="E220" s="76"/>
+      <c r="C220" s="73"/>
+      <c r="D220" s="73"/>
+      <c r="E220" s="74"/>
       <c r="F220" s="72">
         <v>0</v>
       </c>
@@ -23122,12 +23152,12 @@
       <c r="A221" s="27">
         <v>45961</v>
       </c>
-      <c r="B221" s="75" t="s">
+      <c r="B221" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C221" s="75"/>
-      <c r="D221" s="75"/>
-      <c r="E221" s="76"/>
+      <c r="C221" s="73"/>
+      <c r="D221" s="73"/>
+      <c r="E221" s="74"/>
       <c r="F221" s="72">
         <v>0</v>
       </c>
@@ -23159,12 +23189,12 @@
       <c r="A222" s="27">
         <v>45962</v>
       </c>
-      <c r="B222" s="75" t="s">
+      <c r="B222" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C222" s="75"/>
-      <c r="D222" s="75"/>
-      <c r="E222" s="76"/>
+      <c r="C222" s="73"/>
+      <c r="D222" s="73"/>
+      <c r="E222" s="74"/>
       <c r="F222" s="72">
         <v>0</v>
       </c>
@@ -23196,12 +23226,12 @@
       <c r="A223" s="29">
         <v>45963</v>
       </c>
-      <c r="B223" s="73" t="s">
+      <c r="B223" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C223" s="73"/>
-      <c r="D223" s="73"/>
-      <c r="E223" s="74"/>
+      <c r="C223" s="75"/>
+      <c r="D223" s="75"/>
+      <c r="E223" s="76"/>
       <c r="F223" s="71">
         <v>0</v>
       </c>
@@ -23233,12 +23263,12 @@
       <c r="A224" s="27">
         <v>45964</v>
       </c>
-      <c r="B224" s="75" t="s">
+      <c r="B224" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C224" s="75"/>
-      <c r="D224" s="75"/>
-      <c r="E224" s="76"/>
+      <c r="C224" s="73"/>
+      <c r="D224" s="73"/>
+      <c r="E224" s="74"/>
       <c r="F224" s="72">
         <v>0</v>
       </c>
@@ -23270,12 +23300,12 @@
       <c r="A225" s="27">
         <v>45965</v>
       </c>
-      <c r="B225" s="75" t="s">
+      <c r="B225" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C225" s="75"/>
-      <c r="D225" s="75"/>
-      <c r="E225" s="76"/>
+      <c r="C225" s="73"/>
+      <c r="D225" s="73"/>
+      <c r="E225" s="74"/>
       <c r="F225" s="72">
         <v>0</v>
       </c>
@@ -23307,12 +23337,12 @@
       <c r="A226" s="27">
         <v>45966</v>
       </c>
-      <c r="B226" s="75" t="s">
+      <c r="B226" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C226" s="75"/>
-      <c r="D226" s="75"/>
-      <c r="E226" s="76"/>
+      <c r="C226" s="73"/>
+      <c r="D226" s="73"/>
+      <c r="E226" s="74"/>
       <c r="F226" s="72">
         <v>0</v>
       </c>
@@ -23344,12 +23374,12 @@
       <c r="A227" s="27">
         <v>45967</v>
       </c>
-      <c r="B227" s="75" t="s">
+      <c r="B227" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C227" s="75"/>
-      <c r="D227" s="75"/>
-      <c r="E227" s="76"/>
+      <c r="C227" s="73"/>
+      <c r="D227" s="73"/>
+      <c r="E227" s="74"/>
       <c r="F227" s="72">
         <v>0</v>
       </c>
@@ -23381,12 +23411,12 @@
       <c r="A228" s="27">
         <v>45968</v>
       </c>
-      <c r="B228" s="75" t="s">
+      <c r="B228" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C228" s="75"/>
-      <c r="D228" s="75"/>
-      <c r="E228" s="76"/>
+      <c r="C228" s="73"/>
+      <c r="D228" s="73"/>
+      <c r="E228" s="74"/>
       <c r="F228" s="72">
         <v>0</v>
       </c>
@@ -23418,12 +23448,12 @@
       <c r="A229" s="27">
         <v>45968</v>
       </c>
-      <c r="B229" s="75" t="s">
+      <c r="B229" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C229" s="75"/>
-      <c r="D229" s="75"/>
-      <c r="E229" s="76"/>
+      <c r="C229" s="73"/>
+      <c r="D229" s="73"/>
+      <c r="E229" s="74"/>
       <c r="F229" s="72">
         <v>0</v>
       </c>
@@ -23455,12 +23485,12 @@
       <c r="A230" s="27">
         <v>45969</v>
       </c>
-      <c r="B230" s="75" t="s">
+      <c r="B230" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C230" s="75"/>
-      <c r="D230" s="75"/>
-      <c r="E230" s="76"/>
+      <c r="C230" s="73"/>
+      <c r="D230" s="73"/>
+      <c r="E230" s="74"/>
       <c r="F230" s="72">
         <v>0</v>
       </c>
@@ -23492,12 +23522,12 @@
       <c r="A231" s="27">
         <v>45970</v>
       </c>
-      <c r="B231" s="75" t="s">
+      <c r="B231" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C231" s="75"/>
-      <c r="D231" s="75"/>
-      <c r="E231" s="76"/>
+      <c r="C231" s="73"/>
+      <c r="D231" s="73"/>
+      <c r="E231" s="74"/>
       <c r="F231" s="72">
         <v>0</v>
       </c>
@@ -23529,12 +23559,12 @@
       <c r="A232" s="27">
         <v>45970</v>
       </c>
-      <c r="B232" s="75" t="s">
+      <c r="B232" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C232" s="75"/>
-      <c r="D232" s="75"/>
-      <c r="E232" s="76"/>
+      <c r="C232" s="73"/>
+      <c r="D232" s="73"/>
+      <c r="E232" s="74"/>
       <c r="F232" s="72">
         <v>0</v>
       </c>
@@ -23566,12 +23596,12 @@
       <c r="A233" s="27">
         <v>45971</v>
       </c>
-      <c r="B233" s="75" t="s">
+      <c r="B233" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C233" s="75"/>
-      <c r="D233" s="75"/>
-      <c r="E233" s="76"/>
+      <c r="C233" s="73"/>
+      <c r="D233" s="73"/>
+      <c r="E233" s="74"/>
       <c r="F233" s="4">
         <v>7457</v>
       </c>
@@ -23603,12 +23633,12 @@
       <c r="A234" s="27">
         <v>45971</v>
       </c>
-      <c r="B234" s="75" t="s">
+      <c r="B234" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C234" s="75"/>
-      <c r="D234" s="75"/>
-      <c r="E234" s="76"/>
+      <c r="C234" s="73"/>
+      <c r="D234" s="73"/>
+      <c r="E234" s="74"/>
       <c r="F234" s="72">
         <v>0</v>
       </c>
@@ -23640,12 +23670,12 @@
       <c r="A235" s="27">
         <v>45972</v>
       </c>
-      <c r="B235" s="75" t="s">
+      <c r="B235" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C235" s="75"/>
-      <c r="D235" s="75"/>
-      <c r="E235" s="76"/>
+      <c r="C235" s="73"/>
+      <c r="D235" s="73"/>
+      <c r="E235" s="74"/>
       <c r="F235" s="72">
         <v>0</v>
       </c>
@@ -23677,12 +23707,12 @@
       <c r="A236" s="27">
         <v>45973</v>
       </c>
-      <c r="B236" s="75" t="s">
+      <c r="B236" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C236" s="75"/>
-      <c r="D236" s="75"/>
-      <c r="E236" s="76"/>
+      <c r="C236" s="73"/>
+      <c r="D236" s="73"/>
+      <c r="E236" s="74"/>
       <c r="F236" s="72">
         <v>0</v>
       </c>
@@ -23714,12 +23744,12 @@
       <c r="A237" s="27">
         <v>45974</v>
       </c>
-      <c r="B237" s="75" t="s">
+      <c r="B237" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C237" s="75"/>
-      <c r="D237" s="75"/>
-      <c r="E237" s="76"/>
+      <c r="C237" s="73"/>
+      <c r="D237" s="73"/>
+      <c r="E237" s="74"/>
       <c r="F237" s="72">
         <v>0</v>
       </c>
@@ -23751,12 +23781,12 @@
       <c r="A238" s="27">
         <v>45975</v>
       </c>
-      <c r="B238" s="75" t="s">
+      <c r="B238" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C238" s="75"/>
-      <c r="D238" s="75"/>
-      <c r="E238" s="76"/>
+      <c r="C238" s="73"/>
+      <c r="D238" s="73"/>
+      <c r="E238" s="74"/>
       <c r="F238" s="72">
         <v>0</v>
       </c>
@@ -23788,12 +23818,12 @@
       <c r="A239" s="27">
         <v>45976</v>
       </c>
-      <c r="B239" s="75" t="s">
+      <c r="B239" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C239" s="75"/>
-      <c r="D239" s="75"/>
-      <c r="E239" s="76"/>
+      <c r="C239" s="73"/>
+      <c r="D239" s="73"/>
+      <c r="E239" s="74"/>
       <c r="F239" s="72">
         <v>0</v>
       </c>
@@ -23825,12 +23855,12 @@
       <c r="A240" s="29">
         <v>45977</v>
       </c>
-      <c r="B240" s="73" t="s">
+      <c r="B240" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C240" s="73"/>
-      <c r="D240" s="73"/>
-      <c r="E240" s="74"/>
+      <c r="C240" s="75"/>
+      <c r="D240" s="75"/>
+      <c r="E240" s="76"/>
       <c r="F240" s="71">
         <v>0</v>
       </c>
@@ -23862,12 +23892,12 @@
       <c r="A241" s="27">
         <v>45978</v>
       </c>
-      <c r="B241" s="75" t="s">
+      <c r="B241" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C241" s="75"/>
-      <c r="D241" s="75"/>
-      <c r="E241" s="76"/>
+      <c r="C241" s="73"/>
+      <c r="D241" s="73"/>
+      <c r="E241" s="74"/>
       <c r="F241" s="72">
         <v>0</v>
       </c>
@@ -23899,12 +23929,12 @@
       <c r="A242" s="27">
         <v>45979</v>
       </c>
-      <c r="B242" s="75" t="s">
+      <c r="B242" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C242" s="75"/>
-      <c r="D242" s="75"/>
-      <c r="E242" s="76"/>
+      <c r="C242" s="73"/>
+      <c r="D242" s="73"/>
+      <c r="E242" s="74"/>
       <c r="F242" s="72">
         <v>0</v>
       </c>
@@ -24022,12 +24052,12 @@
       <c r="A245" s="27">
         <v>45980</v>
       </c>
-      <c r="B245" s="75" t="s">
+      <c r="B245" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C245" s="75"/>
-      <c r="D245" s="75"/>
-      <c r="E245" s="76"/>
+      <c r="C245" s="73"/>
+      <c r="D245" s="73"/>
+      <c r="E245" s="74"/>
       <c r="F245" s="72">
         <v>0</v>
       </c>
@@ -24102,12 +24132,12 @@
       <c r="A247" s="27">
         <v>45981</v>
       </c>
-      <c r="B247" s="75" t="s">
+      <c r="B247" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C247" s="75"/>
-      <c r="D247" s="75"/>
-      <c r="E247" s="76"/>
+      <c r="C247" s="73"/>
+      <c r="D247" s="73"/>
+      <c r="E247" s="74"/>
       <c r="F247" s="72">
         <v>0</v>
       </c>
@@ -24139,12 +24169,12 @@
       <c r="A248" s="27">
         <v>45982</v>
       </c>
-      <c r="B248" s="75" t="s">
+      <c r="B248" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C248" s="75"/>
-      <c r="D248" s="75"/>
-      <c r="E248" s="76"/>
+      <c r="C248" s="73"/>
+      <c r="D248" s="73"/>
+      <c r="E248" s="74"/>
       <c r="F248" s="72">
         <v>0</v>
       </c>
@@ -24219,12 +24249,12 @@
       <c r="A250" s="27">
         <v>45983</v>
       </c>
-      <c r="B250" s="75" t="s">
+      <c r="B250" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C250" s="75"/>
-      <c r="D250" s="75"/>
-      <c r="E250" s="76"/>
+      <c r="C250" s="73"/>
+      <c r="D250" s="73"/>
+      <c r="E250" s="74"/>
       <c r="F250" s="72">
         <v>0</v>
       </c>
@@ -24256,12 +24286,12 @@
       <c r="A251" s="27">
         <v>45984</v>
       </c>
-      <c r="B251" s="75" t="s">
+      <c r="B251" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C251" s="75"/>
-      <c r="D251" s="75"/>
-      <c r="E251" s="76"/>
+      <c r="C251" s="73"/>
+      <c r="D251" s="73"/>
+      <c r="E251" s="74"/>
       <c r="F251" s="72">
         <v>0</v>
       </c>
@@ -24336,12 +24366,12 @@
       <c r="A253" s="27">
         <v>45985</v>
       </c>
-      <c r="B253" s="75" t="s">
+      <c r="B253" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C253" s="75"/>
-      <c r="D253" s="75"/>
-      <c r="E253" s="76"/>
+      <c r="C253" s="73"/>
+      <c r="D253" s="73"/>
+      <c r="E253" s="74"/>
       <c r="F253" s="72">
         <v>0</v>
       </c>
@@ -24416,12 +24446,12 @@
       <c r="A255" s="27">
         <v>45986</v>
       </c>
-      <c r="B255" s="75" t="s">
+      <c r="B255" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C255" s="75"/>
-      <c r="D255" s="75"/>
-      <c r="E255" s="76"/>
+      <c r="C255" s="73"/>
+      <c r="D255" s="73"/>
+      <c r="E255" s="74"/>
       <c r="F255" s="72">
         <v>0</v>
       </c>
@@ -24496,12 +24526,12 @@
       <c r="A257" s="27">
         <v>45987</v>
       </c>
-      <c r="B257" s="75" t="s">
+      <c r="B257" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C257" s="75"/>
-      <c r="D257" s="75"/>
-      <c r="E257" s="76"/>
+      <c r="C257" s="73"/>
+      <c r="D257" s="73"/>
+      <c r="E257" s="74"/>
       <c r="F257" s="72">
         <v>0</v>
       </c>
@@ -24576,12 +24606,12 @@
       <c r="A259" s="27">
         <v>45988</v>
       </c>
-      <c r="B259" s="75" t="s">
+      <c r="B259" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C259" s="75"/>
-      <c r="D259" s="75"/>
-      <c r="E259" s="76"/>
+      <c r="C259" s="73"/>
+      <c r="D259" s="73"/>
+      <c r="E259" s="74"/>
       <c r="F259" s="72">
         <v>0</v>
       </c>
@@ -24613,12 +24643,12 @@
       <c r="A260" s="27">
         <v>45989</v>
       </c>
-      <c r="B260" s="75" t="s">
+      <c r="B260" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C260" s="75"/>
-      <c r="D260" s="75"/>
-      <c r="E260" s="76"/>
+      <c r="C260" s="73"/>
+      <c r="D260" s="73"/>
+      <c r="E260" s="74"/>
       <c r="F260" s="72">
         <v>0</v>
       </c>
@@ -24650,12 +24680,12 @@
       <c r="A261" s="29">
         <v>45990</v>
       </c>
-      <c r="B261" s="73" t="s">
+      <c r="B261" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C261" s="73"/>
-      <c r="D261" s="73"/>
-      <c r="E261" s="74"/>
+      <c r="C261" s="75"/>
+      <c r="D261" s="75"/>
+      <c r="E261" s="76"/>
       <c r="F261" s="71">
         <v>0</v>
       </c>
@@ -24687,12 +24717,12 @@
       <c r="A262" s="27">
         <v>45991</v>
       </c>
-      <c r="B262" s="75" t="s">
+      <c r="B262" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C262" s="75"/>
-      <c r="D262" s="75"/>
-      <c r="E262" s="76"/>
+      <c r="C262" s="73"/>
+      <c r="D262" s="73"/>
+      <c r="E262" s="74"/>
       <c r="F262" s="72">
         <v>0</v>
       </c>
@@ -24767,12 +24797,12 @@
       <c r="A264" s="27">
         <v>45992</v>
       </c>
-      <c r="B264" s="75" t="s">
+      <c r="B264" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C264" s="75"/>
-      <c r="D264" s="75"/>
-      <c r="E264" s="76"/>
+      <c r="C264" s="73"/>
+      <c r="D264" s="73"/>
+      <c r="E264" s="74"/>
       <c r="F264" s="72">
         <v>0</v>
       </c>
@@ -24847,12 +24877,12 @@
       <c r="A266" s="27">
         <v>45993</v>
       </c>
-      <c r="B266" s="75" t="s">
+      <c r="B266" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C266" s="75"/>
-      <c r="D266" s="75"/>
-      <c r="E266" s="76"/>
+      <c r="C266" s="73"/>
+      <c r="D266" s="73"/>
+      <c r="E266" s="74"/>
       <c r="F266" s="72">
         <v>0</v>
       </c>
@@ -25271,12 +25301,12 @@
       <c r="A276" s="27">
         <v>45994</v>
       </c>
-      <c r="B276" s="75" t="s">
+      <c r="B276" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C276" s="75"/>
-      <c r="D276" s="75"/>
-      <c r="E276" s="76"/>
+      <c r="C276" s="73"/>
+      <c r="D276" s="73"/>
+      <c r="E276" s="74"/>
       <c r="F276" s="72">
         <v>0</v>
       </c>
@@ -25308,12 +25338,12 @@
       <c r="A277" s="27">
         <v>45995</v>
       </c>
-      <c r="B277" s="75" t="s">
+      <c r="B277" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C277" s="75"/>
-      <c r="D277" s="75"/>
-      <c r="E277" s="76"/>
+      <c r="C277" s="73"/>
+      <c r="D277" s="73"/>
+      <c r="E277" s="74"/>
       <c r="F277" s="72">
         <v>0</v>
       </c>
@@ -25345,12 +25375,12 @@
       <c r="A278" s="27">
         <v>45996</v>
       </c>
-      <c r="B278" s="75" t="s">
+      <c r="B278" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C278" s="75"/>
-      <c r="D278" s="75"/>
-      <c r="E278" s="76"/>
+      <c r="C278" s="73"/>
+      <c r="D278" s="73"/>
+      <c r="E278" s="74"/>
       <c r="F278" s="72">
         <v>0</v>
       </c>
@@ -25382,12 +25412,12 @@
       <c r="A279" s="29">
         <v>45997</v>
       </c>
-      <c r="B279" s="73" t="s">
+      <c r="B279" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C279" s="73"/>
-      <c r="D279" s="73"/>
-      <c r="E279" s="74"/>
+      <c r="C279" s="75"/>
+      <c r="D279" s="75"/>
+      <c r="E279" s="76"/>
       <c r="F279" s="71">
         <v>0</v>
       </c>
@@ -25419,12 +25449,12 @@
       <c r="A280" s="27">
         <v>45998</v>
       </c>
-      <c r="B280" s="75" t="s">
+      <c r="B280" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C280" s="75"/>
-      <c r="D280" s="75"/>
-      <c r="E280" s="76"/>
+      <c r="C280" s="73"/>
+      <c r="D280" s="73"/>
+      <c r="E280" s="74"/>
       <c r="F280" s="72">
         <v>0</v>
       </c>
@@ -25456,12 +25486,12 @@
       <c r="A281" s="27">
         <v>45999</v>
       </c>
-      <c r="B281" s="75" t="s">
+      <c r="B281" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C281" s="75"/>
-      <c r="D281" s="75"/>
-      <c r="E281" s="76"/>
+      <c r="C281" s="73"/>
+      <c r="D281" s="73"/>
+      <c r="E281" s="74"/>
       <c r="F281" s="72">
         <v>0</v>
       </c>
@@ -25493,12 +25523,12 @@
       <c r="A282" s="27">
         <v>46000</v>
       </c>
-      <c r="B282" s="75" t="s">
+      <c r="B282" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C282" s="75"/>
-      <c r="D282" s="75"/>
-      <c r="E282" s="76"/>
+      <c r="C282" s="73"/>
+      <c r="D282" s="73"/>
+      <c r="E282" s="74"/>
       <c r="F282" s="72">
         <v>0</v>
       </c>
@@ -25530,12 +25560,12 @@
       <c r="A283" s="27">
         <v>46001</v>
       </c>
-      <c r="B283" s="75" t="s">
+      <c r="B283" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C283" s="75"/>
-      <c r="D283" s="75"/>
-      <c r="E283" s="76"/>
+      <c r="C283" s="73"/>
+      <c r="D283" s="73"/>
+      <c r="E283" s="74"/>
       <c r="F283" s="4">
         <v>3093</v>
       </c>
@@ -25567,12 +25597,12 @@
       <c r="A284" s="27">
         <v>46001</v>
       </c>
-      <c r="B284" s="75" t="s">
+      <c r="B284" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C284" s="75"/>
-      <c r="D284" s="75"/>
-      <c r="E284" s="76"/>
+      <c r="C284" s="73"/>
+      <c r="D284" s="73"/>
+      <c r="E284" s="74"/>
       <c r="F284" s="72">
         <v>27</v>
       </c>
@@ -25604,12 +25634,12 @@
       <c r="A285" s="27">
         <v>46001</v>
       </c>
-      <c r="B285" s="75" t="s">
+      <c r="B285" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C285" s="75"/>
-      <c r="D285" s="75"/>
-      <c r="E285" s="76"/>
+      <c r="C285" s="73"/>
+      <c r="D285" s="73"/>
+      <c r="E285" s="74"/>
       <c r="F285" s="72">
         <v>0</v>
       </c>
@@ -25641,12 +25671,12 @@
       <c r="A286" s="27">
         <v>46001</v>
       </c>
-      <c r="B286" s="75" t="s">
+      <c r="B286" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C286" s="75"/>
-      <c r="D286" s="75"/>
-      <c r="E286" s="76"/>
+      <c r="C286" s="73"/>
+      <c r="D286" s="73"/>
+      <c r="E286" s="74"/>
       <c r="F286" s="72">
         <v>0</v>
       </c>
@@ -25678,12 +25708,12 @@
       <c r="A287" s="27">
         <v>46002</v>
       </c>
-      <c r="B287" s="75" t="s">
+      <c r="B287" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C287" s="75"/>
-      <c r="D287" s="75"/>
-      <c r="E287" s="76"/>
+      <c r="C287" s="73"/>
+      <c r="D287" s="73"/>
+      <c r="E287" s="74"/>
       <c r="F287" s="72">
         <v>0</v>
       </c>
@@ -25715,12 +25745,12 @@
       <c r="A288" s="27">
         <v>46003</v>
       </c>
-      <c r="B288" s="75" t="s">
+      <c r="B288" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C288" s="75"/>
-      <c r="D288" s="75"/>
-      <c r="E288" s="76"/>
+      <c r="C288" s="73"/>
+      <c r="D288" s="73"/>
+      <c r="E288" s="74"/>
       <c r="F288" s="72">
         <v>0</v>
       </c>
@@ -25752,12 +25782,12 @@
       <c r="A289" s="27">
         <v>46003</v>
       </c>
-      <c r="B289" s="75" t="s">
+      <c r="B289" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C289" s="75"/>
-      <c r="D289" s="75"/>
-      <c r="E289" s="76"/>
+      <c r="C289" s="73"/>
+      <c r="D289" s="73"/>
+      <c r="E289" s="74"/>
       <c r="F289" s="72">
         <v>0</v>
       </c>
@@ -25789,12 +25819,12 @@
       <c r="A290" s="27">
         <v>46004</v>
       </c>
-      <c r="B290" s="75" t="s">
+      <c r="B290" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C290" s="75"/>
-      <c r="D290" s="75"/>
-      <c r="E290" s="76"/>
+      <c r="C290" s="73"/>
+      <c r="D290" s="73"/>
+      <c r="E290" s="74"/>
       <c r="F290" s="72">
         <v>0</v>
       </c>
@@ -25826,12 +25856,12 @@
       <c r="A291" s="27">
         <v>46004</v>
       </c>
-      <c r="B291" s="75" t="s">
+      <c r="B291" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C291" s="75"/>
-      <c r="D291" s="75"/>
-      <c r="E291" s="76"/>
+      <c r="C291" s="73"/>
+      <c r="D291" s="73"/>
+      <c r="E291" s="74"/>
       <c r="F291" s="72">
         <v>0</v>
       </c>
@@ -25863,12 +25893,12 @@
       <c r="A292" s="27">
         <v>46005</v>
       </c>
-      <c r="B292" s="75" t="s">
+      <c r="B292" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C292" s="75"/>
-      <c r="D292" s="75"/>
-      <c r="E292" s="76"/>
+      <c r="C292" s="73"/>
+      <c r="D292" s="73"/>
+      <c r="E292" s="74"/>
       <c r="F292" s="72">
         <v>0</v>
       </c>
@@ -25900,12 +25930,12 @@
       <c r="A293" s="27">
         <v>46005</v>
       </c>
-      <c r="B293" s="75" t="s">
+      <c r="B293" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C293" s="75"/>
-      <c r="D293" s="75"/>
-      <c r="E293" s="76"/>
+      <c r="C293" s="73"/>
+      <c r="D293" s="73"/>
+      <c r="E293" s="74"/>
       <c r="F293" s="72">
         <v>0</v>
       </c>
@@ -25937,12 +25967,12 @@
       <c r="A294" s="27">
         <v>46006</v>
       </c>
-      <c r="B294" s="75" t="s">
+      <c r="B294" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C294" s="75"/>
-      <c r="D294" s="75"/>
-      <c r="E294" s="76"/>
+      <c r="C294" s="73"/>
+      <c r="D294" s="73"/>
+      <c r="E294" s="74"/>
       <c r="F294" s="72">
         <v>0</v>
       </c>
@@ -25974,12 +26004,12 @@
       <c r="A295" s="27">
         <v>46007</v>
       </c>
-      <c r="B295" s="75" t="s">
+      <c r="B295" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="C295" s="75"/>
-      <c r="D295" s="75"/>
-      <c r="E295" s="76"/>
+      <c r="C295" s="73"/>
+      <c r="D295" s="73"/>
+      <c r="E295" s="74"/>
       <c r="F295" s="72">
         <v>0</v>
       </c>
@@ -26011,12 +26041,12 @@
       <c r="A296" s="27">
         <v>46007</v>
       </c>
-      <c r="B296" s="75" t="s">
+      <c r="B296" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C296" s="75"/>
-      <c r="D296" s="75"/>
-      <c r="E296" s="76"/>
+      <c r="C296" s="73"/>
+      <c r="D296" s="73"/>
+      <c r="E296" s="74"/>
       <c r="F296" s="72">
         <v>0</v>
       </c>
@@ -26048,12 +26078,12 @@
       <c r="A297" s="27">
         <v>46008</v>
       </c>
-      <c r="B297" s="75" t="s">
+      <c r="B297" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C297" s="75"/>
-      <c r="D297" s="75"/>
-      <c r="E297" s="76"/>
+      <c r="C297" s="73"/>
+      <c r="D297" s="73"/>
+      <c r="E297" s="74"/>
       <c r="F297" s="72">
         <v>0</v>
       </c>
@@ -26128,12 +26158,12 @@
       <c r="A299" s="27">
         <v>46009</v>
       </c>
-      <c r="B299" s="75" t="s">
+      <c r="B299" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="C299" s="75"/>
-      <c r="D299" s="75"/>
-      <c r="E299" s="76"/>
+      <c r="C299" s="73"/>
+      <c r="D299" s="73"/>
+      <c r="E299" s="74"/>
       <c r="F299" s="72">
         <v>0</v>
       </c>
@@ -26165,12 +26195,12 @@
       <c r="A300" s="27">
         <v>46009</v>
       </c>
-      <c r="B300" s="75" t="s">
+      <c r="B300" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C300" s="75"/>
-      <c r="D300" s="75"/>
-      <c r="E300" s="76"/>
+      <c r="C300" s="73"/>
+      <c r="D300" s="73"/>
+      <c r="E300" s="74"/>
       <c r="F300" s="72">
         <v>0</v>
       </c>
@@ -26202,12 +26232,12 @@
       <c r="A301" s="27">
         <v>46010</v>
       </c>
-      <c r="B301" s="75" t="s">
+      <c r="B301" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C301" s="75"/>
-      <c r="D301" s="75"/>
-      <c r="E301" s="76"/>
+      <c r="C301" s="73"/>
+      <c r="D301" s="73"/>
+      <c r="E301" s="74"/>
       <c r="F301" s="72">
         <v>0</v>
       </c>
@@ -26239,12 +26269,12 @@
       <c r="A302" s="29">
         <v>46011</v>
       </c>
-      <c r="B302" s="73" t="s">
+      <c r="B302" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C302" s="73"/>
-      <c r="D302" s="73"/>
-      <c r="E302" s="74"/>
+      <c r="C302" s="75"/>
+      <c r="D302" s="75"/>
+      <c r="E302" s="76"/>
       <c r="F302" s="71">
         <v>0</v>
       </c>
@@ -26276,12 +26306,12 @@
       <c r="A303" s="27">
         <v>46011</v>
       </c>
-      <c r="B303" s="75" t="s">
+      <c r="B303" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C303" s="75"/>
-      <c r="D303" s="75"/>
-      <c r="E303" s="76"/>
+      <c r="C303" s="73"/>
+      <c r="D303" s="73"/>
+      <c r="E303" s="74"/>
       <c r="F303" s="72">
         <v>0</v>
       </c>
@@ -26313,12 +26343,12 @@
       <c r="A304" s="27">
         <v>46011</v>
       </c>
-      <c r="B304" s="75" t="s">
+      <c r="B304" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C304" s="75"/>
-      <c r="D304" s="75"/>
-      <c r="E304" s="76"/>
+      <c r="C304" s="73"/>
+      <c r="D304" s="73"/>
+      <c r="E304" s="74"/>
       <c r="F304" s="72">
         <v>0</v>
       </c>
@@ -26393,12 +26423,12 @@
       <c r="A306" s="27">
         <v>46012</v>
       </c>
-      <c r="B306" s="75" t="s">
+      <c r="B306" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C306" s="75"/>
-      <c r="D306" s="75"/>
-      <c r="E306" s="76"/>
+      <c r="C306" s="73"/>
+      <c r="D306" s="73"/>
+      <c r="E306" s="74"/>
       <c r="F306" s="72">
         <v>0</v>
       </c>
@@ -26430,12 +26460,12 @@
       <c r="A307" s="27">
         <v>46012</v>
       </c>
-      <c r="B307" s="75" t="s">
+      <c r="B307" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="C307" s="75"/>
-      <c r="D307" s="75"/>
-      <c r="E307" s="76"/>
+      <c r="C307" s="73"/>
+      <c r="D307" s="73"/>
+      <c r="E307" s="74"/>
       <c r="F307" s="72">
         <v>0</v>
       </c>
@@ -26467,12 +26497,12 @@
       <c r="A308" s="27">
         <v>46012</v>
       </c>
-      <c r="B308" s="75" t="s">
+      <c r="B308" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C308" s="75"/>
-      <c r="D308" s="75"/>
-      <c r="E308" s="76"/>
+      <c r="C308" s="73"/>
+      <c r="D308" s="73"/>
+      <c r="E308" s="74"/>
       <c r="F308" s="72">
         <v>0</v>
       </c>
@@ -26504,12 +26534,12 @@
       <c r="A309" s="27">
         <v>46013</v>
       </c>
-      <c r="B309" s="75" t="s">
+      <c r="B309" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C309" s="75"/>
-      <c r="D309" s="75"/>
-      <c r="E309" s="76"/>
+      <c r="C309" s="73"/>
+      <c r="D309" s="73"/>
+      <c r="E309" s="74"/>
       <c r="F309" s="72">
         <v>0</v>
       </c>
@@ -26584,12 +26614,12 @@
       <c r="A311" s="27">
         <v>46014</v>
       </c>
-      <c r="B311" s="75" t="s">
+      <c r="B311" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C311" s="75"/>
-      <c r="D311" s="75"/>
-      <c r="E311" s="76"/>
+      <c r="C311" s="73"/>
+      <c r="D311" s="73"/>
+      <c r="E311" s="74"/>
       <c r="F311" s="72">
         <v>0</v>
       </c>
@@ -26621,12 +26651,12 @@
       <c r="A312" s="27">
         <v>46015</v>
       </c>
-      <c r="B312" s="75" t="s">
+      <c r="B312" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C312" s="75"/>
-      <c r="D312" s="75"/>
-      <c r="E312" s="76"/>
+      <c r="C312" s="73"/>
+      <c r="D312" s="73"/>
+      <c r="E312" s="74"/>
       <c r="F312" s="72">
         <v>0</v>
       </c>
@@ -26658,12 +26688,12 @@
       <c r="A313" s="27">
         <v>46016</v>
       </c>
-      <c r="B313" s="75" t="s">
+      <c r="B313" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C313" s="75"/>
-      <c r="D313" s="75"/>
-      <c r="E313" s="76"/>
+      <c r="C313" s="73"/>
+      <c r="D313" s="73"/>
+      <c r="E313" s="74"/>
       <c r="F313" s="72">
         <v>0</v>
       </c>
@@ -26695,12 +26725,12 @@
       <c r="A314" s="27">
         <v>46017</v>
       </c>
-      <c r="B314" s="75" t="s">
+      <c r="B314" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C314" s="75"/>
-      <c r="D314" s="75"/>
-      <c r="E314" s="76"/>
+      <c r="C314" s="73"/>
+      <c r="D314" s="73"/>
+      <c r="E314" s="74"/>
       <c r="F314" s="72">
         <v>0</v>
       </c>
@@ -26732,12 +26762,12 @@
       <c r="A315" s="27">
         <v>46018</v>
       </c>
-      <c r="B315" s="75" t="s">
+      <c r="B315" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C315" s="75"/>
-      <c r="D315" s="75"/>
-      <c r="E315" s="76"/>
+      <c r="C315" s="73"/>
+      <c r="D315" s="73"/>
+      <c r="E315" s="74"/>
       <c r="F315" s="72">
         <v>0</v>
       </c>
@@ -26769,12 +26799,12 @@
       <c r="A316" s="27">
         <v>46019</v>
       </c>
-      <c r="B316" s="75" t="s">
+      <c r="B316" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C316" s="75"/>
-      <c r="D316" s="75"/>
-      <c r="E316" s="76"/>
+      <c r="C316" s="73"/>
+      <c r="D316" s="73"/>
+      <c r="E316" s="74"/>
       <c r="F316" s="72">
         <v>0</v>
       </c>
@@ -26806,12 +26836,12 @@
       <c r="A317" s="27">
         <v>46020</v>
       </c>
-      <c r="B317" s="75" t="s">
+      <c r="B317" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C317" s="75"/>
-      <c r="D317" s="75"/>
-      <c r="E317" s="76"/>
+      <c r="C317" s="73"/>
+      <c r="D317" s="73"/>
+      <c r="E317" s="74"/>
       <c r="F317" s="72">
         <v>0</v>
       </c>
@@ -26843,12 +26873,12 @@
       <c r="A318" s="27">
         <v>46021</v>
       </c>
-      <c r="B318" s="75" t="s">
+      <c r="B318" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C318" s="75"/>
-      <c r="D318" s="75"/>
-      <c r="E318" s="76"/>
+      <c r="C318" s="73"/>
+      <c r="D318" s="73"/>
+      <c r="E318" s="74"/>
       <c r="F318" s="72">
         <v>0</v>
       </c>
@@ -26880,12 +26910,12 @@
       <c r="A319" s="29">
         <v>46022</v>
       </c>
-      <c r="B319" s="73" t="s">
+      <c r="B319" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C319" s="73"/>
-      <c r="D319" s="73"/>
-      <c r="E319" s="74"/>
+      <c r="C319" s="75"/>
+      <c r="D319" s="75"/>
+      <c r="E319" s="76"/>
       <c r="F319" s="71">
         <v>0</v>
       </c>
@@ -26917,12 +26947,12 @@
       <c r="A320" s="27">
         <v>46023</v>
       </c>
-      <c r="B320" s="75" t="s">
+      <c r="B320" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C320" s="75"/>
-      <c r="D320" s="75"/>
-      <c r="E320" s="76"/>
+      <c r="C320" s="73"/>
+      <c r="D320" s="73"/>
+      <c r="E320" s="74"/>
       <c r="F320" s="72">
         <v>0</v>
       </c>
@@ -26954,12 +26984,12 @@
       <c r="A321" s="27">
         <v>46024</v>
       </c>
-      <c r="B321" s="75" t="s">
+      <c r="B321" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C321" s="75"/>
-      <c r="D321" s="75"/>
-      <c r="E321" s="76"/>
+      <c r="C321" s="73"/>
+      <c r="D321" s="73"/>
+      <c r="E321" s="74"/>
       <c r="F321" s="72">
         <v>0</v>
       </c>
@@ -26991,12 +27021,12 @@
       <c r="A322" s="27">
         <v>46025</v>
       </c>
-      <c r="B322" s="75" t="s">
+      <c r="B322" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C322" s="75"/>
-      <c r="D322" s="75"/>
-      <c r="E322" s="76"/>
+      <c r="C322" s="73"/>
+      <c r="D322" s="73"/>
+      <c r="E322" s="74"/>
       <c r="F322" s="72">
         <v>0</v>
       </c>
@@ -27028,12 +27058,12 @@
       <c r="A323" s="27">
         <v>46026</v>
       </c>
-      <c r="B323" s="75" t="s">
+      <c r="B323" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C323" s="75"/>
-      <c r="D323" s="75"/>
-      <c r="E323" s="76"/>
+      <c r="C323" s="73"/>
+      <c r="D323" s="73"/>
+      <c r="E323" s="74"/>
       <c r="F323" s="72">
         <v>0</v>
       </c>
@@ -27065,12 +27095,12 @@
       <c r="A324" s="27">
         <v>46027</v>
       </c>
-      <c r="B324" s="75" t="s">
+      <c r="B324" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C324" s="75"/>
-      <c r="D324" s="75"/>
-      <c r="E324" s="76"/>
+      <c r="C324" s="73"/>
+      <c r="D324" s="73"/>
+      <c r="E324" s="74"/>
       <c r="F324" s="72">
         <v>0</v>
       </c>
@@ -27102,12 +27132,12 @@
       <c r="A325" s="27">
         <v>46027</v>
       </c>
-      <c r="B325" s="75" t="s">
+      <c r="B325" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C325" s="75"/>
-      <c r="D325" s="75"/>
-      <c r="E325" s="76"/>
+      <c r="C325" s="73"/>
+      <c r="D325" s="73"/>
+      <c r="E325" s="74"/>
       <c r="F325" s="72">
         <v>0</v>
       </c>
@@ -27182,12 +27212,12 @@
       <c r="A327" s="27">
         <v>46028</v>
       </c>
-      <c r="B327" s="75" t="s">
+      <c r="B327" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C327" s="75"/>
-      <c r="D327" s="75"/>
-      <c r="E327" s="76"/>
+      <c r="C327" s="73"/>
+      <c r="D327" s="73"/>
+      <c r="E327" s="74"/>
       <c r="F327" s="72">
         <v>0</v>
       </c>
@@ -27219,12 +27249,12 @@
       <c r="A328" s="27">
         <v>46028</v>
       </c>
-      <c r="B328" s="75" t="s">
+      <c r="B328" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="C328" s="75"/>
-      <c r="D328" s="75"/>
-      <c r="E328" s="76"/>
+      <c r="C328" s="73"/>
+      <c r="D328" s="73"/>
+      <c r="E328" s="74"/>
       <c r="F328" s="72">
         <v>0</v>
       </c>
@@ -27256,12 +27286,12 @@
       <c r="A329" s="27">
         <v>46029</v>
       </c>
-      <c r="B329" s="75" t="s">
+      <c r="B329" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C329" s="75"/>
-      <c r="D329" s="75"/>
-      <c r="E329" s="76"/>
+      <c r="C329" s="73"/>
+      <c r="D329" s="73"/>
+      <c r="E329" s="74"/>
       <c r="F329" s="72">
         <v>0</v>
       </c>
@@ -27379,12 +27409,12 @@
       <c r="A332" s="27">
         <v>46030</v>
       </c>
-      <c r="B332" s="75" t="s">
+      <c r="B332" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C332" s="75"/>
-      <c r="D332" s="75"/>
-      <c r="E332" s="76"/>
+      <c r="C332" s="73"/>
+      <c r="D332" s="73"/>
+      <c r="E332" s="74"/>
       <c r="F332" s="72">
         <v>0</v>
       </c>
@@ -27416,12 +27446,12 @@
       <c r="A333" s="27">
         <v>46030</v>
       </c>
-      <c r="B333" s="75" t="s">
+      <c r="B333" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C333" s="75"/>
-      <c r="D333" s="75"/>
-      <c r="E333" s="76"/>
+      <c r="C333" s="73"/>
+      <c r="D333" s="73"/>
+      <c r="E333" s="74"/>
       <c r="F333" s="72">
         <v>0</v>
       </c>
@@ -27797,12 +27827,12 @@
       <c r="A342" s="27">
         <v>46031</v>
       </c>
-      <c r="B342" s="75" t="s">
+      <c r="B342" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C342" s="75"/>
-      <c r="D342" s="75"/>
-      <c r="E342" s="76"/>
+      <c r="C342" s="73"/>
+      <c r="D342" s="73"/>
+      <c r="E342" s="74"/>
       <c r="F342" s="72">
         <v>0</v>
       </c>
@@ -28006,12 +28036,12 @@
       <c r="A347" s="27">
         <v>46032</v>
       </c>
-      <c r="B347" s="75" t="s">
+      <c r="B347" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C347" s="75"/>
-      <c r="D347" s="75"/>
-      <c r="E347" s="76"/>
+      <c r="C347" s="73"/>
+      <c r="D347" s="73"/>
+      <c r="E347" s="74"/>
       <c r="F347" s="72">
         <v>0</v>
       </c>
@@ -28387,12 +28417,12 @@
       <c r="A356" s="27">
         <v>46033</v>
       </c>
-      <c r="B356" s="75" t="s">
+      <c r="B356" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C356" s="75"/>
-      <c r="D356" s="75"/>
-      <c r="E356" s="76"/>
+      <c r="C356" s="73"/>
+      <c r="D356" s="73"/>
+      <c r="E356" s="74"/>
       <c r="F356" s="72">
         <v>0</v>
       </c>
@@ -28424,12 +28454,12 @@
       <c r="A357" s="27">
         <v>46033</v>
       </c>
-      <c r="B357" s="75" t="s">
+      <c r="B357" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C357" s="75"/>
-      <c r="D357" s="75"/>
-      <c r="E357" s="76"/>
+      <c r="C357" s="73"/>
+      <c r="D357" s="73"/>
+      <c r="E357" s="74"/>
       <c r="F357" s="72">
         <v>0</v>
       </c>
@@ -28461,12 +28491,12 @@
       <c r="A358" s="27">
         <v>46034</v>
       </c>
-      <c r="B358" s="75" t="s">
+      <c r="B358" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C358" s="75"/>
-      <c r="D358" s="75"/>
-      <c r="E358" s="76"/>
+      <c r="C358" s="73"/>
+      <c r="D358" s="73"/>
+      <c r="E358" s="74"/>
       <c r="F358" s="72">
         <v>0</v>
       </c>
@@ -28498,12 +28528,12 @@
       <c r="A359" s="27">
         <v>46035</v>
       </c>
-      <c r="B359" s="75" t="s">
+      <c r="B359" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C359" s="75"/>
-      <c r="D359" s="75"/>
-      <c r="E359" s="76"/>
+      <c r="C359" s="73"/>
+      <c r="D359" s="73"/>
+      <c r="E359" s="74"/>
       <c r="F359" s="4">
         <v>12624</v>
       </c>
@@ -28535,12 +28565,12 @@
       <c r="A360" s="27">
         <v>46035</v>
       </c>
-      <c r="B360" s="75" t="s">
+      <c r="B360" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C360" s="75"/>
-      <c r="D360" s="75"/>
-      <c r="E360" s="76"/>
+      <c r="C360" s="73"/>
+      <c r="D360" s="73"/>
+      <c r="E360" s="74"/>
       <c r="F360" s="72">
         <v>0</v>
       </c>
@@ -28572,12 +28602,12 @@
       <c r="A361" s="27">
         <v>46036</v>
       </c>
-      <c r="B361" s="75" t="s">
+      <c r="B361" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="C361" s="75"/>
-      <c r="D361" s="75"/>
-      <c r="E361" s="76"/>
+      <c r="C361" s="73"/>
+      <c r="D361" s="73"/>
+      <c r="E361" s="74"/>
       <c r="F361" s="72">
         <v>0</v>
       </c>
@@ -28609,12 +28639,12 @@
       <c r="A362" s="27">
         <v>46036</v>
       </c>
-      <c r="B362" s="75" t="s">
+      <c r="B362" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C362" s="75"/>
-      <c r="D362" s="75"/>
-      <c r="E362" s="76"/>
+      <c r="C362" s="73"/>
+      <c r="D362" s="73"/>
+      <c r="E362" s="74"/>
       <c r="F362" s="72">
         <v>0</v>
       </c>
@@ -28689,12 +28719,12 @@
       <c r="A364" s="27">
         <v>46037</v>
       </c>
-      <c r="B364" s="75" t="s">
+      <c r="B364" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C364" s="75"/>
-      <c r="D364" s="75"/>
-      <c r="E364" s="76"/>
+      <c r="C364" s="73"/>
+      <c r="D364" s="73"/>
+      <c r="E364" s="74"/>
       <c r="F364" s="72">
         <v>0</v>
       </c>
@@ -28726,12 +28756,12 @@
       <c r="A365" s="27">
         <v>46037</v>
       </c>
-      <c r="B365" s="75" t="s">
+      <c r="B365" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C365" s="75"/>
-      <c r="D365" s="75"/>
-      <c r="E365" s="76"/>
+      <c r="C365" s="73"/>
+      <c r="D365" s="73"/>
+      <c r="E365" s="74"/>
       <c r="F365" s="72">
         <v>0</v>
       </c>
@@ -28806,12 +28836,12 @@
       <c r="A367" s="27">
         <v>46038</v>
       </c>
-      <c r="B367" s="75" t="s">
+      <c r="B367" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C367" s="75"/>
-      <c r="D367" s="75"/>
-      <c r="E367" s="76"/>
+      <c r="C367" s="73"/>
+      <c r="D367" s="73"/>
+      <c r="E367" s="74"/>
       <c r="F367" s="72">
         <v>0</v>
       </c>
@@ -28843,12 +28873,12 @@
       <c r="A368" s="27">
         <v>46039</v>
       </c>
-      <c r="B368" s="75" t="s">
+      <c r="B368" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C368" s="75"/>
-      <c r="D368" s="75"/>
-      <c r="E368" s="76"/>
+      <c r="C368" s="73"/>
+      <c r="D368" s="73"/>
+      <c r="E368" s="74"/>
       <c r="F368" s="72">
         <v>0</v>
       </c>
@@ -28880,12 +28910,12 @@
       <c r="A369" s="27">
         <v>46040</v>
       </c>
-      <c r="B369" s="75" t="s">
+      <c r="B369" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C369" s="75"/>
-      <c r="D369" s="75"/>
-      <c r="E369" s="76"/>
+      <c r="C369" s="73"/>
+      <c r="D369" s="73"/>
+      <c r="E369" s="74"/>
       <c r="F369" s="72">
         <v>0</v>
       </c>
@@ -28917,12 +28947,12 @@
       <c r="A370" s="27">
         <v>46041</v>
       </c>
-      <c r="B370" s="75" t="s">
+      <c r="B370" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C370" s="75"/>
-      <c r="D370" s="75"/>
-      <c r="E370" s="76"/>
+      <c r="C370" s="73"/>
+      <c r="D370" s="73"/>
+      <c r="E370" s="74"/>
       <c r="F370" s="72">
         <v>0</v>
       </c>
@@ -28954,12 +28984,12 @@
       <c r="A371" s="27">
         <v>46041</v>
       </c>
-      <c r="B371" s="75" t="s">
+      <c r="B371" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C371" s="75"/>
-      <c r="D371" s="75"/>
-      <c r="E371" s="76"/>
+      <c r="C371" s="73"/>
+      <c r="D371" s="73"/>
+      <c r="E371" s="74"/>
       <c r="F371" s="72">
         <v>0</v>
       </c>
@@ -29077,12 +29107,12 @@
       <c r="A374" s="27">
         <v>46042</v>
       </c>
-      <c r="B374" s="75" t="s">
+      <c r="B374" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C374" s="75"/>
-      <c r="D374" s="75"/>
-      <c r="E374" s="76"/>
+      <c r="C374" s="73"/>
+      <c r="D374" s="73"/>
+      <c r="E374" s="74"/>
       <c r="F374" s="72">
         <v>0</v>
       </c>
@@ -29114,12 +29144,12 @@
       <c r="A375" s="27">
         <v>46043</v>
       </c>
-      <c r="B375" s="75" t="s">
+      <c r="B375" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C375" s="75"/>
-      <c r="D375" s="75"/>
-      <c r="E375" s="76"/>
+      <c r="C375" s="73"/>
+      <c r="D375" s="73"/>
+      <c r="E375" s="74"/>
       <c r="F375" s="72">
         <v>0</v>
       </c>
@@ -29151,12 +29181,12 @@
       <c r="A376" s="27">
         <v>46044</v>
       </c>
-      <c r="B376" s="75" t="s">
+      <c r="B376" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C376" s="75"/>
-      <c r="D376" s="75"/>
-      <c r="E376" s="76"/>
+      <c r="C376" s="73"/>
+      <c r="D376" s="73"/>
+      <c r="E376" s="74"/>
       <c r="F376" s="72">
         <v>0</v>
       </c>
@@ -29188,12 +29218,12 @@
       <c r="A377" s="27">
         <v>46045</v>
       </c>
-      <c r="B377" s="75" t="s">
+      <c r="B377" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C377" s="75"/>
-      <c r="D377" s="75"/>
-      <c r="E377" s="76"/>
+      <c r="C377" s="73"/>
+      <c r="D377" s="73"/>
+      <c r="E377" s="74"/>
       <c r="F377" s="72">
         <v>0</v>
       </c>
@@ -29225,12 +29255,12 @@
       <c r="A378" s="27">
         <v>46045</v>
       </c>
-      <c r="B378" s="75" t="s">
+      <c r="B378" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="C378" s="75"/>
-      <c r="D378" s="75"/>
-      <c r="E378" s="76"/>
+      <c r="C378" s="73"/>
+      <c r="D378" s="73"/>
+      <c r="E378" s="74"/>
       <c r="F378" s="72">
         <v>0</v>
       </c>
@@ -29262,12 +29292,12 @@
       <c r="A379" s="27">
         <v>46045</v>
       </c>
-      <c r="B379" s="75" t="s">
+      <c r="B379" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C379" s="75"/>
-      <c r="D379" s="75"/>
-      <c r="E379" s="76"/>
+      <c r="C379" s="73"/>
+      <c r="D379" s="73"/>
+      <c r="E379" s="74"/>
       <c r="F379" s="72">
         <v>0</v>
       </c>
@@ -29557,12 +29587,12 @@
       <c r="A386" s="27">
         <v>46046</v>
       </c>
-      <c r="B386" s="75" t="s">
+      <c r="B386" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C386" s="75"/>
-      <c r="D386" s="75"/>
-      <c r="E386" s="76"/>
+      <c r="C386" s="73"/>
+      <c r="D386" s="73"/>
+      <c r="E386" s="74"/>
       <c r="F386" s="72">
         <v>0</v>
       </c>
@@ -29594,12 +29624,12 @@
       <c r="A387" s="27">
         <v>46047</v>
       </c>
-      <c r="B387" s="75" t="s">
+      <c r="B387" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="C387" s="75"/>
-      <c r="D387" s="75"/>
-      <c r="E387" s="76"/>
+      <c r="C387" s="73"/>
+      <c r="D387" s="73"/>
+      <c r="E387" s="74"/>
       <c r="F387" s="72">
         <v>0</v>
       </c>
@@ -29631,12 +29661,12 @@
       <c r="A388" s="27">
         <v>46047</v>
       </c>
-      <c r="B388" s="75" t="s">
+      <c r="B388" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C388" s="75"/>
-      <c r="D388" s="75"/>
-      <c r="E388" s="76"/>
+      <c r="C388" s="73"/>
+      <c r="D388" s="73"/>
+      <c r="E388" s="74"/>
       <c r="F388" s="72">
         <v>0</v>
       </c>
@@ -29668,12 +29698,12 @@
       <c r="A389" s="27">
         <v>46048</v>
       </c>
-      <c r="B389" s="75" t="s">
+      <c r="B389" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="C389" s="75"/>
-      <c r="D389" s="75"/>
-      <c r="E389" s="76"/>
+      <c r="C389" s="73"/>
+      <c r="D389" s="73"/>
+      <c r="E389" s="74"/>
       <c r="F389" s="72">
         <v>0</v>
       </c>
@@ -29705,12 +29735,12 @@
       <c r="A390" s="27">
         <v>46048</v>
       </c>
-      <c r="B390" s="75" t="s">
+      <c r="B390" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C390" s="75"/>
-      <c r="D390" s="75"/>
-      <c r="E390" s="76"/>
+      <c r="C390" s="73"/>
+      <c r="D390" s="73"/>
+      <c r="E390" s="74"/>
       <c r="F390" s="72">
         <v>0</v>
       </c>
@@ -29785,12 +29815,12 @@
       <c r="A392" s="27">
         <v>46049</v>
       </c>
-      <c r="B392" s="75" t="s">
+      <c r="B392" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C392" s="75"/>
-      <c r="D392" s="75"/>
-      <c r="E392" s="76"/>
+      <c r="C392" s="73"/>
+      <c r="D392" s="73"/>
+      <c r="E392" s="74"/>
       <c r="F392" s="72">
         <v>0</v>
       </c>
@@ -29822,12 +29852,12 @@
       <c r="A393" s="27">
         <v>46049</v>
       </c>
-      <c r="B393" s="75" t="s">
+      <c r="B393" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C393" s="75"/>
-      <c r="D393" s="75"/>
-      <c r="E393" s="76"/>
+      <c r="C393" s="73"/>
+      <c r="D393" s="73"/>
+      <c r="E393" s="74"/>
       <c r="F393" s="72">
         <v>0</v>
       </c>
@@ -29902,12 +29932,12 @@
       <c r="A395" s="27">
         <v>46050</v>
       </c>
-      <c r="B395" s="75" t="s">
+      <c r="B395" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C395" s="75"/>
-      <c r="D395" s="75"/>
-      <c r="E395" s="76"/>
+      <c r="C395" s="73"/>
+      <c r="D395" s="73"/>
+      <c r="E395" s="74"/>
       <c r="F395" s="72">
         <v>0</v>
       </c>
@@ -29939,12 +29969,12 @@
       <c r="A396" s="27">
         <v>46051</v>
       </c>
-      <c r="B396" s="75" t="s">
+      <c r="B396" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C396" s="75"/>
-      <c r="D396" s="75"/>
-      <c r="E396" s="76"/>
+      <c r="C396" s="73"/>
+      <c r="D396" s="73"/>
+      <c r="E396" s="74"/>
       <c r="F396" s="72">
         <v>0</v>
       </c>
@@ -30019,12 +30049,12 @@
       <c r="A398" s="27">
         <v>46052</v>
       </c>
-      <c r="B398" s="75" t="s">
+      <c r="B398" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C398" s="75"/>
-      <c r="D398" s="75"/>
-      <c r="E398" s="76"/>
+      <c r="C398" s="73"/>
+      <c r="D398" s="73"/>
+      <c r="E398" s="74"/>
       <c r="F398" s="72">
         <v>0</v>
       </c>
@@ -30056,12 +30086,12 @@
       <c r="A399" s="27">
         <v>46052</v>
       </c>
-      <c r="B399" s="75" t="s">
+      <c r="B399" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C399" s="75"/>
-      <c r="D399" s="75"/>
-      <c r="E399" s="76"/>
+      <c r="C399" s="73"/>
+      <c r="D399" s="73"/>
+      <c r="E399" s="74"/>
       <c r="F399" s="72">
         <v>0</v>
       </c>
@@ -30093,12 +30123,12 @@
       <c r="A400" s="27">
         <v>46053</v>
       </c>
-      <c r="B400" s="75" t="s">
+      <c r="B400" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="C400" s="75"/>
-      <c r="D400" s="75"/>
-      <c r="E400" s="76"/>
+      <c r="C400" s="73"/>
+      <c r="D400" s="73"/>
+      <c r="E400" s="74"/>
       <c r="F400" s="72">
         <v>0</v>
       </c>
@@ -30130,12 +30160,12 @@
       <c r="A401" s="27">
         <v>46053</v>
       </c>
-      <c r="B401" s="75" t="s">
+      <c r="B401" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="C401" s="75"/>
-      <c r="D401" s="75"/>
-      <c r="E401" s="76"/>
+      <c r="C401" s="73"/>
+      <c r="D401" s="73"/>
+      <c r="E401" s="74"/>
       <c r="F401" s="72">
         <v>0</v>
       </c>
@@ -30167,12 +30197,12 @@
       <c r="A402" s="27">
         <v>46053</v>
       </c>
-      <c r="B402" s="75" t="s">
+      <c r="B402" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="C402" s="75"/>
-      <c r="D402" s="75"/>
-      <c r="E402" s="76"/>
+      <c r="C402" s="73"/>
+      <c r="D402" s="73"/>
+      <c r="E402" s="74"/>
       <c r="F402" s="72">
         <v>0</v>
       </c>
@@ -30204,12 +30234,12 @@
       <c r="A403" s="27">
         <v>46053</v>
       </c>
-      <c r="B403" s="75" t="s">
+      <c r="B403" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="C403" s="75"/>
-      <c r="D403" s="75"/>
-      <c r="E403" s="76"/>
+      <c r="C403" s="73"/>
+      <c r="D403" s="73"/>
+      <c r="E403" s="74"/>
       <c r="F403" s="72">
         <v>0</v>
       </c>
@@ -30241,12 +30271,12 @@
       <c r="A404" s="27">
         <v>46053</v>
       </c>
-      <c r="B404" s="75" t="s">
+      <c r="B404" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C404" s="75"/>
-      <c r="D404" s="75"/>
-      <c r="E404" s="76"/>
+      <c r="C404" s="73"/>
+      <c r="D404" s="73"/>
+      <c r="E404" s="74"/>
       <c r="F404" s="72">
         <v>0</v>
       </c>
@@ -30321,12 +30351,12 @@
       <c r="A406" s="27">
         <v>46054</v>
       </c>
-      <c r="B406" s="75" t="s">
+      <c r="B406" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C406" s="75"/>
-      <c r="D406" s="75"/>
-      <c r="E406" s="76"/>
+      <c r="C406" s="73"/>
+      <c r="D406" s="73"/>
+      <c r="E406" s="74"/>
       <c r="F406" s="72">
         <v>0</v>
       </c>
@@ -30401,12 +30431,12 @@
       <c r="A408" s="27">
         <v>46055</v>
       </c>
-      <c r="B408" s="75" t="s">
+      <c r="B408" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C408" s="75"/>
-      <c r="D408" s="75"/>
-      <c r="E408" s="76"/>
+      <c r="C408" s="73"/>
+      <c r="D408" s="73"/>
+      <c r="E408" s="74"/>
       <c r="F408" s="72">
         <v>0</v>
       </c>
@@ -30438,12 +30468,12 @@
       <c r="A409" s="27">
         <v>46056</v>
       </c>
-      <c r="B409" s="75" t="s">
+      <c r="B409" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C409" s="75"/>
-      <c r="D409" s="75"/>
-      <c r="E409" s="76"/>
+      <c r="C409" s="73"/>
+      <c r="D409" s="73"/>
+      <c r="E409" s="74"/>
       <c r="F409" s="72">
         <v>0</v>
       </c>
@@ -30475,12 +30505,12 @@
       <c r="A410" s="27">
         <v>46056</v>
       </c>
-      <c r="B410" s="75" t="s">
+      <c r="B410" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C410" s="75"/>
-      <c r="D410" s="75"/>
-      <c r="E410" s="76"/>
+      <c r="C410" s="73"/>
+      <c r="D410" s="73"/>
+      <c r="E410" s="74"/>
       <c r="F410" s="72">
         <v>0</v>
       </c>
@@ -30555,12 +30585,12 @@
       <c r="A412" s="27">
         <v>46058</v>
       </c>
-      <c r="B412" s="75" t="s">
+      <c r="B412" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C412" s="75"/>
-      <c r="D412" s="75"/>
-      <c r="E412" s="76"/>
+      <c r="C412" s="73"/>
+      <c r="D412" s="73"/>
+      <c r="E412" s="74"/>
       <c r="F412" s="72">
         <v>0</v>
       </c>
@@ -30850,12 +30880,12 @@
       <c r="A419" s="27">
         <v>46059</v>
       </c>
-      <c r="B419" s="75" t="s">
+      <c r="B419" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C419" s="75"/>
-      <c r="D419" s="75"/>
-      <c r="E419" s="76"/>
+      <c r="C419" s="73"/>
+      <c r="D419" s="73"/>
+      <c r="E419" s="74"/>
       <c r="F419" s="72">
         <v>0</v>
       </c>
@@ -31102,12 +31132,12 @@
       <c r="A425" s="27">
         <v>46060</v>
       </c>
-      <c r="B425" s="75" t="s">
+      <c r="B425" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C425" s="75"/>
-      <c r="D425" s="75"/>
-      <c r="E425" s="76"/>
+      <c r="C425" s="73"/>
+      <c r="D425" s="73"/>
+      <c r="E425" s="74"/>
       <c r="F425" s="72">
         <v>0</v>
       </c>
@@ -31139,12 +31169,12 @@
       <c r="A426" s="27">
         <v>46060</v>
       </c>
-      <c r="B426" s="75" t="s">
+      <c r="B426" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C426" s="75"/>
-      <c r="D426" s="75"/>
-      <c r="E426" s="76"/>
+      <c r="C426" s="73"/>
+      <c r="D426" s="73"/>
+      <c r="E426" s="74"/>
       <c r="F426" s="72">
         <v>0</v>
       </c>
@@ -31563,12 +31593,12 @@
       <c r="A436" s="27">
         <v>46061</v>
       </c>
-      <c r="B436" s="75" t="s">
+      <c r="B436" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C436" s="75"/>
-      <c r="D436" s="75"/>
-      <c r="E436" s="76"/>
+      <c r="C436" s="73"/>
+      <c r="D436" s="73"/>
+      <c r="E436" s="74"/>
       <c r="F436" s="72">
         <v>0</v>
       </c>
@@ -31643,12 +31673,12 @@
       <c r="A438" s="27">
         <v>46062</v>
       </c>
-      <c r="B438" s="75" t="s">
+      <c r="B438" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C438" s="75"/>
-      <c r="D438" s="75"/>
-      <c r="E438" s="76"/>
+      <c r="C438" s="73"/>
+      <c r="D438" s="73"/>
+      <c r="E438" s="74"/>
       <c r="F438" s="72">
         <v>0</v>
       </c>
@@ -31680,12 +31710,12 @@
       <c r="A439" s="27">
         <v>46063</v>
       </c>
-      <c r="B439" s="75" t="s">
+      <c r="B439" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C439" s="75"/>
-      <c r="D439" s="75"/>
-      <c r="E439" s="76"/>
+      <c r="C439" s="73"/>
+      <c r="D439" s="73"/>
+      <c r="E439" s="74"/>
       <c r="F439" s="4">
         <v>4117</v>
       </c>
@@ -31803,12 +31833,12 @@
       <c r="A442" s="27">
         <v>46063</v>
       </c>
-      <c r="B442" s="75" t="s">
+      <c r="B442" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C442" s="75"/>
-      <c r="D442" s="75"/>
-      <c r="E442" s="76"/>
+      <c r="C442" s="73"/>
+      <c r="D442" s="73"/>
+      <c r="E442" s="74"/>
       <c r="F442" s="72">
         <v>0</v>
       </c>
@@ -32098,12 +32128,12 @@
       <c r="A449" s="27">
         <v>46064</v>
       </c>
-      <c r="B449" s="75" t="s">
+      <c r="B449" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C449" s="75"/>
-      <c r="D449" s="75"/>
-      <c r="E449" s="76"/>
+      <c r="C449" s="73"/>
+      <c r="D449" s="73"/>
+      <c r="E449" s="74"/>
       <c r="F449" s="72">
         <v>0</v>
       </c>
@@ -32135,12 +32165,12 @@
       <c r="A450" s="27">
         <v>46065</v>
       </c>
-      <c r="B450" s="75" t="s">
+      <c r="B450" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C450" s="75"/>
-      <c r="D450" s="75"/>
-      <c r="E450" s="76"/>
+      <c r="C450" s="73"/>
+      <c r="D450" s="73"/>
+      <c r="E450" s="74"/>
       <c r="F450" s="72">
         <v>0</v>
       </c>
@@ -32172,12 +32202,12 @@
       <c r="A451" s="27">
         <v>46065</v>
       </c>
-      <c r="B451" s="75" t="s">
+      <c r="B451" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C451" s="75"/>
-      <c r="D451" s="75"/>
-      <c r="E451" s="76"/>
+      <c r="C451" s="73"/>
+      <c r="D451" s="73"/>
+      <c r="E451" s="74"/>
       <c r="F451" s="72">
         <v>0</v>
       </c>
@@ -32209,12 +32239,12 @@
       <c r="A452" s="27">
         <v>46066</v>
       </c>
-      <c r="B452" s="75" t="s">
+      <c r="B452" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C452" s="75"/>
-      <c r="D452" s="75"/>
-      <c r="E452" s="76"/>
+      <c r="C452" s="73"/>
+      <c r="D452" s="73"/>
+      <c r="E452" s="74"/>
       <c r="F452" s="72">
         <v>0</v>
       </c>
@@ -32246,12 +32276,12 @@
       <c r="A453" s="27">
         <v>46067</v>
       </c>
-      <c r="B453" s="75" t="s">
+      <c r="B453" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C453" s="75"/>
-      <c r="D453" s="75"/>
-      <c r="E453" s="76"/>
+      <c r="C453" s="73"/>
+      <c r="D453" s="73"/>
+      <c r="E453" s="74"/>
       <c r="F453" s="72">
         <v>0</v>
       </c>
@@ -32283,12 +32313,12 @@
       <c r="A454" s="27">
         <v>46068</v>
       </c>
-      <c r="B454" s="75" t="s">
+      <c r="B454" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C454" s="75"/>
-      <c r="D454" s="75"/>
-      <c r="E454" s="76"/>
+      <c r="C454" s="73"/>
+      <c r="D454" s="73"/>
+      <c r="E454" s="74"/>
       <c r="F454" s="72">
         <v>0</v>
       </c>
@@ -32320,12 +32350,12 @@
       <c r="A455" s="27">
         <v>46069</v>
       </c>
-      <c r="B455" s="75" t="s">
+      <c r="B455" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C455" s="75"/>
-      <c r="D455" s="75"/>
-      <c r="E455" s="76"/>
+      <c r="C455" s="73"/>
+      <c r="D455" s="73"/>
+      <c r="E455" s="74"/>
       <c r="F455" s="72">
         <v>0</v>
       </c>
@@ -32357,12 +32387,12 @@
       <c r="A456" s="27">
         <v>46069</v>
       </c>
-      <c r="B456" s="75" t="s">
+      <c r="B456" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C456" s="75"/>
-      <c r="D456" s="75"/>
-      <c r="E456" s="76"/>
+      <c r="C456" s="73"/>
+      <c r="D456" s="73"/>
+      <c r="E456" s="74"/>
       <c r="F456" s="72">
         <v>0</v>
       </c>
@@ -32394,12 +32424,12 @@
       <c r="A457" s="27">
         <v>46070</v>
       </c>
-      <c r="B457" s="75" t="s">
+      <c r="B457" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C457" s="75"/>
-      <c r="D457" s="75"/>
-      <c r="E457" s="76"/>
+      <c r="C457" s="73"/>
+      <c r="D457" s="73"/>
+      <c r="E457" s="74"/>
       <c r="F457" s="72">
         <v>0</v>
       </c>
@@ -32431,12 +32461,12 @@
       <c r="A458" s="27">
         <v>46071</v>
       </c>
-      <c r="B458" s="75" t="s">
+      <c r="B458" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C458" s="75"/>
-      <c r="D458" s="75"/>
-      <c r="E458" s="76"/>
+      <c r="C458" s="73"/>
+      <c r="D458" s="73"/>
+      <c r="E458" s="74"/>
       <c r="F458" s="72">
         <v>0</v>
       </c>
@@ -32468,12 +32498,12 @@
       <c r="A459" s="27">
         <v>46072</v>
       </c>
-      <c r="B459" s="75" t="s">
+      <c r="B459" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C459" s="75"/>
-      <c r="D459" s="75"/>
-      <c r="E459" s="76"/>
+      <c r="C459" s="73"/>
+      <c r="D459" s="73"/>
+      <c r="E459" s="74"/>
       <c r="F459" s="72">
         <v>0</v>
       </c>
@@ -32505,12 +32535,12 @@
       <c r="A460" s="27">
         <v>46073</v>
       </c>
-      <c r="B460" s="75" t="s">
+      <c r="B460" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C460" s="75"/>
-      <c r="D460" s="75"/>
-      <c r="E460" s="76"/>
+      <c r="C460" s="73"/>
+      <c r="D460" s="73"/>
+      <c r="E460" s="74"/>
       <c r="F460" s="72">
         <v>0</v>
       </c>
@@ -32542,12 +32572,12 @@
       <c r="A461" s="27">
         <v>46073</v>
       </c>
-      <c r="B461" s="75" t="s">
+      <c r="B461" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C461" s="75"/>
-      <c r="D461" s="75"/>
-      <c r="E461" s="76"/>
+      <c r="C461" s="73"/>
+      <c r="D461" s="73"/>
+      <c r="E461" s="74"/>
       <c r="F461" s="72">
         <v>0</v>
       </c>
@@ -32708,12 +32738,12 @@
       <c r="A465" s="27">
         <v>46074</v>
       </c>
-      <c r="B465" s="75" t="s">
+      <c r="B465" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="C465" s="75"/>
-      <c r="D465" s="75"/>
-      <c r="E465" s="76"/>
+      <c r="C465" s="73"/>
+      <c r="D465" s="73"/>
+      <c r="E465" s="74"/>
       <c r="F465" s="72">
         <v>0</v>
       </c>
@@ -32745,12 +32775,12 @@
       <c r="A466" s="27">
         <v>46074</v>
       </c>
-      <c r="B466" s="75" t="s">
+      <c r="B466" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="C466" s="75"/>
-      <c r="D466" s="75"/>
-      <c r="E466" s="76"/>
+      <c r="C466" s="73"/>
+      <c r="D466" s="73"/>
+      <c r="E466" s="74"/>
       <c r="F466" s="72">
         <v>0</v>
       </c>
@@ -32782,12 +32812,12 @@
       <c r="A467" s="27">
         <v>46074</v>
       </c>
-      <c r="B467" s="75" t="s">
+      <c r="B467" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="C467" s="75"/>
-      <c r="D467" s="75"/>
-      <c r="E467" s="76"/>
+      <c r="C467" s="73"/>
+      <c r="D467" s="73"/>
+      <c r="E467" s="74"/>
       <c r="F467" s="72">
         <v>0</v>
       </c>
@@ -32819,12 +32849,12 @@
       <c r="A468" s="27">
         <v>46074</v>
       </c>
-      <c r="B468" s="75" t="s">
+      <c r="B468" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C468" s="75"/>
-      <c r="D468" s="75"/>
-      <c r="E468" s="76"/>
+      <c r="C468" s="73"/>
+      <c r="D468" s="73"/>
+      <c r="E468" s="74"/>
       <c r="F468" s="72">
         <v>0</v>
       </c>
@@ -32856,12 +32886,12 @@
       <c r="A469" s="27">
         <v>46074</v>
       </c>
-      <c r="B469" s="75" t="s">
+      <c r="B469" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="C469" s="75"/>
-      <c r="D469" s="75"/>
-      <c r="E469" s="76"/>
+      <c r="C469" s="73"/>
+      <c r="D469" s="73"/>
+      <c r="E469" s="74"/>
       <c r="F469" s="4">
         <v>-70000</v>
       </c>
@@ -33237,12 +33267,12 @@
       <c r="A478" s="27">
         <v>46075</v>
       </c>
-      <c r="B478" s="75" t="s">
+      <c r="B478" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="C478" s="75"/>
-      <c r="D478" s="75"/>
-      <c r="E478" s="76"/>
+      <c r="C478" s="73"/>
+      <c r="D478" s="73"/>
+      <c r="E478" s="74"/>
       <c r="F478" s="72">
         <v>0</v>
       </c>
@@ -33274,12 +33304,12 @@
       <c r="A479" s="27">
         <v>46075</v>
       </c>
-      <c r="B479" s="75" t="s">
+      <c r="B479" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C479" s="75"/>
-      <c r="D479" s="75"/>
-      <c r="E479" s="76"/>
+      <c r="C479" s="73"/>
+      <c r="D479" s="73"/>
+      <c r="E479" s="74"/>
       <c r="F479" s="72">
         <v>0</v>
       </c>
@@ -33311,12 +33341,12 @@
       <c r="A480" s="27">
         <v>46076</v>
       </c>
-      <c r="B480" s="75" t="s">
+      <c r="B480" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C480" s="75"/>
-      <c r="D480" s="75"/>
-      <c r="E480" s="76"/>
+      <c r="C480" s="73"/>
+      <c r="D480" s="73"/>
+      <c r="E480" s="74"/>
       <c r="F480" s="72">
         <v>0</v>
       </c>
@@ -33348,12 +33378,12 @@
       <c r="A481" s="27">
         <v>46077</v>
       </c>
-      <c r="B481" s="75" t="s">
+      <c r="B481" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C481" s="75"/>
-      <c r="D481" s="75"/>
-      <c r="E481" s="76"/>
+      <c r="C481" s="73"/>
+      <c r="D481" s="73"/>
+      <c r="E481" s="74"/>
       <c r="F481" s="72">
         <v>0</v>
       </c>
@@ -33686,12 +33716,12 @@
       <c r="A489" s="27">
         <v>46078</v>
       </c>
-      <c r="B489" s="75" t="s">
+      <c r="B489" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C489" s="75"/>
-      <c r="D489" s="75"/>
-      <c r="E489" s="76"/>
+      <c r="C489" s="73"/>
+      <c r="D489" s="73"/>
+      <c r="E489" s="74"/>
       <c r="F489" s="72">
         <v>0</v>
       </c>
@@ -33723,12 +33753,12 @@
       <c r="A490" s="27">
         <v>46079</v>
       </c>
-      <c r="B490" s="75" t="s">
+      <c r="B490" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C490" s="75"/>
-      <c r="D490" s="75"/>
-      <c r="E490" s="76"/>
+      <c r="C490" s="73"/>
+      <c r="D490" s="73"/>
+      <c r="E490" s="74"/>
       <c r="F490" s="72">
         <v>0</v>
       </c>
@@ -33760,12 +33790,12 @@
       <c r="A491" s="27">
         <v>46080</v>
       </c>
-      <c r="B491" s="75" t="s">
+      <c r="B491" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C491" s="75"/>
-      <c r="D491" s="75"/>
-      <c r="E491" s="76"/>
+      <c r="C491" s="73"/>
+      <c r="D491" s="73"/>
+      <c r="E491" s="74"/>
       <c r="F491" s="72">
         <v>0</v>
       </c>
@@ -33797,12 +33827,12 @@
       <c r="A492" s="27">
         <v>46080</v>
       </c>
-      <c r="B492" s="75" t="s">
+      <c r="B492" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="C492" s="75"/>
-      <c r="D492" s="75"/>
-      <c r="E492" s="76"/>
+      <c r="C492" s="73"/>
+      <c r="D492" s="73"/>
+      <c r="E492" s="74"/>
       <c r="F492" s="4">
         <v>-18000</v>
       </c>
@@ -33834,12 +33864,12 @@
       <c r="A493" s="27">
         <v>46080</v>
       </c>
-      <c r="B493" s="75" t="s">
+      <c r="B493" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="C493" s="75"/>
-      <c r="D493" s="75"/>
-      <c r="E493" s="76"/>
+      <c r="C493" s="73"/>
+      <c r="D493" s="73"/>
+      <c r="E493" s="74"/>
       <c r="F493" s="4">
         <v>-18000</v>
       </c>
@@ -33871,12 +33901,12 @@
       <c r="A494" s="27">
         <v>46080</v>
       </c>
-      <c r="B494" s="75" t="s">
+      <c r="B494" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="C494" s="75"/>
-      <c r="D494" s="75"/>
-      <c r="E494" s="76"/>
+      <c r="C494" s="73"/>
+      <c r="D494" s="73"/>
+      <c r="E494" s="74"/>
       <c r="F494" s="4">
         <v>-18000</v>
       </c>
@@ -33994,12 +34024,12 @@
       <c r="A497" s="27">
         <v>46081</v>
       </c>
-      <c r="B497" s="75" t="s">
+      <c r="B497" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C497" s="75"/>
-      <c r="D497" s="75"/>
-      <c r="E497" s="76"/>
+      <c r="C497" s="73"/>
+      <c r="D497" s="73"/>
+      <c r="E497" s="74"/>
       <c r="F497" s="72">
         <v>0</v>
       </c>
@@ -34031,12 +34061,12 @@
       <c r="A498" s="27">
         <v>46081</v>
       </c>
-      <c r="B498" s="75" t="s">
+      <c r="B498" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C498" s="75"/>
-      <c r="D498" s="75"/>
-      <c r="E498" s="76"/>
+      <c r="C498" s="73"/>
+      <c r="D498" s="73"/>
+      <c r="E498" s="74"/>
       <c r="F498" s="72">
         <v>0</v>
       </c>
@@ -34068,12 +34098,12 @@
       <c r="A499" s="27">
         <v>46082</v>
       </c>
-      <c r="B499" s="75" t="s">
+      <c r="B499" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C499" s="75"/>
-      <c r="D499" s="75"/>
-      <c r="E499" s="76"/>
+      <c r="C499" s="73"/>
+      <c r="D499" s="73"/>
+      <c r="E499" s="74"/>
       <c r="F499" s="72">
         <v>0</v>
       </c>
@@ -34105,12 +34135,12 @@
       <c r="A500" s="27">
         <v>46083</v>
       </c>
-      <c r="B500" s="75" t="s">
+      <c r="B500" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C500" s="75"/>
-      <c r="D500" s="75"/>
-      <c r="E500" s="76"/>
+      <c r="C500" s="73"/>
+      <c r="D500" s="73"/>
+      <c r="E500" s="74"/>
       <c r="F500" s="72">
         <v>0</v>
       </c>
@@ -34142,12 +34172,12 @@
       <c r="A501" s="27">
         <v>46084</v>
       </c>
-      <c r="B501" s="75" t="s">
+      <c r="B501" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="C501" s="75"/>
-      <c r="D501" s="75"/>
-      <c r="E501" s="76"/>
+      <c r="C501" s="73"/>
+      <c r="D501" s="73"/>
+      <c r="E501" s="74"/>
       <c r="F501" s="72">
         <v>0</v>
       </c>
@@ -34179,12 +34209,12 @@
       <c r="A502" s="27">
         <v>46084</v>
       </c>
-      <c r="B502" s="75" t="s">
+      <c r="B502" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C502" s="75"/>
-      <c r="D502" s="75"/>
-      <c r="E502" s="76"/>
+      <c r="C502" s="73"/>
+      <c r="D502" s="73"/>
+      <c r="E502" s="74"/>
       <c r="F502" s="72">
         <v>0</v>
       </c>
@@ -34216,12 +34246,12 @@
       <c r="A503" s="27">
         <v>46085</v>
       </c>
-      <c r="B503" s="75" t="s">
+      <c r="B503" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C503" s="75"/>
-      <c r="D503" s="75"/>
-      <c r="E503" s="76"/>
+      <c r="C503" s="73"/>
+      <c r="D503" s="73"/>
+      <c r="E503" s="74"/>
       <c r="F503" s="72">
         <v>0</v>
       </c>
@@ -34253,12 +34283,12 @@
       <c r="A504" s="27">
         <v>46086</v>
       </c>
-      <c r="B504" s="75" t="s">
+      <c r="B504" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C504" s="75"/>
-      <c r="D504" s="75"/>
-      <c r="E504" s="76"/>
+      <c r="C504" s="73"/>
+      <c r="D504" s="73"/>
+      <c r="E504" s="74"/>
       <c r="F504" s="72">
         <v>0</v>
       </c>
@@ -34290,12 +34320,12 @@
       <c r="A505" s="27">
         <v>46087</v>
       </c>
-      <c r="B505" s="75" t="s">
+      <c r="B505" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C505" s="75"/>
-      <c r="D505" s="75"/>
-      <c r="E505" s="76"/>
+      <c r="C505" s="73"/>
+      <c r="D505" s="73"/>
+      <c r="E505" s="74"/>
       <c r="F505" s="72">
         <v>0</v>
       </c>
@@ -34327,12 +34357,12 @@
       <c r="A506" s="27">
         <v>46088</v>
       </c>
-      <c r="B506" s="75" t="s">
+      <c r="B506" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C506" s="75"/>
-      <c r="D506" s="75"/>
-      <c r="E506" s="76"/>
+      <c r="C506" s="73"/>
+      <c r="D506" s="73"/>
+      <c r="E506" s="74"/>
       <c r="F506" s="72">
         <v>0</v>
       </c>
@@ -34364,12 +34394,12 @@
       <c r="A507" s="27">
         <v>46088</v>
       </c>
-      <c r="B507" s="75" t="s">
+      <c r="B507" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C507" s="75"/>
-      <c r="D507" s="75"/>
-      <c r="E507" s="76"/>
+      <c r="C507" s="73"/>
+      <c r="D507" s="73"/>
+      <c r="E507" s="74"/>
       <c r="F507" s="72">
         <v>0</v>
       </c>
@@ -34401,12 +34431,12 @@
       <c r="A508" s="27">
         <v>46089</v>
       </c>
-      <c r="B508" s="75" t="s">
+      <c r="B508" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C508" s="75"/>
-      <c r="D508" s="75"/>
-      <c r="E508" s="76"/>
+      <c r="C508" s="73"/>
+      <c r="D508" s="73"/>
+      <c r="E508" s="74"/>
       <c r="F508" s="72">
         <v>0</v>
       </c>
@@ -34438,12 +34468,12 @@
       <c r="A509" s="27">
         <v>46090</v>
       </c>
-      <c r="B509" s="75" t="s">
+      <c r="B509" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C509" s="75"/>
-      <c r="D509" s="75"/>
-      <c r="E509" s="76"/>
+      <c r="C509" s="73"/>
+      <c r="D509" s="73"/>
+      <c r="E509" s="74"/>
       <c r="F509" s="72">
         <v>0</v>
       </c>
@@ -34475,12 +34505,12 @@
       <c r="A510" s="27">
         <v>46091</v>
       </c>
-      <c r="B510" s="75" t="s">
+      <c r="B510" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C510" s="75"/>
-      <c r="D510" s="75"/>
-      <c r="E510" s="76"/>
+      <c r="C510" s="73"/>
+      <c r="D510" s="73"/>
+      <c r="E510" s="74"/>
       <c r="F510" s="4">
         <v>4315</v>
       </c>
@@ -34942,12 +34972,12 @@
       <c r="A521" s="27">
         <v>46091</v>
       </c>
-      <c r="B521" s="75" t="s">
+      <c r="B521" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C521" s="75"/>
-      <c r="D521" s="75"/>
-      <c r="E521" s="76"/>
+      <c r="C521" s="73"/>
+      <c r="D521" s="73"/>
+      <c r="E521" s="74"/>
       <c r="F521" s="72">
         <v>0</v>
       </c>
@@ -34979,12 +35009,12 @@
       <c r="A522" s="27">
         <v>46092</v>
       </c>
-      <c r="B522" s="75" t="s">
+      <c r="B522" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C522" s="75"/>
-      <c r="D522" s="75"/>
-      <c r="E522" s="76"/>
+      <c r="C522" s="73"/>
+      <c r="D522" s="73"/>
+      <c r="E522" s="74"/>
       <c r="F522" s="72">
         <v>0</v>
       </c>
@@ -35016,12 +35046,12 @@
       <c r="A523" s="27">
         <v>46093</v>
       </c>
-      <c r="B523" s="75" t="s">
+      <c r="B523" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C523" s="75"/>
-      <c r="D523" s="75"/>
-      <c r="E523" s="76"/>
+      <c r="C523" s="73"/>
+      <c r="D523" s="73"/>
+      <c r="E523" s="74"/>
       <c r="F523" s="72">
         <v>0</v>
       </c>
@@ -35053,12 +35083,12 @@
       <c r="A524" s="27">
         <v>46094</v>
       </c>
-      <c r="B524" s="75" t="s">
+      <c r="B524" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C524" s="75"/>
-      <c r="D524" s="75"/>
-      <c r="E524" s="76"/>
+      <c r="C524" s="73"/>
+      <c r="D524" s="73"/>
+      <c r="E524" s="74"/>
       <c r="F524" s="72">
         <v>0</v>
       </c>
@@ -35087,7 +35117,7 @@
       </c>
     </row>
     <row r="525" spans="1:13">
-      <c r="A525" s="29">
+      <c r="A525" s="27">
         <v>46095</v>
       </c>
       <c r="B525" s="73" t="s">
@@ -35096,22 +35126,22 @@
       <c r="C525" s="73"/>
       <c r="D525" s="73"/>
       <c r="E525" s="74"/>
-      <c r="F525" s="71">
-        <v>0</v>
-      </c>
-      <c r="G525" s="71">
+      <c r="F525" s="72">
+        <v>0</v>
+      </c>
+      <c r="G525" s="72">
         <v>9</v>
       </c>
-      <c r="H525" s="71">
+      <c r="H525" s="72">
         <v>9</v>
       </c>
-      <c r="I525" s="30">
-        <v>37566</v>
-      </c>
-      <c r="J525" s="71">
-        <v>0</v>
-      </c>
-      <c r="K525" s="71">
+      <c r="I525" s="4">
+        <v>37572</v>
+      </c>
+      <c r="J525" s="72">
+        <v>0</v>
+      </c>
+      <c r="K525" s="72">
         <v>0</v>
       </c>
       <c r="L525" s="72">
@@ -35123,42 +35153,551 @@
         <v>167</v>
       </c>
     </row>
+    <row r="526" spans="1:13">
+      <c r="A526" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B526" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="C526" s="73"/>
+      <c r="D526" s="73"/>
+      <c r="E526" s="74"/>
+      <c r="F526" s="72">
+        <v>0</v>
+      </c>
+      <c r="G526" s="72">
+        <v>2</v>
+      </c>
+      <c r="H526" s="72">
+        <v>2</v>
+      </c>
+      <c r="I526" s="4">
+        <v>37574</v>
+      </c>
+      <c r="J526" s="72">
+        <v>0</v>
+      </c>
+      <c r="K526" s="72">
+        <v>0</v>
+      </c>
+      <c r="L526" s="72">
+        <f t="shared" ref="L526:L532" si="70">J526+L525</f>
+        <v>138882</v>
+      </c>
+      <c r="M526" s="72">
+        <f t="shared" ref="M526:M532" si="71">K526+M525</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13">
+      <c r="A527" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B527" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C527" s="73"/>
+      <c r="D527" s="73"/>
+      <c r="E527" s="74"/>
+      <c r="F527" s="72">
+        <v>0</v>
+      </c>
+      <c r="G527" s="72">
+        <v>20</v>
+      </c>
+      <c r="H527" s="72">
+        <v>20</v>
+      </c>
+      <c r="I527" s="4">
+        <v>37594</v>
+      </c>
+      <c r="J527" s="72">
+        <v>0</v>
+      </c>
+      <c r="K527" s="72">
+        <v>0</v>
+      </c>
+      <c r="L527" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M527" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13">
+      <c r="A528" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B528" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C528" s="73"/>
+      <c r="D528" s="73"/>
+      <c r="E528" s="74"/>
+      <c r="F528" s="72">
+        <v>0</v>
+      </c>
+      <c r="G528" s="72">
+        <v>11</v>
+      </c>
+      <c r="H528" s="72">
+        <v>11</v>
+      </c>
+      <c r="I528" s="4">
+        <v>37605</v>
+      </c>
+      <c r="J528" s="72">
+        <v>0</v>
+      </c>
+      <c r="K528" s="72">
+        <v>0</v>
+      </c>
+      <c r="L528" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M528" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13">
+      <c r="A529" s="27">
+        <v>46098</v>
+      </c>
+      <c r="B529" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C529" s="73"/>
+      <c r="D529" s="73"/>
+      <c r="E529" s="74"/>
+      <c r="F529" s="72">
+        <v>0</v>
+      </c>
+      <c r="G529" s="72">
+        <v>5</v>
+      </c>
+      <c r="H529" s="72">
+        <v>5</v>
+      </c>
+      <c r="I529" s="4">
+        <v>37610</v>
+      </c>
+      <c r="J529" s="72">
+        <v>0</v>
+      </c>
+      <c r="K529" s="72">
+        <v>0</v>
+      </c>
+      <c r="L529" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M529" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13">
+      <c r="A530" s="27">
+        <v>46099</v>
+      </c>
+      <c r="B530" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C530" s="73"/>
+      <c r="D530" s="73"/>
+      <c r="E530" s="74"/>
+      <c r="F530" s="72">
+        <v>0</v>
+      </c>
+      <c r="G530" s="72">
+        <v>8</v>
+      </c>
+      <c r="H530" s="72">
+        <v>8</v>
+      </c>
+      <c r="I530" s="4">
+        <v>37618</v>
+      </c>
+      <c r="J530" s="72">
+        <v>0</v>
+      </c>
+      <c r="K530" s="72">
+        <v>0</v>
+      </c>
+      <c r="L530" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M530" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13">
+      <c r="A531" s="27">
+        <v>46100</v>
+      </c>
+      <c r="B531" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C531" s="73"/>
+      <c r="D531" s="73"/>
+      <c r="E531" s="74"/>
+      <c r="F531" s="72">
+        <v>0</v>
+      </c>
+      <c r="G531" s="72">
+        <v>11</v>
+      </c>
+      <c r="H531" s="72">
+        <v>11</v>
+      </c>
+      <c r="I531" s="4">
+        <v>37629</v>
+      </c>
+      <c r="J531" s="72">
+        <v>0</v>
+      </c>
+      <c r="K531" s="72">
+        <v>0</v>
+      </c>
+      <c r="L531" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M531" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13">
+      <c r="A532" s="29">
+        <v>46101</v>
+      </c>
+      <c r="B532" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C532" s="75"/>
+      <c r="D532" s="75"/>
+      <c r="E532" s="76"/>
+      <c r="F532" s="71">
+        <v>0</v>
+      </c>
+      <c r="G532" s="71">
+        <v>9</v>
+      </c>
+      <c r="H532" s="71">
+        <v>9</v>
+      </c>
+      <c r="I532" s="30">
+        <v>37638</v>
+      </c>
+      <c r="J532" s="71">
+        <v>0</v>
+      </c>
+      <c r="K532" s="71">
+        <v>0</v>
+      </c>
+      <c r="L532" s="72">
+        <f t="shared" si="70"/>
+        <v>138882</v>
+      </c>
+      <c r="M532" s="72">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="335">
-    <mergeCell ref="B524:E524"/>
-    <mergeCell ref="B525:E525"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B489:E489"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B497:E497"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
+  <mergeCells count="342">
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B522:E522"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
     <mergeCell ref="B292:E292"/>
     <mergeCell ref="B458:E458"/>
     <mergeCell ref="B466:E466"/>
@@ -35183,284 +35722,41 @@
     <mergeCell ref="B404:E404"/>
     <mergeCell ref="B406:E406"/>
     <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B524:E524"/>
+    <mergeCell ref="B525:E525"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B489:E489"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B497:E497"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
     <mergeCell ref="B523:E523"/>
     <mergeCell ref="B521:E521"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B522:E522"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -35672,7 +35968,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="34">
         <f t="shared" ref="G3:G161" si="0">G4+F3</f>
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15">
@@ -35683,7 +35979,7 @@
       <c r="F4" s="45"/>
       <c r="G4" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I4" t="s">
         <v>216</v>
@@ -35701,7 +35997,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I5" t="s">
         <v>217</v>
@@ -35719,7 +36015,7 @@
       <c r="F6" s="45"/>
       <c r="G6" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I6" t="s">
         <v>218</v>
@@ -35737,14 +36033,14 @@
       <c r="F7" s="45"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I7" t="s">
         <v>219</v>
       </c>
       <c r="J7">
         <f>SUMIFS(F3:F30115,D3:D30115, "*JALモバイル*")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15">
@@ -35755,14 +36051,14 @@
       <c r="F8" s="45"/>
       <c r="G8" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>220</v>
       </c>
       <c r="J8">
         <f>SUMIFS(F3:F30115,D3:D30115, "*JAL Wellness &amp; Travel*")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15">
@@ -35773,7 +36069,7 @@
       <c r="F9" s="45"/>
       <c r="G9" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>221</v>
@@ -35791,7 +36087,7 @@
       <c r="F10" s="45"/>
       <c r="G10" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>222</v>
@@ -35809,14 +36105,14 @@
       <c r="F11" s="45"/>
       <c r="G11" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>223</v>
       </c>
       <c r="J11">
         <f>SUM(J4:J10)</f>
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15">
@@ -35827,7 +36123,7 @@
       <c r="F12" s="45"/>
       <c r="G12" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -35839,7 +36135,7 @@
       <c r="F13" s="45"/>
       <c r="G13" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -35851,7 +36147,7 @@
       <c r="F14" s="45"/>
       <c r="G14" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -35863,7 +36159,7 @@
       <c r="F15" s="45"/>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I15" s="31"/>
     </row>
@@ -35875,7 +36171,7 @@
       <c r="F16" s="45"/>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I16" s="31"/>
     </row>
@@ -35887,7 +36183,7 @@
       <c r="F17" s="45"/>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I17" s="31"/>
     </row>
@@ -35899,7 +36195,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I18" s="31"/>
     </row>
@@ -35911,7 +36207,7 @@
       <c r="F19" s="45"/>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I19" s="31"/>
     </row>
@@ -35923,7 +36219,7 @@
       <c r="F20" s="45"/>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I20" s="31"/>
     </row>
@@ -35935,7 +36231,7 @@
       <c r="F21" s="45"/>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I21" s="31"/>
     </row>
@@ -35947,7 +36243,7 @@
       <c r="F22" s="45"/>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I22" s="31"/>
     </row>
@@ -35959,7 +36255,7 @@
       <c r="F23" s="45"/>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I23" s="31"/>
     </row>
@@ -35971,7 +36267,7 @@
       <c r="F24" s="45"/>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I24" s="31"/>
     </row>
@@ -35983,7 +36279,7 @@
       <c r="F25" s="45"/>
       <c r="G25" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I25" s="31"/>
     </row>
@@ -35995,7 +36291,7 @@
       <c r="F26" s="45"/>
       <c r="G26" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I26" s="31"/>
     </row>
@@ -36007,7 +36303,7 @@
       <c r="F27" s="45"/>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I27" s="31"/>
     </row>
@@ -36019,7 +36315,7 @@
       <c r="F28" s="45"/>
       <c r="G28" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I28" s="31"/>
     </row>
@@ -36031,7 +36327,7 @@
       <c r="F29" s="45"/>
       <c r="G29" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I29" s="31"/>
     </row>
@@ -36043,7 +36339,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I30" s="31"/>
     </row>
@@ -36055,7 +36351,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I31" s="31"/>
     </row>
@@ -36067,7 +36363,7 @@
       <c r="F32" s="45"/>
       <c r="G32" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I32" s="31"/>
     </row>
@@ -36079,7 +36375,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I33" s="31"/>
     </row>
@@ -36091,7 +36387,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I34" s="31"/>
     </row>
@@ -36103,7 +36399,7 @@
       <c r="F35" s="45"/>
       <c r="G35" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I35" s="31"/>
     </row>
@@ -36115,7 +36411,7 @@
       <c r="F36" s="45"/>
       <c r="G36" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I36" s="31"/>
     </row>
@@ -36127,7 +36423,7 @@
       <c r="F37" s="45"/>
       <c r="G37" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I37" s="31"/>
     </row>
@@ -36139,7 +36435,7 @@
       <c r="F38" s="45"/>
       <c r="G38" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I38" s="31"/>
     </row>
@@ -36151,7 +36447,7 @@
       <c r="F39" s="45"/>
       <c r="G39" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I39" s="31"/>
     </row>
@@ -36163,7 +36459,7 @@
       <c r="F40" s="45"/>
       <c r="G40" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I40" s="31"/>
     </row>
@@ -36175,7 +36471,7 @@
       <c r="F41" s="45"/>
       <c r="G41" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I41" s="31"/>
     </row>
@@ -36187,7 +36483,7 @@
       <c r="F42" s="45"/>
       <c r="G42" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I42" s="31"/>
     </row>
@@ -36199,7 +36495,7 @@
       <c r="F43" s="45"/>
       <c r="G43" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I43" s="31"/>
     </row>
@@ -36211,7 +36507,7 @@
       <c r="F44" s="45"/>
       <c r="G44" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I44" s="31"/>
     </row>
@@ -36223,7 +36519,7 @@
       <c r="F45" s="45"/>
       <c r="G45" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I45" s="31"/>
     </row>
@@ -36235,7 +36531,7 @@
       <c r="F46" s="45"/>
       <c r="G46" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I46" s="31"/>
     </row>
@@ -36247,7 +36543,7 @@
       <c r="F47" s="45"/>
       <c r="G47" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I47" s="31"/>
     </row>
@@ -36259,7 +36555,7 @@
       <c r="F48" s="45"/>
       <c r="G48" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I48" s="31"/>
     </row>
@@ -36271,7 +36567,7 @@
       <c r="F49" s="45"/>
       <c r="G49" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I49" s="31"/>
     </row>
@@ -36283,31 +36579,51 @@
       <c r="F50" s="45"/>
       <c r="G50" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I50" s="31"/>
     </row>
-    <row r="51" spans="2:9" ht="15">
-      <c r="B51" s="44"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+    <row r="51" spans="2:9" ht="17.25">
+      <c r="B51" s="44">
+        <v>46099</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F51" s="45">
+        <v>1</v>
+      </c>
       <c r="G51" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I51" s="31"/>
     </row>
-    <row r="52" spans="2:9" ht="15">
-      <c r="B52" s="44"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
+    <row r="52" spans="2:9" ht="17.25">
+      <c r="B52" s="44">
+        <v>46096</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="F52" s="45">
+        <v>1</v>
+      </c>
       <c r="G52" s="34">
         <f t="shared" si="0"/>
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="I52" s="31"/>
     </row>
@@ -36316,13 +36632,13 @@
         <v>46093</v>
       </c>
       <c r="C53" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D53" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F53" s="45">
         <v>50</v>
@@ -36338,13 +36654,13 @@
         <v>46092</v>
       </c>
       <c r="C54" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D54" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F54" s="45">
         <v>10</v>
@@ -36360,13 +36676,13 @@
         <v>46083</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D55" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F55" s="45">
         <v>10</v>
@@ -36382,13 +36698,13 @@
         <v>46080</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D56" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F56" s="45">
         <v>35</v>
@@ -36404,13 +36720,13 @@
         <v>46077</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D57" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F57" s="45">
         <v>40</v>
@@ -36426,13 +36742,13 @@
         <v>46076</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D58" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F58" s="45">
         <v>15</v>
@@ -36448,13 +36764,13 @@
         <v>46074</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D59" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F59" s="45">
         <v>1</v>
@@ -36470,7 +36786,7 @@
         <v>46071</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D60" s="45" t="s">
         <v>219</v>
@@ -36492,13 +36808,13 @@
         <v>46068</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D61" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F61" s="45">
         <v>1</v>
@@ -36514,13 +36830,13 @@
         <v>46066</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D62" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F62" s="45">
         <v>30</v>
@@ -36536,13 +36852,13 @@
         <v>46065</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D63" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F63" s="45">
         <v>10</v>
@@ -36558,13 +36874,13 @@
         <v>46064</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D64" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F64" s="45">
         <v>10</v>
@@ -36580,13 +36896,13 @@
         <v>46064</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D65" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F65" s="45">
         <v>5</v>
@@ -36602,13 +36918,13 @@
         <v>46063</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D66" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F66" s="45">
         <v>45</v>
@@ -36624,13 +36940,13 @@
         <v>46062</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D67" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F67" s="45">
         <v>25</v>
@@ -36646,13 +36962,13 @@
         <v>46061</v>
       </c>
       <c r="C68" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D68" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F68" s="45">
         <v>30</v>
@@ -36668,13 +36984,13 @@
         <v>46059</v>
       </c>
       <c r="C69" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D69" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F69" s="45">
         <v>5</v>
@@ -36690,13 +37006,13 @@
         <v>46057</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D70" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F70" s="45">
         <v>5</v>
@@ -36712,13 +37028,13 @@
         <v>46056</v>
       </c>
       <c r="C71" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D71" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F71" s="45">
         <v>5</v>
@@ -36756,13 +37072,13 @@
         <v>46054</v>
       </c>
       <c r="C73" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D73" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F73" s="45">
         <v>5</v>
@@ -36778,13 +37094,13 @@
         <v>46052</v>
       </c>
       <c r="C74" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D74" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E74" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F74" s="45">
         <v>5</v>
@@ -36800,13 +37116,13 @@
         <v>46051</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D75" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F75" s="45">
         <v>5</v>
@@ -36822,13 +37138,13 @@
         <v>46048</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D76" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F76" s="45">
         <v>30</v>
@@ -36844,13 +37160,13 @@
         <v>46047</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D77" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E77" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F77" s="45">
         <v>2</v>
@@ -36866,13 +37182,13 @@
         <v>46044</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D78" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F78" s="45">
         <v>10</v>
@@ -36888,7 +37204,7 @@
         <v>46041</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D79" s="45" t="s">
         <v>219</v>
@@ -36910,13 +37226,13 @@
         <v>46040</v>
       </c>
       <c r="C80" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D80" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F80" s="45">
         <v>5</v>
@@ -36932,13 +37248,13 @@
         <v>46039</v>
       </c>
       <c r="C81" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D81" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F81" s="45">
         <v>5</v>
@@ -36954,13 +37270,13 @@
         <v>46037</v>
       </c>
       <c r="C82" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D82" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F82" s="45">
         <v>1</v>
@@ -36976,13 +37292,13 @@
         <v>46035</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D83" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F83" s="45">
         <v>40</v>
@@ -36998,13 +37314,13 @@
         <v>46034</v>
       </c>
       <c r="C84" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D84" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F84" s="45">
         <v>20</v>
@@ -37020,13 +37336,13 @@
         <v>46033</v>
       </c>
       <c r="C85" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D85" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F85" s="45">
         <v>30</v>
@@ -37037,7 +37353,7 @@
       </c>
       <c r="J85">
         <f>SUM(J4:J11)</f>
-        <v>2366</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="86" spans="2:10" ht="17.25">
@@ -37045,13 +37361,13 @@
         <v>46033</v>
       </c>
       <c r="C86" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D86" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F86" s="45">
         <v>40</v>
@@ -37066,13 +37382,13 @@
         <v>46032</v>
       </c>
       <c r="C87" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D87" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F87" s="45">
         <v>10</v>
@@ -37087,13 +37403,13 @@
         <v>46030</v>
       </c>
       <c r="C88" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D88" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E88" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F88" s="45">
         <v>5</v>
@@ -37108,13 +37424,13 @@
         <v>46016</v>
       </c>
       <c r="C89" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D89" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F89" s="45">
         <v>5</v>
@@ -37129,13 +37445,13 @@
         <v>46014</v>
       </c>
       <c r="C90" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D90" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E90" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F90" s="45">
         <v>5</v>
@@ -37150,13 +37466,13 @@
         <v>46012</v>
       </c>
       <c r="C91" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D91" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E91" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F91" s="45">
         <v>1</v>
@@ -37171,13 +37487,13 @@
         <v>46012</v>
       </c>
       <c r="C92" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D92" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F92" s="45">
         <v>5</v>
@@ -37192,13 +37508,13 @@
         <v>46011</v>
       </c>
       <c r="C93" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D93" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F93" s="45">
         <v>5</v>
@@ -37213,7 +37529,7 @@
         <v>46008</v>
       </c>
       <c r="C94" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D94" s="45" t="s">
         <v>219</v>
@@ -37234,13 +37550,13 @@
         <v>46006</v>
       </c>
       <c r="C95" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D95" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F95" s="45">
         <v>1</v>
@@ -37255,13 +37571,13 @@
         <v>46002</v>
       </c>
       <c r="C96" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D96" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" s="45">
         <v>10</v>
@@ -37276,13 +37592,13 @@
         <v>45996</v>
       </c>
       <c r="C97" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D97" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F97" s="45">
         <v>45</v>
@@ -37297,13 +37613,13 @@
         <v>45995</v>
       </c>
       <c r="C98" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D98" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F98" s="45">
         <v>5</v>
@@ -37318,13 +37634,13 @@
         <v>45994</v>
       </c>
       <c r="C99" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D99" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F99" s="45">
         <v>5</v>
@@ -37339,13 +37655,13 @@
         <v>45990</v>
       </c>
       <c r="C100" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D100" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E100" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F100" s="45">
         <v>5</v>
@@ -37360,13 +37676,13 @@
         <v>45989</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D101" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F101" s="45">
         <v>5</v>
@@ -37402,13 +37718,13 @@
         <v>45988</v>
       </c>
       <c r="C103" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D103" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F103" s="45">
         <v>5</v>
@@ -37423,13 +37739,13 @@
         <v>45987</v>
       </c>
       <c r="C104" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D104" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F104" s="45">
         <v>5</v>
@@ -37444,13 +37760,13 @@
         <v>45985</v>
       </c>
       <c r="C105" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D105" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F105" s="45">
         <v>5</v>
@@ -37465,13 +37781,13 @@
         <v>45983</v>
       </c>
       <c r="C106" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D106" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F106" s="45">
         <v>5</v>
@@ -37486,13 +37802,13 @@
         <v>45982</v>
       </c>
       <c r="C107" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D107" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E107" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F107" s="45">
         <v>1</v>
@@ -37507,7 +37823,7 @@
         <v>45978</v>
       </c>
       <c r="C108" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D108" s="45" t="s">
         <v>219</v>
@@ -37528,13 +37844,13 @@
         <v>45976</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D109" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F109" s="45">
         <v>1</v>
@@ -37549,13 +37865,13 @@
         <v>45972</v>
       </c>
       <c r="C110" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D110" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F110" s="45">
         <v>20</v>
@@ -37591,13 +37907,13 @@
         <v>45956</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D112" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F112" s="45">
         <v>5</v>
@@ -37612,13 +37928,13 @@
         <v>45955</v>
       </c>
       <c r="C113" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D113" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F113" s="45">
         <v>5</v>
@@ -37633,13 +37949,13 @@
         <v>45953</v>
       </c>
       <c r="C114" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D114" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F114" s="45">
         <v>5</v>
@@ -37654,13 +37970,13 @@
         <v>45952</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D115" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F115" s="45">
         <v>1</v>
@@ -37675,13 +37991,13 @@
         <v>45951</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D116" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F116" s="45">
         <v>10</v>
@@ -37696,7 +38012,7 @@
         <v>45947</v>
       </c>
       <c r="C117" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D117" s="45" t="s">
         <v>219</v>
@@ -37717,13 +38033,13 @@
         <v>45945</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D118" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E118" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F118" s="45">
         <v>1</v>
@@ -37738,13 +38054,13 @@
         <v>45943</v>
       </c>
       <c r="C119" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D119" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F119" s="45">
         <v>5</v>
@@ -37759,13 +38075,13 @@
         <v>45941</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D120" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E120" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F120" s="45">
         <v>15</v>
@@ -37780,13 +38096,13 @@
         <v>45941</v>
       </c>
       <c r="C121" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D121" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E121" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F121" s="45">
         <v>5</v>
@@ -37801,13 +38117,13 @@
         <v>45937</v>
       </c>
       <c r="C122" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D122" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E122" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F122" s="45">
         <v>35</v>
@@ -37822,13 +38138,13 @@
         <v>45936</v>
       </c>
       <c r="C123" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D123" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E123" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F123" s="45">
         <v>5</v>
@@ -37843,13 +38159,13 @@
         <v>45934</v>
       </c>
       <c r="C124" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D124" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E124" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F124" s="45">
         <v>5</v>
@@ -37864,13 +38180,13 @@
         <v>45930</v>
       </c>
       <c r="C125" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D125" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E125" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F125" s="45">
         <v>45</v>
@@ -37885,13 +38201,13 @@
         <v>45929</v>
       </c>
       <c r="C126" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D126" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E126" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F126" s="45">
         <v>45</v>
@@ -37906,13 +38222,13 @@
         <v>45928</v>
       </c>
       <c r="C127" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D127" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E127" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F127" s="45">
         <v>35</v>
@@ -37927,13 +38243,13 @@
         <v>45919</v>
       </c>
       <c r="C128" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D128" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E128" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F128" s="45">
         <v>5</v>
@@ -37948,13 +38264,13 @@
         <v>45917</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D129" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E129" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F129" s="45">
         <v>5</v>
@@ -37969,7 +38285,7 @@
         <v>45916</v>
       </c>
       <c r="C130" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D130" s="45" t="s">
         <v>219</v>
@@ -37990,13 +38306,13 @@
         <v>45915</v>
       </c>
       <c r="C131" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D131" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E131" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F131" s="45">
         <v>1</v>
@@ -38011,13 +38327,13 @@
         <v>45911</v>
       </c>
       <c r="C132" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D132" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E132" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F132" s="45">
         <v>5</v>
@@ -38032,13 +38348,13 @@
         <v>45905</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D133" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E133" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F133" s="45">
         <v>5</v>
@@ -38053,13 +38369,13 @@
         <v>45903</v>
       </c>
       <c r="C134" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D134" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E134" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F134" s="45">
         <v>5</v>
@@ -38074,13 +38390,13 @@
         <v>45893</v>
       </c>
       <c r="C135" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D135" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E135" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F135" s="45">
         <v>5</v>
@@ -38095,13 +38411,13 @@
         <v>45892</v>
       </c>
       <c r="C136" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D136" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E136" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F136" s="45">
         <v>5</v>
@@ -38116,7 +38432,7 @@
         <v>45888</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D137" s="45" t="s">
         <v>219</v>
@@ -38137,13 +38453,13 @@
         <v>45884</v>
       </c>
       <c r="C138" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D138" s="45" t="s">
         <v>220</v>
       </c>
       <c r="E138" s="45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F138" s="45">
         <v>1</v>
@@ -38158,13 +38474,13 @@
         <v>45877</v>
       </c>
       <c r="C139" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D139" s="45" t="s">
         <v>216</v>
       </c>
       <c r="E139" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F139" s="45">
         <v>10</v>
@@ -38179,13 +38495,13 @@
         <v>45874</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D140" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E140" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F140" s="33">
         <v>5</v>
@@ -38200,13 +38516,13 @@
         <v>45873</v>
       </c>
       <c r="C141" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D141" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E141" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F141" s="33">
         <v>5</v>
@@ -38221,13 +38537,13 @@
         <v>45867</v>
       </c>
       <c r="C142" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D142" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E142" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F142" s="33">
         <v>5</v>
@@ -38242,13 +38558,13 @@
         <v>45862</v>
       </c>
       <c r="C143" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D143" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E143" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F143" s="33">
         <v>5</v>
@@ -38263,13 +38579,13 @@
         <v>45838</v>
       </c>
       <c r="C144" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D144" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E144" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F144" s="33">
         <v>5</v>
@@ -38284,13 +38600,13 @@
         <v>45836</v>
       </c>
       <c r="C145" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D145" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E145" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F145" s="33">
         <v>5</v>
@@ -38305,13 +38621,13 @@
         <v>45789</v>
       </c>
       <c r="C146" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D146" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E146" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F146" s="33">
         <v>5</v>
@@ -38326,13 +38642,13 @@
         <v>45786</v>
       </c>
       <c r="C147" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D147" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E147" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F147" s="33">
         <v>5</v>
@@ -38347,13 +38663,13 @@
         <v>45729</v>
       </c>
       <c r="C148" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D148" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E148" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F148" s="33">
         <v>10</v>
@@ -38368,13 +38684,13 @@
         <v>45684</v>
       </c>
       <c r="C149" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D149" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E149" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F149" s="33">
         <v>5</v>
@@ -38389,13 +38705,13 @@
         <v>45682</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D150" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E150" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F150" s="33">
         <v>5</v>
@@ -38410,13 +38726,13 @@
         <v>45652</v>
       </c>
       <c r="C151" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D151" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E151" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F151" s="33">
         <v>5</v>
@@ -38431,13 +38747,13 @@
         <v>45649</v>
       </c>
       <c r="C152" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D152" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E152" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F152" s="33">
         <v>5</v>
@@ -38452,13 +38768,13 @@
         <v>45648</v>
       </c>
       <c r="C153" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D153" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E153" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F153" s="33">
         <v>5</v>
@@ -38473,13 +38789,13 @@
         <v>45614</v>
       </c>
       <c r="C154" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D154" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E154" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F154" s="33">
         <v>5</v>
@@ -38494,13 +38810,13 @@
         <v>45613</v>
       </c>
       <c r="C155" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D155" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E155" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F155" s="33">
         <v>5</v>
@@ -38515,13 +38831,13 @@
         <v>45592</v>
       </c>
       <c r="C156" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D156" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E156" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F156" s="33">
         <v>5</v>
@@ -38536,13 +38852,13 @@
         <v>45591</v>
       </c>
       <c r="C157" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D157" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E157" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F157" s="33">
         <v>5</v>
@@ -38557,13 +38873,13 @@
         <v>45514</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D158" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E158" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F158" s="33">
         <v>5</v>
@@ -38578,13 +38894,13 @@
         <v>45513</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>216</v>
       </c>
       <c r="E159" s="33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F159" s="33">
         <v>5</v>
@@ -38599,7 +38915,7 @@
         <v>45335</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D160" s="33" t="s">
         <v>233</v>
@@ -38620,7 +38936,7 @@
         <v>45334</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D161" s="33" t="s">
         <v>233</v>
@@ -38641,7 +38957,7 @@
         <v>45291</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D162" s="33" t="s">
         <v>233</v>
@@ -38662,13 +38978,13 @@
         <v>45291</v>
       </c>
       <c r="C163" s="68" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D163" s="68" t="s">
         <v>216</v>
       </c>
       <c r="E163" s="68" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F163" s="68">
         <v>10</v>
@@ -44350,7 +44666,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -44385,7 +44701,7 @@
       </c>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -44420,7 +44736,7 @@
       </c>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -44455,7 +44771,7 @@
       </c>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -44490,7 +44806,7 @@
       </c>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -44525,7 +44841,7 @@
       </c>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -44560,7 +44876,7 @@
       </c>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -44595,7 +44911,7 @@
       </c>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -44630,7 +44946,7 @@
       </c>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -44665,7 +44981,7 @@
       </c>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -45980,7 +46296,7 @@
       <c r="C211" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D211" s="12"/>
+      <c r="D211" s="81"/>
       <c r="E211" s="12" t="s">
         <v>248</v>
       </c>
@@ -46009,7 +46325,7 @@
       <c r="C212" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D212" s="12"/>
+      <c r="D212" s="81"/>
       <c r="E212" s="12" t="s">
         <v>249</v>
       </c>
@@ -46028,37 +46344,69 @@
       </c>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" ht="15.75">
       <c r="A213" s="14">
         <v>221</v>
       </c>
-      <c r="B213" s="42"/>
-      <c r="C213" s="12"/>
-      <c r="D213" s="12"/>
-      <c r="E213" s="12"/>
-      <c r="F213" s="13"/>
-      <c r="G213" s="12"/>
-      <c r="H213" s="13"/>
+      <c r="B213" s="42">
+        <v>46104</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="F213" s="13">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="G213" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="H213" s="13">
+        <v>0.65625</v>
+      </c>
       <c r="I213" s="26"/>
       <c r="J213" s="15"/>
-      <c r="K213" s="22"/>
+      <c r="K213" s="22">
+        <v>0</v>
+      </c>
       <c r="L213" s="15"/>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" ht="15.75">
       <c r="A214" s="14">
         <v>222</v>
       </c>
-      <c r="B214" s="42"/>
-      <c r="C214" s="12"/>
-      <c r="D214" s="12"/>
-      <c r="E214" s="12"/>
-      <c r="F214" s="13"/>
-      <c r="G214" s="12"/>
-      <c r="H214" s="13"/>
+      <c r="B214" s="42">
+        <v>46105</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="E214" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F214" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="G214" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="H214" s="13">
+        <v>0.75</v>
+      </c>
       <c r="I214" s="26"/>
       <c r="J214" s="15"/>
-      <c r="K214" s="22"/>
+      <c r="K214" s="22">
+        <v>0</v>
+      </c>
       <c r="L214" s="15"/>
       <c r="M214" s="15"/>
     </row>
@@ -47016,7 +47364,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -47025,11 +47373,11 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1035</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -47038,16 +47386,16 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1290.6125603864734</v>
+        <v>1278.2622009569377</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -47125,7 +47473,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -47177,7 +47525,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -47281,7 +47629,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -47515,7 +47863,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -47569,7 +47917,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -47704,7 +48052,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD256AE2-0CF0-4243-AC90-B5641DE3AC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC3AB958-AB4A-4403-AF36-6DCCD004DD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2682" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="371">
   <si>
     <t>日付</t>
   </si>
@@ -814,16 +814,16 @@
     <t>合計</t>
   </si>
   <si>
+    <t>航空</t>
+  </si>
+  <si>
+    <t>JAL国内線利用</t>
+  </si>
+  <si>
     <t>ライフスタイルサービス</t>
   </si>
   <si>
     <t>JALマイレージパーク利用</t>
-  </si>
-  <si>
-    <t>航空</t>
-  </si>
-  <si>
-    <t>JAL国内線利用</t>
   </si>
   <si>
     <t>JAL Wellness &amp; Travel利用</t>
@@ -2328,10 +2328,10 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5944</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>93</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8582,6 +8582,12 @@
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="191"/>
+                <c:pt idx="56">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46139</c:v>
+                </c:pt>
                 <c:pt idx="58">
                   <c:v>46134</c:v>
                 </c:pt>
@@ -8985,178 +8991,178 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="191"/>
                 <c:pt idx="0">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1551</c:v>
+                  <c:v>1611</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1551</c:v>
+                  <c:v>1571</c:v>
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1551</c:v>
@@ -10009,7 +10015,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1035</c:v>
+                  <c:v>1095</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>70</c:v>
@@ -14600,11 +14606,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <dateGroupItem year="2026" dateTimeGrouping="year"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="11">
       <filters blank="1"/>
     </filterColumn>
@@ -14915,7 +14916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O598"/>
+  <dimension ref="A1:O604"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15483,7 +15484,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>5944</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15533,7 +15534,7 @@
       </c>
       <c r="O17">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＪＭＢアプリ*")</f>
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1">
@@ -15725,7 +15726,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>154445</v>
+        <v>154503</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -38175,31 +38176,31 @@
       </c>
     </row>
     <row r="598" spans="1:13">
-      <c r="A598" s="29">
+      <c r="A598" s="27">
         <v>46139</v>
       </c>
-      <c r="B598" s="78" t="s">
+      <c r="B598" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C598" s="78"/>
-      <c r="D598" s="78"/>
-      <c r="E598" s="79"/>
-      <c r="F598" s="75">
-        <v>0</v>
-      </c>
-      <c r="G598" s="75">
+      <c r="C598" s="76"/>
+      <c r="D598" s="76"/>
+      <c r="E598" s="77"/>
+      <c r="F598" s="74">
+        <v>0</v>
+      </c>
+      <c r="G598" s="74">
         <v>10</v>
       </c>
-      <c r="H598" s="75">
+      <c r="H598" s="74">
         <v>10</v>
       </c>
-      <c r="I598" s="30">
-        <v>60387</v>
-      </c>
-      <c r="J598" s="75">
-        <v>0</v>
-      </c>
-      <c r="K598" s="75">
+      <c r="I598" s="4">
+        <v>62946</v>
+      </c>
+      <c r="J598" s="74">
+        <v>0</v>
+      </c>
+      <c r="K598" s="74">
         <v>0</v>
       </c>
       <c r="L598" s="74">
@@ -38211,33 +38212,578 @@
         <v>186</v>
       </c>
     </row>
+    <row r="599" spans="1:13">
+      <c r="A599" s="27">
+        <v>46140</v>
+      </c>
+      <c r="B599" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C599" s="76"/>
+      <c r="D599" s="76"/>
+      <c r="E599" s="77"/>
+      <c r="F599" s="74">
+        <v>0</v>
+      </c>
+      <c r="G599" s="74">
+        <v>17</v>
+      </c>
+      <c r="H599" s="74">
+        <v>17</v>
+      </c>
+      <c r="I599" s="4">
+        <v>62963</v>
+      </c>
+      <c r="J599" s="74">
+        <v>0</v>
+      </c>
+      <c r="K599" s="74">
+        <v>0</v>
+      </c>
+      <c r="L599" s="74">
+        <f t="shared" ref="L599:L604" si="80">J599+L598</f>
+        <v>151768</v>
+      </c>
+      <c r="M599" s="74">
+        <f t="shared" ref="M599:M604" si="81">K599+M598</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13">
+      <c r="A600" s="27">
+        <v>46141</v>
+      </c>
+      <c r="B600" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C600" s="76"/>
+      <c r="D600" s="76"/>
+      <c r="E600" s="77"/>
+      <c r="F600" s="74">
+        <v>0</v>
+      </c>
+      <c r="G600" s="74">
+        <v>9</v>
+      </c>
+      <c r="H600" s="74">
+        <v>9</v>
+      </c>
+      <c r="I600" s="4">
+        <v>62972</v>
+      </c>
+      <c r="J600" s="74">
+        <v>0</v>
+      </c>
+      <c r="K600" s="74">
+        <v>0</v>
+      </c>
+      <c r="L600" s="74">
+        <f t="shared" si="80"/>
+        <v>151768</v>
+      </c>
+      <c r="M600" s="74">
+        <f t="shared" si="81"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13">
+      <c r="A601" s="27">
+        <v>46142</v>
+      </c>
+      <c r="B601" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C601" s="76"/>
+      <c r="D601" s="76"/>
+      <c r="E601" s="77"/>
+      <c r="F601" s="74">
+        <v>0</v>
+      </c>
+      <c r="G601" s="74">
+        <v>10</v>
+      </c>
+      <c r="H601" s="74">
+        <v>10</v>
+      </c>
+      <c r="I601" s="4">
+        <v>62982</v>
+      </c>
+      <c r="J601" s="74">
+        <v>0</v>
+      </c>
+      <c r="K601" s="74">
+        <v>0</v>
+      </c>
+      <c r="L601" s="74">
+        <f t="shared" si="80"/>
+        <v>151768</v>
+      </c>
+      <c r="M601" s="74">
+        <f t="shared" si="81"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13">
+      <c r="A602" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B602" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C602" s="76"/>
+      <c r="D602" s="76"/>
+      <c r="E602" s="77"/>
+      <c r="F602" s="74">
+        <v>0</v>
+      </c>
+      <c r="G602" s="74">
+        <v>1</v>
+      </c>
+      <c r="H602" s="74">
+        <v>1</v>
+      </c>
+      <c r="I602" s="4">
+        <v>62983</v>
+      </c>
+      <c r="J602" s="74">
+        <v>0</v>
+      </c>
+      <c r="K602" s="74">
+        <v>0</v>
+      </c>
+      <c r="L602" s="74">
+        <f t="shared" si="80"/>
+        <v>151768</v>
+      </c>
+      <c r="M602" s="74">
+        <f t="shared" si="81"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13">
+      <c r="A603" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B603" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C603" s="76"/>
+      <c r="D603" s="76"/>
+      <c r="E603" s="77"/>
+      <c r="F603" s="74">
+        <v>0</v>
+      </c>
+      <c r="G603" s="74">
+        <v>20</v>
+      </c>
+      <c r="H603" s="74">
+        <v>20</v>
+      </c>
+      <c r="I603" s="4">
+        <v>63003</v>
+      </c>
+      <c r="J603" s="74">
+        <v>0</v>
+      </c>
+      <c r="K603" s="74">
+        <v>0</v>
+      </c>
+      <c r="L603" s="74">
+        <f t="shared" si="80"/>
+        <v>151768</v>
+      </c>
+      <c r="M603" s="74">
+        <f t="shared" si="81"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13">
+      <c r="A604" s="29">
+        <v>46143</v>
+      </c>
+      <c r="B604" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="C604" s="78"/>
+      <c r="D604" s="78"/>
+      <c r="E604" s="79"/>
+      <c r="F604" s="75">
+        <v>0</v>
+      </c>
+      <c r="G604" s="75">
+        <v>1</v>
+      </c>
+      <c r="H604" s="75">
+        <v>1</v>
+      </c>
+      <c r="I604" s="30">
+        <v>63004</v>
+      </c>
+      <c r="J604" s="75">
+        <v>0</v>
+      </c>
+      <c r="K604" s="75">
+        <v>0</v>
+      </c>
+      <c r="L604" s="74">
+        <f t="shared" si="80"/>
+        <v>151768</v>
+      </c>
+      <c r="M604" s="74">
+        <f t="shared" si="81"/>
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="389">
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B582:E582"/>
-    <mergeCell ref="B583:E583"/>
-    <mergeCell ref="B584:E584"/>
-    <mergeCell ref="B585:E585"/>
-    <mergeCell ref="B586:E586"/>
-    <mergeCell ref="B587:E587"/>
-    <mergeCell ref="B588:E588"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B590:E590"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B550:E550"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B554:E554"/>
-    <mergeCell ref="B557:E557"/>
+  <mergeCells count="395">
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B581:E581"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B545:E545"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B524:E524"/>
+    <mergeCell ref="B525:E525"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B489:E489"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B497:E497"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B523:E523"/>
+    <mergeCell ref="B521:E521"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
     <mergeCell ref="B526:E526"/>
     <mergeCell ref="B527:E527"/>
     <mergeCell ref="B528:E528"/>
@@ -38262,347 +38808,30 @@
     <mergeCell ref="B459:E459"/>
     <mergeCell ref="B460:E460"/>
     <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B524:E524"/>
-    <mergeCell ref="B525:E525"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B489:E489"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B497:E497"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B523:E523"/>
-    <mergeCell ref="B521:E521"/>
-    <mergeCell ref="B545:E545"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B581:E581"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B550:E550"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B554:E554"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B582:E582"/>
+    <mergeCell ref="B583:E583"/>
+    <mergeCell ref="B584:E584"/>
+    <mergeCell ref="B585:E585"/>
+    <mergeCell ref="B586:E586"/>
+    <mergeCell ref="B587:E587"/>
+    <mergeCell ref="B588:E588"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B590:E590"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -38833,7 +39062,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="34">
         <f t="shared" ref="G3:G189" si="0">G4+F3</f>
-        <v>1551</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15">
@@ -38844,14 +39073,14 @@
       <c r="F4" s="45"/>
       <c r="G4" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I4" t="s">
         <v>246</v>
       </c>
       <c r="J4">
         <f>SUMIFS(F3:F30143,D3:D30143, "*JAL国内線*")</f>
-        <v>1035</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15">
@@ -38862,7 +39091,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -38880,7 +39109,7 @@
       <c r="F6" s="45"/>
       <c r="G6" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I6" t="s">
         <v>248</v>
@@ -38898,7 +39127,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I7" t="s">
         <v>249</v>
@@ -38916,7 +39145,7 @@
       <c r="F8" s="45"/>
       <c r="G8" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>250</v>
@@ -38934,7 +39163,7 @@
       <c r="F9" s="45"/>
       <c r="G9" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>251</v>
@@ -38952,7 +39181,7 @@
       <c r="F10" s="45"/>
       <c r="G10" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>252</v>
@@ -38970,14 +39199,14 @@
       <c r="F11" s="45"/>
       <c r="G11" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>253</v>
       </c>
       <c r="J11">
         <f>SUM(J4:J10)</f>
-        <v>1551</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15">
@@ -38988,7 +39217,7 @@
       <c r="F12" s="45"/>
       <c r="G12" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -39000,7 +39229,7 @@
       <c r="F13" s="45"/>
       <c r="G13" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -39012,7 +39241,7 @@
       <c r="F14" s="45"/>
       <c r="G14" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -39024,7 +39253,7 @@
       <c r="F15" s="45"/>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I15" s="31"/>
     </row>
@@ -39036,7 +39265,7 @@
       <c r="F16" s="45"/>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I16" s="31"/>
     </row>
@@ -39048,7 +39277,7 @@
       <c r="F17" s="45"/>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I17" s="31"/>
     </row>
@@ -39060,7 +39289,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I18" s="31"/>
     </row>
@@ -39072,7 +39301,7 @@
       <c r="F19" s="45"/>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I19" s="31"/>
     </row>
@@ -39084,7 +39313,7 @@
       <c r="F20" s="45"/>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I20" s="31"/>
     </row>
@@ -39096,7 +39325,7 @@
       <c r="F21" s="45"/>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I21" s="31"/>
     </row>
@@ -39108,7 +39337,7 @@
       <c r="F22" s="45"/>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I22" s="31"/>
     </row>
@@ -39120,7 +39349,7 @@
       <c r="F23" s="45"/>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I23" s="31"/>
     </row>
@@ -39132,7 +39361,7 @@
       <c r="F24" s="45"/>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I24" s="31"/>
     </row>
@@ -39144,7 +39373,7 @@
       <c r="F25" s="45"/>
       <c r="G25" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I25" s="31"/>
     </row>
@@ -39156,7 +39385,7 @@
       <c r="F26" s="45"/>
       <c r="G26" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I26" s="31"/>
     </row>
@@ -39168,7 +39397,7 @@
       <c r="F27" s="45"/>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I27" s="31"/>
     </row>
@@ -39180,7 +39409,7 @@
       <c r="F28" s="45"/>
       <c r="G28" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I28" s="31"/>
     </row>
@@ -39192,7 +39421,7 @@
       <c r="F29" s="45"/>
       <c r="G29" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I29" s="31"/>
     </row>
@@ -39204,7 +39433,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I30" s="31"/>
     </row>
@@ -39216,7 +39445,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I31" s="31"/>
     </row>
@@ -39228,7 +39457,7 @@
       <c r="F32" s="45"/>
       <c r="G32" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I32" s="31"/>
     </row>
@@ -39240,7 +39469,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I33" s="31"/>
     </row>
@@ -39252,7 +39481,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I34" s="31"/>
     </row>
@@ -39264,7 +39493,7 @@
       <c r="F35" s="45"/>
       <c r="G35" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I35" s="31"/>
     </row>
@@ -39276,7 +39505,7 @@
       <c r="F36" s="45"/>
       <c r="G36" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I36" s="31"/>
     </row>
@@ -39288,7 +39517,7 @@
       <c r="F37" s="45"/>
       <c r="G37" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I37" s="31"/>
     </row>
@@ -39300,7 +39529,7 @@
       <c r="F38" s="45"/>
       <c r="G38" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I38" s="31"/>
     </row>
@@ -39312,7 +39541,7 @@
       <c r="F39" s="45"/>
       <c r="G39" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I39" s="31"/>
     </row>
@@ -39324,7 +39553,7 @@
       <c r="F40" s="45"/>
       <c r="G40" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I40" s="31"/>
     </row>
@@ -39336,7 +39565,7 @@
       <c r="F41" s="45"/>
       <c r="G41" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I41" s="31"/>
     </row>
@@ -39348,7 +39577,7 @@
       <c r="F42" s="45"/>
       <c r="G42" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I42" s="31"/>
     </row>
@@ -39360,7 +39589,7 @@
       <c r="F43" s="45"/>
       <c r="G43" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I43" s="31"/>
     </row>
@@ -39372,7 +39601,7 @@
       <c r="F44" s="45"/>
       <c r="G44" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I44" s="31"/>
     </row>
@@ -39384,7 +39613,7 @@
       <c r="F45" s="45"/>
       <c r="G45" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I45" s="31"/>
     </row>
@@ -39396,7 +39625,7 @@
       <c r="F46" s="45"/>
       <c r="G46" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I46" s="31"/>
     </row>
@@ -39408,7 +39637,7 @@
       <c r="F47" s="45"/>
       <c r="G47" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I47" s="31"/>
     </row>
@@ -39420,7 +39649,7 @@
       <c r="F48" s="45"/>
       <c r="G48" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I48" s="31"/>
     </row>
@@ -39432,7 +39661,7 @@
       <c r="F49" s="45"/>
       <c r="G49" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I49" s="31"/>
     </row>
@@ -39444,7 +39673,7 @@
       <c r="F50" s="45"/>
       <c r="G50" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I50" s="31"/>
     </row>
@@ -39456,7 +39685,7 @@
       <c r="F51" s="45"/>
       <c r="G51" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I51" s="31"/>
     </row>
@@ -39468,7 +39697,7 @@
       <c r="F52" s="45"/>
       <c r="G52" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I52" s="31"/>
     </row>
@@ -39480,7 +39709,7 @@
       <c r="F53" s="45"/>
       <c r="G53" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I53" s="31"/>
     </row>
@@ -39492,7 +39721,7 @@
       <c r="F54" s="45"/>
       <c r="G54" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I54" s="31"/>
     </row>
@@ -39504,7 +39733,7 @@
       <c r="F55" s="45"/>
       <c r="G55" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I55" s="31"/>
     </row>
@@ -39516,7 +39745,7 @@
       <c r="F56" s="45"/>
       <c r="G56" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I56" s="31"/>
     </row>
@@ -39528,7 +39757,7 @@
       <c r="F57" s="45"/>
       <c r="G57" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I57" s="31"/>
     </row>
@@ -39540,31 +39769,51 @@
       <c r="F58" s="45"/>
       <c r="G58" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I58" s="31"/>
     </row>
-    <row r="59" spans="2:9" ht="15">
-      <c r="B59" s="44"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
+    <row r="59" spans="2:9" ht="17.25">
+      <c r="B59" s="44">
+        <v>46140</v>
+      </c>
+      <c r="C59" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="D59" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="F59" s="45">
+        <v>40</v>
+      </c>
       <c r="G59" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1611</v>
       </c>
       <c r="I59" s="31"/>
     </row>
-    <row r="60" spans="2:9" ht="15">
-      <c r="B60" s="44"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="45"/>
-      <c r="F60" s="45"/>
+    <row r="60" spans="2:9" ht="17.25">
+      <c r="B60" s="44">
+        <v>46139</v>
+      </c>
+      <c r="C60" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="D60" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="F60" s="45">
+        <v>20</v>
+      </c>
       <c r="G60" s="34">
         <f t="shared" si="0"/>
-        <v>1551</v>
+        <v>1571</v>
       </c>
       <c r="I60" s="31"/>
     </row>
@@ -39573,13 +39822,13 @@
         <v>46134</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D61" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F61" s="45">
         <v>1</v>
@@ -39595,13 +39844,13 @@
         <v>46131</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D62" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F62" s="45">
         <v>1</v>
@@ -39617,13 +39866,13 @@
         <v>46130</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D63" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F63" s="45">
         <v>5</v>
@@ -39639,7 +39888,7 @@
         <v>46129</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D64" s="45" t="s">
         <v>249</v>
@@ -39661,13 +39910,13 @@
         <v>46129</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D65" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F65" s="45">
         <v>5</v>
@@ -39683,7 +39932,7 @@
         <v>46127</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D66" s="45" t="s">
         <v>250</v>
@@ -39705,13 +39954,13 @@
         <v>46127</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D67" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F67" s="45">
         <v>40</v>
@@ -39727,13 +39976,13 @@
         <v>46125</v>
       </c>
       <c r="C68" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D68" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F68" s="45">
         <v>5</v>
@@ -39749,7 +39998,7 @@
         <v>46124</v>
       </c>
       <c r="C69" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D69" s="45" t="s">
         <v>248</v>
@@ -39771,13 +40020,13 @@
         <v>46121</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D70" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F70" s="45">
         <v>5</v>
@@ -39793,13 +40042,13 @@
         <v>46113</v>
       </c>
       <c r="C71" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D71" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F71" s="45">
         <v>5</v>
@@ -39815,13 +40064,13 @@
         <v>46111</v>
       </c>
       <c r="C72" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D72" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F72" s="45">
         <v>5</v>
@@ -39837,13 +40086,13 @@
         <v>46110</v>
       </c>
       <c r="C73" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D73" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F73" s="45">
         <v>1</v>
@@ -39881,13 +40130,13 @@
         <v>46107</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D75" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F75" s="45">
         <v>5</v>
@@ -39903,13 +40152,13 @@
         <v>46106</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D76" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F76" s="45">
         <v>5</v>
@@ -39947,13 +40196,13 @@
         <v>46102</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D78" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F78" s="45">
         <v>1</v>
@@ -39969,7 +40218,7 @@
         <v>46099</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D79" s="45" t="s">
         <v>249</v>
@@ -39991,7 +40240,7 @@
         <v>46096</v>
       </c>
       <c r="C80" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D80" s="45" t="s">
         <v>250</v>
@@ -40013,13 +40262,13 @@
         <v>46093</v>
       </c>
       <c r="C81" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D81" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F81" s="45">
         <v>50</v>
@@ -40035,7 +40284,7 @@
         <v>46092</v>
       </c>
       <c r="C82" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D82" s="45" t="s">
         <v>248</v>
@@ -40057,13 +40306,13 @@
         <v>46083</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D83" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F83" s="45">
         <v>10</v>
@@ -40079,13 +40328,13 @@
         <v>46080</v>
       </c>
       <c r="C84" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D84" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F84" s="45">
         <v>35</v>
@@ -40101,13 +40350,13 @@
         <v>46077</v>
       </c>
       <c r="C85" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D85" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F85" s="45">
         <v>40</v>
@@ -40123,13 +40372,13 @@
         <v>46076</v>
       </c>
       <c r="C86" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D86" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F86" s="45">
         <v>15</v>
@@ -40145,13 +40394,13 @@
         <v>46074</v>
       </c>
       <c r="C87" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D87" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F87" s="45">
         <v>1</v>
@@ -40167,7 +40416,7 @@
         <v>46071</v>
       </c>
       <c r="C88" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D88" s="45" t="s">
         <v>249</v>
@@ -40189,7 +40438,7 @@
         <v>46068</v>
       </c>
       <c r="C89" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D89" s="45" t="s">
         <v>250</v>
@@ -40211,13 +40460,13 @@
         <v>46066</v>
       </c>
       <c r="C90" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D90" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E90" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F90" s="45">
         <v>30</v>
@@ -40233,13 +40482,13 @@
         <v>46065</v>
       </c>
       <c r="C91" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D91" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E91" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F91" s="45">
         <v>10</v>
@@ -40255,7 +40504,7 @@
         <v>46064</v>
       </c>
       <c r="C92" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D92" s="45" t="s">
         <v>248</v>
@@ -40277,13 +40526,13 @@
         <v>46064</v>
       </c>
       <c r="C93" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D93" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F93" s="45">
         <v>5</v>
@@ -40299,13 +40548,13 @@
         <v>46063</v>
       </c>
       <c r="C94" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D94" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F94" s="45">
         <v>45</v>
@@ -40321,13 +40570,13 @@
         <v>46062</v>
       </c>
       <c r="C95" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D95" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F95" s="45">
         <v>25</v>
@@ -40343,13 +40592,13 @@
         <v>46061</v>
       </c>
       <c r="C96" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D96" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F96" s="45">
         <v>30</v>
@@ -40365,13 +40614,13 @@
         <v>46059</v>
       </c>
       <c r="C97" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D97" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F97" s="45">
         <v>5</v>
@@ -40387,13 +40636,13 @@
         <v>46057</v>
       </c>
       <c r="C98" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D98" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F98" s="45">
         <v>5</v>
@@ -40409,13 +40658,13 @@
         <v>46056</v>
       </c>
       <c r="C99" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D99" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F99" s="45">
         <v>5</v>
@@ -40453,13 +40702,13 @@
         <v>46054</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D101" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F101" s="45">
         <v>5</v>
@@ -40475,13 +40724,13 @@
         <v>46052</v>
       </c>
       <c r="C102" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D102" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F102" s="45">
         <v>5</v>
@@ -40497,13 +40746,13 @@
         <v>46051</v>
       </c>
       <c r="C103" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D103" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F103" s="45">
         <v>5</v>
@@ -40519,13 +40768,13 @@
         <v>46048</v>
       </c>
       <c r="C104" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D104" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F104" s="45">
         <v>30</v>
@@ -40541,13 +40790,13 @@
         <v>46047</v>
       </c>
       <c r="C105" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D105" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F105" s="45">
         <v>2</v>
@@ -40563,13 +40812,13 @@
         <v>46044</v>
       </c>
       <c r="C106" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D106" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F106" s="45">
         <v>10</v>
@@ -40585,7 +40834,7 @@
         <v>46041</v>
       </c>
       <c r="C107" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D107" s="45" t="s">
         <v>249</v>
@@ -40607,13 +40856,13 @@
         <v>46040</v>
       </c>
       <c r="C108" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D108" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F108" s="45">
         <v>5</v>
@@ -40629,13 +40878,13 @@
         <v>46039</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D109" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F109" s="45">
         <v>5</v>
@@ -40651,7 +40900,7 @@
         <v>46037</v>
       </c>
       <c r="C110" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D110" s="45" t="s">
         <v>250</v>
@@ -40673,13 +40922,13 @@
         <v>46035</v>
       </c>
       <c r="C111" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D111" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F111" s="45">
         <v>40</v>
@@ -40695,13 +40944,13 @@
         <v>46034</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D112" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F112" s="45">
         <v>20</v>
@@ -40717,7 +40966,7 @@
         <v>46033</v>
       </c>
       <c r="C113" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D113" s="45" t="s">
         <v>248</v>
@@ -40734,7 +40983,7 @@
       </c>
       <c r="J113">
         <f>SUM(J4:J11)</f>
-        <v>3102</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="17.25">
@@ -40742,13 +40991,13 @@
         <v>46033</v>
       </c>
       <c r="C114" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D114" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F114" s="45">
         <v>40</v>
@@ -40763,13 +41012,13 @@
         <v>46032</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D115" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F115" s="45">
         <v>10</v>
@@ -40784,13 +41033,13 @@
         <v>46030</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D116" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F116" s="45">
         <v>5</v>
@@ -40805,13 +41054,13 @@
         <v>46016</v>
       </c>
       <c r="C117" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D117" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E117" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F117" s="45">
         <v>5</v>
@@ -40826,13 +41075,13 @@
         <v>46014</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D118" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E118" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F118" s="45">
         <v>5</v>
@@ -40847,13 +41096,13 @@
         <v>46012</v>
       </c>
       <c r="C119" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D119" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F119" s="45">
         <v>1</v>
@@ -40868,13 +41117,13 @@
         <v>46012</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D120" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E120" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F120" s="45">
         <v>5</v>
@@ -40889,13 +41138,13 @@
         <v>46011</v>
       </c>
       <c r="C121" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D121" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E121" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F121" s="45">
         <v>5</v>
@@ -40910,7 +41159,7 @@
         <v>46008</v>
       </c>
       <c r="C122" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D122" s="45" t="s">
         <v>249</v>
@@ -40931,7 +41180,7 @@
         <v>46006</v>
       </c>
       <c r="C123" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D123" s="45" t="s">
         <v>250</v>
@@ -40952,7 +41201,7 @@
         <v>46002</v>
       </c>
       <c r="C124" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D124" s="45" t="s">
         <v>248</v>
@@ -40973,13 +41222,13 @@
         <v>45996</v>
       </c>
       <c r="C125" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D125" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E125" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F125" s="45">
         <v>45</v>
@@ -40994,13 +41243,13 @@
         <v>45995</v>
       </c>
       <c r="C126" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D126" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E126" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F126" s="45">
         <v>5</v>
@@ -41015,13 +41264,13 @@
         <v>45994</v>
       </c>
       <c r="C127" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D127" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E127" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F127" s="45">
         <v>5</v>
@@ -41036,13 +41285,13 @@
         <v>45990</v>
       </c>
       <c r="C128" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D128" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E128" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F128" s="45">
         <v>5</v>
@@ -41057,13 +41306,13 @@
         <v>45989</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D129" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E129" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F129" s="45">
         <v>5</v>
@@ -41099,13 +41348,13 @@
         <v>45988</v>
       </c>
       <c r="C131" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D131" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E131" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F131" s="45">
         <v>5</v>
@@ -41120,13 +41369,13 @@
         <v>45987</v>
       </c>
       <c r="C132" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D132" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E132" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F132" s="45">
         <v>5</v>
@@ -41141,13 +41390,13 @@
         <v>45985</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D133" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E133" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F133" s="45">
         <v>5</v>
@@ -41162,13 +41411,13 @@
         <v>45983</v>
       </c>
       <c r="C134" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D134" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E134" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F134" s="45">
         <v>5</v>
@@ -41183,13 +41432,13 @@
         <v>45982</v>
       </c>
       <c r="C135" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D135" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E135" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F135" s="45">
         <v>1</v>
@@ -41204,7 +41453,7 @@
         <v>45978</v>
       </c>
       <c r="C136" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D136" s="45" t="s">
         <v>249</v>
@@ -41225,7 +41474,7 @@
         <v>45976</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D137" s="45" t="s">
         <v>250</v>
@@ -41246,7 +41495,7 @@
         <v>45972</v>
       </c>
       <c r="C138" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D138" s="45" t="s">
         <v>248</v>
@@ -41288,13 +41537,13 @@
         <v>45956</v>
       </c>
       <c r="C140" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D140" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E140" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F140" s="45">
         <v>5</v>
@@ -41309,13 +41558,13 @@
         <v>45955</v>
       </c>
       <c r="C141" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D141" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E141" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F141" s="45">
         <v>5</v>
@@ -41330,13 +41579,13 @@
         <v>45953</v>
       </c>
       <c r="C142" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D142" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E142" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F142" s="45">
         <v>5</v>
@@ -41351,13 +41600,13 @@
         <v>45952</v>
       </c>
       <c r="C143" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D143" s="45" t="s">
         <v>251</v>
       </c>
       <c r="E143" s="45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F143" s="45">
         <v>1</v>
@@ -41372,13 +41621,13 @@
         <v>45951</v>
       </c>
       <c r="C144" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D144" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E144" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F144" s="45">
         <v>10</v>
@@ -41393,7 +41642,7 @@
         <v>45947</v>
       </c>
       <c r="C145" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D145" s="45" t="s">
         <v>249</v>
@@ -41414,7 +41663,7 @@
         <v>45945</v>
       </c>
       <c r="C146" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D146" s="45" t="s">
         <v>250</v>
@@ -41435,13 +41684,13 @@
         <v>45943</v>
       </c>
       <c r="C147" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D147" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E147" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F147" s="45">
         <v>5</v>
@@ -41456,7 +41705,7 @@
         <v>45941</v>
       </c>
       <c r="C148" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D148" s="45" t="s">
         <v>248</v>
@@ -41477,13 +41726,13 @@
         <v>45941</v>
       </c>
       <c r="C149" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D149" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E149" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F149" s="45">
         <v>5</v>
@@ -41498,13 +41747,13 @@
         <v>45937</v>
       </c>
       <c r="C150" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D150" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E150" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F150" s="45">
         <v>35</v>
@@ -41519,13 +41768,13 @@
         <v>45936</v>
       </c>
       <c r="C151" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D151" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E151" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F151" s="45">
         <v>5</v>
@@ -41540,13 +41789,13 @@
         <v>45934</v>
       </c>
       <c r="C152" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D152" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E152" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F152" s="45">
         <v>5</v>
@@ -41561,13 +41810,13 @@
         <v>45930</v>
       </c>
       <c r="C153" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D153" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E153" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F153" s="45">
         <v>45</v>
@@ -41582,13 +41831,13 @@
         <v>45929</v>
       </c>
       <c r="C154" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D154" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E154" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F154" s="45">
         <v>45</v>
@@ -41603,13 +41852,13 @@
         <v>45928</v>
       </c>
       <c r="C155" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D155" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E155" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F155" s="45">
         <v>35</v>
@@ -41624,13 +41873,13 @@
         <v>45919</v>
       </c>
       <c r="C156" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D156" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E156" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F156" s="45">
         <v>5</v>
@@ -41645,13 +41894,13 @@
         <v>45917</v>
       </c>
       <c r="C157" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D157" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E157" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F157" s="45">
         <v>5</v>
@@ -41666,7 +41915,7 @@
         <v>45916</v>
       </c>
       <c r="C158" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D158" s="45" t="s">
         <v>249</v>
@@ -41687,7 +41936,7 @@
         <v>45915</v>
       </c>
       <c r="C159" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D159" s="45" t="s">
         <v>250</v>
@@ -41708,7 +41957,7 @@
         <v>45911</v>
       </c>
       <c r="C160" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D160" s="45" t="s">
         <v>248</v>
@@ -41729,13 +41978,13 @@
         <v>45905</v>
       </c>
       <c r="C161" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D161" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E161" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F161" s="45">
         <v>5</v>
@@ -41750,13 +41999,13 @@
         <v>45903</v>
       </c>
       <c r="C162" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D162" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E162" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F162" s="45">
         <v>5</v>
@@ -41771,13 +42020,13 @@
         <v>45893</v>
       </c>
       <c r="C163" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D163" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E163" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F163" s="45">
         <v>5</v>
@@ -41792,13 +42041,13 @@
         <v>45892</v>
       </c>
       <c r="C164" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D164" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F164" s="45">
         <v>5</v>
@@ -41813,7 +42062,7 @@
         <v>45888</v>
       </c>
       <c r="C165" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D165" s="45" t="s">
         <v>249</v>
@@ -41834,7 +42083,7 @@
         <v>45884</v>
       </c>
       <c r="C166" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D166" s="45" t="s">
         <v>250</v>
@@ -41855,13 +42104,13 @@
         <v>45877</v>
       </c>
       <c r="C167" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D167" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E167" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F167" s="45">
         <v>10</v>
@@ -41876,13 +42125,13 @@
         <v>45874</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D168" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E168" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F168" s="33">
         <v>5</v>
@@ -41897,13 +42146,13 @@
         <v>45873</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D169" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E169" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F169" s="33">
         <v>5</v>
@@ -41918,13 +42167,13 @@
         <v>45867</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D170" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E170" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F170" s="33">
         <v>5</v>
@@ -41939,13 +42188,13 @@
         <v>45862</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D171" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E171" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F171" s="33">
         <v>5</v>
@@ -41960,13 +42209,13 @@
         <v>45838</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F172" s="33">
         <v>5</v>
@@ -41981,13 +42230,13 @@
         <v>45836</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F173" s="33">
         <v>5</v>
@@ -42002,13 +42251,13 @@
         <v>45789</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D174" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F174" s="33">
         <v>5</v>
@@ -42023,13 +42272,13 @@
         <v>45786</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D175" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E175" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F175" s="33">
         <v>5</v>
@@ -42044,13 +42293,13 @@
         <v>45729</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D176" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E176" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F176" s="33">
         <v>10</v>
@@ -42065,13 +42314,13 @@
         <v>45684</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D177" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E177" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F177" s="33">
         <v>5</v>
@@ -42086,13 +42335,13 @@
         <v>45682</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D178" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E178" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F178" s="33">
         <v>5</v>
@@ -42107,13 +42356,13 @@
         <v>45652</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D179" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E179" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F179" s="33">
         <v>5</v>
@@ -42128,13 +42377,13 @@
         <v>45649</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D180" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E180" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F180" s="33">
         <v>5</v>
@@ -42149,13 +42398,13 @@
         <v>45648</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D181" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E181" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F181" s="33">
         <v>5</v>
@@ -42170,13 +42419,13 @@
         <v>45614</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D182" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F182" s="33">
         <v>5</v>
@@ -42191,13 +42440,13 @@
         <v>45613</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E183" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F183" s="33">
         <v>5</v>
@@ -42212,13 +42461,13 @@
         <v>45592</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D184" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E184" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F184" s="33">
         <v>5</v>
@@ -42233,13 +42482,13 @@
         <v>45591</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D185" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E185" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F185" s="33">
         <v>5</v>
@@ -42254,13 +42503,13 @@
         <v>45514</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D186" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E186" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F186" s="33">
         <v>5</v>
@@ -42275,13 +42524,13 @@
         <v>45513</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>246</v>
       </c>
       <c r="E187" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F187" s="33">
         <v>5</v>
@@ -42296,7 +42545,7 @@
         <v>45335</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D188" s="33" t="s">
         <v>265</v>
@@ -42317,7 +42566,7 @@
         <v>45334</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D189" s="33" t="s">
         <v>265</v>
@@ -42338,7 +42587,7 @@
         <v>45291</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D190" s="33" t="s">
         <v>265</v>
@@ -42359,13 +42608,13 @@
         <v>45291</v>
       </c>
       <c r="C191" s="68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D191" s="68" t="s">
         <v>246</v>
       </c>
       <c r="E191" s="68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F191" s="68">
         <v>10</v>
@@ -48905,7 +49154,7 @@
       </c>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -48944,7 +49193,7 @@
       </c>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -48983,7 +49232,7 @@
       </c>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -49022,7 +49271,7 @@
       </c>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -49059,7 +49308,7 @@
       </c>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -49098,7 +49347,7 @@
       </c>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -49137,7 +49386,7 @@
       </c>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -49176,7 +49425,7 @@
       </c>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -49215,7 +49464,7 @@
       </c>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -49254,7 +49503,7 @@
       </c>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -49293,7 +49542,7 @@
       </c>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -49332,7 +49581,7 @@
       </c>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -49369,7 +49618,7 @@
       </c>
       <c r="M200" s="15"/>
     </row>
-    <row r="201" spans="1:13" hidden="1">
+    <row r="201" spans="1:13">
       <c r="A201" s="14">
         <v>209</v>
       </c>
@@ -49402,7 +49651,7 @@
       <c r="L201" s="15"/>
       <c r="M201" s="15"/>
     </row>
-    <row r="202" spans="1:13" hidden="1">
+    <row r="202" spans="1:13">
       <c r="A202" s="14">
         <v>210</v>
       </c>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC3AB958-AB4A-4403-AF36-6DCCD004DD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B592611-7B57-4FEE-ADA9-0BF62941FEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="371">
   <si>
     <t>日付</t>
   </si>
@@ -14916,7 +14916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O604"/>
+  <dimension ref="A1:O614"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -38434,15 +38434,384 @@
         <v>186</v>
       </c>
     </row>
+    <row r="605" spans="1:13">
+      <c r="A605" s="27">
+        <v>46144</v>
+      </c>
+      <c r="B605" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C605" s="76"/>
+      <c r="D605" s="76"/>
+      <c r="E605" s="77"/>
+      <c r="F605" s="74">
+        <v>0</v>
+      </c>
+      <c r="G605" s="74">
+        <v>24</v>
+      </c>
+      <c r="H605" s="74">
+        <v>24</v>
+      </c>
+      <c r="I605" s="4">
+        <v>63328</v>
+      </c>
+      <c r="J605" s="74">
+        <v>0</v>
+      </c>
+      <c r="K605" s="74">
+        <v>0</v>
+      </c>
+      <c r="L605" s="74">
+        <f t="shared" ref="L605:L614" si="82">J605+L604</f>
+        <v>151768</v>
+      </c>
+      <c r="M605" s="74">
+        <f t="shared" ref="M605:M614" si="83">K605+M604</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13">
+      <c r="A606" s="27">
+        <v>46145</v>
+      </c>
+      <c r="B606" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C606" s="76"/>
+      <c r="D606" s="76"/>
+      <c r="E606" s="77"/>
+      <c r="F606" s="74">
+        <v>0</v>
+      </c>
+      <c r="G606" s="74">
+        <v>19</v>
+      </c>
+      <c r="H606" s="74">
+        <v>19</v>
+      </c>
+      <c r="I606" s="4">
+        <v>63347</v>
+      </c>
+      <c r="J606" s="74">
+        <v>0</v>
+      </c>
+      <c r="K606" s="74">
+        <v>0</v>
+      </c>
+      <c r="L606" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M606" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13">
+      <c r="A607" s="27">
+        <v>46146</v>
+      </c>
+      <c r="B607" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C607" s="76"/>
+      <c r="D607" s="76"/>
+      <c r="E607" s="77"/>
+      <c r="F607" s="74">
+        <v>0</v>
+      </c>
+      <c r="G607" s="74">
+        <v>9</v>
+      </c>
+      <c r="H607" s="74">
+        <v>9</v>
+      </c>
+      <c r="I607" s="4">
+        <v>63356</v>
+      </c>
+      <c r="J607" s="74">
+        <v>0</v>
+      </c>
+      <c r="K607" s="74">
+        <v>0</v>
+      </c>
+      <c r="L607" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M607" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13">
+      <c r="A608" s="27">
+        <v>46147</v>
+      </c>
+      <c r="B608" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C608" s="76"/>
+      <c r="D608" s="76"/>
+      <c r="E608" s="77"/>
+      <c r="F608" s="74">
+        <v>0</v>
+      </c>
+      <c r="G608" s="74">
+        <v>18</v>
+      </c>
+      <c r="H608" s="74">
+        <v>18</v>
+      </c>
+      <c r="I608" s="4">
+        <v>63374</v>
+      </c>
+      <c r="J608" s="74">
+        <v>0</v>
+      </c>
+      <c r="K608" s="74">
+        <v>0</v>
+      </c>
+      <c r="L608" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M608" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13">
+      <c r="A609" s="27">
+        <v>46148</v>
+      </c>
+      <c r="B609" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C609" s="76"/>
+      <c r="D609" s="76"/>
+      <c r="E609" s="77"/>
+      <c r="F609" s="74">
+        <v>0</v>
+      </c>
+      <c r="G609" s="74">
+        <v>1</v>
+      </c>
+      <c r="H609" s="74">
+        <v>1</v>
+      </c>
+      <c r="I609" s="4">
+        <v>63375</v>
+      </c>
+      <c r="J609" s="74">
+        <v>0</v>
+      </c>
+      <c r="K609" s="74">
+        <v>0</v>
+      </c>
+      <c r="L609" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M609" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13">
+      <c r="A610" s="27">
+        <v>46148</v>
+      </c>
+      <c r="B610" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C610" s="76"/>
+      <c r="D610" s="76"/>
+      <c r="E610" s="77"/>
+      <c r="F610" s="74">
+        <v>0</v>
+      </c>
+      <c r="G610" s="74">
+        <v>15</v>
+      </c>
+      <c r="H610" s="74">
+        <v>15</v>
+      </c>
+      <c r="I610" s="4">
+        <v>63390</v>
+      </c>
+      <c r="J610" s="74">
+        <v>0</v>
+      </c>
+      <c r="K610" s="74">
+        <v>0</v>
+      </c>
+      <c r="L610" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M610" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13">
+      <c r="A611" s="27">
+        <v>46148</v>
+      </c>
+      <c r="B611" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C611" s="76"/>
+      <c r="D611" s="76"/>
+      <c r="E611" s="77"/>
+      <c r="F611" s="74">
+        <v>0</v>
+      </c>
+      <c r="G611" s="74">
+        <v>1</v>
+      </c>
+      <c r="H611" s="74">
+        <v>1</v>
+      </c>
+      <c r="I611" s="4">
+        <v>63391</v>
+      </c>
+      <c r="J611" s="74">
+        <v>0</v>
+      </c>
+      <c r="K611" s="74">
+        <v>0</v>
+      </c>
+      <c r="L611" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M611" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13">
+      <c r="A612" s="27">
+        <v>46148</v>
+      </c>
+      <c r="B612" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C612" s="76"/>
+      <c r="D612" s="76"/>
+      <c r="E612" s="77"/>
+      <c r="F612" s="74">
+        <v>0</v>
+      </c>
+      <c r="G612" s="74">
+        <v>1</v>
+      </c>
+      <c r="H612" s="74">
+        <v>1</v>
+      </c>
+      <c r="I612" s="4">
+        <v>63392</v>
+      </c>
+      <c r="J612" s="74">
+        <v>0</v>
+      </c>
+      <c r="K612" s="74">
+        <v>0</v>
+      </c>
+      <c r="L612" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M612" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13">
+      <c r="A613" s="27">
+        <v>46148</v>
+      </c>
+      <c r="B613" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C613" s="76"/>
+      <c r="D613" s="76"/>
+      <c r="E613" s="77"/>
+      <c r="F613" s="74">
+        <v>0</v>
+      </c>
+      <c r="G613" s="74">
+        <v>1</v>
+      </c>
+      <c r="H613" s="74">
+        <v>1</v>
+      </c>
+      <c r="I613" s="4">
+        <v>63393</v>
+      </c>
+      <c r="J613" s="74">
+        <v>0</v>
+      </c>
+      <c r="K613" s="74">
+        <v>0</v>
+      </c>
+      <c r="L613" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M613" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13">
+      <c r="A614" s="29">
+        <v>46149</v>
+      </c>
+      <c r="B614" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C614" s="78"/>
+      <c r="D614" s="78"/>
+      <c r="E614" s="79"/>
+      <c r="F614" s="75">
+        <v>0</v>
+      </c>
+      <c r="G614" s="75">
+        <v>24</v>
+      </c>
+      <c r="H614" s="75">
+        <v>24</v>
+      </c>
+      <c r="I614" s="30">
+        <v>63417</v>
+      </c>
+      <c r="J614" s="75">
+        <v>0</v>
+      </c>
+      <c r="K614" s="75">
+        <v>0</v>
+      </c>
+      <c r="L614" s="74">
+        <f t="shared" si="82"/>
+        <v>151768</v>
+      </c>
+      <c r="M614" s="74">
+        <f t="shared" si="83"/>
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="395">
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
+  <mergeCells count="405">
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B582:E582"/>
+    <mergeCell ref="B583:E583"/>
+    <mergeCell ref="B584:E584"/>
     <mergeCell ref="B580:E580"/>
     <mergeCell ref="B581:E581"/>
     <mergeCell ref="B561:E561"/>
@@ -38819,19 +39188,30 @@
     <mergeCell ref="B553:E553"/>
     <mergeCell ref="B554:E554"/>
     <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B582:E582"/>
-    <mergeCell ref="B583:E583"/>
-    <mergeCell ref="B584:E584"/>
+    <mergeCell ref="B608:E608"/>
+    <mergeCell ref="B609:E609"/>
+    <mergeCell ref="B610:E610"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B612:E612"/>
+    <mergeCell ref="B613:E613"/>
+    <mergeCell ref="B614:E614"/>
     <mergeCell ref="B585:E585"/>
     <mergeCell ref="B586:E586"/>
     <mergeCell ref="B587:E587"/>
     <mergeCell ref="B588:E588"/>
     <mergeCell ref="B589:E589"/>
     <mergeCell ref="B590:E590"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B607:E607"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B592611-7B57-4FEE-ADA9-0BF62941FEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{193F7780-3230-428C-BDC1-1738436B9FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="373">
   <si>
     <t>日付</t>
   </si>
@@ -1139,6 +1139,12 @@
   </si>
   <si>
     <t>JAL４８４</t>
+  </si>
+  <si>
+    <t>JAL153</t>
+  </si>
+  <si>
+    <t>三沢</t>
   </si>
   <si>
     <t>総額</t>
@@ -14916,7 +14922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O614"/>
+  <dimension ref="A1:O616"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -38804,14 +38810,90 @@
         <v>186</v>
       </c>
     </row>
+    <row r="615" spans="1:13">
+      <c r="A615" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B615" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C615" s="76"/>
+      <c r="D615" s="76"/>
+      <c r="E615" s="77"/>
+      <c r="F615" s="74">
+        <v>0</v>
+      </c>
+      <c r="G615" s="74">
+        <v>9</v>
+      </c>
+      <c r="H615" s="74">
+        <v>9</v>
+      </c>
+      <c r="I615" s="4">
+        <v>63426</v>
+      </c>
+      <c r="J615" s="74">
+        <v>0</v>
+      </c>
+      <c r="K615" s="74">
+        <v>0</v>
+      </c>
+      <c r="L615" s="74">
+        <f t="shared" ref="L615:L616" si="84">J615+L614</f>
+        <v>151768</v>
+      </c>
+      <c r="M615" s="74">
+        <f t="shared" ref="M615:M616" si="85">K615+M614</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13">
+      <c r="A616" s="29">
+        <v>46151</v>
+      </c>
+      <c r="B616" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C616" s="78"/>
+      <c r="D616" s="78"/>
+      <c r="E616" s="79"/>
+      <c r="F616" s="75">
+        <v>0</v>
+      </c>
+      <c r="G616" s="75">
+        <v>19</v>
+      </c>
+      <c r="H616" s="75">
+        <v>19</v>
+      </c>
+      <c r="I616" s="30">
+        <v>63445</v>
+      </c>
+      <c r="J616" s="75">
+        <v>0</v>
+      </c>
+      <c r="K616" s="75">
+        <v>0</v>
+      </c>
+      <c r="L616" s="74">
+        <f t="shared" si="84"/>
+        <v>151768</v>
+      </c>
+      <c r="M616" s="74">
+        <f t="shared" si="85"/>
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="405">
+  <mergeCells count="407">
     <mergeCell ref="B597:E597"/>
     <mergeCell ref="B598:E598"/>
     <mergeCell ref="B582:E582"/>
     <mergeCell ref="B583:E583"/>
     <mergeCell ref="B584:E584"/>
+    <mergeCell ref="B615:E615"/>
+    <mergeCell ref="B616:E616"/>
     <mergeCell ref="B580:E580"/>
     <mergeCell ref="B581:E581"/>
     <mergeCell ref="B561:E561"/>
@@ -50546,15 +50628,31 @@
       <c r="A217" s="14">
         <v>225</v>
       </c>
-      <c r="B217" s="42"/>
-      <c r="C217" s="12"/>
-      <c r="D217" s="12"/>
-      <c r="E217" s="12"/>
-      <c r="F217" s="13"/>
-      <c r="G217" s="12"/>
-      <c r="H217" s="13"/>
+      <c r="B217" s="42">
+        <v>46177</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F217" s="13">
+        <v>0.34375</v>
+      </c>
+      <c r="G217" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="H217" s="13">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="I217" s="26"/>
-      <c r="J217" s="15"/>
+      <c r="J217" s="15" t="s">
+        <v>344</v>
+      </c>
       <c r="K217" s="22"/>
       <c r="L217" s="15"/>
       <c r="M217" s="15"/>
@@ -50563,15 +50661,31 @@
       <c r="A218" s="14">
         <v>226</v>
       </c>
-      <c r="B218" s="42"/>
-      <c r="C218" s="12"/>
-      <c r="D218" s="12"/>
-      <c r="E218" s="12"/>
-      <c r="F218" s="13"/>
-      <c r="G218" s="12"/>
-      <c r="H218" s="13"/>
+      <c r="B218" s="42">
+        <v>46177</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F218" s="13">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="G218" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="H218" s="13">
+        <v>0.85763888888888884</v>
+      </c>
       <c r="I218" s="26"/>
-      <c r="J218" s="15"/>
+      <c r="J218" s="15" t="s">
+        <v>344</v>
+      </c>
       <c r="K218" s="22"/>
       <c r="L218" s="15"/>
       <c r="M218" s="15"/>
@@ -51462,7 +51576,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -51471,7 +51585,7 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
@@ -51489,7 +51603,7 @@
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
@@ -51571,7 +51685,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -51623,7 +51737,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -51727,7 +51841,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -51961,7 +52075,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -52015,7 +52129,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -52150,7 +52264,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{193F7780-3230-428C-BDC1-1738436B9FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCEB2A3E-86B5-4515-8182-F9B8227C5A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="374">
   <si>
     <t>日付</t>
   </si>
@@ -1145,6 +1145,9 @@
   </si>
   <si>
     <t>三沢</t>
+  </si>
+  <si>
+    <t>JAL113</t>
   </si>
   <si>
     <t>総額</t>
@@ -2325,7 +2328,7 @@
                   <c:v>116946</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52462</c:v>
+                  <c:v>55244</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5000</c:v>
@@ -2334,10 +2337,10 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6000</c:v>
+                  <c:v>6163</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>95</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14611,11 +14614,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="11">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{E936A600-BB79-446A-9797-5E2C4AB43B97}" name="日付" dataDxfId="11"/>
@@ -14922,7 +14921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O616"/>
+  <dimension ref="A1:O625"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15340,7 +15339,7 @@
       </c>
       <c r="O13">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＣｌｕｂＱ*")</f>
-        <v>52462</v>
+        <v>55244</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="12.75" customHeight="1">
@@ -15490,7 +15489,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>6000</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15540,7 +15539,7 @@
       </c>
       <c r="O17">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＪＭＢアプリ*")</f>
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1">
@@ -15732,7 +15731,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>154503</v>
+        <v>157458</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -38848,31 +38847,31 @@
       </c>
     </row>
     <row r="616" spans="1:13">
-      <c r="A616" s="29">
+      <c r="A616" s="27">
         <v>46151</v>
       </c>
-      <c r="B616" s="78" t="s">
+      <c r="B616" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C616" s="78"/>
-      <c r="D616" s="78"/>
-      <c r="E616" s="79"/>
-      <c r="F616" s="75">
-        <v>0</v>
-      </c>
-      <c r="G616" s="75">
+      <c r="C616" s="76"/>
+      <c r="D616" s="76"/>
+      <c r="E616" s="77"/>
+      <c r="F616" s="74">
+        <v>0</v>
+      </c>
+      <c r="G616" s="74">
         <v>19</v>
       </c>
-      <c r="H616" s="75">
+      <c r="H616" s="74">
         <v>19</v>
       </c>
-      <c r="I616" s="30">
-        <v>63445</v>
-      </c>
-      <c r="J616" s="75">
-        <v>0</v>
-      </c>
-      <c r="K616" s="75">
+      <c r="I616" s="4">
+        <v>63472</v>
+      </c>
+      <c r="J616" s="74">
+        <v>0</v>
+      </c>
+      <c r="K616" s="74">
         <v>0</v>
       </c>
       <c r="L616" s="74">
@@ -38884,11 +38883,351 @@
         <v>186</v>
       </c>
     </row>
+    <row r="617" spans="1:13">
+      <c r="A617" s="27">
+        <v>46152</v>
+      </c>
+      <c r="B617" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C617" s="76"/>
+      <c r="D617" s="76"/>
+      <c r="E617" s="77"/>
+      <c r="F617" s="74">
+        <v>0</v>
+      </c>
+      <c r="G617" s="74">
+        <v>19</v>
+      </c>
+      <c r="H617" s="74">
+        <v>19</v>
+      </c>
+      <c r="I617" s="4">
+        <v>63491</v>
+      </c>
+      <c r="J617" s="74">
+        <v>0</v>
+      </c>
+      <c r="K617" s="74">
+        <v>0</v>
+      </c>
+      <c r="L617" s="74">
+        <f t="shared" ref="L617:L625" si="86">J617+L616</f>
+        <v>151768</v>
+      </c>
+      <c r="M617" s="74">
+        <f t="shared" ref="M617:M625" si="87">K617+M616</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13">
+      <c r="A618" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B618" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="C618" s="76"/>
+      <c r="D618" s="76"/>
+      <c r="E618" s="77"/>
+      <c r="F618" s="4">
+        <v>2782</v>
+      </c>
+      <c r="G618" s="74">
+        <v>0</v>
+      </c>
+      <c r="H618" s="4">
+        <v>2782</v>
+      </c>
+      <c r="I618" s="4">
+        <v>66273</v>
+      </c>
+      <c r="J618" s="74">
+        <v>0</v>
+      </c>
+      <c r="K618" s="74">
+        <v>0</v>
+      </c>
+      <c r="L618" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M618" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13">
+      <c r="A619" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B619" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C619" s="76"/>
+      <c r="D619" s="76"/>
+      <c r="E619" s="77"/>
+      <c r="F619" s="74">
+        <v>0</v>
+      </c>
+      <c r="G619" s="74">
+        <v>1</v>
+      </c>
+      <c r="H619" s="74">
+        <v>1</v>
+      </c>
+      <c r="I619" s="4">
+        <v>66274</v>
+      </c>
+      <c r="J619" s="74">
+        <v>0</v>
+      </c>
+      <c r="K619" s="74">
+        <v>0</v>
+      </c>
+      <c r="L619" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M619" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13">
+      <c r="A620" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B620" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C620" s="76"/>
+      <c r="D620" s="76"/>
+      <c r="E620" s="77"/>
+      <c r="F620" s="74">
+        <v>0</v>
+      </c>
+      <c r="G620" s="74">
+        <v>7</v>
+      </c>
+      <c r="H620" s="74">
+        <v>7</v>
+      </c>
+      <c r="I620" s="4">
+        <v>66281</v>
+      </c>
+      <c r="J620" s="74">
+        <v>0</v>
+      </c>
+      <c r="K620" s="74">
+        <v>0</v>
+      </c>
+      <c r="L620" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M620" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13">
+      <c r="A621" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B621" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C621" s="76"/>
+      <c r="D621" s="76"/>
+      <c r="E621" s="77"/>
+      <c r="F621" s="74">
+        <v>0</v>
+      </c>
+      <c r="G621" s="74">
+        <v>1</v>
+      </c>
+      <c r="H621" s="74">
+        <v>1</v>
+      </c>
+      <c r="I621" s="4">
+        <v>66282</v>
+      </c>
+      <c r="J621" s="74">
+        <v>0</v>
+      </c>
+      <c r="K621" s="74">
+        <v>0</v>
+      </c>
+      <c r="L621" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M621" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13">
+      <c r="A622" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B622" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C622" s="76"/>
+      <c r="D622" s="76"/>
+      <c r="E622" s="77"/>
+      <c r="F622" s="74">
+        <v>0</v>
+      </c>
+      <c r="G622" s="74">
+        <v>1</v>
+      </c>
+      <c r="H622" s="74">
+        <v>1</v>
+      </c>
+      <c r="I622" s="4">
+        <v>66283</v>
+      </c>
+      <c r="J622" s="74">
+        <v>0</v>
+      </c>
+      <c r="K622" s="74">
+        <v>0</v>
+      </c>
+      <c r="L622" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M622" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13">
+      <c r="A623" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B623" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C623" s="76"/>
+      <c r="D623" s="76"/>
+      <c r="E623" s="77"/>
+      <c r="F623" s="74">
+        <v>0</v>
+      </c>
+      <c r="G623" s="74">
+        <v>1</v>
+      </c>
+      <c r="H623" s="74">
+        <v>1</v>
+      </c>
+      <c r="I623" s="4">
+        <v>66284</v>
+      </c>
+      <c r="J623" s="74">
+        <v>0</v>
+      </c>
+      <c r="K623" s="74">
+        <v>0</v>
+      </c>
+      <c r="L623" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M623" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13">
+      <c r="A624" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B624" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C624" s="76"/>
+      <c r="D624" s="76"/>
+      <c r="E624" s="77"/>
+      <c r="F624" s="74">
+        <v>0</v>
+      </c>
+      <c r="G624" s="74">
+        <v>1</v>
+      </c>
+      <c r="H624" s="74">
+        <v>1</v>
+      </c>
+      <c r="I624" s="4">
+        <v>66285</v>
+      </c>
+      <c r="J624" s="74">
+        <v>0</v>
+      </c>
+      <c r="K624" s="74">
+        <v>0</v>
+      </c>
+      <c r="L624" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M624" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13">
+      <c r="A625" s="29">
+        <v>46153</v>
+      </c>
+      <c r="B625" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="C625" s="78"/>
+      <c r="D625" s="78"/>
+      <c r="E625" s="79"/>
+      <c r="F625" s="75">
+        <v>0</v>
+      </c>
+      <c r="G625" s="75">
+        <v>1</v>
+      </c>
+      <c r="H625" s="75">
+        <v>1</v>
+      </c>
+      <c r="I625" s="30">
+        <v>66286</v>
+      </c>
+      <c r="J625" s="75">
+        <v>0</v>
+      </c>
+      <c r="K625" s="75">
+        <v>0</v>
+      </c>
+      <c r="L625" s="74">
+        <f t="shared" si="86"/>
+        <v>151768</v>
+      </c>
+      <c r="M625" s="74">
+        <f t="shared" si="87"/>
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="407">
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
+  <mergeCells count="416">
+    <mergeCell ref="B617:E617"/>
+    <mergeCell ref="B618:E618"/>
+    <mergeCell ref="B619:E619"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
     <mergeCell ref="B582:E582"/>
     <mergeCell ref="B583:E583"/>
     <mergeCell ref="B584:E584"/>
@@ -38896,6 +39235,21 @@
     <mergeCell ref="B616:E616"/>
     <mergeCell ref="B580:E580"/>
     <mergeCell ref="B581:E581"/>
+    <mergeCell ref="B608:E608"/>
+    <mergeCell ref="B609:E609"/>
+    <mergeCell ref="B610:E610"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B612:E612"/>
+    <mergeCell ref="B613:E613"/>
+    <mergeCell ref="B614:E614"/>
+    <mergeCell ref="B585:E585"/>
+    <mergeCell ref="B586:E586"/>
+    <mergeCell ref="B587:E587"/>
+    <mergeCell ref="B588:E588"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B590:E590"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B606:E606"/>
     <mergeCell ref="B561:E561"/>
     <mergeCell ref="B562:E562"/>
     <mergeCell ref="B563:E563"/>
@@ -39270,21 +39624,6 @@
     <mergeCell ref="B553:E553"/>
     <mergeCell ref="B554:E554"/>
     <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B608:E608"/>
-    <mergeCell ref="B609:E609"/>
-    <mergeCell ref="B610:E610"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B612:E612"/>
-    <mergeCell ref="B613:E613"/>
-    <mergeCell ref="B614:E614"/>
-    <mergeCell ref="B585:E585"/>
-    <mergeCell ref="B586:E586"/>
-    <mergeCell ref="B587:E587"/>
-    <mergeCell ref="B588:E588"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B590:E590"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B606:E606"/>
     <mergeCell ref="B607:E607"/>
     <mergeCell ref="B599:E599"/>
     <mergeCell ref="B600:E600"/>
@@ -39294,6 +39633,8 @@
     <mergeCell ref="B604:E604"/>
     <mergeCell ref="B595:E595"/>
     <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -43307,7 +43648,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:13">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -43344,7 +43685,7 @@
       </c>
       <c r="M2" s="63"/>
     </row>
-    <row r="3" spans="1:13" hidden="1">
+    <row r="3" spans="1:13">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -43381,7 +43722,7 @@
       </c>
       <c r="M3" s="15"/>
     </row>
-    <row r="4" spans="1:13" hidden="1">
+    <row r="4" spans="1:13">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -43418,7 +43759,7 @@
       </c>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13" hidden="1">
+    <row r="5" spans="1:13">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -43455,7 +43796,7 @@
       </c>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13" hidden="1">
+    <row r="6" spans="1:13">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -43492,7 +43833,7 @@
       </c>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" hidden="1">
+    <row r="7" spans="1:13">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -43529,7 +43870,7 @@
       </c>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" hidden="1">
+    <row r="8" spans="1:13">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -43566,7 +43907,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" hidden="1">
+    <row r="9" spans="1:13">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -43603,7 +43944,7 @@
       </c>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" hidden="1">
+    <row r="10" spans="1:13">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -43640,7 +43981,7 @@
       </c>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:13">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -43677,7 +44018,7 @@
       </c>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" hidden="1">
+    <row r="12" spans="1:13">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -43714,7 +44055,7 @@
       </c>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" hidden="1">
+    <row r="13" spans="1:13">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -43751,7 +44092,7 @@
       </c>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" hidden="1">
+    <row r="14" spans="1:13">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -43788,7 +44129,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" hidden="1">
+    <row r="15" spans="1:13">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -43825,7 +44166,7 @@
       </c>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13" hidden="1">
+    <row r="16" spans="1:13">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -43862,7 +44203,7 @@
       </c>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13" hidden="1">
+    <row r="17" spans="1:13">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -43899,7 +44240,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13" hidden="1">
+    <row r="18" spans="1:13">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -43936,7 +44277,7 @@
       </c>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" hidden="1">
+    <row r="19" spans="1:13">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -43973,7 +44314,7 @@
       </c>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13" hidden="1">
+    <row r="20" spans="1:13">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -44010,7 +44351,7 @@
       </c>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" hidden="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -44047,7 +44388,7 @@
       </c>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13" hidden="1">
+    <row r="22" spans="1:13">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -44084,7 +44425,7 @@
       </c>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13" hidden="1">
+    <row r="23" spans="1:13">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -44121,7 +44462,7 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="1:13" hidden="1">
+    <row r="24" spans="1:13">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -44158,7 +44499,7 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" hidden="1">
+    <row r="25" spans="1:13">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -44195,7 +44536,7 @@
       </c>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" hidden="1">
+    <row r="26" spans="1:13">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -44232,7 +44573,7 @@
       </c>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" hidden="1">
+    <row r="27" spans="1:13">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -44267,7 +44608,7 @@
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" hidden="1">
+    <row r="28" spans="1:13">
       <c r="A28" s="14">
         <v>27</v>
       </c>
@@ -44304,7 +44645,7 @@
       </c>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" hidden="1">
+    <row r="29" spans="1:13">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -44341,7 +44682,7 @@
       </c>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" hidden="1">
+    <row r="30" spans="1:13">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -44378,7 +44719,7 @@
       </c>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" hidden="1">
+    <row r="31" spans="1:13">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -44415,7 +44756,7 @@
       </c>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" hidden="1">
+    <row r="32" spans="1:13">
       <c r="A32" s="14">
         <v>31</v>
       </c>
@@ -44452,7 +44793,7 @@
       </c>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13" hidden="1">
+    <row r="33" spans="1:13">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -44489,7 +44830,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" hidden="1">
+    <row r="34" spans="1:13">
       <c r="A34" s="14">
         <v>33</v>
       </c>
@@ -44526,7 +44867,7 @@
       </c>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13" hidden="1">
+    <row r="35" spans="1:13">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -44561,7 +44902,7 @@
       </c>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:13" hidden="1">
+    <row r="36" spans="1:13">
       <c r="A36" s="14">
         <v>35</v>
       </c>
@@ -44596,7 +44937,7 @@
       </c>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13" hidden="1">
+    <row r="37" spans="1:13">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -44631,7 +44972,7 @@
       </c>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="1:13" hidden="1">
+    <row r="38" spans="1:13">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -44666,7 +45007,7 @@
       </c>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13" hidden="1">
+    <row r="39" spans="1:13">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -44701,7 +45042,7 @@
       </c>
       <c r="M39" s="15"/>
     </row>
-    <row r="40" spans="1:13" hidden="1">
+    <row r="40" spans="1:13">
       <c r="A40" s="14">
         <v>39</v>
       </c>
@@ -44736,7 +45077,7 @@
       </c>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13" hidden="1">
+    <row r="41" spans="1:13">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -44767,7 +45108,7 @@
       </c>
       <c r="M41" s="15"/>
     </row>
-    <row r="42" spans="1:13" hidden="1">
+    <row r="42" spans="1:13">
       <c r="A42" s="14">
         <v>41</v>
       </c>
@@ -44798,7 +45139,7 @@
       </c>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13" hidden="1">
+    <row r="43" spans="1:13">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -44829,7 +45170,7 @@
       </c>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="1:13" hidden="1">
+    <row r="44" spans="1:13">
       <c r="A44" s="14">
         <v>43</v>
       </c>
@@ -44860,7 +45201,7 @@
       </c>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13" hidden="1">
+    <row r="45" spans="1:13">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -44891,7 +45232,7 @@
       </c>
       <c r="M45" s="15"/>
     </row>
-    <row r="46" spans="1:13" hidden="1">
+    <row r="46" spans="1:13">
       <c r="A46" s="14">
         <v>45</v>
       </c>
@@ -44922,7 +45263,7 @@
       </c>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13" hidden="1">
+    <row r="47" spans="1:13">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -44953,7 +45294,7 @@
       </c>
       <c r="M47" s="15"/>
     </row>
-    <row r="48" spans="1:13" hidden="1">
+    <row r="48" spans="1:13">
       <c r="A48" s="14">
         <v>47</v>
       </c>
@@ -44984,7 +45325,7 @@
       </c>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13" hidden="1">
+    <row r="49" spans="1:13">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -45015,7 +45356,7 @@
       </c>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13" hidden="1">
+    <row r="50" spans="1:13">
       <c r="A50" s="14">
         <v>49</v>
       </c>
@@ -45046,7 +45387,7 @@
       </c>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13" hidden="1">
+    <row r="51" spans="1:13">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -45077,7 +45418,7 @@
       </c>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13" hidden="1">
+    <row r="52" spans="1:13">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -45108,7 +45449,7 @@
       </c>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13" hidden="1">
+    <row r="53" spans="1:13">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -45139,7 +45480,7 @@
       </c>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13" hidden="1">
+    <row r="54" spans="1:13">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -45170,7 +45511,7 @@
       </c>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13" hidden="1">
+    <row r="55" spans="1:13">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -45201,7 +45542,7 @@
       </c>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="1:13" hidden="1">
+    <row r="56" spans="1:13">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -45232,7 +45573,7 @@
       </c>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13" hidden="1">
+    <row r="57" spans="1:13">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -45263,7 +45604,7 @@
       </c>
       <c r="M57" s="15"/>
     </row>
-    <row r="58" spans="1:13" hidden="1">
+    <row r="58" spans="1:13">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -45294,7 +45635,7 @@
       </c>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13" hidden="1">
+    <row r="59" spans="1:13">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -45325,7 +45666,7 @@
       </c>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13" hidden="1">
+    <row r="60" spans="1:13">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -45360,7 +45701,7 @@
       </c>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13" hidden="1">
+    <row r="61" spans="1:13">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -45395,7 +45736,7 @@
       </c>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13" hidden="1">
+    <row r="62" spans="1:13">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -45430,7 +45771,7 @@
       </c>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13" hidden="1">
+    <row r="63" spans="1:13">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -45465,7 +45806,7 @@
       </c>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="1:13" hidden="1">
+    <row r="64" spans="1:13">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -45500,7 +45841,7 @@
       </c>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13" hidden="1">
+    <row r="65" spans="1:13">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -45535,7 +45876,7 @@
       </c>
       <c r="M65" s="15"/>
     </row>
-    <row r="66" spans="1:13" hidden="1">
+    <row r="66" spans="1:13">
       <c r="A66" s="14">
         <v>65</v>
       </c>
@@ -45570,7 +45911,7 @@
       </c>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13" hidden="1">
+    <row r="67" spans="1:13">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -45605,7 +45946,7 @@
       </c>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="1:13" hidden="1">
+    <row r="68" spans="1:13">
       <c r="A68" s="14">
         <v>67</v>
       </c>
@@ -45640,7 +45981,7 @@
       </c>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13" hidden="1">
+    <row r="69" spans="1:13">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -45671,7 +46012,7 @@
       </c>
       <c r="M69" s="15"/>
     </row>
-    <row r="70" spans="1:13" hidden="1">
+    <row r="70" spans="1:13">
       <c r="A70" s="14">
         <v>69</v>
       </c>
@@ -45702,7 +46043,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -45738,7 +46079,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13" hidden="1">
+    <row r="72" spans="1:13">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -45773,7 +46114,7 @@
       </c>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13" hidden="1">
+    <row r="73" spans="1:13">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -45802,7 +46143,7 @@
       </c>
       <c r="M73" s="15"/>
     </row>
-    <row r="74" spans="1:13" hidden="1">
+    <row r="74" spans="1:13">
       <c r="A74" s="14">
         <v>73</v>
       </c>
@@ -45831,7 +46172,7 @@
       </c>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13" hidden="1">
+    <row r="75" spans="1:13">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -45860,7 +46201,7 @@
       </c>
       <c r="M75" s="15"/>
     </row>
-    <row r="76" spans="1:13" hidden="1">
+    <row r="76" spans="1:13">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -45889,7 +46230,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13" hidden="1">
+    <row r="77" spans="1:13">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -45922,7 +46263,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13" hidden="1">
+    <row r="78" spans="1:13">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -45955,7 +46296,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13" hidden="1">
+    <row r="79" spans="1:13">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -45988,7 +46329,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13" hidden="1">
+    <row r="80" spans="1:13">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -46021,7 +46362,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -46054,7 +46395,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -46087,7 +46428,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -46120,7 +46461,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -46153,7 +46494,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -46186,7 +46527,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -46219,7 +46560,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -46252,7 +46593,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -46285,7 +46626,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -46318,7 +46659,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -46351,7 +46692,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -46384,7 +46725,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -46417,7 +46758,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -46450,7 +46791,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -46483,7 +46824,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -46516,7 +46857,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -46549,7 +46890,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13" hidden="1">
+    <row r="97" spans="1:13">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -46582,7 +46923,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13" hidden="1">
+    <row r="98" spans="1:13">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -46615,7 +46956,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13" hidden="1">
+    <row r="99" spans="1:13">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -46648,7 +46989,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13" hidden="1">
+    <row r="100" spans="1:13">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -46681,7 +47022,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13" hidden="1">
+    <row r="101" spans="1:13">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -46714,7 +47055,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13" hidden="1">
+    <row r="102" spans="1:13">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -46747,7 +47088,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13" hidden="1">
+    <row r="103" spans="1:13">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -46780,7 +47121,7 @@
       </c>
       <c r="M103" s="15"/>
     </row>
-    <row r="104" spans="1:13" hidden="1">
+    <row r="104" spans="1:13">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -46809,7 +47150,7 @@
       </c>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="1:13" hidden="1">
+    <row r="105" spans="1:13">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -46838,7 +47179,7 @@
       </c>
       <c r="M105" s="15"/>
     </row>
-    <row r="106" spans="1:13" hidden="1">
+    <row r="106" spans="1:13">
       <c r="A106" s="14">
         <v>105</v>
       </c>
@@ -46867,7 +47208,7 @@
       </c>
       <c r="M106" s="15"/>
     </row>
-    <row r="107" spans="1:13" hidden="1">
+    <row r="107" spans="1:13">
       <c r="A107" s="14">
         <v>106</v>
       </c>
@@ -46896,7 +47237,7 @@
       </c>
       <c r="M107" s="15"/>
     </row>
-    <row r="108" spans="1:13" hidden="1">
+    <row r="108" spans="1:13">
       <c r="A108" s="14">
         <v>107</v>
       </c>
@@ -46925,7 +47266,7 @@
       </c>
       <c r="M108" s="15"/>
     </row>
-    <row r="109" spans="1:13" hidden="1">
+    <row r="109" spans="1:13">
       <c r="A109" s="14">
         <v>108</v>
       </c>
@@ -46954,7 +47295,7 @@
       </c>
       <c r="M109" s="15"/>
     </row>
-    <row r="110" spans="1:13" hidden="1">
+    <row r="110" spans="1:13">
       <c r="A110" s="14">
         <v>109</v>
       </c>
@@ -46983,7 +47324,7 @@
       </c>
       <c r="M110" s="15"/>
     </row>
-    <row r="111" spans="1:13" hidden="1">
+    <row r="111" spans="1:13">
       <c r="A111" s="14">
         <v>110</v>
       </c>
@@ -47012,7 +47353,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13" hidden="1">
+    <row r="112" spans="1:13">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -47047,7 +47388,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13" hidden="1">
+    <row r="113" spans="1:13">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -47082,7 +47423,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13" hidden="1">
+    <row r="114" spans="1:13">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -47117,7 +47458,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13" hidden="1">
+    <row r="115" spans="1:13">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -47150,7 +47491,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13" hidden="1">
+    <row r="116" spans="1:13">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -47183,7 +47524,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13" hidden="1">
+    <row r="117" spans="1:13">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -47218,7 +47559,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13" hidden="1">
+    <row r="118" spans="1:13">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -47249,7 +47590,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13" hidden="1">
+    <row r="119" spans="1:13">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -47280,7 +47621,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13" hidden="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -47311,7 +47652,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13" hidden="1">
+    <row r="121" spans="1:13">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -47342,7 +47683,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13" hidden="1">
+    <row r="122" spans="1:13">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -47377,7 +47718,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13" hidden="1">
+    <row r="123" spans="1:13">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -47408,7 +47749,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13" hidden="1">
+    <row r="124" spans="1:13">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -47443,7 +47784,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13" hidden="1">
+    <row r="125" spans="1:13">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -47478,7 +47819,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13" hidden="1">
+    <row r="126" spans="1:13">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -47513,7 +47854,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13" hidden="1">
+    <row r="127" spans="1:13">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -47544,7 +47885,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13" hidden="1">
+    <row r="128" spans="1:13">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -47575,7 +47916,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13" hidden="1">
+    <row r="129" spans="1:13">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -47606,7 +47947,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13" hidden="1">
+    <row r="130" spans="1:13">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -47637,7 +47978,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13" hidden="1">
+    <row r="131" spans="1:13">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -47668,7 +48009,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13" hidden="1">
+    <row r="132" spans="1:13">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -47703,7 +48044,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13" hidden="1">
+    <row r="133" spans="1:13">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -47738,7 +48079,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13" hidden="1">
+    <row r="134" spans="1:13">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -47769,7 +48110,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13" hidden="1">
+    <row r="135" spans="1:13">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -47800,7 +48141,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13" hidden="1">
+    <row r="136" spans="1:13">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -47835,7 +48176,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13" hidden="1">
+    <row r="137" spans="1:13">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -47866,7 +48207,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13" hidden="1">
+    <row r="138" spans="1:13">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -47901,7 +48242,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13" hidden="1">
+    <row r="139" spans="1:13">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -47939,7 +48280,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1">
+    <row r="140" spans="1:13">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -47974,7 +48315,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13" hidden="1">
+    <row r="141" spans="1:13">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -48009,7 +48350,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13" hidden="1">
+    <row r="142" spans="1:13">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -48044,7 +48385,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13" hidden="1">
+    <row r="143" spans="1:13">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -48075,7 +48416,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13" hidden="1">
+    <row r="144" spans="1:13">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -48106,7 +48447,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13" hidden="1">
+    <row r="145" spans="1:13">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -48141,7 +48482,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13" hidden="1">
+    <row r="146" spans="1:13">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -48176,7 +48517,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13" hidden="1">
+    <row r="147" spans="1:13">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -48211,7 +48552,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13" hidden="1">
+    <row r="148" spans="1:13">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -48246,7 +48587,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13" hidden="1">
+    <row r="149" spans="1:13">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -48281,7 +48622,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13" hidden="1">
+    <row r="150" spans="1:13">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -48316,7 +48657,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13" hidden="1">
+    <row r="151" spans="1:13">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -48351,7 +48692,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13" hidden="1">
+    <row r="152" spans="1:13">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -48386,7 +48727,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13" hidden="1">
+    <row r="153" spans="1:13">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -48421,7 +48762,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13" hidden="1">
+    <row r="154" spans="1:13">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -48456,7 +48797,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13" hidden="1">
+    <row r="155" spans="1:13">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -48491,7 +48832,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13" hidden="1">
+    <row r="156" spans="1:13">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -48526,7 +48867,7 @@
       </c>
       <c r="M156" s="15"/>
     </row>
-    <row r="157" spans="1:13" hidden="1">
+    <row r="157" spans="1:13">
       <c r="A157" s="14">
         <v>165</v>
       </c>
@@ -48555,7 +48896,7 @@
       </c>
       <c r="M157" s="15"/>
     </row>
-    <row r="158" spans="1:13" hidden="1">
+    <row r="158" spans="1:13">
       <c r="A158" s="14">
         <v>166</v>
       </c>
@@ -48584,7 +48925,7 @@
       </c>
       <c r="M158" s="15"/>
     </row>
-    <row r="159" spans="1:13" hidden="1">
+    <row r="159" spans="1:13">
       <c r="A159" s="14">
         <v>167</v>
       </c>
@@ -48613,7 +48954,7 @@
       </c>
       <c r="M159" s="15"/>
     </row>
-    <row r="160" spans="1:13" hidden="1">
+    <row r="160" spans="1:13">
       <c r="A160" s="14">
         <v>168</v>
       </c>
@@ -48642,7 +48983,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13" hidden="1">
+    <row r="161" spans="1:13">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -48671,7 +49012,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13" hidden="1">
+    <row r="162" spans="1:13">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -48700,7 +49041,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13" hidden="1">
+    <row r="163" spans="1:13">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -48729,7 +49070,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13" hidden="1">
+    <row r="164" spans="1:13">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -48758,7 +49099,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13" hidden="1">
+    <row r="165" spans="1:13">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -48793,7 +49134,7 @@
       </c>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13" hidden="1">
+    <row r="166" spans="1:13">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -48828,7 +49169,7 @@
       </c>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13" hidden="1">
+    <row r="167" spans="1:13">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -48863,7 +49204,7 @@
       </c>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13" hidden="1">
+    <row r="168" spans="1:13">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -48898,7 +49239,7 @@
       </c>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13" hidden="1">
+    <row r="169" spans="1:13">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -48933,7 +49274,7 @@
       </c>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13" hidden="1">
+    <row r="170" spans="1:13">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -48968,7 +49309,7 @@
       </c>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13" hidden="1">
+    <row r="171" spans="1:13">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -49003,7 +49344,7 @@
       </c>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13" hidden="1">
+    <row r="172" spans="1:13">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -49038,7 +49379,7 @@
       </c>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13" hidden="1">
+    <row r="173" spans="1:13">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -49073,7 +49414,7 @@
       </c>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13" hidden="1">
+    <row r="174" spans="1:13">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -49108,7 +49449,7 @@
       </c>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13" hidden="1">
+    <row r="175" spans="1:13">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -49141,7 +49482,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13" hidden="1">
+    <row r="176" spans="1:13">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -49174,7 +49515,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -49207,7 +49548,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -49240,7 +49581,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -49273,7 +49614,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -49306,7 +49647,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13" hidden="1">
+    <row r="181" spans="1:13">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -49345,7 +49686,7 @@
       </c>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13" hidden="1">
+    <row r="182" spans="1:13">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -49384,7 +49725,7 @@
       </c>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13" hidden="1">
+    <row r="183" spans="1:13">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -49423,7 +49764,7 @@
       </c>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13" hidden="1">
+    <row r="184" spans="1:13">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -49462,7 +49803,7 @@
       </c>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13" hidden="1">
+    <row r="185" spans="1:13">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -49501,7 +49842,7 @@
       </c>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13" hidden="1">
+    <row r="186" spans="1:13">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -49540,7 +49881,7 @@
       </c>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13" hidden="1">
+    <row r="187" spans="1:13">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -49579,7 +49920,7 @@
       </c>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13" hidden="1">
+    <row r="188" spans="1:13">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -49616,7 +49957,7 @@
       </c>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13" hidden="1">
+    <row r="189" spans="1:13">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -49655,7 +49996,7 @@
       </c>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13" hidden="1">
+    <row r="190" spans="1:13">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -49694,7 +50035,7 @@
       </c>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13" hidden="1">
+    <row r="191" spans="1:13">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -49733,7 +50074,7 @@
       </c>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13" hidden="1">
+    <row r="192" spans="1:13">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -49770,7 +50111,7 @@
       </c>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13" hidden="1">
+    <row r="193" spans="1:13">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -49809,7 +50150,7 @@
       </c>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13" hidden="1">
+    <row r="194" spans="1:13">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -49848,7 +50189,7 @@
       </c>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13" hidden="1">
+    <row r="195" spans="1:13">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -49887,7 +50228,7 @@
       </c>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13" hidden="1">
+    <row r="196" spans="1:13">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -49926,7 +50267,7 @@
       </c>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13" hidden="1">
+    <row r="197" spans="1:13">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -49965,7 +50306,7 @@
       </c>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13" hidden="1">
+    <row r="198" spans="1:13">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -50004,7 +50345,7 @@
       </c>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13" hidden="1">
+    <row r="199" spans="1:13">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -50043,7 +50384,7 @@
       </c>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13" hidden="1">
+    <row r="200" spans="1:13">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -50212,7 +50553,7 @@
       <c r="L204" s="15"/>
       <c r="M204" s="15"/>
     </row>
-    <row r="205" spans="1:13" hidden="1">
+    <row r="205" spans="1:13">
       <c r="A205" s="14">
         <v>213</v>
       </c>
@@ -50249,7 +50590,7 @@
       </c>
       <c r="M205" s="15"/>
     </row>
-    <row r="206" spans="1:13" hidden="1">
+    <row r="206" spans="1:13">
       <c r="A206" s="14">
         <v>214</v>
       </c>
@@ -50286,7 +50627,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13" hidden="1">
+    <row r="207" spans="1:13">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -50321,7 +50662,7 @@
       </c>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13" hidden="1">
+    <row r="208" spans="1:13">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -50356,7 +50697,7 @@
       </c>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13" hidden="1">
+    <row r="209" spans="1:13">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -50391,7 +50732,7 @@
       </c>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13" hidden="1">
+    <row r="210" spans="1:13">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -50426,7 +50767,7 @@
       </c>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13" hidden="1">
+    <row r="211" spans="1:13">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -50455,7 +50796,7 @@
       </c>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13" hidden="1">
+    <row r="212" spans="1:13">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -50484,7 +50825,7 @@
       </c>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13" ht="15.75" hidden="1">
+    <row r="213" spans="1:13" ht="15.75">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -50519,7 +50860,7 @@
       </c>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13" ht="15.75" hidden="1">
+    <row r="214" spans="1:13" ht="15.75">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -50554,7 +50895,7 @@
       </c>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13" hidden="1">
+    <row r="215" spans="1:13">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -50589,7 +50930,7 @@
       </c>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13" hidden="1">
+    <row r="216" spans="1:13">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -50694,16 +51035,34 @@
       <c r="A219" s="14">
         <v>227</v>
       </c>
-      <c r="B219" s="42"/>
-      <c r="C219" s="12"/>
-      <c r="D219" s="12"/>
-      <c r="E219" s="12"/>
-      <c r="F219" s="13"/>
-      <c r="G219" s="12"/>
-      <c r="H219" s="13"/>
+      <c r="B219" s="42">
+        <v>46153</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F219" s="13">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G219" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="H219" s="13">
+        <v>0.49305555555555558</v>
+      </c>
       <c r="I219" s="26"/>
-      <c r="J219" s="15"/>
-      <c r="K219" s="22"/>
+      <c r="J219" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="K219" s="22">
+        <v>0</v>
+      </c>
       <c r="L219" s="15"/>
       <c r="M219" s="15"/>
     </row>
@@ -51576,7 +51935,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -51585,11 +51944,11 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1055</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -51598,16 +51957,16 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1266.145971563981</v>
+        <v>1260.1735849056604</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -51685,7 +52044,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -51737,7 +52096,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -51841,7 +52200,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -52075,7 +52434,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -52129,7 +52488,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -52264,7 +52623,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{324523DC-8517-45D2-A3EA-AD5869E49DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F044AA3-1247-4DF3-8349-AD3FA3279C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2759" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="377">
   <si>
     <t>日付</t>
   </si>
@@ -51383,7 +51383,9 @@
       <c r="K219" s="22">
         <v>0</v>
       </c>
-      <c r="L219" s="15"/>
+      <c r="L219" s="15" t="s">
+        <v>284</v>
+      </c>
       <c r="M219" s="15"/>
     </row>
     <row r="220" spans="1:13">

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F044AA3-1247-4DF3-8349-AD3FA3279C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F5DBAA-4A43-4734-83CD-1F49E941A3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="382">
   <si>
     <t>日付</t>
   </si>
@@ -820,6 +820,9 @@
     <t>ライフスタイルサービス</t>
   </si>
   <si>
+    <t>JALマイレージパーク利用</t>
+  </si>
+  <si>
     <t>JAL Wellness &amp; Travel利用</t>
   </si>
   <si>
@@ -830,9 +833,6 @@
   </si>
   <si>
     <t>JALカード利用</t>
-  </si>
-  <si>
-    <t>JALマイレージパーク利用</t>
   </si>
   <si>
     <t>2周年キャンペーン（国内線）</t>
@@ -1157,6 +1157,21 @@
   </si>
   <si>
     <t>JAL308</t>
+  </si>
+  <si>
+    <t>JAL315</t>
+  </si>
+  <si>
+    <t>JAL477</t>
+  </si>
+  <si>
+    <t>JAL486</t>
+  </si>
+  <si>
+    <t>JAL629</t>
+  </si>
+  <si>
+    <t>JAL630</t>
   </si>
   <si>
     <t>総額</t>
@@ -2346,7 +2361,7 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6202</c:v>
+                  <c:v>6259</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>107</c:v>
@@ -8600,6 +8615,9 @@
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="191"/>
+                <c:pt idx="52">
+                  <c:v>46159</c:v>
+                </c:pt>
                 <c:pt idx="53">
                   <c:v>46157</c:v>
                 </c:pt>
@@ -9018,163 +9036,163 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="191"/>
                 <c:pt idx="0">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1622</c:v>
+                  <c:v>1623</c:v>
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1622</c:v>
@@ -10057,7 +10075,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>288</c:v>
@@ -14939,7 +14957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O632"/>
+  <dimension ref="A1:O635"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15507,7 +15525,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>6202</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15749,7 +15767,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>158257</v>
+        <v>158314</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -39463,31 +39481,31 @@
       </c>
     </row>
     <row r="632" spans="1:13">
-      <c r="A632" s="29">
+      <c r="A632" s="27">
         <v>46157</v>
       </c>
-      <c r="B632" s="78" t="s">
+      <c r="B632" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="C632" s="78"/>
-      <c r="D632" s="78"/>
-      <c r="E632" s="79"/>
-      <c r="F632" s="75">
-        <v>0</v>
-      </c>
-      <c r="G632" s="75">
+      <c r="C632" s="76"/>
+      <c r="D632" s="76"/>
+      <c r="E632" s="77"/>
+      <c r="F632" s="74">
+        <v>0</v>
+      </c>
+      <c r="G632" s="74">
         <v>1</v>
       </c>
-      <c r="H632" s="75">
+      <c r="H632" s="74">
         <v>1</v>
       </c>
-      <c r="I632" s="30">
+      <c r="I632" s="4">
         <v>72085</v>
       </c>
-      <c r="J632" s="75">
-        <v>0</v>
-      </c>
-      <c r="K632" s="75">
+      <c r="J632" s="74">
+        <v>0</v>
+      </c>
+      <c r="K632" s="74">
         <v>0</v>
       </c>
       <c r="L632" s="74">
@@ -39499,35 +39517,477 @@
         <v>187</v>
       </c>
     </row>
+    <row r="633" spans="1:13">
+      <c r="A633" s="27">
+        <v>46159</v>
+      </c>
+      <c r="B633" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="C633" s="76"/>
+      <c r="D633" s="76"/>
+      <c r="E633" s="77"/>
+      <c r="F633" s="74">
+        <v>0</v>
+      </c>
+      <c r="G633" s="74">
+        <v>109</v>
+      </c>
+      <c r="H633" s="74">
+        <v>109</v>
+      </c>
+      <c r="I633" s="4">
+        <v>72194</v>
+      </c>
+      <c r="J633" s="74">
+        <v>0</v>
+      </c>
+      <c r="K633" s="74">
+        <v>0</v>
+      </c>
+      <c r="L633" s="74">
+        <f t="shared" ref="L633:L635" si="90">J633+L632</f>
+        <v>152784</v>
+      </c>
+      <c r="M633" s="74">
+        <f t="shared" ref="M633:M635" si="91">K633+M632</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13">
+      <c r="A634" s="27">
+        <v>46159</v>
+      </c>
+      <c r="B634" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C634" s="76"/>
+      <c r="D634" s="76"/>
+      <c r="E634" s="77"/>
+      <c r="F634" s="74">
+        <v>0</v>
+      </c>
+      <c r="G634" s="74">
+        <v>48</v>
+      </c>
+      <c r="H634" s="74">
+        <v>48</v>
+      </c>
+      <c r="I634" s="4">
+        <v>72242</v>
+      </c>
+      <c r="J634" s="74">
+        <v>0</v>
+      </c>
+      <c r="K634" s="74">
+        <v>0</v>
+      </c>
+      <c r="L634" s="74">
+        <f t="shared" si="90"/>
+        <v>152784</v>
+      </c>
+      <c r="M634" s="74">
+        <f t="shared" si="91"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13">
+      <c r="A635" s="29">
+        <v>46160</v>
+      </c>
+      <c r="B635" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C635" s="78"/>
+      <c r="D635" s="78"/>
+      <c r="E635" s="79"/>
+      <c r="F635" s="75">
+        <v>0</v>
+      </c>
+      <c r="G635" s="75">
+        <v>9</v>
+      </c>
+      <c r="H635" s="75">
+        <v>9</v>
+      </c>
+      <c r="I635" s="30">
+        <v>72251</v>
+      </c>
+      <c r="J635" s="75">
+        <v>0</v>
+      </c>
+      <c r="K635" s="75">
+        <v>0</v>
+      </c>
+      <c r="L635" s="74">
+        <f t="shared" si="90"/>
+        <v>152784</v>
+      </c>
+      <c r="M635" s="74">
+        <f t="shared" si="91"/>
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="422">
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B550:E550"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B554:E554"/>
-    <mergeCell ref="B557:E557"/>
+  <mergeCells count="425">
+    <mergeCell ref="B633:E633"/>
+    <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B635:E635"/>
+    <mergeCell ref="B582:E582"/>
+    <mergeCell ref="B583:E583"/>
+    <mergeCell ref="B584:E584"/>
+    <mergeCell ref="B615:E615"/>
+    <mergeCell ref="B616:E616"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B581:E581"/>
+    <mergeCell ref="B608:E608"/>
+    <mergeCell ref="B609:E609"/>
+    <mergeCell ref="B610:E610"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B612:E612"/>
+    <mergeCell ref="B613:E613"/>
+    <mergeCell ref="B614:E614"/>
+    <mergeCell ref="B585:E585"/>
+    <mergeCell ref="B586:E586"/>
+    <mergeCell ref="B587:E587"/>
+    <mergeCell ref="B588:E588"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B590:E590"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B607:E607"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B545:E545"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B524:E524"/>
+    <mergeCell ref="B525:E525"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B489:E489"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B497:E497"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B523:E523"/>
+    <mergeCell ref="B521:E521"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
     <mergeCell ref="B526:E526"/>
     <mergeCell ref="B527:E527"/>
     <mergeCell ref="B528:E528"/>
@@ -39552,336 +40012,21 @@
     <mergeCell ref="B459:E459"/>
     <mergeCell ref="B460:E460"/>
     <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B524:E524"/>
-    <mergeCell ref="B525:E525"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B489:E489"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B497:E497"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B523:E523"/>
-    <mergeCell ref="B521:E521"/>
-    <mergeCell ref="B545:E545"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B550:E550"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B554:E554"/>
+    <mergeCell ref="B557:E557"/>
     <mergeCell ref="B561:E561"/>
     <mergeCell ref="B562:E562"/>
     <mergeCell ref="B563:E563"/>
@@ -39891,30 +40036,17 @@
     <mergeCell ref="B575:E575"/>
     <mergeCell ref="B577:E577"/>
     <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B582:E582"/>
-    <mergeCell ref="B583:E583"/>
-    <mergeCell ref="B584:E584"/>
-    <mergeCell ref="B615:E615"/>
-    <mergeCell ref="B616:E616"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B581:E581"/>
-    <mergeCell ref="B608:E608"/>
-    <mergeCell ref="B609:E609"/>
-    <mergeCell ref="B610:E610"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B612:E612"/>
-    <mergeCell ref="B613:E613"/>
-    <mergeCell ref="B614:E614"/>
-    <mergeCell ref="B585:E585"/>
-    <mergeCell ref="B586:E586"/>
-    <mergeCell ref="B587:E587"/>
-    <mergeCell ref="B588:E588"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B590:E590"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B607:E607"/>
-    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
     <mergeCell ref="B617:E617"/>
     <mergeCell ref="B618:E618"/>
     <mergeCell ref="B619:E619"/>
@@ -40155,7 +40287,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="34">
         <f t="shared" ref="G3:G189" si="0">G4+F3</f>
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15">
@@ -40166,7 +40298,7 @@
       <c r="F4" s="45"/>
       <c r="G4" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I4" t="s">
         <v>247</v>
@@ -40184,7 +40316,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I5" t="s">
         <v>248</v>
@@ -40202,7 +40334,7 @@
       <c r="F6" s="45"/>
       <c r="G6" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I6" t="s">
         <v>249</v>
@@ -40220,7 +40352,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I7" t="s">
         <v>250</v>
@@ -40238,7 +40370,7 @@
       <c r="F8" s="45"/>
       <c r="G8" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>251</v>
@@ -40256,14 +40388,14 @@
       <c r="F9" s="45"/>
       <c r="G9" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>252</v>
       </c>
       <c r="J9">
         <f>SUMIFS(F3:F30143,D3:D30143, "*JALマイレージパーク*")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="15">
@@ -40274,7 +40406,7 @@
       <c r="F10" s="45"/>
       <c r="G10" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>253</v>
@@ -40292,14 +40424,14 @@
       <c r="F11" s="45"/>
       <c r="G11" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>254</v>
       </c>
       <c r="J11">
         <f>SUM(J4:J10)</f>
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15">
@@ -40310,7 +40442,7 @@
       <c r="F12" s="45"/>
       <c r="G12" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -40322,7 +40454,7 @@
       <c r="F13" s="45"/>
       <c r="G13" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -40334,7 +40466,7 @@
       <c r="F14" s="45"/>
       <c r="G14" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -40346,7 +40478,7 @@
       <c r="F15" s="45"/>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I15" s="31"/>
     </row>
@@ -40358,7 +40490,7 @@
       <c r="F16" s="45"/>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I16" s="31"/>
     </row>
@@ -40370,7 +40502,7 @@
       <c r="F17" s="45"/>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I17" s="31"/>
     </row>
@@ -40382,7 +40514,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I18" s="31"/>
     </row>
@@ -40394,7 +40526,7 @@
       <c r="F19" s="45"/>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I19" s="31"/>
     </row>
@@ -40406,7 +40538,7 @@
       <c r="F20" s="45"/>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I20" s="31"/>
     </row>
@@ -40418,7 +40550,7 @@
       <c r="F21" s="45"/>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I21" s="31"/>
     </row>
@@ -40430,7 +40562,7 @@
       <c r="F22" s="45"/>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I22" s="31"/>
     </row>
@@ -40442,7 +40574,7 @@
       <c r="F23" s="45"/>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I23" s="31"/>
     </row>
@@ -40454,7 +40586,7 @@
       <c r="F24" s="45"/>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I24" s="31"/>
     </row>
@@ -40466,7 +40598,7 @@
       <c r="F25" s="45"/>
       <c r="G25" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I25" s="31"/>
     </row>
@@ -40478,7 +40610,7 @@
       <c r="F26" s="45"/>
       <c r="G26" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I26" s="31"/>
     </row>
@@ -40490,7 +40622,7 @@
       <c r="F27" s="45"/>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I27" s="31"/>
     </row>
@@ -40502,7 +40634,7 @@
       <c r="F28" s="45"/>
       <c r="G28" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I28" s="31"/>
     </row>
@@ -40514,7 +40646,7 @@
       <c r="F29" s="45"/>
       <c r="G29" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I29" s="31"/>
     </row>
@@ -40526,7 +40658,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I30" s="31"/>
     </row>
@@ -40538,7 +40670,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I31" s="31"/>
     </row>
@@ -40550,7 +40682,7 @@
       <c r="F32" s="45"/>
       <c r="G32" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I32" s="31"/>
     </row>
@@ -40562,7 +40694,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I33" s="31"/>
     </row>
@@ -40574,7 +40706,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I34" s="31"/>
     </row>
@@ -40586,7 +40718,7 @@
       <c r="F35" s="45"/>
       <c r="G35" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I35" s="31"/>
     </row>
@@ -40598,7 +40730,7 @@
       <c r="F36" s="45"/>
       <c r="G36" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I36" s="31"/>
     </row>
@@ -40610,7 +40742,7 @@
       <c r="F37" s="45"/>
       <c r="G37" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I37" s="31"/>
     </row>
@@ -40622,7 +40754,7 @@
       <c r="F38" s="45"/>
       <c r="G38" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I38" s="31"/>
     </row>
@@ -40634,7 +40766,7 @@
       <c r="F39" s="45"/>
       <c r="G39" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I39" s="31"/>
     </row>
@@ -40646,7 +40778,7 @@
       <c r="F40" s="45"/>
       <c r="G40" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I40" s="31"/>
     </row>
@@ -40658,7 +40790,7 @@
       <c r="F41" s="45"/>
       <c r="G41" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I41" s="31"/>
     </row>
@@ -40670,7 +40802,7 @@
       <c r="F42" s="45"/>
       <c r="G42" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I42" s="31"/>
     </row>
@@ -40682,7 +40814,7 @@
       <c r="F43" s="45"/>
       <c r="G43" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I43" s="31"/>
     </row>
@@ -40694,7 +40826,7 @@
       <c r="F44" s="45"/>
       <c r="G44" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I44" s="31"/>
     </row>
@@ -40706,7 +40838,7 @@
       <c r="F45" s="45"/>
       <c r="G45" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I45" s="31"/>
     </row>
@@ -40718,7 +40850,7 @@
       <c r="F46" s="45"/>
       <c r="G46" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I46" s="31"/>
     </row>
@@ -40730,7 +40862,7 @@
       <c r="F47" s="45"/>
       <c r="G47" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I47" s="31"/>
     </row>
@@ -40742,7 +40874,7 @@
       <c r="F48" s="45"/>
       <c r="G48" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I48" s="31"/>
     </row>
@@ -40754,7 +40886,7 @@
       <c r="F49" s="45"/>
       <c r="G49" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I49" s="31"/>
     </row>
@@ -40766,7 +40898,7 @@
       <c r="F50" s="45"/>
       <c r="G50" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I50" s="31"/>
     </row>
@@ -40778,7 +40910,7 @@
       <c r="F51" s="45"/>
       <c r="G51" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I51" s="31"/>
     </row>
@@ -40790,7 +40922,7 @@
       <c r="F52" s="45"/>
       <c r="G52" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I52" s="31"/>
     </row>
@@ -40802,7 +40934,7 @@
       <c r="F53" s="45"/>
       <c r="G53" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I53" s="31"/>
     </row>
@@ -40814,19 +40946,29 @@
       <c r="F54" s="45"/>
       <c r="G54" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I54" s="31"/>
     </row>
-    <row r="55" spans="2:9" ht="15">
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
+    <row r="55" spans="2:9" ht="17.25">
+      <c r="B55" s="44">
+        <v>46159</v>
+      </c>
+      <c r="C55" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="D55" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" s="45">
+        <v>1</v>
+      </c>
       <c r="G55" s="34">
         <f t="shared" si="0"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="I55" s="31"/>
     </row>
@@ -40841,7 +40983,7 @@
         <v>251</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F56" s="45">
         <v>1</v>
@@ -40857,13 +40999,13 @@
         <v>46157</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D57" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F57" s="45">
         <v>5</v>
@@ -40885,7 +41027,7 @@
         <v>249</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F58" s="45">
         <v>5</v>
@@ -40901,13 +41043,13 @@
         <v>46140</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D59" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F59" s="45">
         <v>40</v>
@@ -40923,13 +41065,13 @@
         <v>46139</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D60" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F60" s="45">
         <v>20</v>
@@ -40951,7 +41093,7 @@
         <v>252</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F61" s="45">
         <v>1</v>
@@ -40973,7 +41115,7 @@
         <v>252</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F62" s="45">
         <v>1</v>
@@ -40989,13 +41131,13 @@
         <v>46130</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D63" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F63" s="45">
         <v>5</v>
@@ -41033,13 +41175,13 @@
         <v>46129</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D65" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F65" s="45">
         <v>5</v>
@@ -41061,7 +41203,7 @@
         <v>251</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F66" s="45">
         <v>1</v>
@@ -41077,13 +41219,13 @@
         <v>46127</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D67" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F67" s="45">
         <v>40</v>
@@ -41099,13 +41241,13 @@
         <v>46125</v>
       </c>
       <c r="C68" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D68" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F68" s="45">
         <v>5</v>
@@ -41127,7 +41269,7 @@
         <v>249</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F69" s="45">
         <v>30</v>
@@ -41143,13 +41285,13 @@
         <v>46121</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D70" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F70" s="45">
         <v>5</v>
@@ -41165,13 +41307,13 @@
         <v>46113</v>
       </c>
       <c r="C71" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D71" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F71" s="45">
         <v>5</v>
@@ -41187,13 +41329,13 @@
         <v>46111</v>
       </c>
       <c r="C72" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D72" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F72" s="45">
         <v>5</v>
@@ -41215,7 +41357,7 @@
         <v>252</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F73" s="45">
         <v>1</v>
@@ -41253,13 +41395,13 @@
         <v>46107</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D75" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" s="45">
         <v>5</v>
@@ -41275,13 +41417,13 @@
         <v>46106</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D76" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F76" s="45">
         <v>5</v>
@@ -41325,7 +41467,7 @@
         <v>252</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F78" s="45">
         <v>1</v>
@@ -41369,7 +41511,7 @@
         <v>251</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="45">
         <v>1</v>
@@ -41385,13 +41527,13 @@
         <v>46093</v>
       </c>
       <c r="C81" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D81" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="45">
         <v>50</v>
@@ -41413,7 +41555,7 @@
         <v>249</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F82" s="45">
         <v>10</v>
@@ -41429,13 +41571,13 @@
         <v>46083</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D83" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="45">
         <v>10</v>
@@ -41451,13 +41593,13 @@
         <v>46080</v>
       </c>
       <c r="C84" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D84" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F84" s="45">
         <v>35</v>
@@ -41473,13 +41615,13 @@
         <v>46077</v>
       </c>
       <c r="C85" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D85" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F85" s="45">
         <v>40</v>
@@ -41495,13 +41637,13 @@
         <v>46076</v>
       </c>
       <c r="C86" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D86" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F86" s="45">
         <v>15</v>
@@ -41523,7 +41665,7 @@
         <v>252</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F87" s="45">
         <v>1</v>
@@ -41567,7 +41709,7 @@
         <v>251</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F89" s="45">
         <v>1</v>
@@ -41583,13 +41725,13 @@
         <v>46066</v>
       </c>
       <c r="C90" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E90" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F90" s="45">
         <v>30</v>
@@ -41605,13 +41747,13 @@
         <v>46065</v>
       </c>
       <c r="C91" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E91" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F91" s="45">
         <v>10</v>
@@ -41633,7 +41775,7 @@
         <v>249</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F92" s="45">
         <v>10</v>
@@ -41649,13 +41791,13 @@
         <v>46064</v>
       </c>
       <c r="C93" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D93" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F93" s="45">
         <v>5</v>
@@ -41671,13 +41813,13 @@
         <v>46063</v>
       </c>
       <c r="C94" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D94" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F94" s="45">
         <v>45</v>
@@ -41693,13 +41835,13 @@
         <v>46062</v>
       </c>
       <c r="C95" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D95" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F95" s="45">
         <v>25</v>
@@ -41715,13 +41857,13 @@
         <v>46061</v>
       </c>
       <c r="C96" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D96" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F96" s="45">
         <v>30</v>
@@ -41737,13 +41879,13 @@
         <v>46059</v>
       </c>
       <c r="C97" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D97" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F97" s="45">
         <v>5</v>
@@ -41759,13 +41901,13 @@
         <v>46057</v>
       </c>
       <c r="C98" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D98" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F98" s="45">
         <v>5</v>
@@ -41781,13 +41923,13 @@
         <v>46056</v>
       </c>
       <c r="C99" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D99" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F99" s="45">
         <v>5</v>
@@ -41825,13 +41967,13 @@
         <v>46054</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D101" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F101" s="45">
         <v>5</v>
@@ -41847,13 +41989,13 @@
         <v>46052</v>
       </c>
       <c r="C102" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D102" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F102" s="45">
         <v>5</v>
@@ -41869,13 +42011,13 @@
         <v>46051</v>
       </c>
       <c r="C103" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D103" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F103" s="45">
         <v>5</v>
@@ -41891,13 +42033,13 @@
         <v>46048</v>
       </c>
       <c r="C104" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D104" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F104" s="45">
         <v>30</v>
@@ -41919,7 +42061,7 @@
         <v>252</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F105" s="45">
         <v>2</v>
@@ -41935,13 +42077,13 @@
         <v>46044</v>
       </c>
       <c r="C106" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D106" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F106" s="45">
         <v>10</v>
@@ -41979,13 +42121,13 @@
         <v>46040</v>
       </c>
       <c r="C108" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D108" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F108" s="45">
         <v>5</v>
@@ -42001,13 +42143,13 @@
         <v>46039</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D109" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F109" s="45">
         <v>5</v>
@@ -42029,7 +42171,7 @@
         <v>251</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" s="45">
         <v>1</v>
@@ -42045,13 +42187,13 @@
         <v>46035</v>
       </c>
       <c r="C111" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D111" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F111" s="45">
         <v>40</v>
@@ -42067,13 +42209,13 @@
         <v>46034</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D112" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F112" s="45">
         <v>20</v>
@@ -42095,7 +42237,7 @@
         <v>249</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F113" s="45">
         <v>30</v>
@@ -42106,7 +42248,7 @@
       </c>
       <c r="J113">
         <f>SUM(J4:J11)</f>
-        <v>3244</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="17.25">
@@ -42114,13 +42256,13 @@
         <v>46033</v>
       </c>
       <c r="C114" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D114" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F114" s="45">
         <v>40</v>
@@ -42135,13 +42277,13 @@
         <v>46032</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D115" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F115" s="45">
         <v>10</v>
@@ -42156,13 +42298,13 @@
         <v>46030</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D116" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F116" s="45">
         <v>5</v>
@@ -42177,13 +42319,13 @@
         <v>46016</v>
       </c>
       <c r="C117" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D117" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E117" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F117" s="45">
         <v>5</v>
@@ -42198,13 +42340,13 @@
         <v>46014</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D118" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E118" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F118" s="45">
         <v>5</v>
@@ -42225,7 +42367,7 @@
         <v>252</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F119" s="45">
         <v>1</v>
@@ -42240,13 +42382,13 @@
         <v>46012</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D120" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E120" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F120" s="45">
         <v>5</v>
@@ -42261,13 +42403,13 @@
         <v>46011</v>
       </c>
       <c r="C121" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D121" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E121" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F121" s="45">
         <v>5</v>
@@ -42309,7 +42451,7 @@
         <v>251</v>
       </c>
       <c r="E123" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F123" s="45">
         <v>1</v>
@@ -42330,7 +42472,7 @@
         <v>249</v>
       </c>
       <c r="E124" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F124" s="45">
         <v>10</v>
@@ -42345,13 +42487,13 @@
         <v>45996</v>
       </c>
       <c r="C125" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D125" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E125" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F125" s="45">
         <v>45</v>
@@ -42366,13 +42508,13 @@
         <v>45995</v>
       </c>
       <c r="C126" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D126" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E126" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F126" s="45">
         <v>5</v>
@@ -42387,13 +42529,13 @@
         <v>45994</v>
       </c>
       <c r="C127" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D127" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E127" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F127" s="45">
         <v>5</v>
@@ -42408,13 +42550,13 @@
         <v>45990</v>
       </c>
       <c r="C128" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D128" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E128" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F128" s="45">
         <v>5</v>
@@ -42429,13 +42571,13 @@
         <v>45989</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D129" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E129" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F129" s="45">
         <v>5</v>
@@ -42471,13 +42613,13 @@
         <v>45988</v>
       </c>
       <c r="C131" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D131" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E131" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F131" s="45">
         <v>5</v>
@@ -42492,13 +42634,13 @@
         <v>45987</v>
       </c>
       <c r="C132" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D132" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E132" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F132" s="45">
         <v>5</v>
@@ -42513,13 +42655,13 @@
         <v>45985</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D133" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E133" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F133" s="45">
         <v>5</v>
@@ -42534,13 +42676,13 @@
         <v>45983</v>
       </c>
       <c r="C134" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D134" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E134" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F134" s="45">
         <v>5</v>
@@ -42561,7 +42703,7 @@
         <v>252</v>
       </c>
       <c r="E135" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F135" s="45">
         <v>1</v>
@@ -42603,7 +42745,7 @@
         <v>251</v>
       </c>
       <c r="E137" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F137" s="45">
         <v>1</v>
@@ -42624,7 +42766,7 @@
         <v>249</v>
       </c>
       <c r="E138" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F138" s="45">
         <v>20</v>
@@ -42660,13 +42802,13 @@
         <v>45956</v>
       </c>
       <c r="C140" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D140" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E140" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F140" s="45">
         <v>5</v>
@@ -42681,13 +42823,13 @@
         <v>45955</v>
       </c>
       <c r="C141" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D141" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E141" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F141" s="45">
         <v>5</v>
@@ -42702,13 +42844,13 @@
         <v>45953</v>
       </c>
       <c r="C142" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D142" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E142" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F142" s="45">
         <v>5</v>
@@ -42729,7 +42871,7 @@
         <v>252</v>
       </c>
       <c r="E143" s="45" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F143" s="45">
         <v>1</v>
@@ -42744,13 +42886,13 @@
         <v>45951</v>
       </c>
       <c r="C144" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D144" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E144" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F144" s="45">
         <v>10</v>
@@ -42792,7 +42934,7 @@
         <v>251</v>
       </c>
       <c r="E146" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F146" s="45">
         <v>1</v>
@@ -42807,13 +42949,13 @@
         <v>45943</v>
       </c>
       <c r="C147" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D147" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E147" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F147" s="45">
         <v>5</v>
@@ -42834,7 +42976,7 @@
         <v>249</v>
       </c>
       <c r="E148" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F148" s="45">
         <v>15</v>
@@ -42849,13 +42991,13 @@
         <v>45941</v>
       </c>
       <c r="C149" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D149" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E149" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F149" s="45">
         <v>5</v>
@@ -42870,13 +43012,13 @@
         <v>45937</v>
       </c>
       <c r="C150" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D150" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E150" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F150" s="45">
         <v>35</v>
@@ -42891,13 +43033,13 @@
         <v>45936</v>
       </c>
       <c r="C151" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D151" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E151" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F151" s="45">
         <v>5</v>
@@ -42912,13 +43054,13 @@
         <v>45934</v>
       </c>
       <c r="C152" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D152" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E152" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F152" s="45">
         <v>5</v>
@@ -42933,13 +43075,13 @@
         <v>45930</v>
       </c>
       <c r="C153" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D153" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E153" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F153" s="45">
         <v>45</v>
@@ -42954,13 +43096,13 @@
         <v>45929</v>
       </c>
       <c r="C154" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D154" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E154" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F154" s="45">
         <v>45</v>
@@ -42975,13 +43117,13 @@
         <v>45928</v>
       </c>
       <c r="C155" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D155" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E155" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F155" s="45">
         <v>35</v>
@@ -42996,13 +43138,13 @@
         <v>45919</v>
       </c>
       <c r="C156" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D156" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E156" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F156" s="45">
         <v>5</v>
@@ -43017,13 +43159,13 @@
         <v>45917</v>
       </c>
       <c r="C157" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D157" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E157" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F157" s="45">
         <v>5</v>
@@ -43065,7 +43207,7 @@
         <v>251</v>
       </c>
       <c r="E159" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F159" s="45">
         <v>1</v>
@@ -43086,7 +43228,7 @@
         <v>249</v>
       </c>
       <c r="E160" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F160" s="45">
         <v>5</v>
@@ -43101,13 +43243,13 @@
         <v>45905</v>
       </c>
       <c r="C161" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D161" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E161" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F161" s="45">
         <v>5</v>
@@ -43122,13 +43264,13 @@
         <v>45903</v>
       </c>
       <c r="C162" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D162" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E162" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F162" s="45">
         <v>5</v>
@@ -43143,13 +43285,13 @@
         <v>45893</v>
       </c>
       <c r="C163" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D163" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E163" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F163" s="45">
         <v>5</v>
@@ -43164,13 +43306,13 @@
         <v>45892</v>
       </c>
       <c r="C164" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D164" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F164" s="45">
         <v>5</v>
@@ -43212,7 +43354,7 @@
         <v>251</v>
       </c>
       <c r="E166" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F166" s="45">
         <v>1</v>
@@ -43227,13 +43369,13 @@
         <v>45877</v>
       </c>
       <c r="C167" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D167" s="45" t="s">
         <v>247</v>
       </c>
       <c r="E167" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F167" s="45">
         <v>10</v>
@@ -43248,13 +43390,13 @@
         <v>45874</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D168" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E168" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F168" s="33">
         <v>5</v>
@@ -43269,13 +43411,13 @@
         <v>45873</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D169" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E169" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F169" s="33">
         <v>5</v>
@@ -43290,13 +43432,13 @@
         <v>45867</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D170" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E170" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F170" s="33">
         <v>5</v>
@@ -43311,13 +43453,13 @@
         <v>45862</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D171" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E171" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F171" s="33">
         <v>5</v>
@@ -43332,13 +43474,13 @@
         <v>45838</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F172" s="33">
         <v>5</v>
@@ -43353,13 +43495,13 @@
         <v>45836</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F173" s="33">
         <v>5</v>
@@ -43374,13 +43516,13 @@
         <v>45789</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D174" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F174" s="33">
         <v>5</v>
@@ -43395,13 +43537,13 @@
         <v>45786</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D175" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E175" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F175" s="33">
         <v>5</v>
@@ -43416,13 +43558,13 @@
         <v>45729</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D176" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E176" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F176" s="33">
         <v>10</v>
@@ -43437,13 +43579,13 @@
         <v>45684</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D177" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E177" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F177" s="33">
         <v>5</v>
@@ -43458,13 +43600,13 @@
         <v>45682</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D178" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E178" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F178" s="33">
         <v>5</v>
@@ -43479,13 +43621,13 @@
         <v>45652</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D179" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E179" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F179" s="33">
         <v>5</v>
@@ -43500,13 +43642,13 @@
         <v>45649</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D180" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E180" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F180" s="33">
         <v>5</v>
@@ -43521,13 +43663,13 @@
         <v>45648</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D181" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E181" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F181" s="33">
         <v>5</v>
@@ -43542,13 +43684,13 @@
         <v>45614</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D182" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F182" s="33">
         <v>5</v>
@@ -43563,13 +43705,13 @@
         <v>45613</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E183" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F183" s="33">
         <v>5</v>
@@ -43584,13 +43726,13 @@
         <v>45592</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D184" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E184" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F184" s="33">
         <v>5</v>
@@ -43605,13 +43747,13 @@
         <v>45591</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D185" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E185" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F185" s="33">
         <v>5</v>
@@ -43626,13 +43768,13 @@
         <v>45514</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D186" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E186" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F186" s="33">
         <v>5</v>
@@ -43647,13 +43789,13 @@
         <v>45513</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F187" s="33">
         <v>5</v>
@@ -43668,7 +43810,7 @@
         <v>45335</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D188" s="33" t="s">
         <v>266</v>
@@ -43689,7 +43831,7 @@
         <v>45334</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D189" s="33" t="s">
         <v>266</v>
@@ -43710,7 +43852,7 @@
         <v>45291</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D190" s="33" t="s">
         <v>266</v>
@@ -43731,13 +43873,13 @@
         <v>45291</v>
       </c>
       <c r="C191" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D191" s="68" t="s">
         <v>247</v>
       </c>
       <c r="E191" s="68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F191" s="68">
         <v>10</v>
@@ -51462,16 +51604,32 @@
       <c r="A222" s="14">
         <v>230</v>
       </c>
-      <c r="B222" s="42"/>
-      <c r="C222" s="12"/>
-      <c r="D222" s="12"/>
-      <c r="E222" s="12"/>
-      <c r="F222" s="13"/>
-      <c r="G222" s="12"/>
-      <c r="H222" s="13"/>
+      <c r="B222" s="42">
+        <v>46168</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F222" s="13">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="G222" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="H222" s="13">
+        <v>0.53819444444444442</v>
+      </c>
       <c r="I222" s="26"/>
       <c r="J222" s="15"/>
-      <c r="K222" s="22"/>
+      <c r="K222" s="22">
+        <v>0</v>
+      </c>
       <c r="L222" s="15"/>
       <c r="M222" s="15"/>
     </row>
@@ -51479,16 +51637,32 @@
       <c r="A223" s="14">
         <v>231</v>
       </c>
-      <c r="B223" s="42"/>
-      <c r="C223" s="12"/>
-      <c r="D223" s="12"/>
-      <c r="E223" s="12"/>
-      <c r="F223" s="13"/>
-      <c r="G223" s="12"/>
-      <c r="H223" s="13"/>
+      <c r="B223" s="42">
+        <v>46169</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F223" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G223" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H223" s="13">
+        <v>0.74305555555555558</v>
+      </c>
       <c r="I223" s="26"/>
       <c r="J223" s="15"/>
-      <c r="K223" s="22"/>
+      <c r="K223" s="22">
+        <v>0</v>
+      </c>
       <c r="L223" s="15"/>
       <c r="M223" s="15"/>
     </row>
@@ -51496,16 +51670,32 @@
       <c r="A224" s="14">
         <v>232</v>
       </c>
-      <c r="B224" s="42"/>
-      <c r="C224" s="12"/>
-      <c r="D224" s="12"/>
-      <c r="E224" s="12"/>
-      <c r="F224" s="13"/>
-      <c r="G224" s="12"/>
-      <c r="H224" s="13"/>
+      <c r="B224" s="42">
+        <v>46171</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F224" s="13">
+        <v>0.40625</v>
+      </c>
+      <c r="G224" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="H224" s="13">
+        <v>0.48958333333333331</v>
+      </c>
       <c r="I224" s="26"/>
       <c r="J224" s="15"/>
-      <c r="K224" s="22"/>
+      <c r="K224" s="22">
+        <v>0</v>
+      </c>
       <c r="L224" s="15"/>
       <c r="M224" s="15"/>
     </row>
@@ -51513,16 +51703,32 @@
       <c r="A225" s="14">
         <v>233</v>
       </c>
-      <c r="B225" s="42"/>
-      <c r="C225" s="12"/>
-      <c r="D225" s="12"/>
-      <c r="E225" s="12"/>
-      <c r="F225" s="13"/>
-      <c r="G225" s="12"/>
-      <c r="H225" s="13"/>
+      <c r="B225" s="42">
+        <v>46171</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F225" s="13">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="G225" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H225" s="13">
+        <v>0.91319444444444442</v>
+      </c>
       <c r="I225" s="26"/>
       <c r="J225" s="15"/>
-      <c r="K225" s="22"/>
+      <c r="K225" s="22">
+        <v>0</v>
+      </c>
       <c r="L225" s="15"/>
       <c r="M225" s="15"/>
     </row>
@@ -51530,33 +51736,65 @@
       <c r="A226" s="14">
         <v>234</v>
       </c>
-      <c r="B226" s="42"/>
-      <c r="C226" s="12"/>
-      <c r="D226" s="12"/>
-      <c r="E226" s="12"/>
-      <c r="F226" s="13"/>
-      <c r="G226" s="12"/>
-      <c r="H226" s="13"/>
+      <c r="B226" s="42">
+        <v>46175</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F226" s="13">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="G226" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H226" s="13">
+        <v>0.55208333333333337</v>
+      </c>
       <c r="I226" s="26"/>
       <c r="J226" s="15"/>
-      <c r="K226" s="22"/>
+      <c r="K226" s="22">
+        <v>0</v>
+      </c>
       <c r="L226" s="15"/>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" ht="14.25">
+    <row r="227" spans="1:13">
       <c r="A227" s="14">
         <v>235</v>
       </c>
-      <c r="B227" s="42"/>
-      <c r="C227" s="61"/>
-      <c r="D227" s="61"/>
-      <c r="E227" s="61"/>
-      <c r="F227" s="62"/>
-      <c r="G227" s="61"/>
-      <c r="H227" s="62"/>
-      <c r="I227" s="61"/>
+      <c r="B227" s="42">
+        <v>46175</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="F227" s="13">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="G227" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H227" s="13">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="I227" s="26"/>
       <c r="J227" s="15"/>
-      <c r="K227" s="22"/>
+      <c r="K227" s="22">
+        <v>0</v>
+      </c>
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
@@ -52293,7 +52531,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -52302,11 +52540,11 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1070</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -52315,16 +52553,16 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1274.3214953271029</v>
+        <v>1239.5672727272727</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -52402,7 +52640,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -52454,7 +52692,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -52558,7 +52796,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -52792,7 +53030,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -52846,7 +53084,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -52981,7 +53219,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F5DBAA-4A43-4734-83CD-1F49E941A3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2132E77-E04B-449E-ADC6-3A027B575966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="383">
   <si>
     <t>日付</t>
   </si>
@@ -1159,10 +1159,13 @@
     <t>JAL308</t>
   </si>
   <si>
-    <t>JAL315</t>
+    <t>JAL313</t>
   </si>
   <si>
-    <t>JAL477</t>
+    <t>JAL324</t>
+  </si>
+  <si>
+    <t>JAL479</t>
   </si>
   <si>
     <t>JAL486</t>
@@ -8615,6 +8618,9 @@
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="191"/>
+                <c:pt idx="51">
+                  <c:v>46163</c:v>
+                </c:pt>
                 <c:pt idx="52">
                   <c:v>46159</c:v>
                 </c:pt>
@@ -9036,160 +9042,160 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="191"/>
                 <c:pt idx="0">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1623</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>1623</c:v>
@@ -10069,7 +10075,7 @@
                   <c:v>135</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>10</c:v>
@@ -14650,7 +14656,11 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M270" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}"/>
+  <autoFilter ref="A1:M270" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
+    <filterColumn colId="11">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{E936A600-BB79-446A-9797-5E2C4AB43B97}" name="日付" dataDxfId="11"/>
@@ -14957,7 +14967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O635"/>
+  <dimension ref="A1:O641"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -39628,9 +39638,638 @@
         <v>187</v>
       </c>
     </row>
+    <row r="636" spans="1:13">
+      <c r="A636" s="27">
+        <v>46161</v>
+      </c>
+      <c r="B636" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C636" s="76"/>
+      <c r="D636" s="76"/>
+      <c r="E636" s="77"/>
+      <c r="F636" s="74">
+        <v>0</v>
+      </c>
+      <c r="G636" s="74">
+        <v>7</v>
+      </c>
+      <c r="H636" s="74">
+        <v>7</v>
+      </c>
+      <c r="I636" s="4">
+        <v>72381</v>
+      </c>
+      <c r="J636" s="74">
+        <v>0</v>
+      </c>
+      <c r="K636" s="74">
+        <v>0</v>
+      </c>
+      <c r="L636" s="74">
+        <f t="shared" ref="L636:L641" si="92">J636+L635</f>
+        <v>152784</v>
+      </c>
+      <c r="M636" s="74">
+        <f t="shared" ref="M636:M641" si="93">K636+M635</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13">
+      <c r="A637" s="27">
+        <v>46162</v>
+      </c>
+      <c r="B637" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C637" s="76"/>
+      <c r="D637" s="76"/>
+      <c r="E637" s="77"/>
+      <c r="F637" s="74">
+        <v>0</v>
+      </c>
+      <c r="G637" s="74">
+        <v>1</v>
+      </c>
+      <c r="H637" s="74">
+        <v>1</v>
+      </c>
+      <c r="I637" s="4">
+        <v>72382</v>
+      </c>
+      <c r="J637" s="74">
+        <v>0</v>
+      </c>
+      <c r="K637" s="74">
+        <v>0</v>
+      </c>
+      <c r="L637" s="74">
+        <f t="shared" si="92"/>
+        <v>152784</v>
+      </c>
+      <c r="M637" s="74">
+        <f t="shared" si="93"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="638" spans="1:13">
+      <c r="A638" s="27">
+        <v>46162</v>
+      </c>
+      <c r="B638" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C638" s="76"/>
+      <c r="D638" s="76"/>
+      <c r="E638" s="77"/>
+      <c r="F638" s="74">
+        <v>0</v>
+      </c>
+      <c r="G638" s="74">
+        <v>8</v>
+      </c>
+      <c r="H638" s="74">
+        <v>8</v>
+      </c>
+      <c r="I638" s="4">
+        <v>72390</v>
+      </c>
+      <c r="J638" s="74">
+        <v>0</v>
+      </c>
+      <c r="K638" s="74">
+        <v>0</v>
+      </c>
+      <c r="L638" s="74">
+        <f t="shared" si="92"/>
+        <v>152784</v>
+      </c>
+      <c r="M638" s="74">
+        <f t="shared" si="93"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="639" spans="1:13">
+      <c r="A639" s="27">
+        <v>46162</v>
+      </c>
+      <c r="B639" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C639" s="76"/>
+      <c r="D639" s="76"/>
+      <c r="E639" s="77"/>
+      <c r="F639" s="74">
+        <v>0</v>
+      </c>
+      <c r="G639" s="74">
+        <v>1</v>
+      </c>
+      <c r="H639" s="74">
+        <v>1</v>
+      </c>
+      <c r="I639" s="4">
+        <v>72391</v>
+      </c>
+      <c r="J639" s="74">
+        <v>0</v>
+      </c>
+      <c r="K639" s="74">
+        <v>0</v>
+      </c>
+      <c r="L639" s="74">
+        <f t="shared" si="92"/>
+        <v>152784</v>
+      </c>
+      <c r="M639" s="74">
+        <f t="shared" si="93"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="640" spans="1:13">
+      <c r="A640" s="27">
+        <v>46163</v>
+      </c>
+      <c r="B640" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C640" s="76"/>
+      <c r="D640" s="76"/>
+      <c r="E640" s="77"/>
+      <c r="F640" s="74">
+        <v>0</v>
+      </c>
+      <c r="G640" s="74">
+        <v>4</v>
+      </c>
+      <c r="H640" s="74">
+        <v>4</v>
+      </c>
+      <c r="I640" s="4">
+        <v>72395</v>
+      </c>
+      <c r="J640" s="74">
+        <v>0</v>
+      </c>
+      <c r="K640" s="74">
+        <v>0</v>
+      </c>
+      <c r="L640" s="74">
+        <f t="shared" si="92"/>
+        <v>152784</v>
+      </c>
+      <c r="M640" s="74">
+        <f t="shared" si="93"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13">
+      <c r="A641" s="29">
+        <v>46164</v>
+      </c>
+      <c r="B641" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C641" s="78"/>
+      <c r="D641" s="78"/>
+      <c r="E641" s="79"/>
+      <c r="F641" s="75">
+        <v>0</v>
+      </c>
+      <c r="G641" s="75">
+        <v>7</v>
+      </c>
+      <c r="H641" s="75">
+        <v>7</v>
+      </c>
+      <c r="I641" s="30">
+        <v>72402</v>
+      </c>
+      <c r="J641" s="75">
+        <v>0</v>
+      </c>
+      <c r="K641" s="75">
+        <v>0</v>
+      </c>
+      <c r="L641" s="74">
+        <f t="shared" si="92"/>
+        <v>152784</v>
+      </c>
+      <c r="M641" s="74">
+        <f t="shared" si="93"/>
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="425">
+  <mergeCells count="431">
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B617:E617"/>
+    <mergeCell ref="B618:E618"/>
+    <mergeCell ref="B619:E619"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B550:E550"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B554:E554"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B522:E522"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B524:E524"/>
+    <mergeCell ref="B525:E525"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B489:E489"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B497:E497"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B523:E523"/>
+    <mergeCell ref="B521:E521"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B607:E607"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B545:E545"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
     <mergeCell ref="B633:E633"/>
     <mergeCell ref="B634:E634"/>
     <mergeCell ref="B635:E635"/>
@@ -39655,407 +40294,6 @@
     <mergeCell ref="B589:E589"/>
     <mergeCell ref="B590:E590"/>
     <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B607:E607"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B545:E545"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B524:E524"/>
-    <mergeCell ref="B525:E525"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B489:E489"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B497:E497"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B523:E523"/>
-    <mergeCell ref="B521:E521"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B522:E522"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B550:E550"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B554:E554"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B617:E617"/>
-    <mergeCell ref="B618:E618"/>
-    <mergeCell ref="B619:E619"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B621:E621"/>
-    <mergeCell ref="B622:E622"/>
-    <mergeCell ref="B623:E623"/>
-    <mergeCell ref="B624:E624"/>
-    <mergeCell ref="B625:E625"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -40287,7 +40525,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="34">
         <f t="shared" ref="G3:G189" si="0">G4+F3</f>
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15">
@@ -40298,7 +40536,7 @@
       <c r="F4" s="45"/>
       <c r="G4" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I4" t="s">
         <v>247</v>
@@ -40316,7 +40554,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I5" t="s">
         <v>248</v>
@@ -40334,7 +40572,7 @@
       <c r="F6" s="45"/>
       <c r="G6" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I6" t="s">
         <v>249</v>
@@ -40352,14 +40590,14 @@
       <c r="F7" s="45"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I7" t="s">
         <v>250</v>
       </c>
       <c r="J7">
         <f>SUMIFS(F3:F30143,D3:D30143, "*JALモバイル*")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15">
@@ -40370,7 +40608,7 @@
       <c r="F8" s="45"/>
       <c r="G8" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>251</v>
@@ -40388,7 +40626,7 @@
       <c r="F9" s="45"/>
       <c r="G9" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>252</v>
@@ -40406,7 +40644,7 @@
       <c r="F10" s="45"/>
       <c r="G10" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>253</v>
@@ -40424,14 +40662,14 @@
       <c r="F11" s="45"/>
       <c r="G11" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>254</v>
       </c>
       <c r="J11">
         <f>SUM(J4:J10)</f>
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15">
@@ -40442,7 +40680,7 @@
       <c r="F12" s="45"/>
       <c r="G12" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -40454,7 +40692,7 @@
       <c r="F13" s="45"/>
       <c r="G13" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -40466,7 +40704,7 @@
       <c r="F14" s="45"/>
       <c r="G14" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -40478,7 +40716,7 @@
       <c r="F15" s="45"/>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I15" s="31"/>
     </row>
@@ -40490,7 +40728,7 @@
       <c r="F16" s="45"/>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I16" s="31"/>
     </row>
@@ -40502,7 +40740,7 @@
       <c r="F17" s="45"/>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I17" s="31"/>
     </row>
@@ -40514,7 +40752,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I18" s="31"/>
     </row>
@@ -40526,7 +40764,7 @@
       <c r="F19" s="45"/>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I19" s="31"/>
     </row>
@@ -40538,7 +40776,7 @@
       <c r="F20" s="45"/>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I20" s="31"/>
     </row>
@@ -40550,7 +40788,7 @@
       <c r="F21" s="45"/>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I21" s="31"/>
     </row>
@@ -40562,7 +40800,7 @@
       <c r="F22" s="45"/>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I22" s="31"/>
     </row>
@@ -40574,7 +40812,7 @@
       <c r="F23" s="45"/>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I23" s="31"/>
     </row>
@@ -40586,7 +40824,7 @@
       <c r="F24" s="45"/>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I24" s="31"/>
     </row>
@@ -40598,7 +40836,7 @@
       <c r="F25" s="45"/>
       <c r="G25" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I25" s="31"/>
     </row>
@@ -40610,7 +40848,7 @@
       <c r="F26" s="45"/>
       <c r="G26" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I26" s="31"/>
     </row>
@@ -40622,7 +40860,7 @@
       <c r="F27" s="45"/>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I27" s="31"/>
     </row>
@@ -40634,7 +40872,7 @@
       <c r="F28" s="45"/>
       <c r="G28" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I28" s="31"/>
     </row>
@@ -40646,7 +40884,7 @@
       <c r="F29" s="45"/>
       <c r="G29" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I29" s="31"/>
     </row>
@@ -40658,7 +40896,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I30" s="31"/>
     </row>
@@ -40670,7 +40908,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I31" s="31"/>
     </row>
@@ -40682,7 +40920,7 @@
       <c r="F32" s="45"/>
       <c r="G32" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I32" s="31"/>
     </row>
@@ -40694,7 +40932,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I33" s="31"/>
     </row>
@@ -40706,7 +40944,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I34" s="31"/>
     </row>
@@ -40718,7 +40956,7 @@
       <c r="F35" s="45"/>
       <c r="G35" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I35" s="31"/>
     </row>
@@ -40730,7 +40968,7 @@
       <c r="F36" s="45"/>
       <c r="G36" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I36" s="31"/>
     </row>
@@ -40742,7 +40980,7 @@
       <c r="F37" s="45"/>
       <c r="G37" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I37" s="31"/>
     </row>
@@ -40754,7 +40992,7 @@
       <c r="F38" s="45"/>
       <c r="G38" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I38" s="31"/>
     </row>
@@ -40766,7 +41004,7 @@
       <c r="F39" s="45"/>
       <c r="G39" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I39" s="31"/>
     </row>
@@ -40778,7 +41016,7 @@
       <c r="F40" s="45"/>
       <c r="G40" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I40" s="31"/>
     </row>
@@ -40790,7 +41028,7 @@
       <c r="F41" s="45"/>
       <c r="G41" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I41" s="31"/>
     </row>
@@ -40802,7 +41040,7 @@
       <c r="F42" s="45"/>
       <c r="G42" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I42" s="31"/>
     </row>
@@ -40814,7 +41052,7 @@
       <c r="F43" s="45"/>
       <c r="G43" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I43" s="31"/>
     </row>
@@ -40826,7 +41064,7 @@
       <c r="F44" s="45"/>
       <c r="G44" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I44" s="31"/>
     </row>
@@ -40838,7 +41076,7 @@
       <c r="F45" s="45"/>
       <c r="G45" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I45" s="31"/>
     </row>
@@ -40850,7 +41088,7 @@
       <c r="F46" s="45"/>
       <c r="G46" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I46" s="31"/>
     </row>
@@ -40862,7 +41100,7 @@
       <c r="F47" s="45"/>
       <c r="G47" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I47" s="31"/>
     </row>
@@ -40874,7 +41112,7 @@
       <c r="F48" s="45"/>
       <c r="G48" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I48" s="31"/>
     </row>
@@ -40886,7 +41124,7 @@
       <c r="F49" s="45"/>
       <c r="G49" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I49" s="31"/>
     </row>
@@ -40898,7 +41136,7 @@
       <c r="F50" s="45"/>
       <c r="G50" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I50" s="31"/>
     </row>
@@ -40910,7 +41148,7 @@
       <c r="F51" s="45"/>
       <c r="G51" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I51" s="31"/>
     </row>
@@ -40922,7 +41160,7 @@
       <c r="F52" s="45"/>
       <c r="G52" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I52" s="31"/>
     </row>
@@ -40934,19 +41172,29 @@
       <c r="F53" s="45"/>
       <c r="G53" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I53" s="31"/>
     </row>
-    <row r="54" spans="2:9" ht="15">
-      <c r="B54" s="44"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
+    <row r="54" spans="2:9" ht="17.25">
+      <c r="B54" s="44">
+        <v>46163</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="F54" s="45">
+        <v>1</v>
+      </c>
       <c r="G54" s="34">
         <f t="shared" si="0"/>
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I54" s="31"/>
     </row>
@@ -42248,7 +42496,7 @@
       </c>
       <c r="J113">
         <f>SUM(J4:J11)</f>
-        <v>3246</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="17.25">
@@ -44110,7 +44358,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" hidden="1">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -44147,7 +44395,7 @@
       </c>
       <c r="M2" s="63"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" hidden="1">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -44184,7 +44432,7 @@
       </c>
       <c r="M3" s="15"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" hidden="1">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -44221,7 +44469,7 @@
       </c>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" hidden="1">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -44258,7 +44506,7 @@
       </c>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" hidden="1">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -44295,7 +44543,7 @@
       </c>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" hidden="1">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -44332,7 +44580,7 @@
       </c>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" hidden="1">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -44369,7 +44617,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" hidden="1">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -44406,7 +44654,7 @@
       </c>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" hidden="1">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -44443,7 +44691,7 @@
       </c>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" hidden="1">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -44480,7 +44728,7 @@
       </c>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" hidden="1">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -44517,7 +44765,7 @@
       </c>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" hidden="1">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -44554,7 +44802,7 @@
       </c>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" hidden="1">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -44591,7 +44839,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" hidden="1">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -44628,7 +44876,7 @@
       </c>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" hidden="1">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -44665,7 +44913,7 @@
       </c>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" hidden="1">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -44702,7 +44950,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" hidden="1">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -44739,7 +44987,7 @@
       </c>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" hidden="1">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -44776,7 +45024,7 @@
       </c>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" hidden="1">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -44813,7 +45061,7 @@
       </c>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" hidden="1">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -44850,7 +45098,7 @@
       </c>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" hidden="1">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -44887,7 +45135,7 @@
       </c>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" hidden="1">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -44924,7 +45172,7 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" hidden="1">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -44961,7 +45209,7 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" hidden="1">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -44998,7 +45246,7 @@
       </c>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" hidden="1">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -45035,7 +45283,7 @@
       </c>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" hidden="1">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -45070,7 +45318,7 @@
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" hidden="1">
       <c r="A28" s="14">
         <v>27</v>
       </c>
@@ -45107,7 +45355,7 @@
       </c>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" hidden="1">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -45144,7 +45392,7 @@
       </c>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" hidden="1">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -45181,7 +45429,7 @@
       </c>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" hidden="1">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -45218,7 +45466,7 @@
       </c>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" hidden="1">
       <c r="A32" s="14">
         <v>31</v>
       </c>
@@ -45255,7 +45503,7 @@
       </c>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" hidden="1">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -45292,7 +45540,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" hidden="1">
       <c r="A34" s="14">
         <v>33</v>
       </c>
@@ -45329,7 +45577,7 @@
       </c>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" hidden="1">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -45364,7 +45612,7 @@
       </c>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" hidden="1">
       <c r="A36" s="14">
         <v>35</v>
       </c>
@@ -45399,7 +45647,7 @@
       </c>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" hidden="1">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -45434,7 +45682,7 @@
       </c>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" hidden="1">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -45469,7 +45717,7 @@
       </c>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" hidden="1">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -45504,7 +45752,7 @@
       </c>
       <c r="M39" s="15"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" hidden="1">
       <c r="A40" s="14">
         <v>39</v>
       </c>
@@ -45539,7 +45787,7 @@
       </c>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" hidden="1">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -45570,7 +45818,7 @@
       </c>
       <c r="M41" s="15"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" hidden="1">
       <c r="A42" s="14">
         <v>41</v>
       </c>
@@ -45601,7 +45849,7 @@
       </c>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" hidden="1">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -45632,7 +45880,7 @@
       </c>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" hidden="1">
       <c r="A44" s="14">
         <v>43</v>
       </c>
@@ -45663,7 +45911,7 @@
       </c>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" hidden="1">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -45694,7 +45942,7 @@
       </c>
       <c r="M45" s="15"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" hidden="1">
       <c r="A46" s="14">
         <v>45</v>
       </c>
@@ -45725,7 +45973,7 @@
       </c>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" hidden="1">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -45756,7 +46004,7 @@
       </c>
       <c r="M47" s="15"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" hidden="1">
       <c r="A48" s="14">
         <v>47</v>
       </c>
@@ -45787,7 +46035,7 @@
       </c>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" hidden="1">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -45818,7 +46066,7 @@
       </c>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" hidden="1">
       <c r="A50" s="14">
         <v>49</v>
       </c>
@@ -45849,7 +46097,7 @@
       </c>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" hidden="1">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -45880,7 +46128,7 @@
       </c>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" hidden="1">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -45911,7 +46159,7 @@
       </c>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" hidden="1">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -45942,7 +46190,7 @@
       </c>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" hidden="1">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -45973,7 +46221,7 @@
       </c>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" hidden="1">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -46004,7 +46252,7 @@
       </c>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" hidden="1">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -46035,7 +46283,7 @@
       </c>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" hidden="1">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -46066,7 +46314,7 @@
       </c>
       <c r="M57" s="15"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" hidden="1">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -46097,7 +46345,7 @@
       </c>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" hidden="1">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -46128,7 +46376,7 @@
       </c>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" hidden="1">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -46163,7 +46411,7 @@
       </c>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" hidden="1">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -46198,7 +46446,7 @@
       </c>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" hidden="1">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -46233,7 +46481,7 @@
       </c>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" hidden="1">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -46268,7 +46516,7 @@
       </c>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" hidden="1">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -46303,7 +46551,7 @@
       </c>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" hidden="1">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -46338,7 +46586,7 @@
       </c>
       <c r="M65" s="15"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" hidden="1">
       <c r="A66" s="14">
         <v>65</v>
       </c>
@@ -46373,7 +46621,7 @@
       </c>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" hidden="1">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -46408,7 +46656,7 @@
       </c>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" hidden="1">
       <c r="A68" s="14">
         <v>67</v>
       </c>
@@ -46443,7 +46691,7 @@
       </c>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" hidden="1">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -46474,7 +46722,7 @@
       </c>
       <c r="M69" s="15"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" hidden="1">
       <c r="A70" s="14">
         <v>69</v>
       </c>
@@ -46505,7 +46753,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -46541,7 +46789,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" hidden="1">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -46576,7 +46824,7 @@
       </c>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" hidden="1">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -46605,7 +46853,7 @@
       </c>
       <c r="M73" s="15"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" hidden="1">
       <c r="A74" s="14">
         <v>73</v>
       </c>
@@ -46634,7 +46882,7 @@
       </c>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" hidden="1">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -46663,7 +46911,7 @@
       </c>
       <c r="M75" s="15"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" hidden="1">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -46692,7 +46940,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -46725,7 +46973,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -46758,7 +47006,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" hidden="1">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -46791,7 +47039,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" hidden="1">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -46824,7 +47072,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" hidden="1">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -46857,7 +47105,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" hidden="1">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -46890,7 +47138,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" hidden="1">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -46923,7 +47171,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" hidden="1">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -46956,7 +47204,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" hidden="1">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -46989,7 +47237,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" hidden="1">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -47022,7 +47270,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" hidden="1">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -47055,7 +47303,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" hidden="1">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -47088,7 +47336,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" hidden="1">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -47121,7 +47369,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" hidden="1">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -47154,7 +47402,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" hidden="1">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -47187,7 +47435,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" hidden="1">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -47220,7 +47468,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" hidden="1">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -47253,7 +47501,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" hidden="1">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -47286,7 +47534,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" hidden="1">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -47319,7 +47567,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" hidden="1">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -47352,7 +47600,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" hidden="1">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -47385,7 +47633,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" hidden="1">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -47418,7 +47666,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" hidden="1">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -47451,7 +47699,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" hidden="1">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -47484,7 +47732,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" hidden="1">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -47517,7 +47765,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" hidden="1">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -47550,7 +47798,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" hidden="1">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -47583,7 +47831,7 @@
       </c>
       <c r="M103" s="15"/>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" hidden="1">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -47612,7 +47860,7 @@
       </c>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" hidden="1">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -47641,7 +47889,7 @@
       </c>
       <c r="M105" s="15"/>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" hidden="1">
       <c r="A106" s="14">
         <v>105</v>
       </c>
@@ -47670,7 +47918,7 @@
       </c>
       <c r="M106" s="15"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" hidden="1">
       <c r="A107" s="14">
         <v>106</v>
       </c>
@@ -47699,7 +47947,7 @@
       </c>
       <c r="M107" s="15"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" hidden="1">
       <c r="A108" s="14">
         <v>107</v>
       </c>
@@ -47728,7 +47976,7 @@
       </c>
       <c r="M108" s="15"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" hidden="1">
       <c r="A109" s="14">
         <v>108</v>
       </c>
@@ -47757,7 +48005,7 @@
       </c>
       <c r="M109" s="15"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" hidden="1">
       <c r="A110" s="14">
         <v>109</v>
       </c>
@@ -47786,7 +48034,7 @@
       </c>
       <c r="M110" s="15"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" hidden="1">
       <c r="A111" s="14">
         <v>110</v>
       </c>
@@ -47815,7 +48063,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" hidden="1">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -47850,7 +48098,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" hidden="1">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -47885,7 +48133,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" hidden="1">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -47920,7 +48168,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" hidden="1">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -47953,7 +48201,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" hidden="1">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -47986,7 +48234,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" hidden="1">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -48021,7 +48269,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" hidden="1">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -48052,7 +48300,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" hidden="1">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -48083,7 +48331,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" hidden="1">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -48114,7 +48362,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" hidden="1">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -48145,7 +48393,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" hidden="1">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -48180,7 +48428,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" hidden="1">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -48211,7 +48459,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" hidden="1">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -48246,7 +48494,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" hidden="1">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -48281,7 +48529,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" hidden="1">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -48316,7 +48564,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" hidden="1">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -48347,7 +48595,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" hidden="1">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -48378,7 +48626,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" hidden="1">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -48409,7 +48657,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" hidden="1">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -48440,7 +48688,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" hidden="1">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -48471,7 +48719,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" hidden="1">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -48506,7 +48754,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" hidden="1">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -48541,7 +48789,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" hidden="1">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -48572,7 +48820,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" hidden="1">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -48603,7 +48851,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" hidden="1">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -48638,7 +48886,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" hidden="1">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -48669,7 +48917,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" hidden="1">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -48704,7 +48952,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" hidden="1">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -48742,7 +48990,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" hidden="1">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -48777,7 +49025,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" hidden="1">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -48812,7 +49060,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" hidden="1">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -48847,7 +49095,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" hidden="1">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -48878,7 +49126,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" hidden="1">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -48909,7 +49157,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" hidden="1">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -48944,7 +49192,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" hidden="1">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -48979,7 +49227,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" hidden="1">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -49014,7 +49262,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" hidden="1">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -49049,7 +49297,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" hidden="1">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -49084,7 +49332,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" hidden="1">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -49119,7 +49367,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" hidden="1">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -49154,7 +49402,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" hidden="1">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -49189,7 +49437,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" hidden="1">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -49224,7 +49472,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" hidden="1">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -49259,7 +49507,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" hidden="1">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -49294,7 +49542,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" hidden="1">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -49329,7 +49577,7 @@
       </c>
       <c r="M156" s="15"/>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" hidden="1">
       <c r="A157" s="14">
         <v>165</v>
       </c>
@@ -49358,7 +49606,7 @@
       </c>
       <c r="M157" s="15"/>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" hidden="1">
       <c r="A158" s="14">
         <v>166</v>
       </c>
@@ -49387,7 +49635,7 @@
       </c>
       <c r="M158" s="15"/>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" hidden="1">
       <c r="A159" s="14">
         <v>167</v>
       </c>
@@ -49416,7 +49664,7 @@
       </c>
       <c r="M159" s="15"/>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" hidden="1">
       <c r="A160" s="14">
         <v>168</v>
       </c>
@@ -49445,7 +49693,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" hidden="1">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -49474,7 +49722,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" hidden="1">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -49503,7 +49751,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" hidden="1">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -49532,7 +49780,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" hidden="1">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -49561,7 +49809,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -49596,7 +49844,7 @@
       </c>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -49631,7 +49879,7 @@
       </c>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -49666,7 +49914,7 @@
       </c>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -49701,7 +49949,7 @@
       </c>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -49736,7 +49984,7 @@
       </c>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -49771,7 +50019,7 @@
       </c>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -49806,7 +50054,7 @@
       </c>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -49841,7 +50089,7 @@
       </c>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -49876,7 +50124,7 @@
       </c>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -49911,7 +50159,7 @@
       </c>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" hidden="1">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -49944,7 +50192,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" hidden="1">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -49977,7 +50225,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" hidden="1">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -50010,7 +50258,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" hidden="1">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -50043,7 +50291,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" hidden="1">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -50076,7 +50324,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" hidden="1">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -50109,7 +50357,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -50148,7 +50396,7 @@
       </c>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -50187,7 +50435,7 @@
       </c>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -50226,7 +50474,7 @@
       </c>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -50265,7 +50513,7 @@
       </c>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -50304,7 +50552,7 @@
       </c>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -50343,7 +50591,7 @@
       </c>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -50382,7 +50630,7 @@
       </c>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -50419,7 +50667,7 @@
       </c>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -50458,7 +50706,7 @@
       </c>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -50497,7 +50745,7 @@
       </c>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -50536,7 +50784,7 @@
       </c>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -50573,7 +50821,7 @@
       </c>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -50612,7 +50860,7 @@
       </c>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -50651,7 +50899,7 @@
       </c>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -50690,7 +50938,7 @@
       </c>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -50729,7 +50977,7 @@
       </c>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -50768,7 +51016,7 @@
       </c>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -50807,7 +51055,7 @@
       </c>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -50846,7 +51094,7 @@
       </c>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -51015,7 +51263,7 @@
       <c r="L204" s="15"/>
       <c r="M204" s="15"/>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" hidden="1">
       <c r="A205" s="14">
         <v>213</v>
       </c>
@@ -51052,7 +51300,7 @@
       </c>
       <c r="M205" s="15"/>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" hidden="1">
       <c r="A206" s="14">
         <v>214</v>
       </c>
@@ -51089,7 +51337,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -51124,7 +51372,7 @@
       </c>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -51159,7 +51407,7 @@
       </c>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -51194,7 +51442,7 @@
       </c>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -51229,7 +51477,7 @@
       </c>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" hidden="1">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -51258,7 +51506,7 @@
       </c>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" hidden="1">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -51287,7 +51535,7 @@
       </c>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13" ht="15.75">
+    <row r="213" spans="1:13" ht="15.75" hidden="1">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -51322,7 +51570,7 @@
       </c>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13" ht="15.75">
+    <row r="214" spans="1:13" ht="15.75" hidden="1">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -51357,7 +51605,7 @@
       </c>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" hidden="1">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -51392,7 +51640,7 @@
       </c>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" hidden="1">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -51493,7 +51741,7 @@
       <c r="L218" s="15"/>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" hidden="1">
       <c r="A219" s="14">
         <v>227</v>
       </c>
@@ -51605,7 +51853,7 @@
         <v>230</v>
       </c>
       <c r="B222" s="42">
-        <v>46168</v>
+        <v>46178</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>280</v>
@@ -51617,13 +51865,13 @@
         <v>281</v>
       </c>
       <c r="F222" s="13">
-        <v>0.4548611111111111</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>282</v>
       </c>
       <c r="H222" s="13">
-        <v>0.53819444444444442</v>
+        <v>0.49652777777777779</v>
       </c>
       <c r="I222" s="26"/>
       <c r="J222" s="15"/>
@@ -51638,25 +51886,25 @@
         <v>231</v>
       </c>
       <c r="B223" s="42">
-        <v>46169</v>
+        <v>46178</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>280</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="E223" s="12" t="s">
         <v>282</v>
       </c>
       <c r="F223" s="13">
-        <v>0.66666666666666663</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="G223" s="12" t="s">
         <v>281</v>
       </c>
       <c r="H223" s="13">
-        <v>0.74305555555555558</v>
+        <v>0.78819444444444442</v>
       </c>
       <c r="I223" s="26"/>
       <c r="J223" s="15"/>
@@ -51671,25 +51919,25 @@
         <v>232</v>
       </c>
       <c r="B224" s="42">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>280</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>281</v>
       </c>
       <c r="F224" s="13">
-        <v>0.40625</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="G224" s="12" t="s">
         <v>325</v>
       </c>
       <c r="H224" s="13">
-        <v>0.48958333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="I224" s="26"/>
       <c r="J224" s="15"/>
@@ -51710,19 +51958,19 @@
         <v>280</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E225" s="12" t="s">
         <v>325</v>
       </c>
       <c r="F225" s="13">
-        <v>0.86111111111111116</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="G225" s="12" t="s">
         <v>281</v>
       </c>
       <c r="H225" s="13">
-        <v>0.91319444444444442</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="I225" s="26"/>
       <c r="J225" s="15"/>
@@ -51743,7 +51991,7 @@
         <v>280</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E226" s="12" t="s">
         <v>281</v>
@@ -51776,7 +52024,7 @@
         <v>280</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E227" s="12" t="s">
         <v>362</v>
@@ -51788,7 +52036,7 @@
         <v>281</v>
       </c>
       <c r="H227" s="13">
-        <v>0.64930555555555558</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="I227" s="26"/>
       <c r="J227" s="15"/>
@@ -51802,16 +52050,32 @@
       <c r="A228" s="14">
         <v>236</v>
       </c>
-      <c r="B228" s="42"/>
-      <c r="C228" s="61"/>
-      <c r="D228" s="61"/>
-      <c r="E228" s="61"/>
-      <c r="F228" s="62"/>
-      <c r="G228" s="61"/>
-      <c r="H228" s="62"/>
+      <c r="B228" s="42">
+        <v>46181</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F228" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G228" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H228" s="13">
+        <v>0.40625</v>
+      </c>
       <c r="I228" s="61"/>
       <c r="J228" s="15"/>
-      <c r="K228" s="22"/>
+      <c r="K228" s="22">
+        <v>0</v>
+      </c>
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
@@ -51819,16 +52083,32 @@
       <c r="A229" s="14">
         <v>237</v>
       </c>
-      <c r="B229" s="42"/>
-      <c r="C229" s="61"/>
-      <c r="D229" s="61"/>
-      <c r="E229" s="61"/>
-      <c r="F229" s="62"/>
-      <c r="G229" s="61"/>
-      <c r="H229" s="62"/>
+      <c r="B229" s="42">
+        <v>46181</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="F229" s="13">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="G229" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H229" s="13">
+        <v>0.79513888888888884</v>
+      </c>
       <c r="I229" s="61"/>
       <c r="J229" s="15"/>
-      <c r="K229" s="22"/>
+      <c r="K229" s="22">
+        <v>0</v>
+      </c>
       <c r="L229" s="15"/>
       <c r="M229" s="15"/>
     </row>
@@ -52531,7 +52811,7 @@
     </row>
     <row r="281" spans="10:11">
       <c r="J281" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K281" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -52540,11 +52820,11 @@
     </row>
     <row r="282" spans="10:11">
       <c r="J282" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K282">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1100</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="283" spans="10:11">
@@ -52553,16 +52833,16 @@
       </c>
       <c r="K283">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="10:11">
       <c r="J284" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K284" s="41">
         <f>K281/K282</f>
-        <v>1239.5672727272727</v>
+        <v>1228.4000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -52640,7 +52920,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H298" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -52692,7 +52972,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H300" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -52796,7 +53076,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H304" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -53030,7 +53310,7 @@
         <v>0.375</v>
       </c>
       <c r="H316" s="51" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I316" s="52"/>
     </row>
@@ -53084,7 +53364,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H318" s="49" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I318" s="52"/>
     </row>
@@ -53219,7 +53499,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H323" s="54" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I323" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A91DD1F1-550F-48D5-B0C4-04028FE0273E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09645455-26E2-4DFD-8999-22E8DD0D3AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2896" uniqueCount="392">
   <si>
     <t>日付</t>
   </si>
@@ -1181,12 +1181,6 @@
   </si>
   <si>
     <t>JAL４８４</t>
-  </si>
-  <si>
-    <t>JAL153</t>
-  </si>
-  <si>
-    <t>三沢</t>
   </si>
   <si>
     <t>JAL113</t>
@@ -14700,8 +14694,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M265" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M265" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M263" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:M263" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
     <filterColumn colId="11">
       <filters blank="1"/>
     </filterColumn>
@@ -46445,7 +46439,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EF3C4E-F452-4BBC-81DB-9BE6F59D48AA}">
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -53810,12 +53804,12 @@
       </c>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" hidden="1">
       <c r="A217" s="14">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B217" s="42">
-        <v>46177</v>
+        <v>46153</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>293</v>
@@ -53827,19 +53821,21 @@
         <v>294</v>
       </c>
       <c r="F217" s="13">
-        <v>0.34375</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="G217" s="12" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="H217" s="13">
-        <v>0.39583333333333331</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="I217" s="26"/>
       <c r="J217" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="K217" s="22"/>
+      <c r="K217" s="22">
+        <v>0</v>
+      </c>
       <c r="L217" s="15" t="s">
         <v>297</v>
       </c>
@@ -53847,45 +53843,45 @@
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="14">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B218" s="42">
-        <v>46177</v>
+        <v>46223</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D218" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="F218" s="13">
-        <v>0.79861111111111116</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="G218" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H218" s="13">
-        <v>0.85763888888888884</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="I218" s="26"/>
       <c r="J218" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="K218" s="22"/>
-      <c r="L218" s="15" t="s">
-        <v>297</v>
-      </c>
+      <c r="K218" s="22">
+        <v>27740</v>
+      </c>
+      <c r="L218" s="15"/>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13" hidden="1">
+    <row r="219" spans="1:13">
       <c r="A219" s="14">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B219" s="42">
-        <v>46153</v>
+        <v>46229</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>293</v>
@@ -53894,16 +53890,16 @@
         <v>379</v>
       </c>
       <c r="E219" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F219" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G219" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="F219" s="13">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="G219" s="12" t="s">
-        <v>371</v>
-      </c>
       <c r="H219" s="13">
-        <v>0.49305555555555558</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="I219" s="26"/>
       <c r="J219" s="15" t="s">
@@ -53912,17 +53908,15 @@
       <c r="K219" s="22">
         <v>0</v>
       </c>
-      <c r="L219" s="15" t="s">
-        <v>297</v>
-      </c>
+      <c r="L219" s="15"/>
       <c r="M219" s="15"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="14">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B220" s="42">
-        <v>46223</v>
+        <v>46182</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>293</v>
@@ -53934,48 +53928,48 @@
         <v>294</v>
       </c>
       <c r="F220" s="13">
-        <v>0.2951388888888889</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="G220" s="12" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="H220" s="13">
-        <v>0.36458333333333331</v>
+        <v>0.65625</v>
       </c>
       <c r="I220" s="26"/>
       <c r="J220" s="15" t="s">
         <v>358</v>
       </c>
       <c r="K220" s="22">
-        <v>27740</v>
+        <v>0</v>
       </c>
       <c r="L220" s="15"/>
       <c r="M220" s="15"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="14">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B221" s="42">
-        <v>46229</v>
+        <v>46183</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D221" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="F221" s="13">
-        <v>0.41666666666666669</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>294</v>
       </c>
       <c r="H221" s="13">
-        <v>0.48958333333333331</v>
+        <v>0.78125</v>
       </c>
       <c r="I221" s="26"/>
       <c r="J221" s="15" t="s">
@@ -53987,215 +53981,179 @@
       <c r="L221" s="15"/>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" hidden="1">
       <c r="A222" s="14">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B222" s="42">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E222" s="12" t="s">
         <v>294</v>
       </c>
       <c r="F222" s="13">
-        <v>0.60416666666666663</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="G222" s="12" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H222" s="13">
-        <v>0.65625</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="I222" s="26"/>
-      <c r="J222" s="15" t="s">
-        <v>358</v>
-      </c>
+      <c r="J222" s="15"/>
       <c r="K222" s="22">
         <v>0</v>
       </c>
-      <c r="L222" s="15"/>
+      <c r="L222" s="15" t="s">
+        <v>297</v>
+      </c>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" hidden="1">
       <c r="A223" s="14">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B223" s="42">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F223" s="13">
-        <v>0.72916666666666663</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="G223" s="12" t="s">
         <v>294</v>
       </c>
       <c r="H223" s="13">
-        <v>0.78125</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="I223" s="26"/>
-      <c r="J223" s="15" t="s">
-        <v>358</v>
-      </c>
+      <c r="J223" s="15"/>
       <c r="K223" s="22">
         <v>0</v>
       </c>
-      <c r="L223" s="15"/>
+      <c r="L223" s="15" t="s">
+        <v>297</v>
+      </c>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13" hidden="1">
+    <row r="224" spans="1:13" ht="14.25">
       <c r="A224" s="14">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B224" s="42">
-        <v>46170</v>
+        <v>46180</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>294</v>
       </c>
       <c r="F224" s="13">
-        <v>0.46527777777777779</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G224" s="12" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="H224" s="13">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="I224" s="26"/>
+        <v>0.40625</v>
+      </c>
+      <c r="I224" s="61"/>
       <c r="J224" s="15"/>
       <c r="K224" s="22">
         <v>0</v>
       </c>
-      <c r="L224" s="15" t="s">
-        <v>297</v>
-      </c>
+      <c r="L224" s="15"/>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13" hidden="1">
+    <row r="225" spans="1:13" ht="14.25">
       <c r="A225" s="14">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B225" s="42">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>293</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="F225" s="13">
-        <v>0.63541666666666663</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="G225" s="12" t="s">
         <v>294</v>
       </c>
       <c r="H225" s="13">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="I225" s="26"/>
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="I225" s="61"/>
       <c r="J225" s="15"/>
       <c r="K225" s="22">
         <v>0</v>
       </c>
-      <c r="L225" s="15" t="s">
-        <v>297</v>
-      </c>
+      <c r="L225" s="15"/>
       <c r="M225" s="15"/>
     </row>
     <row r="226" spans="1:13" ht="14.25">
       <c r="A226" s="14">
-        <v>236</v>
-      </c>
-      <c r="B226" s="42">
-        <v>46180</v>
-      </c>
-      <c r="C226" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="D226" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="E226" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="F226" s="13">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G226" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H226" s="13">
-        <v>0.40625</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="B226" s="42"/>
+      <c r="C226" s="61"/>
+      <c r="D226" s="61"/>
+      <c r="E226" s="61"/>
+      <c r="F226" s="62"/>
+      <c r="G226" s="61"/>
+      <c r="H226" s="62"/>
       <c r="I226" s="61"/>
       <c r="J226" s="15"/>
-      <c r="K226" s="22">
-        <v>0</v>
-      </c>
+      <c r="K226" s="22"/>
       <c r="L226" s="15"/>
       <c r="M226" s="15"/>
     </row>
     <row r="227" spans="1:13" ht="14.25">
       <c r="A227" s="14">
-        <v>237</v>
-      </c>
-      <c r="B227" s="42">
-        <v>46181</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="D227" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E227" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="F227" s="13">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="G227" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="H227" s="13">
-        <v>0.79513888888888884</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="B227" s="42"/>
+      <c r="C227" s="61"/>
+      <c r="D227" s="61"/>
+      <c r="E227" s="61"/>
+      <c r="F227" s="62"/>
+      <c r="G227" s="61"/>
+      <c r="H227" s="62"/>
       <c r="I227" s="61"/>
       <c r="J227" s="15"/>
-      <c r="K227" s="22">
-        <v>0</v>
-      </c>
+      <c r="K227" s="22"/>
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
     <row r="228" spans="1:13" ht="14.25">
       <c r="A228" s="14">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B228" s="42"/>
       <c r="C228" s="61"/>
@@ -54212,7 +54170,7 @@
     </row>
     <row r="229" spans="1:13" ht="14.25">
       <c r="A229" s="14">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B229" s="42"/>
       <c r="C229" s="61"/>
@@ -54229,7 +54187,7 @@
     </row>
     <row r="230" spans="1:13" ht="14.25">
       <c r="A230" s="14">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B230" s="42"/>
       <c r="C230" s="61"/>
@@ -54246,7 +54204,7 @@
     </row>
     <row r="231" spans="1:13" ht="14.25">
       <c r="A231" s="14">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B231" s="42"/>
       <c r="C231" s="61"/>
@@ -54263,7 +54221,7 @@
     </row>
     <row r="232" spans="1:13" ht="14.25">
       <c r="A232" s="14">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B232" s="42"/>
       <c r="C232" s="61"/>
@@ -54280,7 +54238,7 @@
     </row>
     <row r="233" spans="1:13" ht="14.25">
       <c r="A233" s="14">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B233" s="42"/>
       <c r="C233" s="61"/>
@@ -54297,7 +54255,7 @@
     </row>
     <row r="234" spans="1:13" ht="14.25">
       <c r="A234" s="14">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B234" s="42"/>
       <c r="C234" s="61"/>
@@ -54314,7 +54272,7 @@
     </row>
     <row r="235" spans="1:13" ht="14.25">
       <c r="A235" s="14">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B235" s="42"/>
       <c r="C235" s="61"/>
@@ -54331,7 +54289,7 @@
     </row>
     <row r="236" spans="1:13" ht="14.25">
       <c r="A236" s="14">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B236" s="42"/>
       <c r="C236" s="61"/>
@@ -54348,7 +54306,7 @@
     </row>
     <row r="237" spans="1:13" ht="14.25">
       <c r="A237" s="14">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B237" s="42"/>
       <c r="C237" s="61"/>
@@ -54365,7 +54323,7 @@
     </row>
     <row r="238" spans="1:13" ht="14.25">
       <c r="A238" s="14">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B238" s="42"/>
       <c r="C238" s="61"/>
@@ -54382,7 +54340,7 @@
     </row>
     <row r="239" spans="1:13" ht="14.25">
       <c r="A239" s="14">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B239" s="42"/>
       <c r="C239" s="61"/>
@@ -54399,7 +54357,7 @@
     </row>
     <row r="240" spans="1:13" ht="14.25">
       <c r="A240" s="14">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B240" s="42"/>
       <c r="C240" s="61"/>
@@ -54416,7 +54374,7 @@
     </row>
     <row r="241" spans="1:13" ht="14.25">
       <c r="A241" s="14">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B241" s="42"/>
       <c r="C241" s="61"/>
@@ -54433,7 +54391,7 @@
     </row>
     <row r="242" spans="1:13" ht="14.25">
       <c r="A242" s="14">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B242" s="42"/>
       <c r="C242" s="61"/>
@@ -54450,7 +54408,7 @@
     </row>
     <row r="243" spans="1:13" ht="14.25">
       <c r="A243" s="14">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B243" s="42"/>
       <c r="C243" s="61"/>
@@ -54467,7 +54425,7 @@
     </row>
     <row r="244" spans="1:13" ht="14.25">
       <c r="A244" s="14">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B244" s="42"/>
       <c r="C244" s="61"/>
@@ -54484,7 +54442,7 @@
     </row>
     <row r="245" spans="1:13" ht="14.25">
       <c r="A245" s="14">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B245" s="42"/>
       <c r="C245" s="61"/>
@@ -54501,7 +54459,7 @@
     </row>
     <row r="246" spans="1:13" ht="14.25">
       <c r="A246" s="14">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B246" s="42"/>
       <c r="C246" s="61"/>
@@ -54518,7 +54476,7 @@
     </row>
     <row r="247" spans="1:13" ht="14.25">
       <c r="A247" s="14">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B247" s="42"/>
       <c r="C247" s="61"/>
@@ -54535,7 +54493,7 @@
     </row>
     <row r="248" spans="1:13" ht="14.25">
       <c r="A248" s="14">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B248" s="42"/>
       <c r="C248" s="61"/>
@@ -54552,7 +54510,7 @@
     </row>
     <row r="249" spans="1:13" ht="14.25">
       <c r="A249" s="14">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B249" s="42"/>
       <c r="C249" s="61"/>
@@ -54569,7 +54527,7 @@
     </row>
     <row r="250" spans="1:13" ht="14.25">
       <c r="A250" s="14">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B250" s="42"/>
       <c r="C250" s="61"/>
@@ -54586,7 +54544,7 @@
     </row>
     <row r="251" spans="1:13" ht="14.25">
       <c r="A251" s="14">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B251" s="42"/>
       <c r="C251" s="61"/>
@@ -54603,7 +54561,7 @@
     </row>
     <row r="252" spans="1:13" ht="14.25">
       <c r="A252" s="14">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B252" s="42"/>
       <c r="C252" s="61"/>
@@ -54620,7 +54578,7 @@
     </row>
     <row r="253" spans="1:13" ht="14.25">
       <c r="A253" s="14">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B253" s="42"/>
       <c r="C253" s="61"/>
@@ -54637,7 +54595,7 @@
     </row>
     <row r="254" spans="1:13" ht="14.25">
       <c r="A254" s="14">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B254" s="42"/>
       <c r="C254" s="61"/>
@@ -54654,7 +54612,7 @@
     </row>
     <row r="255" spans="1:13" ht="14.25">
       <c r="A255" s="14">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B255" s="42"/>
       <c r="C255" s="61"/>
@@ -54671,7 +54629,7 @@
     </row>
     <row r="256" spans="1:13" ht="14.25">
       <c r="A256" s="14">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B256" s="42"/>
       <c r="C256" s="61"/>
@@ -54688,7 +54646,7 @@
     </row>
     <row r="257" spans="1:13" ht="14.25">
       <c r="A257" s="14">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B257" s="42"/>
       <c r="C257" s="61"/>
@@ -54705,7 +54663,7 @@
     </row>
     <row r="258" spans="1:13" ht="14.25">
       <c r="A258" s="14">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B258" s="42"/>
       <c r="C258" s="61"/>
@@ -54722,7 +54680,7 @@
     </row>
     <row r="259" spans="1:13" ht="14.25">
       <c r="A259" s="14">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B259" s="42"/>
       <c r="C259" s="61"/>
@@ -54739,7 +54697,7 @@
     </row>
     <row r="260" spans="1:13" ht="14.25">
       <c r="A260" s="14">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B260" s="42"/>
       <c r="C260" s="61"/>
@@ -54750,39 +54708,39 @@
       <c r="H260" s="62"/>
       <c r="I260" s="61"/>
       <c r="J260" s="15"/>
-      <c r="K260" s="22"/>
+      <c r="K260" s="15"/>
       <c r="L260" s="15"/>
       <c r="M260" s="15"/>
     </row>
-    <row r="261" spans="1:13" ht="14.25">
+    <row r="261" spans="1:13">
       <c r="A261" s="14">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B261" s="42"/>
-      <c r="C261" s="61"/>
-      <c r="D261" s="61"/>
-      <c r="E261" s="61"/>
-      <c r="F261" s="62"/>
-      <c r="G261" s="61"/>
-      <c r="H261" s="62"/>
-      <c r="I261" s="61"/>
+      <c r="C261" s="12"/>
+      <c r="D261" s="12"/>
+      <c r="E261" s="12"/>
+      <c r="F261" s="13"/>
+      <c r="G261" s="12"/>
+      <c r="H261" s="13"/>
+      <c r="I261" s="15"/>
       <c r="J261" s="15"/>
-      <c r="K261" s="22"/>
+      <c r="K261" s="15"/>
       <c r="L261" s="15"/>
       <c r="M261" s="15"/>
     </row>
-    <row r="262" spans="1:13" ht="14.25">
+    <row r="262" spans="1:13">
       <c r="A262" s="14">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B262" s="42"/>
-      <c r="C262" s="61"/>
-      <c r="D262" s="61"/>
-      <c r="E262" s="61"/>
-      <c r="F262" s="62"/>
-      <c r="G262" s="61"/>
-      <c r="H262" s="62"/>
-      <c r="I262" s="61"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="12"/>
+      <c r="E262" s="12"/>
+      <c r="F262" s="13"/>
+      <c r="G262" s="12"/>
+      <c r="H262" s="13"/>
+      <c r="I262" s="15"/>
       <c r="J262" s="15"/>
       <c r="K262" s="15"/>
       <c r="L262" s="15"/>
@@ -54790,242 +54748,260 @@
     </row>
     <row r="263" spans="1:13">
       <c r="A263" s="14">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B263" s="42"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="12"/>
-      <c r="E263" s="12"/>
-      <c r="F263" s="13"/>
-      <c r="G263" s="12"/>
-      <c r="H263" s="13"/>
-      <c r="I263" s="15"/>
-      <c r="J263" s="15"/>
-      <c r="K263" s="15"/>
-      <c r="L263" s="15"/>
-      <c r="M263" s="15"/>
-    </row>
-    <row r="264" spans="1:13">
-      <c r="A264" s="14">
-        <v>277</v>
-      </c>
-      <c r="B264" s="42"/>
-      <c r="C264" s="12"/>
-      <c r="D264" s="12"/>
-      <c r="E264" s="12"/>
-      <c r="F264" s="13"/>
-      <c r="G264" s="12"/>
-      <c r="H264" s="13"/>
-      <c r="I264" s="15"/>
-      <c r="J264" s="15"/>
-      <c r="K264" s="15"/>
-      <c r="L264" s="15"/>
-      <c r="M264" s="15"/>
-    </row>
-    <row r="265" spans="1:13">
-      <c r="A265" s="14">
-        <v>278</v>
-      </c>
-      <c r="B265" s="42"/>
-      <c r="C265" s="19"/>
-      <c r="D265" s="19"/>
-      <c r="E265" s="19"/>
-      <c r="F265" s="20"/>
-      <c r="G265" s="19"/>
-      <c r="H265" s="20"/>
-      <c r="I265" s="21"/>
-      <c r="J265" s="21"/>
-      <c r="K265" s="21"/>
-      <c r="L265" s="21"/>
-      <c r="M265" s="21"/>
+      <c r="C263" s="19"/>
+      <c r="D263" s="19"/>
+      <c r="E263" s="19"/>
+      <c r="F263" s="20"/>
+      <c r="G263" s="19"/>
+      <c r="H263" s="20"/>
+      <c r="I263" s="21"/>
+      <c r="J263" s="21"/>
+      <c r="K263" s="21"/>
+      <c r="L263" s="21"/>
+      <c r="M263" s="21"/>
+    </row>
+    <row r="274" spans="10:11">
+      <c r="J274" t="s">
+        <v>384</v>
+      </c>
+      <c r="K274" s="11">
+        <f>SUM(テーブル4[料金])</f>
+        <v>1363524</v>
+      </c>
+    </row>
+    <row r="275" spans="10:11">
+      <c r="J275" t="s">
+        <v>385</v>
+      </c>
+      <c r="K275">
+        <f>COUNTA(テーブル4[料金])*5</f>
+        <v>1100</v>
+      </c>
     </row>
     <row r="276" spans="10:11">
       <c r="J276" t="s">
-        <v>386</v>
-      </c>
-      <c r="K276" s="11">
-        <f>SUM(テーブル4[料金])</f>
-        <v>1363524</v>
+        <v>5</v>
+      </c>
+      <c r="K276">
+        <f>COUNTA(テーブル4[料金])</f>
+        <v>220</v>
       </c>
     </row>
     <row r="277" spans="10:11">
       <c r="J277" t="s">
+        <v>386</v>
+      </c>
+      <c r="K277" s="41">
+        <f>K274/K275</f>
+        <v>1239.5672727272727</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="B289" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C289" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D289" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E289" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F289" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G289" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H289" s="24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290">
+        <v>1</v>
+      </c>
+      <c r="B290" t="s">
+        <v>304</v>
+      </c>
+      <c r="C290">
+        <v>51</v>
+      </c>
+      <c r="D290" t="s">
+        <v>295</v>
+      </c>
+      <c r="E290" s="25">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F290" t="s">
+        <v>305</v>
+      </c>
+      <c r="G290" s="25">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="H290" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291">
+        <v>2</v>
+      </c>
+      <c r="B291" t="s">
+        <v>309</v>
+      </c>
+      <c r="C291">
+        <v>873</v>
+      </c>
+      <c r="D291" t="s">
+        <v>305</v>
+      </c>
+      <c r="E291" s="25">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="F291" t="s">
+        <v>331</v>
+      </c>
+      <c r="G291" s="25">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="H291" t="s">
         <v>387</v>
-      </c>
-      <c r="K277">
-        <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="278" spans="10:11">
-      <c r="J278" t="s">
-        <v>5</v>
-      </c>
-      <c r="K278">
-        <f>COUNTA(テーブル4[料金])</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="279" spans="10:11">
-      <c r="J279" t="s">
-        <v>388</v>
-      </c>
-      <c r="K279" s="41">
-        <f>K276/K277</f>
-        <v>1239.5672727272727</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8">
-      <c r="A291" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="B291" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C291" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D291" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="E291" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F291" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="G291" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="H291" s="24" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B292" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C292">
-        <v>51</v>
+        <v>874</v>
       </c>
       <c r="D292" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E292" s="25">
-        <v>0.2986111111111111</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F292" t="s">
         <v>305</v>
       </c>
       <c r="G292" s="25">
-        <v>0.36805555555555558</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="H292" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B293" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C293">
-        <v>873</v>
+        <v>609</v>
       </c>
       <c r="D293" t="s">
         <v>305</v>
       </c>
       <c r="E293" s="25">
-        <v>0.41319444444444442</v>
+        <v>0.53472222222222221</v>
       </c>
       <c r="F293" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="G293" s="25">
-        <v>0.43402777777777779</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="H293" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B294" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C294">
-        <v>874</v>
+        <v>614</v>
       </c>
       <c r="D294" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="E294" s="25">
-        <v>0.45833333333333331</v>
+        <v>0.60069444444444442</v>
       </c>
       <c r="F294" t="s">
         <v>305</v>
       </c>
       <c r="G294" s="25">
-        <v>0.4826388888888889</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="H294" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B295" t="s">
         <v>304</v>
       </c>
       <c r="C295">
-        <v>609</v>
+        <v>567</v>
       </c>
       <c r="D295" t="s">
         <v>305</v>
       </c>
       <c r="E295" s="25">
-        <v>0.53472222222222221</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="F295" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G295" s="25">
-        <v>0.57291666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="H295" t="s">
-        <v>390</v>
+        <v>306</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B296" t="s">
         <v>304</v>
       </c>
       <c r="C296">
-        <v>614</v>
+        <v>566</v>
       </c>
       <c r="D296" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E296" s="25">
-        <v>0.60069444444444442</v>
+        <v>0.73611111111111116</v>
       </c>
       <c r="F296" t="s">
         <v>305</v>
       </c>
       <c r="G296" s="25">
-        <v>0.64583333333333337</v>
+        <v>0.77430555555555558</v>
       </c>
       <c r="H296" t="s">
         <v>306</v>
@@ -55033,392 +55009,394 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B297" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C297">
-        <v>567</v>
+        <v>920</v>
       </c>
       <c r="D297" t="s">
         <v>305</v>
       </c>
       <c r="E297" s="25">
-        <v>0.67361111111111116</v>
+        <v>0.80902777777777779</v>
       </c>
       <c r="F297" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="G297" s="25">
-        <v>0.70833333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="H297" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="B300" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C300" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D300" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E300" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F300" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G300" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H300" s="24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301">
+        <v>1</v>
+      </c>
+      <c r="B301" t="s">
+        <v>304</v>
+      </c>
+      <c r="C301">
+        <v>51</v>
+      </c>
+      <c r="D301" t="s">
+        <v>295</v>
+      </c>
+      <c r="E301" s="25">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+      <c r="G301" s="25">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="H301" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302">
+        <v>2</v>
+      </c>
+      <c r="B302" t="s">
+        <v>304</v>
+      </c>
+      <c r="C302">
+        <v>605</v>
+      </c>
+      <c r="D302" t="s">
+        <v>305</v>
+      </c>
+      <c r="E302" s="25">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F302" t="s">
+        <v>308</v>
+      </c>
+      <c r="G302" s="25">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="H302" t="s">
         <v>306</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
-      <c r="A298">
-        <v>7</v>
-      </c>
-      <c r="B298" t="s">
-        <v>304</v>
-      </c>
-      <c r="C298">
-        <v>566</v>
-      </c>
-      <c r="D298" t="s">
-        <v>312</v>
-      </c>
-      <c r="E298" s="25">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F298" t="s">
-        <v>305</v>
-      </c>
-      <c r="G298" s="25">
-        <v>0.77430555555555558</v>
-      </c>
-      <c r="H298" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8">
-      <c r="A299">
-        <v>8</v>
-      </c>
-      <c r="B299" t="s">
-        <v>293</v>
-      </c>
-      <c r="C299">
-        <v>920</v>
-      </c>
-      <c r="D299" t="s">
-        <v>305</v>
-      </c>
-      <c r="E299" s="25">
-        <v>0.80902777777777779</v>
-      </c>
-      <c r="F299" t="s">
-        <v>294</v>
-      </c>
-      <c r="G299" s="25">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="H299" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
-      <c r="A302" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="B302" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C302" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D302" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="E302" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F302" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="G302" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="H302" s="24" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B303" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C303">
-        <v>51</v>
+        <v>743</v>
       </c>
       <c r="D303" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E303" s="25">
-        <v>0.2986111111111111</v>
+        <v>0.52430555555555558</v>
       </c>
       <c r="F303" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G303" s="25">
-        <v>0.36805555555555558</v>
+        <v>0.54513888888888884</v>
       </c>
       <c r="H303" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C304">
-        <v>605</v>
+        <v>744</v>
       </c>
       <c r="D304" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E304" s="25">
-        <v>0.39583333333333331</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="F304" t="s">
         <v>308</v>
       </c>
       <c r="G304" s="25">
-        <v>0.43402777777777779</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="H304" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B305" t="s">
         <v>309</v>
       </c>
       <c r="C305">
-        <v>743</v>
+        <v>834</v>
       </c>
       <c r="D305" t="s">
         <v>308</v>
       </c>
       <c r="E305" s="25">
-        <v>0.52430555555555558</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="F305" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G305" s="25">
-        <v>0.54513888888888884</v>
+        <v>0.63194444444444442</v>
       </c>
       <c r="H305" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B306" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C306">
-        <v>744</v>
+        <v>564</v>
       </c>
       <c r="D306" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E306" s="25">
-        <v>0.56597222222222221</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="F306" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G306" s="25">
-        <v>0.58680555555555558</v>
+        <v>0.73611111111111116</v>
       </c>
       <c r="H306" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B307" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="C307">
-        <v>834</v>
+        <v>920</v>
       </c>
       <c r="D307" t="s">
+        <v>305</v>
+      </c>
+      <c r="E307" s="25">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="F307" t="s">
+        <v>294</v>
+      </c>
+      <c r="G307" s="25">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H307" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="14.25">
+      <c r="A309" s="48">
+        <v>1</v>
+      </c>
+      <c r="B309" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="C309" s="49">
+        <v>901</v>
+      </c>
+      <c r="D309" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="E309" s="50">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="F309" s="49" t="s">
+        <v>305</v>
+      </c>
+      <c r="G309" s="50">
+        <v>0.375</v>
+      </c>
+      <c r="H309" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="I309" s="52"/>
+    </row>
+    <row r="310" spans="1:9" ht="14.25">
+      <c r="A310" s="53">
+        <v>2</v>
+      </c>
+      <c r="B310" s="54" t="s">
+        <v>304</v>
+      </c>
+      <c r="C310" s="54">
+        <v>605</v>
+      </c>
+      <c r="D310" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="E310" s="55">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="F310" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="E307" s="25">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="F307" t="s">
-        <v>312</v>
-      </c>
-      <c r="G307" s="25">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="H307" t="s">
+      <c r="G310" s="55">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="H310" s="54" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="308" spans="1:9">
-      <c r="A308">
-        <v>6</v>
-      </c>
-      <c r="B308" t="s">
-        <v>304</v>
-      </c>
-      <c r="C308">
-        <v>564</v>
-      </c>
-      <c r="D308" t="s">
-        <v>312</v>
-      </c>
-      <c r="E308" s="25">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F308" t="s">
-        <v>305</v>
-      </c>
-      <c r="G308" s="25">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="H308" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9">
-      <c r="A309">
-        <v>7</v>
-      </c>
-      <c r="B309" t="s">
-        <v>293</v>
-      </c>
-      <c r="C309">
-        <v>920</v>
-      </c>
-      <c r="D309" t="s">
-        <v>305</v>
-      </c>
-      <c r="E309" s="25">
-        <v>0.80902777777777779</v>
-      </c>
-      <c r="F309" t="s">
-        <v>294</v>
-      </c>
-      <c r="G309" s="25">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="H309" t="s">
-        <v>324</v>
-      </c>
+      <c r="I310" s="56"/>
     </row>
     <row r="311" spans="1:9" ht="14.25">
       <c r="A311" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B311" s="49" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="C311" s="49">
-        <v>901</v>
+        <v>743</v>
       </c>
       <c r="D311" s="49" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E311" s="50">
-        <v>0.27083333333333331</v>
+        <v>0.52430555555555558</v>
       </c>
       <c r="F311" s="49" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G311" s="50">
-        <v>0.375</v>
-      </c>
-      <c r="H311" s="51" t="s">
-        <v>392</v>
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="H311" s="49" t="s">
+        <v>391</v>
       </c>
       <c r="I311" s="52"/>
     </row>
     <row r="312" spans="1:9" ht="14.25">
       <c r="A312" s="53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B312" s="54" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C312" s="54">
-        <v>605</v>
+        <v>744</v>
       </c>
       <c r="D312" s="54" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E312" s="55">
-        <v>0.39930555555555558</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="F312" s="54" t="s">
         <v>308</v>
       </c>
       <c r="G312" s="55">
-        <v>0.44097222222222221</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="H312" s="54" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I312" s="56"/>
     </row>
     <row r="313" spans="1:9" ht="14.25">
       <c r="A313" s="48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B313" s="49" t="s">
         <v>309</v>
       </c>
       <c r="C313" s="49">
-        <v>743</v>
+        <v>834</v>
       </c>
       <c r="D313" s="49" t="s">
         <v>308</v>
       </c>
       <c r="E313" s="50">
-        <v>0.52430555555555558</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="F313" s="49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G313" s="50">
-        <v>0.54513888888888884</v>
+        <v>0.63194444444444442</v>
       </c>
       <c r="H313" s="49" t="s">
-        <v>393</v>
+        <v>301</v>
       </c>
       <c r="I313" s="52"/>
     </row>
     <row r="314" spans="1:9" ht="14.25">
       <c r="A314" s="53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B314" s="54" t="s">
         <v>309</v>
       </c>
       <c r="C314" s="54">
-        <v>744</v>
+        <v>897</v>
       </c>
       <c r="D314" s="54" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E314" s="55">
-        <v>0.56597222222222221</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="F314" s="54" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G314" s="55">
-        <v>0.58680555555555558</v>
+        <v>0.67013888888888884</v>
       </c>
       <c r="H314" s="54" t="s">
         <v>303</v>
@@ -55427,25 +55405,25 @@
     </row>
     <row r="315" spans="1:9" ht="14.25">
       <c r="A315" s="48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B315" s="49" t="s">
         <v>309</v>
       </c>
       <c r="C315" s="49">
-        <v>834</v>
+        <v>898</v>
       </c>
       <c r="D315" s="49" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E315" s="50">
-        <v>0.61111111111111116</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="F315" s="49" t="s">
         <v>312</v>
       </c>
       <c r="G315" s="50">
-        <v>0.63194444444444442</v>
+        <v>0.71180555555555558</v>
       </c>
       <c r="H315" s="49" t="s">
         <v>301</v>
@@ -55454,111 +55432,57 @@
     </row>
     <row r="316" spans="1:9" ht="14.25">
       <c r="A316" s="53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B316" s="54" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C316" s="54">
-        <v>897</v>
+        <v>572</v>
       </c>
       <c r="D316" s="54" t="s">
         <v>312</v>
       </c>
       <c r="E316" s="55">
-        <v>0.65277777777777779</v>
+        <v>0.74652777777777779</v>
       </c>
       <c r="F316" s="54" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G316" s="55">
-        <v>0.67013888888888884</v>
+        <v>0.78472222222222221</v>
       </c>
       <c r="H316" s="54" t="s">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="I316" s="56"/>
     </row>
     <row r="317" spans="1:9" ht="14.25">
-      <c r="A317" s="48">
-        <v>7</v>
-      </c>
-      <c r="B317" s="49" t="s">
-        <v>309</v>
-      </c>
-      <c r="C317" s="49">
-        <v>898</v>
-      </c>
-      <c r="D317" s="49" t="s">
-        <v>313</v>
-      </c>
-      <c r="E317" s="50">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="F317" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="G317" s="50">
-        <v>0.71180555555555558</v>
-      </c>
-      <c r="H317" s="49" t="s">
-        <v>301</v>
-      </c>
-      <c r="I317" s="52"/>
-    </row>
-    <row r="318" spans="1:9" ht="14.25">
-      <c r="A318" s="53">
-        <v>8</v>
-      </c>
-      <c r="B318" s="54" t="s">
-        <v>304</v>
-      </c>
-      <c r="C318" s="54">
-        <v>572</v>
-      </c>
-      <c r="D318" s="54" t="s">
-        <v>312</v>
-      </c>
-      <c r="E318" s="55">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="F318" s="54" t="s">
+      <c r="A317" s="57">
+        <v>9</v>
+      </c>
+      <c r="B317" s="58" t="s">
+        <v>293</v>
+      </c>
+      <c r="C317" s="58">
+        <v>920</v>
+      </c>
+      <c r="D317" s="58" t="s">
         <v>305</v>
       </c>
-      <c r="G318" s="55">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="H318" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="I318" s="56"/>
-    </row>
-    <row r="319" spans="1:9" ht="14.25">
-      <c r="A319" s="57">
-        <v>9</v>
-      </c>
-      <c r="B319" s="58" t="s">
-        <v>293</v>
-      </c>
-      <c r="C319" s="58">
-        <v>920</v>
-      </c>
-      <c r="D319" s="58" t="s">
-        <v>305</v>
-      </c>
-      <c r="E319" s="59">
+      <c r="E317" s="59">
         <v>0.8125</v>
       </c>
-      <c r="F319" s="58" t="s">
+      <c r="F317" s="58" t="s">
         <v>294</v>
       </c>
-      <c r="G319" s="59">
+      <c r="G317" s="59">
         <v>0.91666666666666663</v>
       </c>
-      <c r="H319" s="58" t="s">
+      <c r="H317" s="58" t="s">
         <v>306</v>
       </c>
-      <c r="I319" s="60"/>
+      <c r="I317" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBC03660-AFE8-4A7A-9052-366499B9E7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84726649-ED8F-45D3-B7E3-A504ADBCFE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -43183,39 +43183,448 @@
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
   <mergeCells count="499">
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B726:E726"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B651:E651"/>
+    <mergeCell ref="B695:E695"/>
+    <mergeCell ref="B696:E696"/>
+    <mergeCell ref="B697:E697"/>
+    <mergeCell ref="B698:E698"/>
+    <mergeCell ref="B699:E699"/>
+    <mergeCell ref="B701:E701"/>
+    <mergeCell ref="B657:E657"/>
+    <mergeCell ref="B658:E658"/>
+    <mergeCell ref="B659:E659"/>
+    <mergeCell ref="B660:E660"/>
+    <mergeCell ref="B667:E667"/>
+    <mergeCell ref="B668:E668"/>
+    <mergeCell ref="B669:E669"/>
+    <mergeCell ref="B670:E670"/>
+    <mergeCell ref="B671:E671"/>
+    <mergeCell ref="B672:E672"/>
+    <mergeCell ref="B673:E673"/>
+    <mergeCell ref="B674:E674"/>
+    <mergeCell ref="B675:E675"/>
+    <mergeCell ref="B687:E687"/>
+    <mergeCell ref="B688:E688"/>
+    <mergeCell ref="B691:E691"/>
+    <mergeCell ref="B692:E692"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
     <mergeCell ref="B594:E594"/>
     <mergeCell ref="B627:E627"/>
     <mergeCell ref="B647:E647"/>
@@ -43240,448 +43649,39 @@
     <mergeCell ref="B624:E624"/>
     <mergeCell ref="B625:E625"/>
     <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B651:E651"/>
-    <mergeCell ref="B695:E695"/>
-    <mergeCell ref="B696:E696"/>
-    <mergeCell ref="B697:E697"/>
-    <mergeCell ref="B698:E698"/>
-    <mergeCell ref="B699:E699"/>
-    <mergeCell ref="B701:E701"/>
-    <mergeCell ref="B657:E657"/>
-    <mergeCell ref="B658:E658"/>
-    <mergeCell ref="B659:E659"/>
-    <mergeCell ref="B660:E660"/>
-    <mergeCell ref="B667:E667"/>
-    <mergeCell ref="B668:E668"/>
-    <mergeCell ref="B669:E669"/>
-    <mergeCell ref="B670:E670"/>
-    <mergeCell ref="B671:E671"/>
-    <mergeCell ref="B672:E672"/>
-    <mergeCell ref="B673:E673"/>
-    <mergeCell ref="B674:E674"/>
-    <mergeCell ref="B675:E675"/>
-    <mergeCell ref="B687:E687"/>
-    <mergeCell ref="B688:E688"/>
-    <mergeCell ref="B691:E691"/>
-    <mergeCell ref="B692:E692"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30219"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84726649-ED8F-45D3-B7E3-A504ADBCFE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1793B22-65D6-4830-907D-B3B2E1BB56D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2974" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="397">
   <si>
     <t>日付</t>
   </si>
@@ -1216,6 +1216,9 @@
     <t>JAL630</t>
   </si>
   <si>
+    <t>JAL481</t>
+  </si>
+  <si>
     <t>総額</t>
   </si>
   <si>
@@ -2403,10 +2406,10 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6842</c:v>
+                  <c:v>6884</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>141</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15042,7 +15045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O726"/>
+  <dimension ref="A1:O733"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15610,7 +15613,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>6842</v>
+        <v>6884</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15660,7 +15663,7 @@
       </c>
       <c r="O17">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＪＭＢアプリ*")</f>
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1">
@@ -15852,7 +15855,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>168129</v>
+        <v>168174</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -43144,31 +43147,31 @@
       </c>
     </row>
     <row r="726" spans="1:13">
-      <c r="A726" s="29">
+      <c r="A726" s="27">
         <v>46196</v>
       </c>
-      <c r="B726" s="78" t="s">
+      <c r="B726" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C726" s="78"/>
-      <c r="D726" s="78"/>
-      <c r="E726" s="79"/>
-      <c r="F726" s="75">
-        <v>0</v>
-      </c>
-      <c r="G726" s="75">
+      <c r="C726" s="76"/>
+      <c r="D726" s="76"/>
+      <c r="E726" s="77"/>
+      <c r="F726" s="74">
+        <v>0</v>
+      </c>
+      <c r="G726" s="74">
         <v>8</v>
       </c>
-      <c r="H726" s="75">
+      <c r="H726" s="74">
         <v>8</v>
       </c>
-      <c r="I726" s="30">
+      <c r="I726" s="4">
         <v>81564</v>
       </c>
-      <c r="J726" s="75">
-        <v>0</v>
-      </c>
-      <c r="K726" s="75">
+      <c r="J726" s="74">
+        <v>0</v>
+      </c>
+      <c r="K726" s="74">
         <v>0</v>
       </c>
       <c r="L726" s="74">
@@ -43180,9 +43183,750 @@
         <v>133</v>
       </c>
     </row>
+    <row r="727" spans="1:13">
+      <c r="A727" s="27">
+        <v>46197</v>
+      </c>
+      <c r="B727" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C727" s="76"/>
+      <c r="D727" s="76"/>
+      <c r="E727" s="77"/>
+      <c r="F727" s="74">
+        <v>0</v>
+      </c>
+      <c r="G727" s="74">
+        <v>12</v>
+      </c>
+      <c r="H727" s="74">
+        <v>12</v>
+      </c>
+      <c r="I727" s="4">
+        <v>81576</v>
+      </c>
+      <c r="J727" s="74">
+        <v>0</v>
+      </c>
+      <c r="K727" s="74">
+        <v>0</v>
+      </c>
+      <c r="L727" s="74">
+        <f t="shared" ref="L727:L733" si="104">J727+L726</f>
+        <v>85476</v>
+      </c>
+      <c r="M727" s="74">
+        <f t="shared" ref="M727:M733" si="105">K727+M726</f>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="728" spans="1:13">
+      <c r="A728" s="27">
+        <v>46198</v>
+      </c>
+      <c r="B728" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C728" s="76"/>
+      <c r="D728" s="76"/>
+      <c r="E728" s="77"/>
+      <c r="F728" s="74">
+        <v>0</v>
+      </c>
+      <c r="G728" s="74">
+        <v>10</v>
+      </c>
+      <c r="H728" s="74">
+        <v>10</v>
+      </c>
+      <c r="I728" s="4">
+        <v>81586</v>
+      </c>
+      <c r="J728" s="74">
+        <v>0</v>
+      </c>
+      <c r="K728" s="74">
+        <v>0</v>
+      </c>
+      <c r="L728" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M728" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="729" spans="1:13">
+      <c r="A729" s="27">
+        <v>46199</v>
+      </c>
+      <c r="B729" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C729" s="76"/>
+      <c r="D729" s="76"/>
+      <c r="E729" s="77"/>
+      <c r="F729" s="74">
+        <v>0</v>
+      </c>
+      <c r="G729" s="74">
+        <v>1</v>
+      </c>
+      <c r="H729" s="74">
+        <v>1</v>
+      </c>
+      <c r="I729" s="4">
+        <v>81587</v>
+      </c>
+      <c r="J729" s="74">
+        <v>0</v>
+      </c>
+      <c r="K729" s="74">
+        <v>0</v>
+      </c>
+      <c r="L729" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M729" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="730" spans="1:13">
+      <c r="A730" s="27">
+        <v>46199</v>
+      </c>
+      <c r="B730" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C730" s="76"/>
+      <c r="D730" s="76"/>
+      <c r="E730" s="77"/>
+      <c r="F730" s="74">
+        <v>0</v>
+      </c>
+      <c r="G730" s="74">
+        <v>11</v>
+      </c>
+      <c r="H730" s="74">
+        <v>11</v>
+      </c>
+      <c r="I730" s="4">
+        <v>81598</v>
+      </c>
+      <c r="J730" s="74">
+        <v>0</v>
+      </c>
+      <c r="K730" s="74">
+        <v>0</v>
+      </c>
+      <c r="L730" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M730" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="731" spans="1:13">
+      <c r="A731" s="27">
+        <v>46199</v>
+      </c>
+      <c r="B731" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C731" s="76"/>
+      <c r="D731" s="76"/>
+      <c r="E731" s="77"/>
+      <c r="F731" s="74">
+        <v>0</v>
+      </c>
+      <c r="G731" s="74">
+        <v>1</v>
+      </c>
+      <c r="H731" s="74">
+        <v>1</v>
+      </c>
+      <c r="I731" s="4">
+        <v>81599</v>
+      </c>
+      <c r="J731" s="74">
+        <v>0</v>
+      </c>
+      <c r="K731" s="74">
+        <v>0</v>
+      </c>
+      <c r="L731" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M731" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="732" spans="1:13">
+      <c r="A732" s="27">
+        <v>46199</v>
+      </c>
+      <c r="B732" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C732" s="76"/>
+      <c r="D732" s="76"/>
+      <c r="E732" s="77"/>
+      <c r="F732" s="74">
+        <v>0</v>
+      </c>
+      <c r="G732" s="74">
+        <v>1</v>
+      </c>
+      <c r="H732" s="74">
+        <v>1</v>
+      </c>
+      <c r="I732" s="4">
+        <v>81600</v>
+      </c>
+      <c r="J732" s="74">
+        <v>0</v>
+      </c>
+      <c r="K732" s="74">
+        <v>0</v>
+      </c>
+      <c r="L732" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M732" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="733" spans="1:13">
+      <c r="A733" s="29">
+        <v>46200</v>
+      </c>
+      <c r="B733" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C733" s="78"/>
+      <c r="D733" s="78"/>
+      <c r="E733" s="79"/>
+      <c r="F733" s="75">
+        <v>0</v>
+      </c>
+      <c r="G733" s="75">
+        <v>9</v>
+      </c>
+      <c r="H733" s="75">
+        <v>9</v>
+      </c>
+      <c r="I733" s="30">
+        <v>81609</v>
+      </c>
+      <c r="J733" s="75">
+        <v>0</v>
+      </c>
+      <c r="K733" s="75">
+        <v>0</v>
+      </c>
+      <c r="L733" s="74">
+        <f t="shared" si="104"/>
+        <v>85476</v>
+      </c>
+      <c r="M733" s="74">
+        <f t="shared" si="105"/>
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="499">
+  <mergeCells count="506">
+    <mergeCell ref="B727:E727"/>
+    <mergeCell ref="B728:E728"/>
+    <mergeCell ref="B729:E729"/>
+    <mergeCell ref="B730:E730"/>
+    <mergeCell ref="B731:E731"/>
+    <mergeCell ref="B732:E732"/>
+    <mergeCell ref="B733:E733"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B594:E594"/>
+    <mergeCell ref="B627:E627"/>
+    <mergeCell ref="B647:E647"/>
+    <mergeCell ref="B661:E661"/>
+    <mergeCell ref="B662:E662"/>
+    <mergeCell ref="B663:E663"/>
+    <mergeCell ref="B664:E664"/>
+    <mergeCell ref="B665:E665"/>
+    <mergeCell ref="B666:E666"/>
+    <mergeCell ref="B633:E633"/>
+    <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B635:E635"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
     <mergeCell ref="B651:E651"/>
     <mergeCell ref="B695:E695"/>
     <mergeCell ref="B696:E696"/>
@@ -43207,481 +43951,6 @@
     <mergeCell ref="B688:E688"/>
     <mergeCell ref="B691:E691"/>
     <mergeCell ref="B692:E692"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B594:E594"/>
-    <mergeCell ref="B627:E627"/>
-    <mergeCell ref="B647:E647"/>
-    <mergeCell ref="B661:E661"/>
-    <mergeCell ref="B662:E662"/>
-    <mergeCell ref="B663:E663"/>
-    <mergeCell ref="B664:E664"/>
-    <mergeCell ref="B665:E665"/>
-    <mergeCell ref="B666:E666"/>
-    <mergeCell ref="B633:E633"/>
-    <mergeCell ref="B634:E634"/>
-    <mergeCell ref="B635:E635"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B621:E621"/>
-    <mergeCell ref="B622:E622"/>
-    <mergeCell ref="B623:E623"/>
-    <mergeCell ref="B624:E624"/>
-    <mergeCell ref="B625:E625"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B726:E726"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -55551,40 +55820,78 @@
       <c r="K226" s="22">
         <v>0</v>
       </c>
-      <c r="L226" s="15"/>
+      <c r="L226" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" ht="14.25">
+    <row r="227" spans="1:13">
       <c r="A227" s="14">
         <v>242</v>
       </c>
-      <c r="B227" s="42"/>
-      <c r="C227" s="61"/>
-      <c r="D227" s="61"/>
-      <c r="E227" s="61"/>
-      <c r="F227" s="62"/>
-      <c r="G227" s="61"/>
-      <c r="H227" s="62"/>
-      <c r="I227" s="61"/>
-      <c r="J227" s="15"/>
-      <c r="K227" s="22"/>
+      <c r="B227" s="42">
+        <v>46215</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F227" s="13">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="G227" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="H227" s="13">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="I227" s="26"/>
+      <c r="J227" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K227" s="22">
+        <v>0</v>
+      </c>
       <c r="L227" s="15"/>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13" ht="14.25">
+    <row r="228" spans="1:13">
       <c r="A228" s="14">
         <v>243</v>
       </c>
-      <c r="B228" s="42"/>
-      <c r="C228" s="61"/>
-      <c r="D228" s="61"/>
-      <c r="E228" s="61"/>
-      <c r="F228" s="62"/>
-      <c r="G228" s="61"/>
-      <c r="H228" s="62"/>
-      <c r="I228" s="61"/>
-      <c r="J228" s="15"/>
-      <c r="K228" s="22"/>
+      <c r="B228" s="42">
+        <v>46217</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="F228" s="13">
+        <v>0.85763888888888884</v>
+      </c>
+      <c r="G228" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="H228" s="13">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="I228" s="26"/>
+      <c r="J228" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K228" s="22">
+        <v>0</v>
+      </c>
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
@@ -56185,7 +56492,7 @@
     </row>
     <row r="274" spans="10:11">
       <c r="J274" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K274" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -56194,11 +56501,11 @@
     </row>
     <row r="275" spans="10:11">
       <c r="J275" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K275">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1105</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="276" spans="10:11">
@@ -56207,16 +56514,16 @@
       </c>
       <c r="K276">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="277" spans="10:11">
       <c r="J277" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K277" s="41">
         <f>K274/K275</f>
-        <v>1233.9583710407239</v>
+        <v>1222.8914798206279</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -56294,7 +56601,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H291" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -56346,7 +56653,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H293" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -56450,7 +56757,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H297" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -56684,7 +56991,7 @@
         <v>0.375</v>
       </c>
       <c r="H309" s="51" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I309" s="52"/>
     </row>
@@ -56738,7 +57045,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H311" s="49" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I311" s="52"/>
     </row>
@@ -56873,7 +57180,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H316" s="54" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I316" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1793B22-65D6-4830-907D-B3B2E1BB56D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B253F34-1BD6-465A-B220-1B923CA0921D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="403">
   <si>
     <t>日付</t>
   </si>
@@ -1219,6 +1219,24 @@
     <t>JAL481</t>
   </si>
   <si>
+    <t>JAL503</t>
+  </si>
+  <si>
+    <t>札幌（新千歳）</t>
+  </si>
+  <si>
+    <t>JAL524</t>
+  </si>
+  <si>
+    <t>JAL153</t>
+  </si>
+  <si>
+    <t>三沢</t>
+  </si>
+  <si>
+    <t>JAL158</t>
+  </si>
+  <si>
     <t>総額</t>
   </si>
   <si>
@@ -2394,7 +2412,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0" formatCode="#,##0">
-                  <c:v>128359</c:v>
+                  <c:v>129223</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>60787</c:v>
@@ -2406,7 +2424,7 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6884</c:v>
+                  <c:v>6914</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>144</c:v>
@@ -15045,7 +15063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O733"/>
+  <dimension ref="A1:O735"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15441,7 +15459,7 @@
       </c>
       <c r="O12" s="11">
         <f>SUMIFS(H2:H29999, B2:B29999, "*JL*")+SUMIFS(H11:H29999, B11:B29999, "*NU*")</f>
-        <v>128359</v>
+        <v>129223</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -15613,7 +15631,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>6884</v>
+        <v>6914</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15855,7 +15873,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>168174</v>
+        <v>169068</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -43261,37 +43279,43 @@
       <c r="A729" s="27">
         <v>46199</v>
       </c>
-      <c r="B729" s="76" t="s">
-        <v>49</v>
-      </c>
-      <c r="C729" s="76"/>
-      <c r="D729" s="76"/>
-      <c r="E729" s="77"/>
+      <c r="B729" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D729" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="F729" s="74">
-        <v>0</v>
-      </c>
-      <c r="G729" s="74">
+        <v>354</v>
+      </c>
+      <c r="G729" s="28">
+        <v>510</v>
+      </c>
+      <c r="H729" s="74">
+        <v>864</v>
+      </c>
+      <c r="I729" s="4">
+        <v>82450</v>
+      </c>
+      <c r="J729" s="4">
+        <v>1108</v>
+      </c>
+      <c r="K729" s="74">
         <v>1</v>
-      </c>
-      <c r="H729" s="74">
-        <v>1</v>
-      </c>
-      <c r="I729" s="4">
-        <v>81587</v>
-      </c>
-      <c r="J729" s="74">
-        <v>0</v>
-      </c>
-      <c r="K729" s="74">
-        <v>0</v>
       </c>
       <c r="L729" s="74">
         <f t="shared" si="104"/>
-        <v>85476</v>
+        <v>86584</v>
       </c>
       <c r="M729" s="74">
         <f t="shared" si="105"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="730" spans="1:13">
@@ -43299,7 +43323,7 @@
         <v>46199</v>
       </c>
       <c r="B730" s="76" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C730" s="76"/>
       <c r="D730" s="76"/>
@@ -43308,13 +43332,13 @@
         <v>0</v>
       </c>
       <c r="G730" s="74">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H730" s="74">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I730" s="4">
-        <v>81598</v>
+        <v>82451</v>
       </c>
       <c r="J730" s="74">
         <v>0</v>
@@ -43324,11 +43348,11 @@
       </c>
       <c r="L730" s="74">
         <f t="shared" si="104"/>
-        <v>85476</v>
+        <v>86584</v>
       </c>
       <c r="M730" s="74">
         <f t="shared" si="105"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="731" spans="1:13">
@@ -43336,7 +43360,7 @@
         <v>46199</v>
       </c>
       <c r="B731" s="76" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C731" s="76"/>
       <c r="D731" s="76"/>
@@ -43345,13 +43369,13 @@
         <v>0</v>
       </c>
       <c r="G731" s="74">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H731" s="74">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I731" s="4">
-        <v>81599</v>
+        <v>82462</v>
       </c>
       <c r="J731" s="74">
         <v>0</v>
@@ -43361,11 +43385,11 @@
       </c>
       <c r="L731" s="74">
         <f t="shared" si="104"/>
-        <v>85476</v>
+        <v>86584</v>
       </c>
       <c r="M731" s="74">
         <f t="shared" si="105"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="732" spans="1:13">
@@ -43388,7 +43412,7 @@
         <v>1</v>
       </c>
       <c r="I732" s="4">
-        <v>81600</v>
+        <v>82463</v>
       </c>
       <c r="J732" s="74">
         <v>0</v>
@@ -43398,56 +43422,131 @@
       </c>
       <c r="L732" s="74">
         <f t="shared" si="104"/>
-        <v>85476</v>
+        <v>86584</v>
       </c>
       <c r="M732" s="74">
         <f t="shared" si="105"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="733" spans="1:13">
-      <c r="A733" s="29">
-        <v>46200</v>
-      </c>
-      <c r="B733" s="78" t="s">
-        <v>33</v>
-      </c>
-      <c r="C733" s="78"/>
-      <c r="D733" s="78"/>
-      <c r="E733" s="79"/>
-      <c r="F733" s="75">
-        <v>0</v>
-      </c>
-      <c r="G733" s="75">
-        <v>9</v>
-      </c>
-      <c r="H733" s="75">
-        <v>9</v>
-      </c>
-      <c r="I733" s="30">
-        <v>81609</v>
-      </c>
-      <c r="J733" s="75">
-        <v>0</v>
-      </c>
-      <c r="K733" s="75">
+      <c r="A733" s="27">
+        <v>46199</v>
+      </c>
+      <c r="B733" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C733" s="76"/>
+      <c r="D733" s="76"/>
+      <c r="E733" s="77"/>
+      <c r="F733" s="74">
+        <v>0</v>
+      </c>
+      <c r="G733" s="74">
+        <v>1</v>
+      </c>
+      <c r="H733" s="74">
+        <v>1</v>
+      </c>
+      <c r="I733" s="4">
+        <v>82464</v>
+      </c>
+      <c r="J733" s="74">
+        <v>0</v>
+      </c>
+      <c r="K733" s="74">
         <v>0</v>
       </c>
       <c r="L733" s="74">
         <f t="shared" si="104"/>
-        <v>85476</v>
+        <v>86584</v>
       </c>
       <c r="M733" s="74">
         <f t="shared" si="105"/>
-        <v>133</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="734" spans="1:13">
+      <c r="A734" s="27">
+        <v>46200</v>
+      </c>
+      <c r="B734" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C734" s="76"/>
+      <c r="D734" s="76"/>
+      <c r="E734" s="77"/>
+      <c r="F734" s="74">
+        <v>0</v>
+      </c>
+      <c r="G734" s="74">
+        <v>9</v>
+      </c>
+      <c r="H734" s="74">
+        <v>9</v>
+      </c>
+      <c r="I734" s="4">
+        <v>82473</v>
+      </c>
+      <c r="J734" s="74">
+        <v>0</v>
+      </c>
+      <c r="K734" s="74">
+        <v>0</v>
+      </c>
+      <c r="L734" s="74">
+        <f t="shared" ref="L734:L735" si="106">J734+L733</f>
+        <v>86584</v>
+      </c>
+      <c r="M734" s="74">
+        <f t="shared" ref="M734:M735" si="107">K734+M733</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="735" spans="1:13">
+      <c r="A735" s="29">
+        <v>46201</v>
+      </c>
+      <c r="B735" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C735" s="78"/>
+      <c r="D735" s="78"/>
+      <c r="E735" s="79"/>
+      <c r="F735" s="75">
+        <v>0</v>
+      </c>
+      <c r="G735" s="75">
+        <v>30</v>
+      </c>
+      <c r="H735" s="75">
+        <v>30</v>
+      </c>
+      <c r="I735" s="30">
+        <v>82503</v>
+      </c>
+      <c r="J735" s="75">
+        <v>0</v>
+      </c>
+      <c r="K735" s="75">
+        <v>0</v>
+      </c>
+      <c r="L735" s="74">
+        <f t="shared" si="106"/>
+        <v>86584</v>
+      </c>
+      <c r="M735" s="74">
+        <f t="shared" si="107"/>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="506">
+  <mergeCells count="507">
+    <mergeCell ref="B734:E734"/>
+    <mergeCell ref="B735:E735"/>
     <mergeCell ref="B727:E727"/>
     <mergeCell ref="B728:E728"/>
-    <mergeCell ref="B729:E729"/>
     <mergeCell ref="B730:E730"/>
     <mergeCell ref="B731:E731"/>
     <mergeCell ref="B732:E732"/>
@@ -44147,9 +44246,10 @@
     <hyperlink ref="G700" r:id="rId192" display="863" xr:uid="{95F5C9F2-6065-40BF-AD9E-E67580350D2F}"/>
     <hyperlink ref="G702" r:id="rId193" display="560" xr:uid="{579C9D04-A680-4706-887F-9A090C67F828}"/>
     <hyperlink ref="G705" r:id="rId194" display="560" xr:uid="{23497521-CF0C-4006-A8C3-37035833FC60}"/>
+    <hyperlink ref="G729" r:id="rId195" display="510" xr:uid="{47E037CC-A9E7-41D0-9CD9-CE09618E527A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId195"/>
+  <drawing r:id="rId196"/>
 </worksheet>
 </file>
 
@@ -55895,72 +55995,148 @@
       <c r="L228" s="15"/>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13" ht="14.25">
+    <row r="229" spans="1:13">
       <c r="A229" s="14">
         <v>244</v>
       </c>
-      <c r="B229" s="42"/>
-      <c r="C229" s="61"/>
-      <c r="D229" s="61"/>
-      <c r="E229" s="61"/>
-      <c r="F229" s="62"/>
-      <c r="G229" s="61"/>
-      <c r="H229" s="62"/>
-      <c r="I229" s="61"/>
-      <c r="J229" s="15"/>
-      <c r="K229" s="22"/>
+      <c r="B229" s="42">
+        <v>46204</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F229" s="13">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="G229" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="H229" s="13">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="I229" s="26"/>
+      <c r="J229" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K229" s="22">
+        <v>0</v>
+      </c>
       <c r="L229" s="15"/>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13" ht="14.25">
+    <row r="230" spans="1:13">
       <c r="A230" s="14">
         <v>245</v>
       </c>
-      <c r="B230" s="42"/>
-      <c r="C230" s="61"/>
-      <c r="D230" s="61"/>
-      <c r="E230" s="61"/>
-      <c r="F230" s="62"/>
-      <c r="G230" s="61"/>
-      <c r="H230" s="62"/>
-      <c r="I230" s="61"/>
-      <c r="J230" s="15"/>
-      <c r="K230" s="22"/>
+      <c r="B230" s="42">
+        <v>46204</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="F230" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G230" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="H230" s="13">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="I230" s="26"/>
+      <c r="J230" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K230" s="22">
+        <v>0</v>
+      </c>
       <c r="L230" s="15"/>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13" ht="14.25">
+    <row r="231" spans="1:13">
       <c r="A231" s="14">
         <v>246</v>
       </c>
-      <c r="B231" s="42"/>
-      <c r="C231" s="61"/>
-      <c r="D231" s="61"/>
-      <c r="E231" s="61"/>
-      <c r="F231" s="62"/>
-      <c r="G231" s="61"/>
-      <c r="H231" s="62"/>
-      <c r="I231" s="61"/>
-      <c r="J231" s="15"/>
-      <c r="K231" s="22"/>
-      <c r="L231" s="15"/>
+      <c r="B231" s="42">
+        <v>46177</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F231" s="13">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="G231" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="H231" s="13">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="I231" s="26"/>
+      <c r="J231" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K231" s="22">
+        <v>0</v>
+      </c>
+      <c r="L231" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13" ht="14.25">
+    <row r="232" spans="1:13">
       <c r="A232" s="14">
         <v>247</v>
       </c>
-      <c r="B232" s="42"/>
-      <c r="C232" s="61"/>
-      <c r="D232" s="61"/>
-      <c r="E232" s="61"/>
-      <c r="F232" s="62"/>
-      <c r="G232" s="61"/>
-      <c r="H232" s="62"/>
-      <c r="I232" s="61"/>
-      <c r="J232" s="15"/>
-      <c r="K232" s="22"/>
-      <c r="L232" s="15"/>
+      <c r="B232" s="42">
+        <v>46177</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="F232" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G232" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="H232" s="13">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="I232" s="26"/>
+      <c r="J232" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="K232" s="22">
+        <v>0</v>
+      </c>
+      <c r="L232" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="M232" s="15"/>
     </row>
     <row r="233" spans="1:13" ht="14.25">
@@ -56492,7 +56668,7 @@
     </row>
     <row r="274" spans="10:11">
       <c r="J274" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K274" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -56501,11 +56677,11 @@
     </row>
     <row r="275" spans="10:11">
       <c r="J275" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="K275">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1115</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="276" spans="10:11">
@@ -56514,16 +56690,16 @@
       </c>
       <c r="K276">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="277" spans="10:11">
       <c r="J277" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="K277" s="41">
         <f>K274/K275</f>
-        <v>1222.8914798206279</v>
+        <v>1201.3427312775329</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -56601,7 +56777,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H291" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -56653,7 +56829,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H293" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -56757,7 +56933,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H297" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -56991,7 +57167,7 @@
         <v>0.375</v>
       </c>
       <c r="H309" s="51" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="I309" s="52"/>
     </row>
@@ -57045,7 +57221,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H311" s="49" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="I311" s="52"/>
     </row>
@@ -57180,7 +57356,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H316" s="54" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="I316" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DEFD905-4442-4FA6-A885-357A8C5C23FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FDF9C1E-0B32-410E-B3CB-FA2D7CEB1961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="408">
   <si>
     <t>日付</t>
   </si>
@@ -1231,6 +1231,9 @@
     <t>JAL481</t>
   </si>
   <si>
+    <t>JAL436</t>
+  </si>
+  <si>
     <t>JAL503</t>
   </si>
   <si>
@@ -2436,10 +2439,10 @@
                   <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7132</c:v>
+                  <c:v>7188</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>148</c:v>
+                  <c:v>151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15078,7 +15081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O748"/>
+  <dimension ref="A1:O757"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -15646,7 +15649,7 @@
       </c>
       <c r="O16">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＷＥＬＬＮＥＳＳ*")</f>
-        <v>7132</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -15696,7 +15699,7 @@
       </c>
       <c r="O17">
         <f>SUMIFS(H11:H29999, B11:B29999, "*ＪＭＢアプリ*")</f>
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1">
@@ -15888,7 +15891,7 @@
       <c r="N21" s="31"/>
       <c r="O21">
         <f>SUM(O12:O18)</f>
-        <v>169290</v>
+        <v>169349</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -44030,38 +44033,852 @@
       <c r="H748" s="75">
         <v>1</v>
       </c>
-      <c r="I748" s="30">
-        <v>82725</v>
-      </c>
-      <c r="J748" s="75">
-        <v>0</v>
-      </c>
-      <c r="K748" s="75">
+      <c r="I748" s="4">
+        <v>82752</v>
+      </c>
+      <c r="J748" s="74">
+        <v>0</v>
+      </c>
+      <c r="K748" s="74">
         <v>0</v>
       </c>
       <c r="L748" s="74">
-        <f t="shared" si="108"/>
+        <f t="shared" ref="L748:L757" si="110">J748+L747</f>
         <v>86584</v>
       </c>
       <c r="M748" s="74">
-        <f t="shared" si="109"/>
+        <f t="shared" ref="M748:M757" si="111">K748+M747</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="749" spans="1:13">
+      <c r="A749" s="27">
+        <v>46209</v>
+      </c>
+      <c r="B749" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C749" s="76"/>
+      <c r="D749" s="76"/>
+      <c r="E749" s="77"/>
+      <c r="F749" s="74">
+        <v>0</v>
+      </c>
+      <c r="G749" s="74">
+        <v>17</v>
+      </c>
+      <c r="H749" s="74">
+        <v>17</v>
+      </c>
+      <c r="I749" s="4">
+        <v>82742</v>
+      </c>
+      <c r="J749" s="74">
+        <v>0</v>
+      </c>
+      <c r="K749" s="74">
+        <v>0</v>
+      </c>
+      <c r="L749" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M749" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="750" spans="1:13">
+      <c r="A750" s="27">
+        <v>46210</v>
+      </c>
+      <c r="B750" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C750" s="76"/>
+      <c r="D750" s="76"/>
+      <c r="E750" s="77"/>
+      <c r="F750" s="74">
+        <v>0</v>
+      </c>
+      <c r="G750" s="74">
+        <v>4</v>
+      </c>
+      <c r="H750" s="74">
+        <v>4</v>
+      </c>
+      <c r="I750" s="4">
+        <v>82746</v>
+      </c>
+      <c r="J750" s="74">
+        <v>0</v>
+      </c>
+      <c r="K750" s="74">
+        <v>0</v>
+      </c>
+      <c r="L750" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M750" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="751" spans="1:13">
+      <c r="A751" s="27">
+        <v>46211</v>
+      </c>
+      <c r="B751" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C751" s="76"/>
+      <c r="D751" s="76"/>
+      <c r="E751" s="77"/>
+      <c r="F751" s="74">
+        <v>0</v>
+      </c>
+      <c r="G751" s="74">
+        <v>16</v>
+      </c>
+      <c r="H751" s="74">
+        <v>16</v>
+      </c>
+      <c r="I751" s="4">
+        <v>82762</v>
+      </c>
+      <c r="J751" s="74">
+        <v>0</v>
+      </c>
+      <c r="K751" s="74">
+        <v>0</v>
+      </c>
+      <c r="L751" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M751" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="752" spans="1:13">
+      <c r="A752" s="27">
+        <v>46212</v>
+      </c>
+      <c r="B752" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C752" s="76"/>
+      <c r="D752" s="76"/>
+      <c r="E752" s="77"/>
+      <c r="F752" s="74">
+        <v>0</v>
+      </c>
+      <c r="G752" s="74">
+        <v>8</v>
+      </c>
+      <c r="H752" s="74">
+        <v>8</v>
+      </c>
+      <c r="I752" s="4">
+        <v>82770</v>
+      </c>
+      <c r="J752" s="74">
+        <v>0</v>
+      </c>
+      <c r="K752" s="74">
+        <v>0</v>
+      </c>
+      <c r="L752" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M752" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="753" spans="1:13">
+      <c r="A753" s="27">
+        <v>46213</v>
+      </c>
+      <c r="B753" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C753" s="76"/>
+      <c r="D753" s="76"/>
+      <c r="E753" s="77"/>
+      <c r="F753" s="74">
+        <v>0</v>
+      </c>
+      <c r="G753" s="74">
+        <v>1</v>
+      </c>
+      <c r="H753" s="74">
+        <v>1</v>
+      </c>
+      <c r="I753" s="4">
+        <v>82771</v>
+      </c>
+      <c r="J753" s="74">
+        <v>0</v>
+      </c>
+      <c r="K753" s="74">
+        <v>0</v>
+      </c>
+      <c r="L753" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M753" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="754" spans="1:13">
+      <c r="A754" s="27">
+        <v>46213</v>
+      </c>
+      <c r="B754" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C754" s="76"/>
+      <c r="D754" s="76"/>
+      <c r="E754" s="77"/>
+      <c r="F754" s="74">
+        <v>0</v>
+      </c>
+      <c r="G754" s="74">
+        <v>8</v>
+      </c>
+      <c r="H754" s="74">
+        <v>8</v>
+      </c>
+      <c r="I754" s="4">
+        <v>82779</v>
+      </c>
+      <c r="J754" s="74">
+        <v>0</v>
+      </c>
+      <c r="K754" s="74">
+        <v>0</v>
+      </c>
+      <c r="L754" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M754" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="755" spans="1:13">
+      <c r="A755" s="27">
+        <v>46213</v>
+      </c>
+      <c r="B755" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C755" s="76"/>
+      <c r="D755" s="76"/>
+      <c r="E755" s="77"/>
+      <c r="F755" s="74">
+        <v>0</v>
+      </c>
+      <c r="G755" s="74">
+        <v>1</v>
+      </c>
+      <c r="H755" s="74">
+        <v>1</v>
+      </c>
+      <c r="I755" s="4">
+        <v>82780</v>
+      </c>
+      <c r="J755" s="74">
+        <v>0</v>
+      </c>
+      <c r="K755" s="74">
+        <v>0</v>
+      </c>
+      <c r="L755" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M755" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="756" spans="1:13">
+      <c r="A756" s="27">
+        <v>46213</v>
+      </c>
+      <c r="B756" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C756" s="76"/>
+      <c r="D756" s="76"/>
+      <c r="E756" s="77"/>
+      <c r="F756" s="74">
+        <v>0</v>
+      </c>
+      <c r="G756" s="74">
+        <v>1</v>
+      </c>
+      <c r="H756" s="74">
+        <v>1</v>
+      </c>
+      <c r="I756" s="4">
+        <v>82781</v>
+      </c>
+      <c r="J756" s="74">
+        <v>0</v>
+      </c>
+      <c r="K756" s="74">
+        <v>0</v>
+      </c>
+      <c r="L756" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M756" s="74">
+        <f t="shared" si="111"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="757" spans="1:13">
+      <c r="A757" s="29">
+        <v>46214</v>
+      </c>
+      <c r="B757" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C757" s="78"/>
+      <c r="D757" s="78"/>
+      <c r="E757" s="79"/>
+      <c r="F757" s="75">
+        <v>0</v>
+      </c>
+      <c r="G757" s="75">
+        <v>3</v>
+      </c>
+      <c r="H757" s="75">
+        <v>3</v>
+      </c>
+      <c r="I757" s="30">
+        <v>82784</v>
+      </c>
+      <c r="J757" s="75">
+        <v>0</v>
+      </c>
+      <c r="K757" s="75">
+        <v>0</v>
+      </c>
+      <c r="L757" s="74">
+        <f t="shared" si="110"/>
+        <v>86584</v>
+      </c>
+      <c r="M757" s="74">
+        <f t="shared" si="111"/>
         <v>134</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="518">
-    <mergeCell ref="B747:E747"/>
-    <mergeCell ref="B748:E748"/>
-    <mergeCell ref="B736:E736"/>
-    <mergeCell ref="B737:E737"/>
-    <mergeCell ref="B740:E740"/>
-    <mergeCell ref="B741:E741"/>
-    <mergeCell ref="B742:E742"/>
-    <mergeCell ref="B743:E743"/>
-    <mergeCell ref="B744:E744"/>
-    <mergeCell ref="B745:E745"/>
-    <mergeCell ref="B746:E746"/>
+  <mergeCells count="527">
+    <mergeCell ref="B749:E749"/>
+    <mergeCell ref="B750:E750"/>
+    <mergeCell ref="B751:E751"/>
+    <mergeCell ref="B752:E752"/>
+    <mergeCell ref="B753:E753"/>
+    <mergeCell ref="B754:E754"/>
+    <mergeCell ref="B755:E755"/>
+    <mergeCell ref="B756:E756"/>
+    <mergeCell ref="B757:E757"/>
+    <mergeCell ref="B734:E734"/>
+    <mergeCell ref="B735:E735"/>
+    <mergeCell ref="B727:E727"/>
+    <mergeCell ref="B728:E728"/>
+    <mergeCell ref="B730:E730"/>
+    <mergeCell ref="B731:E731"/>
+    <mergeCell ref="B732:E732"/>
+    <mergeCell ref="B733:E733"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B594:E594"/>
+    <mergeCell ref="B627:E627"/>
+    <mergeCell ref="B647:E647"/>
+    <mergeCell ref="B661:E661"/>
+    <mergeCell ref="B662:E662"/>
+    <mergeCell ref="B663:E663"/>
+    <mergeCell ref="B664:E664"/>
+    <mergeCell ref="B665:E665"/>
+    <mergeCell ref="B666:E666"/>
+    <mergeCell ref="B633:E633"/>
+    <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B635:E635"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
     <mergeCell ref="B651:E651"/>
     <mergeCell ref="B695:E695"/>
     <mergeCell ref="B696:E696"/>
@@ -44086,489 +44903,17 @@
     <mergeCell ref="B688:E688"/>
     <mergeCell ref="B691:E691"/>
     <mergeCell ref="B692:E692"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B594:E594"/>
-    <mergeCell ref="B627:E627"/>
-    <mergeCell ref="B647:E647"/>
-    <mergeCell ref="B661:E661"/>
-    <mergeCell ref="B662:E662"/>
-    <mergeCell ref="B663:E663"/>
-    <mergeCell ref="B664:E664"/>
-    <mergeCell ref="B665:E665"/>
-    <mergeCell ref="B666:E666"/>
-    <mergeCell ref="B633:E633"/>
-    <mergeCell ref="B634:E634"/>
-    <mergeCell ref="B635:E635"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B621:E621"/>
-    <mergeCell ref="B622:E622"/>
-    <mergeCell ref="B623:E623"/>
-    <mergeCell ref="B624:E624"/>
-    <mergeCell ref="B625:E625"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
-    <mergeCell ref="B734:E734"/>
-    <mergeCell ref="B735:E735"/>
-    <mergeCell ref="B727:E727"/>
-    <mergeCell ref="B728:E728"/>
-    <mergeCell ref="B730:E730"/>
-    <mergeCell ref="B731:E731"/>
-    <mergeCell ref="B732:E732"/>
-    <mergeCell ref="B733:E733"/>
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B747:E747"/>
+    <mergeCell ref="B748:E748"/>
+    <mergeCell ref="B736:E736"/>
+    <mergeCell ref="B737:E737"/>
+    <mergeCell ref="B740:E740"/>
+    <mergeCell ref="B741:E741"/>
+    <mergeCell ref="B742:E742"/>
+    <mergeCell ref="B743:E743"/>
+    <mergeCell ref="B744:E744"/>
+    <mergeCell ref="B745:E745"/>
+    <mergeCell ref="B746:E746"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -56500,19 +56845,19 @@
         <v>301</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E228" s="12" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="F228" s="13">
-        <v>0.85763888888888884</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="G228" s="12" t="s">
         <v>302</v>
       </c>
       <c r="H228" s="13">
-        <v>0.91319444444444442</v>
+        <v>0.65972222222222221</v>
       </c>
       <c r="I228" s="26"/>
       <c r="J228" s="15" t="s">
@@ -56535,7 +56880,7 @@
         <v>301</v>
       </c>
       <c r="D229" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E229" s="12" t="s">
         <v>302</v>
@@ -56544,7 +56889,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G229" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H229" s="13">
         <v>0.36805555555555558</v>
@@ -56572,10 +56917,10 @@
         <v>301</v>
       </c>
       <c r="D230" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E230" s="12" t="s">
         <v>395</v>
-      </c>
-      <c r="E230" s="12" t="s">
-        <v>394</v>
       </c>
       <c r="F230" s="13">
         <v>0.80208333333333337</v>
@@ -56609,7 +56954,7 @@
         <v>301</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E231" s="12" t="s">
         <v>302</v>
@@ -56618,7 +56963,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="G231" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H231" s="13">
         <v>0.36805555555555558</v>
@@ -56646,10 +56991,10 @@
         <v>301</v>
       </c>
       <c r="D232" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E232" s="12" t="s">
         <v>398</v>
-      </c>
-      <c r="E232" s="12" t="s">
-        <v>397</v>
       </c>
       <c r="F232" s="13">
         <v>0.80208333333333337</v>
@@ -57201,7 +57546,7 @@
     </row>
     <row r="274" spans="10:11">
       <c r="J274" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K274" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -57210,7 +57555,7 @@
     </row>
     <row r="275" spans="10:11">
       <c r="J275" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K275">
         <f>COUNTA(テーブル4[料金])*5</f>
@@ -57228,7 +57573,7 @@
     </row>
     <row r="277" spans="10:11">
       <c r="J277" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K277" s="41">
         <f>K274/K275</f>
@@ -57310,7 +57655,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H291" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -57362,7 +57707,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H293" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -57466,7 +57811,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H297" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -57700,7 +58045,7 @@
         <v>0.375</v>
       </c>
       <c r="H309" s="51" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I309" s="52"/>
     </row>
@@ -57754,7 +58099,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H311" s="49" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I311" s="52"/>
     </row>
@@ -57889,7 +58234,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H316" s="54" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I316" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB95C2AD-77E4-47EE-ADFA-624C226B1CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3249" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F495D87-3BC3-4E79-9F10-7BB745EA8E98}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3249" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F495D87-3BC3-4E79-9F10-7BB745EA8E98}"/>
+  <xr:revisionPtr revIDLastSave="3263" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B6A5A8-A5CE-427B-B9AC-ECAFC83EBF90}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="415">
   <si>
     <t>日付</t>
   </si>
@@ -1268,6 +1268,9 @@
   </si>
   <si>
     <t>JAL240</t>
+  </si>
+  <si>
+    <t>JAL106</t>
   </si>
   <si>
     <t>総額</t>
@@ -14836,15 +14839,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M263" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M263" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <dateGroupItem year="2026" month="8" dateTimeGrouping="month"/>
-        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
-        <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M263" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{E936A600-BB79-446A-9797-5E2C4AB43B97}" name="日付" dataDxfId="11"/>
@@ -47823,71 +47818,513 @@
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
   <mergeCells count="611">
-    <mergeCell ref="B837:E837"/>
-    <mergeCell ref="B839:E839"/>
-    <mergeCell ref="B840:E840"/>
-    <mergeCell ref="B842:E842"/>
-    <mergeCell ref="B843:E843"/>
-    <mergeCell ref="B844:E844"/>
-    <mergeCell ref="B845:E845"/>
-    <mergeCell ref="B846:E846"/>
-    <mergeCell ref="B847:E847"/>
-    <mergeCell ref="B828:E828"/>
-    <mergeCell ref="B829:E829"/>
-    <mergeCell ref="B830:E830"/>
-    <mergeCell ref="B831:E831"/>
-    <mergeCell ref="B832:E832"/>
-    <mergeCell ref="B833:E833"/>
-    <mergeCell ref="B834:E834"/>
-    <mergeCell ref="B835:E835"/>
-    <mergeCell ref="B836:E836"/>
-    <mergeCell ref="B819:E819"/>
-    <mergeCell ref="B820:E820"/>
-    <mergeCell ref="B821:E821"/>
-    <mergeCell ref="B822:E822"/>
-    <mergeCell ref="B823:E823"/>
-    <mergeCell ref="B824:E824"/>
-    <mergeCell ref="B825:E825"/>
-    <mergeCell ref="B826:E826"/>
-    <mergeCell ref="B827:E827"/>
-    <mergeCell ref="B779:E779"/>
-    <mergeCell ref="B811:E811"/>
-    <mergeCell ref="B812:E812"/>
-    <mergeCell ref="B813:E813"/>
-    <mergeCell ref="B814:E814"/>
-    <mergeCell ref="B815:E815"/>
-    <mergeCell ref="B816:E816"/>
-    <mergeCell ref="B817:E817"/>
-    <mergeCell ref="B818:E818"/>
-    <mergeCell ref="B769:E769"/>
-    <mergeCell ref="B770:E770"/>
-    <mergeCell ref="B771:E771"/>
-    <mergeCell ref="B773:E773"/>
-    <mergeCell ref="B774:E774"/>
-    <mergeCell ref="B775:E775"/>
-    <mergeCell ref="B776:E776"/>
-    <mergeCell ref="B777:E777"/>
-    <mergeCell ref="B778:E778"/>
-    <mergeCell ref="B759:E759"/>
-    <mergeCell ref="B760:E760"/>
-    <mergeCell ref="B761:E761"/>
-    <mergeCell ref="B762:E762"/>
-    <mergeCell ref="B763:E763"/>
-    <mergeCell ref="B765:E765"/>
-    <mergeCell ref="B766:E766"/>
-    <mergeCell ref="B767:E767"/>
-    <mergeCell ref="B768:E768"/>
-    <mergeCell ref="B747:E747"/>
-    <mergeCell ref="B748:E748"/>
-    <mergeCell ref="B736:E736"/>
-    <mergeCell ref="B737:E737"/>
-    <mergeCell ref="B740:E740"/>
-    <mergeCell ref="B741:E741"/>
-    <mergeCell ref="B742:E742"/>
-    <mergeCell ref="B743:E743"/>
-    <mergeCell ref="B744:E744"/>
-    <mergeCell ref="B745:E745"/>
-    <mergeCell ref="B746:E746"/>
+    <mergeCell ref="B805:E805"/>
+    <mergeCell ref="B806:E806"/>
+    <mergeCell ref="B807:E807"/>
+    <mergeCell ref="B808:E808"/>
+    <mergeCell ref="B809:E809"/>
+    <mergeCell ref="B810:E810"/>
+    <mergeCell ref="B795:E795"/>
+    <mergeCell ref="B796:E796"/>
+    <mergeCell ref="B797:E797"/>
+    <mergeCell ref="B798:E798"/>
+    <mergeCell ref="B799:E799"/>
+    <mergeCell ref="B800:E800"/>
+    <mergeCell ref="B801:E801"/>
+    <mergeCell ref="B802:E802"/>
+    <mergeCell ref="B803:E803"/>
+    <mergeCell ref="B749:E749"/>
+    <mergeCell ref="B750:E750"/>
+    <mergeCell ref="B751:E751"/>
+    <mergeCell ref="B752:E752"/>
+    <mergeCell ref="B753:E753"/>
+    <mergeCell ref="B754:E754"/>
+    <mergeCell ref="B755:E755"/>
+    <mergeCell ref="B756:E756"/>
+    <mergeCell ref="B757:E757"/>
+    <mergeCell ref="B734:E734"/>
+    <mergeCell ref="B735:E735"/>
+    <mergeCell ref="B727:E727"/>
+    <mergeCell ref="B728:E728"/>
+    <mergeCell ref="B730:E730"/>
+    <mergeCell ref="B731:E731"/>
+    <mergeCell ref="B732:E732"/>
+    <mergeCell ref="B733:E733"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B594:E594"/>
+    <mergeCell ref="B627:E627"/>
+    <mergeCell ref="B647:E647"/>
+    <mergeCell ref="B661:E661"/>
+    <mergeCell ref="B662:E662"/>
+    <mergeCell ref="B663:E663"/>
+    <mergeCell ref="B664:E664"/>
+    <mergeCell ref="B665:E665"/>
+    <mergeCell ref="B666:E666"/>
+    <mergeCell ref="B633:E633"/>
+    <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B635:E635"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
     <mergeCell ref="B651:E651"/>
     <mergeCell ref="B695:E695"/>
     <mergeCell ref="B696:E696"/>
@@ -47912,498 +48349,44 @@
     <mergeCell ref="B688:E688"/>
     <mergeCell ref="B691:E691"/>
     <mergeCell ref="B692:E692"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B594:E594"/>
-    <mergeCell ref="B627:E627"/>
-    <mergeCell ref="B647:E647"/>
-    <mergeCell ref="B661:E661"/>
-    <mergeCell ref="B662:E662"/>
-    <mergeCell ref="B663:E663"/>
-    <mergeCell ref="B664:E664"/>
-    <mergeCell ref="B665:E665"/>
-    <mergeCell ref="B666:E666"/>
-    <mergeCell ref="B633:E633"/>
-    <mergeCell ref="B634:E634"/>
-    <mergeCell ref="B635:E635"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B621:E621"/>
-    <mergeCell ref="B622:E622"/>
-    <mergeCell ref="B623:E623"/>
-    <mergeCell ref="B624:E624"/>
-    <mergeCell ref="B625:E625"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
-    <mergeCell ref="B734:E734"/>
-    <mergeCell ref="B735:E735"/>
-    <mergeCell ref="B727:E727"/>
-    <mergeCell ref="B728:E728"/>
-    <mergeCell ref="B730:E730"/>
-    <mergeCell ref="B731:E731"/>
-    <mergeCell ref="B732:E732"/>
-    <mergeCell ref="B733:E733"/>
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B726:E726"/>
-    <mergeCell ref="B749:E749"/>
-    <mergeCell ref="B750:E750"/>
-    <mergeCell ref="B751:E751"/>
-    <mergeCell ref="B752:E752"/>
-    <mergeCell ref="B753:E753"/>
-    <mergeCell ref="B754:E754"/>
-    <mergeCell ref="B755:E755"/>
-    <mergeCell ref="B756:E756"/>
-    <mergeCell ref="B757:E757"/>
+    <mergeCell ref="B747:E747"/>
+    <mergeCell ref="B748:E748"/>
+    <mergeCell ref="B736:E736"/>
+    <mergeCell ref="B737:E737"/>
+    <mergeCell ref="B740:E740"/>
+    <mergeCell ref="B741:E741"/>
+    <mergeCell ref="B742:E742"/>
+    <mergeCell ref="B743:E743"/>
+    <mergeCell ref="B744:E744"/>
+    <mergeCell ref="B745:E745"/>
+    <mergeCell ref="B746:E746"/>
+    <mergeCell ref="B759:E759"/>
+    <mergeCell ref="B760:E760"/>
+    <mergeCell ref="B761:E761"/>
+    <mergeCell ref="B762:E762"/>
+    <mergeCell ref="B763:E763"/>
+    <mergeCell ref="B765:E765"/>
+    <mergeCell ref="B766:E766"/>
+    <mergeCell ref="B767:E767"/>
+    <mergeCell ref="B768:E768"/>
+    <mergeCell ref="B769:E769"/>
+    <mergeCell ref="B770:E770"/>
+    <mergeCell ref="B771:E771"/>
+    <mergeCell ref="B773:E773"/>
+    <mergeCell ref="B774:E774"/>
+    <mergeCell ref="B775:E775"/>
+    <mergeCell ref="B776:E776"/>
+    <mergeCell ref="B777:E777"/>
+    <mergeCell ref="B778:E778"/>
+    <mergeCell ref="B779:E779"/>
+    <mergeCell ref="B811:E811"/>
+    <mergeCell ref="B812:E812"/>
+    <mergeCell ref="B813:E813"/>
+    <mergeCell ref="B814:E814"/>
+    <mergeCell ref="B815:E815"/>
+    <mergeCell ref="B816:E816"/>
+    <mergeCell ref="B817:E817"/>
+    <mergeCell ref="B818:E818"/>
     <mergeCell ref="B780:E780"/>
     <mergeCell ref="B781:E781"/>
     <mergeCell ref="B782:E782"/>
@@ -48419,21 +48402,33 @@
     <mergeCell ref="B793:E793"/>
     <mergeCell ref="B789:E789"/>
     <mergeCell ref="B804:E804"/>
-    <mergeCell ref="B805:E805"/>
-    <mergeCell ref="B806:E806"/>
-    <mergeCell ref="B807:E807"/>
-    <mergeCell ref="B808:E808"/>
-    <mergeCell ref="B809:E809"/>
-    <mergeCell ref="B810:E810"/>
-    <mergeCell ref="B795:E795"/>
-    <mergeCell ref="B796:E796"/>
-    <mergeCell ref="B797:E797"/>
-    <mergeCell ref="B798:E798"/>
-    <mergeCell ref="B799:E799"/>
-    <mergeCell ref="B800:E800"/>
-    <mergeCell ref="B801:E801"/>
-    <mergeCell ref="B802:E802"/>
-    <mergeCell ref="B803:E803"/>
+    <mergeCell ref="B819:E819"/>
+    <mergeCell ref="B820:E820"/>
+    <mergeCell ref="B821:E821"/>
+    <mergeCell ref="B822:E822"/>
+    <mergeCell ref="B823:E823"/>
+    <mergeCell ref="B824:E824"/>
+    <mergeCell ref="B825:E825"/>
+    <mergeCell ref="B826:E826"/>
+    <mergeCell ref="B827:E827"/>
+    <mergeCell ref="B828:E828"/>
+    <mergeCell ref="B829:E829"/>
+    <mergeCell ref="B830:E830"/>
+    <mergeCell ref="B831:E831"/>
+    <mergeCell ref="B832:E832"/>
+    <mergeCell ref="B833:E833"/>
+    <mergeCell ref="B834:E834"/>
+    <mergeCell ref="B835:E835"/>
+    <mergeCell ref="B836:E836"/>
+    <mergeCell ref="B837:E837"/>
+    <mergeCell ref="B839:E839"/>
+    <mergeCell ref="B840:E840"/>
+    <mergeCell ref="B842:E842"/>
+    <mergeCell ref="B843:E843"/>
+    <mergeCell ref="B844:E844"/>
+    <mergeCell ref="B845:E845"/>
+    <mergeCell ref="B846:E846"/>
+    <mergeCell ref="B847:E847"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -52810,7 +52805,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:13">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -52847,7 +52842,7 @@
       </c>
       <c r="M2" s="63"/>
     </row>
-    <row r="3" spans="1:13" hidden="1">
+    <row r="3" spans="1:13">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -52884,7 +52879,7 @@
       </c>
       <c r="M3" s="15"/>
     </row>
-    <row r="4" spans="1:13" hidden="1">
+    <row r="4" spans="1:13">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -52921,7 +52916,7 @@
       </c>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13" hidden="1">
+    <row r="5" spans="1:13">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -52958,7 +52953,7 @@
       </c>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13" hidden="1">
+    <row r="6" spans="1:13">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -52995,7 +52990,7 @@
       </c>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" hidden="1">
+    <row r="7" spans="1:13">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -53032,7 +53027,7 @@
       </c>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" hidden="1">
+    <row r="8" spans="1:13">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -53069,7 +53064,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" hidden="1">
+    <row r="9" spans="1:13">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -53106,7 +53101,7 @@
       </c>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" hidden="1">
+    <row r="10" spans="1:13">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -53143,7 +53138,7 @@
       </c>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:13">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -53180,7 +53175,7 @@
       </c>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" hidden="1">
+    <row r="12" spans="1:13">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -53217,7 +53212,7 @@
       </c>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" hidden="1">
+    <row r="13" spans="1:13">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -53254,7 +53249,7 @@
       </c>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" hidden="1">
+    <row r="14" spans="1:13">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -53291,7 +53286,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" hidden="1">
+    <row r="15" spans="1:13">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -53328,7 +53323,7 @@
       </c>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13" hidden="1">
+    <row r="16" spans="1:13">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -53365,7 +53360,7 @@
       </c>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13" hidden="1">
+    <row r="17" spans="1:13">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -53402,7 +53397,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13" hidden="1">
+    <row r="18" spans="1:13">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -53439,7 +53434,7 @@
       </c>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" hidden="1">
+    <row r="19" spans="1:13">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -53476,7 +53471,7 @@
       </c>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13" hidden="1">
+    <row r="20" spans="1:13">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -53513,7 +53508,7 @@
       </c>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" hidden="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -53550,7 +53545,7 @@
       </c>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13" hidden="1">
+    <row r="22" spans="1:13">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -53587,7 +53582,7 @@
       </c>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13" hidden="1">
+    <row r="23" spans="1:13">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -53624,7 +53619,7 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="1:13" hidden="1">
+    <row r="24" spans="1:13">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -53661,7 +53656,7 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" hidden="1">
+    <row r="25" spans="1:13">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -53698,7 +53693,7 @@
       </c>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" hidden="1">
+    <row r="26" spans="1:13">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -53735,7 +53730,7 @@
       </c>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" hidden="1">
+    <row r="27" spans="1:13">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -53770,7 +53765,7 @@
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" hidden="1">
+    <row r="28" spans="1:13">
       <c r="A28" s="14">
         <v>27</v>
       </c>
@@ -53807,7 +53802,7 @@
       </c>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" hidden="1">
+    <row r="29" spans="1:13">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -53844,7 +53839,7 @@
       </c>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" hidden="1">
+    <row r="30" spans="1:13">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -53881,7 +53876,7 @@
       </c>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" hidden="1">
+    <row r="31" spans="1:13">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -53918,7 +53913,7 @@
       </c>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" hidden="1">
+    <row r="32" spans="1:13">
       <c r="A32" s="14">
         <v>31</v>
       </c>
@@ -53955,7 +53950,7 @@
       </c>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13" hidden="1">
+    <row r="33" spans="1:13">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -53992,7 +53987,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" hidden="1">
+    <row r="34" spans="1:13">
       <c r="A34" s="14">
         <v>33</v>
       </c>
@@ -54029,7 +54024,7 @@
       </c>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13" hidden="1">
+    <row r="35" spans="1:13">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -54064,7 +54059,7 @@
       </c>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:13" hidden="1">
+    <row r="36" spans="1:13">
       <c r="A36" s="14">
         <v>35</v>
       </c>
@@ -54099,7 +54094,7 @@
       </c>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13" hidden="1">
+    <row r="37" spans="1:13">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -54134,7 +54129,7 @@
       </c>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="1:13" hidden="1">
+    <row r="38" spans="1:13">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -54169,7 +54164,7 @@
       </c>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13" hidden="1">
+    <row r="39" spans="1:13">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -54204,7 +54199,7 @@
       </c>
       <c r="M39" s="15"/>
     </row>
-    <row r="40" spans="1:13" hidden="1">
+    <row r="40" spans="1:13">
       <c r="A40" s="14">
         <v>39</v>
       </c>
@@ -54239,7 +54234,7 @@
       </c>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13" hidden="1">
+    <row r="41" spans="1:13">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -54270,7 +54265,7 @@
       </c>
       <c r="M41" s="15"/>
     </row>
-    <row r="42" spans="1:13" hidden="1">
+    <row r="42" spans="1:13">
       <c r="A42" s="14">
         <v>41</v>
       </c>
@@ -54301,7 +54296,7 @@
       </c>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13" hidden="1">
+    <row r="43" spans="1:13">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -54332,7 +54327,7 @@
       </c>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="1:13" hidden="1">
+    <row r="44" spans="1:13">
       <c r="A44" s="14">
         <v>43</v>
       </c>
@@ -54363,7 +54358,7 @@
       </c>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13" hidden="1">
+    <row r="45" spans="1:13">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -54394,7 +54389,7 @@
       </c>
       <c r="M45" s="15"/>
     </row>
-    <row r="46" spans="1:13" hidden="1">
+    <row r="46" spans="1:13">
       <c r="A46" s="14">
         <v>45</v>
       </c>
@@ -54425,7 +54420,7 @@
       </c>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13" hidden="1">
+    <row r="47" spans="1:13">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -54456,7 +54451,7 @@
       </c>
       <c r="M47" s="15"/>
     </row>
-    <row r="48" spans="1:13" hidden="1">
+    <row r="48" spans="1:13">
       <c r="A48" s="14">
         <v>47</v>
       </c>
@@ -54487,7 +54482,7 @@
       </c>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13" hidden="1">
+    <row r="49" spans="1:13">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -54518,7 +54513,7 @@
       </c>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13" hidden="1">
+    <row r="50" spans="1:13">
       <c r="A50" s="14">
         <v>49</v>
       </c>
@@ -54549,7 +54544,7 @@
       </c>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13" hidden="1">
+    <row r="51" spans="1:13">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -54580,7 +54575,7 @@
       </c>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13" hidden="1">
+    <row r="52" spans="1:13">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -54611,7 +54606,7 @@
       </c>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13" hidden="1">
+    <row r="53" spans="1:13">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -54642,7 +54637,7 @@
       </c>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13" hidden="1">
+    <row r="54" spans="1:13">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -54673,7 +54668,7 @@
       </c>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13" hidden="1">
+    <row r="55" spans="1:13">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -54704,7 +54699,7 @@
       </c>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="1:13" hidden="1">
+    <row r="56" spans="1:13">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -54735,7 +54730,7 @@
       </c>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13" hidden="1">
+    <row r="57" spans="1:13">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -54766,7 +54761,7 @@
       </c>
       <c r="M57" s="15"/>
     </row>
-    <row r="58" spans="1:13" hidden="1">
+    <row r="58" spans="1:13">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -54797,7 +54792,7 @@
       </c>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13" hidden="1">
+    <row r="59" spans="1:13">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -54828,7 +54823,7 @@
       </c>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13" hidden="1">
+    <row r="60" spans="1:13">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -54863,7 +54858,7 @@
       </c>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13" hidden="1">
+    <row r="61" spans="1:13">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -54898,7 +54893,7 @@
       </c>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13" hidden="1">
+    <row r="62" spans="1:13">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -54933,7 +54928,7 @@
       </c>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13" hidden="1">
+    <row r="63" spans="1:13">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -54968,7 +54963,7 @@
       </c>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="1:13" hidden="1">
+    <row r="64" spans="1:13">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -55003,7 +54998,7 @@
       </c>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13" hidden="1">
+    <row r="65" spans="1:13">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -55038,7 +55033,7 @@
       </c>
       <c r="M65" s="15"/>
     </row>
-    <row r="66" spans="1:13" hidden="1">
+    <row r="66" spans="1:13">
       <c r="A66" s="14">
         <v>65</v>
       </c>
@@ -55073,7 +55068,7 @@
       </c>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13" hidden="1">
+    <row r="67" spans="1:13">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -55108,7 +55103,7 @@
       </c>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="1:13" hidden="1">
+    <row r="68" spans="1:13">
       <c r="A68" s="14">
         <v>67</v>
       </c>
@@ -55143,7 +55138,7 @@
       </c>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13" hidden="1">
+    <row r="69" spans="1:13">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -55174,7 +55169,7 @@
       </c>
       <c r="M69" s="15"/>
     </row>
-    <row r="70" spans="1:13" hidden="1">
+    <row r="70" spans="1:13">
       <c r="A70" s="14">
         <v>69</v>
       </c>
@@ -55205,7 +55200,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -55241,7 +55236,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13" hidden="1">
+    <row r="72" spans="1:13">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -55276,7 +55271,7 @@
       </c>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13" hidden="1">
+    <row r="73" spans="1:13">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -55305,7 +55300,7 @@
       </c>
       <c r="M73" s="15"/>
     </row>
-    <row r="74" spans="1:13" hidden="1">
+    <row r="74" spans="1:13">
       <c r="A74" s="14">
         <v>73</v>
       </c>
@@ -55334,7 +55329,7 @@
       </c>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13" hidden="1">
+    <row r="75" spans="1:13">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -55363,7 +55358,7 @@
       </c>
       <c r="M75" s="15"/>
     </row>
-    <row r="76" spans="1:13" hidden="1">
+    <row r="76" spans="1:13">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -55392,7 +55387,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13" hidden="1">
+    <row r="77" spans="1:13">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -55425,7 +55420,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13" hidden="1">
+    <row r="78" spans="1:13">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -55458,7 +55453,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13" hidden="1">
+    <row r="79" spans="1:13">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -55491,7 +55486,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13" hidden="1">
+    <row r="80" spans="1:13">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -55524,7 +55519,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -55557,7 +55552,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -55590,7 +55585,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -55623,7 +55618,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -55656,7 +55651,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -55689,7 +55684,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -55722,7 +55717,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -55755,7 +55750,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -55788,7 +55783,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -55821,7 +55816,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -55854,7 +55849,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -55887,7 +55882,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -55920,7 +55915,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -55953,7 +55948,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -55986,7 +55981,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -56019,7 +56014,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -56052,7 +56047,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13" hidden="1">
+    <row r="97" spans="1:13">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -56085,7 +56080,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13" hidden="1">
+    <row r="98" spans="1:13">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -56118,7 +56113,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13" hidden="1">
+    <row r="99" spans="1:13">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -56151,7 +56146,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13" hidden="1">
+    <row r="100" spans="1:13">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -56184,7 +56179,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13" hidden="1">
+    <row r="101" spans="1:13">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -56217,7 +56212,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13" hidden="1">
+    <row r="102" spans="1:13">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -56250,7 +56245,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13" hidden="1">
+    <row r="103" spans="1:13">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -56283,7 +56278,7 @@
       </c>
       <c r="M103" s="15"/>
     </row>
-    <row r="104" spans="1:13" hidden="1">
+    <row r="104" spans="1:13">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -56312,7 +56307,7 @@
       </c>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="1:13" hidden="1">
+    <row r="105" spans="1:13">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -56341,7 +56336,7 @@
       </c>
       <c r="M105" s="15"/>
     </row>
-    <row r="106" spans="1:13" hidden="1">
+    <row r="106" spans="1:13">
       <c r="A106" s="14">
         <v>105</v>
       </c>
@@ -56370,7 +56365,7 @@
       </c>
       <c r="M106" s="15"/>
     </row>
-    <row r="107" spans="1:13" hidden="1">
+    <row r="107" spans="1:13">
       <c r="A107" s="14">
         <v>106</v>
       </c>
@@ -56399,7 +56394,7 @@
       </c>
       <c r="M107" s="15"/>
     </row>
-    <row r="108" spans="1:13" hidden="1">
+    <row r="108" spans="1:13">
       <c r="A108" s="14">
         <v>107</v>
       </c>
@@ -56428,7 +56423,7 @@
       </c>
       <c r="M108" s="15"/>
     </row>
-    <row r="109" spans="1:13" hidden="1">
+    <row r="109" spans="1:13">
       <c r="A109" s="14">
         <v>108</v>
       </c>
@@ -56457,7 +56452,7 @@
       </c>
       <c r="M109" s="15"/>
     </row>
-    <row r="110" spans="1:13" hidden="1">
+    <row r="110" spans="1:13">
       <c r="A110" s="14">
         <v>109</v>
       </c>
@@ -56486,7 +56481,7 @@
       </c>
       <c r="M110" s="15"/>
     </row>
-    <row r="111" spans="1:13" hidden="1">
+    <row r="111" spans="1:13">
       <c r="A111" s="14">
         <v>110</v>
       </c>
@@ -56515,7 +56510,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13" hidden="1">
+    <row r="112" spans="1:13">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -56550,7 +56545,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13" hidden="1">
+    <row r="113" spans="1:13">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -56585,7 +56580,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13" hidden="1">
+    <row r="114" spans="1:13">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -56620,7 +56615,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13" hidden="1">
+    <row r="115" spans="1:13">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -56653,7 +56648,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13" hidden="1">
+    <row r="116" spans="1:13">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -56686,7 +56681,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13" hidden="1">
+    <row r="117" spans="1:13">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -56721,7 +56716,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13" hidden="1">
+    <row r="118" spans="1:13">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -56752,7 +56747,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13" hidden="1">
+    <row r="119" spans="1:13">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -56783,7 +56778,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13" hidden="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -56814,7 +56809,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13" hidden="1">
+    <row r="121" spans="1:13">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -56845,7 +56840,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13" hidden="1">
+    <row r="122" spans="1:13">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -56880,7 +56875,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13" hidden="1">
+    <row r="123" spans="1:13">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -56911,7 +56906,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13" hidden="1">
+    <row r="124" spans="1:13">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -56946,7 +56941,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13" hidden="1">
+    <row r="125" spans="1:13">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -56981,7 +56976,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13" hidden="1">
+    <row r="126" spans="1:13">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -57016,7 +57011,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13" hidden="1">
+    <row r="127" spans="1:13">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -57047,7 +57042,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13" hidden="1">
+    <row r="128" spans="1:13">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -57078,7 +57073,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13" hidden="1">
+    <row r="129" spans="1:13">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -57109,7 +57104,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13" hidden="1">
+    <row r="130" spans="1:13">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -57140,7 +57135,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13" hidden="1">
+    <row r="131" spans="1:13">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -57171,7 +57166,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13" hidden="1">
+    <row r="132" spans="1:13">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -57206,7 +57201,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13" hidden="1">
+    <row r="133" spans="1:13">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -57241,7 +57236,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13" hidden="1">
+    <row r="134" spans="1:13">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -57272,7 +57267,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13" hidden="1">
+    <row r="135" spans="1:13">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -57303,7 +57298,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13" hidden="1">
+    <row r="136" spans="1:13">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -57338,7 +57333,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13" hidden="1">
+    <row r="137" spans="1:13">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -57369,7 +57364,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13" hidden="1">
+    <row r="138" spans="1:13">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -57404,7 +57399,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13" hidden="1">
+    <row r="139" spans="1:13">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -57442,7 +57437,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1">
+    <row r="140" spans="1:13">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -57477,7 +57472,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13" hidden="1">
+    <row r="141" spans="1:13">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -57512,7 +57507,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13" hidden="1">
+    <row r="142" spans="1:13">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -57547,7 +57542,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13" hidden="1">
+    <row r="143" spans="1:13">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -57578,7 +57573,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13" hidden="1">
+    <row r="144" spans="1:13">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -57609,7 +57604,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13" hidden="1">
+    <row r="145" spans="1:13">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -57644,7 +57639,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13" hidden="1">
+    <row r="146" spans="1:13">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -57679,7 +57674,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13" hidden="1">
+    <row r="147" spans="1:13">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -57714,7 +57709,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13" hidden="1">
+    <row r="148" spans="1:13">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -57749,7 +57744,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13" hidden="1">
+    <row r="149" spans="1:13">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -57784,7 +57779,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13" hidden="1">
+    <row r="150" spans="1:13">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -57819,7 +57814,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13" hidden="1">
+    <row r="151" spans="1:13">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -57854,7 +57849,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13" hidden="1">
+    <row r="152" spans="1:13">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -57889,7 +57884,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13" hidden="1">
+    <row r="153" spans="1:13">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -57924,7 +57919,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13" hidden="1">
+    <row r="154" spans="1:13">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -57959,7 +57954,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13" hidden="1">
+    <row r="155" spans="1:13">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -57994,7 +57989,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13" hidden="1">
+    <row r="156" spans="1:13">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -58029,7 +58024,7 @@
       </c>
       <c r="M156" s="15"/>
     </row>
-    <row r="157" spans="1:13" hidden="1">
+    <row r="157" spans="1:13">
       <c r="A157" s="14">
         <v>165</v>
       </c>
@@ -58058,7 +58053,7 @@
       </c>
       <c r="M157" s="15"/>
     </row>
-    <row r="158" spans="1:13" hidden="1">
+    <row r="158" spans="1:13">
       <c r="A158" s="14">
         <v>166</v>
       </c>
@@ -58087,7 +58082,7 @@
       </c>
       <c r="M158" s="15"/>
     </row>
-    <row r="159" spans="1:13" hidden="1">
+    <row r="159" spans="1:13">
       <c r="A159" s="14">
         <v>167</v>
       </c>
@@ -58116,7 +58111,7 @@
       </c>
       <c r="M159" s="15"/>
     </row>
-    <row r="160" spans="1:13" hidden="1">
+    <row r="160" spans="1:13">
       <c r="A160" s="14">
         <v>168</v>
       </c>
@@ -58145,7 +58140,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13" hidden="1">
+    <row r="161" spans="1:13">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -58174,7 +58169,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13" hidden="1">
+    <row r="162" spans="1:13">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -58203,7 +58198,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13" hidden="1">
+    <row r="163" spans="1:13">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -58232,7 +58227,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13" hidden="1">
+    <row r="164" spans="1:13">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -58261,7 +58256,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13" hidden="1">
+    <row r="165" spans="1:13">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -58296,7 +58291,7 @@
       </c>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13" hidden="1">
+    <row r="166" spans="1:13">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -58331,7 +58326,7 @@
       </c>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13" hidden="1">
+    <row r="167" spans="1:13">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -58366,7 +58361,7 @@
       </c>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13" hidden="1">
+    <row r="168" spans="1:13">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -58401,7 +58396,7 @@
       </c>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13" hidden="1">
+    <row r="169" spans="1:13">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -58436,7 +58431,7 @@
       </c>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13" hidden="1">
+    <row r="170" spans="1:13">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -58471,7 +58466,7 @@
       </c>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13" hidden="1">
+    <row r="171" spans="1:13">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -58506,7 +58501,7 @@
       </c>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13" hidden="1">
+    <row r="172" spans="1:13">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -58541,7 +58536,7 @@
       </c>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13" hidden="1">
+    <row r="173" spans="1:13">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -58576,7 +58571,7 @@
       </c>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13" hidden="1">
+    <row r="174" spans="1:13">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -58611,7 +58606,7 @@
       </c>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13" hidden="1">
+    <row r="175" spans="1:13">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -58644,7 +58639,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13" hidden="1">
+    <row r="176" spans="1:13">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -58677,7 +58672,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -58710,7 +58705,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -58743,7 +58738,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -58776,7 +58771,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -58809,7 +58804,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13" hidden="1">
+    <row r="181" spans="1:13">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -58848,7 +58843,7 @@
       </c>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13" hidden="1">
+    <row r="182" spans="1:13">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -58887,7 +58882,7 @@
       </c>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13" hidden="1">
+    <row r="183" spans="1:13">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -58926,7 +58921,7 @@
       </c>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13" hidden="1">
+    <row r="184" spans="1:13">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -58965,7 +58960,7 @@
       </c>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13" hidden="1">
+    <row r="185" spans="1:13">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -59004,7 +58999,7 @@
       </c>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13" hidden="1">
+    <row r="186" spans="1:13">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -59043,7 +59038,7 @@
       </c>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13" hidden="1">
+    <row r="187" spans="1:13">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -59082,7 +59077,7 @@
       </c>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13" hidden="1">
+    <row r="188" spans="1:13">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -59119,7 +59114,7 @@
       </c>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13" hidden="1">
+    <row r="189" spans="1:13">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -59158,7 +59153,7 @@
       </c>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13" hidden="1">
+    <row r="190" spans="1:13">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -59197,7 +59192,7 @@
       </c>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13" hidden="1">
+    <row r="191" spans="1:13">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -59236,7 +59231,7 @@
       </c>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13" hidden="1">
+    <row r="192" spans="1:13">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -59273,7 +59268,7 @@
       </c>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13" hidden="1">
+    <row r="193" spans="1:13">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -59312,7 +59307,7 @@
       </c>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13" hidden="1">
+    <row r="194" spans="1:13">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -59351,7 +59346,7 @@
       </c>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13" hidden="1">
+    <row r="195" spans="1:13">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -59390,7 +59385,7 @@
       </c>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13" hidden="1">
+    <row r="196" spans="1:13">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -59429,7 +59424,7 @@
       </c>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13" hidden="1">
+    <row r="197" spans="1:13">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -59468,7 +59463,7 @@
       </c>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13" hidden="1">
+    <row r="198" spans="1:13">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -59507,7 +59502,7 @@
       </c>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13" hidden="1">
+    <row r="199" spans="1:13">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -59546,7 +59541,7 @@
       </c>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13" hidden="1">
+    <row r="200" spans="1:13">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -59583,7 +59578,7 @@
       </c>
       <c r="M200" s="15"/>
     </row>
-    <row r="201" spans="1:13" hidden="1">
+    <row r="201" spans="1:13">
       <c r="A201" s="14">
         <v>209</v>
       </c>
@@ -59616,7 +59611,7 @@
       <c r="L201" s="15"/>
       <c r="M201" s="15"/>
     </row>
-    <row r="202" spans="1:13" hidden="1">
+    <row r="202" spans="1:13">
       <c r="A202" s="14">
         <v>210</v>
       </c>
@@ -59715,7 +59710,7 @@
       <c r="L204" s="15"/>
       <c r="M204" s="15"/>
     </row>
-    <row r="205" spans="1:13" hidden="1">
+    <row r="205" spans="1:13">
       <c r="A205" s="14">
         <v>213</v>
       </c>
@@ -59752,7 +59747,7 @@
       </c>
       <c r="M205" s="15"/>
     </row>
-    <row r="206" spans="1:13" hidden="1">
+    <row r="206" spans="1:13">
       <c r="A206" s="14">
         <v>214</v>
       </c>
@@ -59789,7 +59784,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13" hidden="1">
+    <row r="207" spans="1:13">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -59824,7 +59819,7 @@
       </c>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13" hidden="1">
+    <row r="208" spans="1:13">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -59859,7 +59854,7 @@
       </c>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13" hidden="1">
+    <row r="209" spans="1:13">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -59894,7 +59889,7 @@
       </c>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13" hidden="1">
+    <row r="210" spans="1:13">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -59929,7 +59924,7 @@
       </c>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13" hidden="1">
+    <row r="211" spans="1:13">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -59958,7 +59953,7 @@
       </c>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13" hidden="1">
+    <row r="212" spans="1:13">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -59987,7 +59982,7 @@
       </c>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13" ht="15.75" hidden="1">
+    <row r="213" spans="1:13" ht="15.75">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -60022,7 +60017,7 @@
       </c>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13" ht="15.75" hidden="1">
+    <row r="214" spans="1:13" ht="15.75">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -60057,7 +60052,7 @@
       </c>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13" hidden="1">
+    <row r="215" spans="1:13">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -60092,7 +60087,7 @@
       </c>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13" hidden="1">
+    <row r="216" spans="1:13">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -60127,7 +60122,7 @@
       </c>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13" hidden="1">
+    <row r="217" spans="1:13">
       <c r="A217" s="14">
         <v>227</v>
       </c>
@@ -60164,7 +60159,7 @@
       </c>
       <c r="M217" s="15"/>
     </row>
-    <row r="218" spans="1:13" hidden="1">
+    <row r="218" spans="1:13">
       <c r="A218" s="14">
         <v>228</v>
       </c>
@@ -60201,7 +60196,7 @@
       </c>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13" hidden="1">
+    <row r="219" spans="1:13">
       <c r="A219" s="14">
         <v>229</v>
       </c>
@@ -60238,7 +60233,7 @@
       </c>
       <c r="M219" s="15"/>
     </row>
-    <row r="220" spans="1:13" hidden="1">
+    <row r="220" spans="1:13">
       <c r="A220" s="14">
         <v>230</v>
       </c>
@@ -60275,7 +60270,7 @@
       </c>
       <c r="M220" s="15"/>
     </row>
-    <row r="221" spans="1:13" hidden="1">
+    <row r="221" spans="1:13">
       <c r="A221" s="14">
         <v>231</v>
       </c>
@@ -60312,7 +60307,7 @@
       </c>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13" hidden="1">
+    <row r="222" spans="1:13">
       <c r="A222" s="14">
         <v>232</v>
       </c>
@@ -60347,7 +60342,7 @@
       </c>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13" hidden="1">
+    <row r="223" spans="1:13">
       <c r="A223" s="14">
         <v>233</v>
       </c>
@@ -60382,7 +60377,7 @@
       </c>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13" ht="14.25" hidden="1">
+    <row r="224" spans="1:13" ht="14.25">
       <c r="A224" s="14">
         <v>236</v>
       </c>
@@ -60417,7 +60412,7 @@
       </c>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13" ht="14.25" hidden="1">
+    <row r="225" spans="1:13" ht="14.25">
       <c r="A225" s="14">
         <v>237</v>
       </c>
@@ -60452,7 +60447,7 @@
       </c>
       <c r="M225" s="15"/>
     </row>
-    <row r="226" spans="1:13" hidden="1">
+    <row r="226" spans="1:13">
       <c r="A226" s="14">
         <v>241</v>
       </c>
@@ -60489,7 +60484,7 @@
       </c>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13" hidden="1">
+    <row r="227" spans="1:13">
       <c r="A227" s="14">
         <v>242</v>
       </c>
@@ -60526,7 +60521,7 @@
       </c>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13" hidden="1">
+    <row r="228" spans="1:13">
       <c r="A228" s="14">
         <v>243</v>
       </c>
@@ -60563,7 +60558,7 @@
       </c>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13" hidden="1">
+    <row r="229" spans="1:13">
       <c r="A229" s="14">
         <v>244</v>
       </c>
@@ -60600,7 +60595,7 @@
       </c>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13" hidden="1">
+    <row r="230" spans="1:13">
       <c r="A230" s="14">
         <v>245</v>
       </c>
@@ -60637,7 +60632,7 @@
       </c>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13" hidden="1">
+    <row r="231" spans="1:13">
       <c r="A231" s="14">
         <v>246</v>
       </c>
@@ -60674,7 +60669,7 @@
       </c>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13" hidden="1">
+    <row r="232" spans="1:13">
       <c r="A232" s="14">
         <v>247</v>
       </c>
@@ -60855,37 +60850,73 @@
       <c r="L236" s="15"/>
       <c r="M236" s="15"/>
     </row>
-    <row r="237" spans="1:13" ht="14.25">
+    <row r="237" spans="1:13">
       <c r="A237" s="14">
         <v>252</v>
       </c>
-      <c r="B237" s="42"/>
-      <c r="C237" s="61"/>
-      <c r="D237" s="61"/>
-      <c r="E237" s="61"/>
-      <c r="F237" s="62"/>
-      <c r="G237" s="61"/>
-      <c r="H237" s="62"/>
-      <c r="I237" s="61"/>
-      <c r="J237" s="15"/>
-      <c r="K237" s="22"/>
+      <c r="B237" s="42">
+        <v>46281</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D237" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E237" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F237" s="13">
+        <v>0.4375</v>
+      </c>
+      <c r="G237" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="H237" s="13">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="I237" s="26"/>
+      <c r="J237" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="K237" s="22">
+        <v>0</v>
+      </c>
       <c r="L237" s="15"/>
       <c r="M237" s="15"/>
     </row>
-    <row r="238" spans="1:13" ht="14.25">
+    <row r="238" spans="1:13">
       <c r="A238" s="14">
         <v>253</v>
       </c>
-      <c r="B238" s="42"/>
-      <c r="C238" s="61"/>
-      <c r="D238" s="61"/>
-      <c r="E238" s="61"/>
-      <c r="F238" s="62"/>
-      <c r="G238" s="61"/>
-      <c r="H238" s="62"/>
-      <c r="I238" s="61"/>
-      <c r="J238" s="15"/>
-      <c r="K238" s="22"/>
+      <c r="B238" s="42">
+        <v>46312</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D238" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="E238" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F238" s="13">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="G238" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="H238" s="13">
+        <v>0.78125</v>
+      </c>
+      <c r="I238" s="26"/>
+      <c r="J238" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="K238" s="22">
+        <v>0</v>
+      </c>
       <c r="L238" s="15"/>
       <c r="M238" s="15"/>
     </row>
@@ -61316,7 +61347,7 @@
     </row>
     <row r="274" spans="10:11">
       <c r="J274" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K274" s="11">
         <f>SUM(テーブル4[料金])</f>
@@ -61325,11 +61356,11 @@
     </row>
     <row r="275" spans="10:11">
       <c r="J275" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K275">
         <f>COUNTA(テーブル4[料金])*5</f>
-        <v>1155</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="276" spans="10:11">
@@ -61338,16 +61369,16 @@
       </c>
       <c r="K276">
         <f>COUNTA(テーブル4[料金])</f>
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="277" spans="10:11">
       <c r="J277" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K277" s="41">
         <f>K274/K275</f>
-        <v>1180.5402597402597</v>
+        <v>1170.4068669527896</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -61425,7 +61456,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="H291" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -61477,7 +61508,7 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="H293" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -61581,7 +61612,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="H297" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -61815,7 +61846,7 @@
         <v>0.375</v>
       </c>
       <c r="H309" s="51" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I309" s="52"/>
     </row>
@@ -61869,7 +61900,7 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="H311" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I311" s="52"/>
     </row>
@@ -62004,7 +62035,7 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="H316" s="54" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I316" s="56"/>
     </row>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3263" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B6A5A8-A5CE-427B-B9AC-ECAFC83EBF90}"/>
+  <xr:revisionPtr revIDLastSave="3266" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FECAF55-847F-4CE8-8716-9B1C23576122}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14839,7 +14839,11 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}" name="テーブル4" displayName="テーブル4" ref="A1:M263" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M263" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}"/>
+  <autoFilter ref="A1:M263" xr:uid="{3FCDC422-27B5-482E-BFE7-6645FF3F845A}">
+    <filterColumn colId="11">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{25F04EEC-FD30-4680-810A-6A32107348BD}" name="#" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{E936A600-BB79-446A-9797-5E2C4AB43B97}" name="日付" dataDxfId="11"/>
@@ -52805,7 +52809,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" hidden="1">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -52842,7 +52846,7 @@
       </c>
       <c r="M2" s="63"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" hidden="1">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -52879,7 +52883,7 @@
       </c>
       <c r="M3" s="15"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" hidden="1">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -52916,7 +52920,7 @@
       </c>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" hidden="1">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -52953,7 +52957,7 @@
       </c>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" hidden="1">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -52990,7 +52994,7 @@
       </c>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" hidden="1">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -53027,7 +53031,7 @@
       </c>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" hidden="1">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -53064,7 +53068,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" hidden="1">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -53101,7 +53105,7 @@
       </c>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" hidden="1">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -53138,7 +53142,7 @@
       </c>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" hidden="1">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -53175,7 +53179,7 @@
       </c>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" hidden="1">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -53212,7 +53216,7 @@
       </c>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" hidden="1">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -53249,7 +53253,7 @@
       </c>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" hidden="1">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -53286,7 +53290,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" hidden="1">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -53323,7 +53327,7 @@
       </c>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" hidden="1">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -53360,7 +53364,7 @@
       </c>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" hidden="1">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -53397,7 +53401,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" hidden="1">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -53434,7 +53438,7 @@
       </c>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" hidden="1">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -53471,7 +53475,7 @@
       </c>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" hidden="1">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -53508,7 +53512,7 @@
       </c>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" hidden="1">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -53545,7 +53549,7 @@
       </c>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" hidden="1">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -53582,7 +53586,7 @@
       </c>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" hidden="1">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -53619,7 +53623,7 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" hidden="1">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -53656,7 +53660,7 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" hidden="1">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -53693,7 +53697,7 @@
       </c>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" hidden="1">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -53730,7 +53734,7 @@
       </c>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" hidden="1">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -53765,7 +53769,7 @@
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" hidden="1">
       <c r="A28" s="14">
         <v>27</v>
       </c>
@@ -53802,7 +53806,7 @@
       </c>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" hidden="1">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -53839,7 +53843,7 @@
       </c>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" hidden="1">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -53876,7 +53880,7 @@
       </c>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" hidden="1">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -53913,7 +53917,7 @@
       </c>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" hidden="1">
       <c r="A32" s="14">
         <v>31</v>
       </c>
@@ -53950,7 +53954,7 @@
       </c>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" hidden="1">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -53987,7 +53991,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" hidden="1">
       <c r="A34" s="14">
         <v>33</v>
       </c>
@@ -54024,7 +54028,7 @@
       </c>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" hidden="1">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -54059,7 +54063,7 @@
       </c>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" hidden="1">
       <c r="A36" s="14">
         <v>35</v>
       </c>
@@ -54094,7 +54098,7 @@
       </c>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" hidden="1">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -54129,7 +54133,7 @@
       </c>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" hidden="1">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -54164,7 +54168,7 @@
       </c>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" hidden="1">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -54199,7 +54203,7 @@
       </c>
       <c r="M39" s="15"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" hidden="1">
       <c r="A40" s="14">
         <v>39</v>
       </c>
@@ -54234,7 +54238,7 @@
       </c>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" hidden="1">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -54265,7 +54269,7 @@
       </c>
       <c r="M41" s="15"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" hidden="1">
       <c r="A42" s="14">
         <v>41</v>
       </c>
@@ -54296,7 +54300,7 @@
       </c>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" hidden="1">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -54327,7 +54331,7 @@
       </c>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" hidden="1">
       <c r="A44" s="14">
         <v>43</v>
       </c>
@@ -54358,7 +54362,7 @@
       </c>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" hidden="1">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -54389,7 +54393,7 @@
       </c>
       <c r="M45" s="15"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" hidden="1">
       <c r="A46" s="14">
         <v>45</v>
       </c>
@@ -54420,7 +54424,7 @@
       </c>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" hidden="1">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -54451,7 +54455,7 @@
       </c>
       <c r="M47" s="15"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" hidden="1">
       <c r="A48" s="14">
         <v>47</v>
       </c>
@@ -54482,7 +54486,7 @@
       </c>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" hidden="1">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -54513,7 +54517,7 @@
       </c>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" hidden="1">
       <c r="A50" s="14">
         <v>49</v>
       </c>
@@ -54544,7 +54548,7 @@
       </c>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" hidden="1">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -54575,7 +54579,7 @@
       </c>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" hidden="1">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -54606,7 +54610,7 @@
       </c>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" hidden="1">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -54637,7 +54641,7 @@
       </c>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" hidden="1">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -54668,7 +54672,7 @@
       </c>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" hidden="1">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -54699,7 +54703,7 @@
       </c>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" hidden="1">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -54730,7 +54734,7 @@
       </c>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" hidden="1">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -54761,7 +54765,7 @@
       </c>
       <c r="M57" s="15"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" hidden="1">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -54792,7 +54796,7 @@
       </c>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" hidden="1">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -54823,7 +54827,7 @@
       </c>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" hidden="1">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -54858,7 +54862,7 @@
       </c>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" hidden="1">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -54893,7 +54897,7 @@
       </c>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" hidden="1">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -54928,7 +54932,7 @@
       </c>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" hidden="1">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -54963,7 +54967,7 @@
       </c>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" hidden="1">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -54998,7 +55002,7 @@
       </c>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" hidden="1">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -55033,7 +55037,7 @@
       </c>
       <c r="M65" s="15"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" hidden="1">
       <c r="A66" s="14">
         <v>65</v>
       </c>
@@ -55068,7 +55072,7 @@
       </c>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" hidden="1">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -55103,7 +55107,7 @@
       </c>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" hidden="1">
       <c r="A68" s="14">
         <v>67</v>
       </c>
@@ -55138,7 +55142,7 @@
       </c>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" hidden="1">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -55169,7 +55173,7 @@
       </c>
       <c r="M69" s="15"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" hidden="1">
       <c r="A70" s="14">
         <v>69</v>
       </c>
@@ -55200,7 +55204,7 @@
       </c>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -55236,7 +55240,7 @@
       </c>
       <c r="M71" s="15"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" hidden="1">
       <c r="A72" s="14">
         <v>71</v>
       </c>
@@ -55271,7 +55275,7 @@
       </c>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" hidden="1">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -55300,7 +55304,7 @@
       </c>
       <c r="M73" s="15"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" hidden="1">
       <c r="A74" s="14">
         <v>73</v>
       </c>
@@ -55329,7 +55333,7 @@
       </c>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" hidden="1">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -55358,7 +55362,7 @@
       </c>
       <c r="M75" s="15"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" hidden="1">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -55387,7 +55391,7 @@
       </c>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -55420,7 +55424,7 @@
       </c>
       <c r="M77" s="15"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -55453,7 +55457,7 @@
       </c>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" hidden="1">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -55486,7 +55490,7 @@
       </c>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" hidden="1">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -55519,7 +55523,7 @@
       </c>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" hidden="1">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -55552,7 +55556,7 @@
       </c>
       <c r="M81" s="15"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" hidden="1">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -55585,7 +55589,7 @@
       </c>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" hidden="1">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -55618,7 +55622,7 @@
       </c>
       <c r="M83" s="15"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" hidden="1">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -55651,7 +55655,7 @@
       </c>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" hidden="1">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -55684,7 +55688,7 @@
       </c>
       <c r="M85" s="15"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" hidden="1">
       <c r="A86" s="14">
         <v>85</v>
       </c>
@@ -55717,7 +55721,7 @@
       </c>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" hidden="1">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -55750,7 +55754,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" hidden="1">
       <c r="A88" s="14">
         <v>87</v>
       </c>
@@ -55783,7 +55787,7 @@
       </c>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" hidden="1">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -55816,7 +55820,7 @@
       </c>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" hidden="1">
       <c r="A90" s="14">
         <v>89</v>
       </c>
@@ -55849,7 +55853,7 @@
       </c>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" hidden="1">
       <c r="A91" s="14">
         <v>90</v>
       </c>
@@ -55882,7 +55886,7 @@
       </c>
       <c r="M91" s="15"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" hidden="1">
       <c r="A92" s="14">
         <v>91</v>
       </c>
@@ -55915,7 +55919,7 @@
       </c>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" hidden="1">
       <c r="A93" s="14">
         <v>92</v>
       </c>
@@ -55948,7 +55952,7 @@
       </c>
       <c r="M93" s="15"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" hidden="1">
       <c r="A94" s="14">
         <v>93</v>
       </c>
@@ -55981,7 +55985,7 @@
       </c>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" hidden="1">
       <c r="A95" s="14">
         <v>94</v>
       </c>
@@ -56014,7 +56018,7 @@
       </c>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" hidden="1">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -56047,7 +56051,7 @@
       </c>
       <c r="M96" s="15"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" hidden="1">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -56080,7 +56084,7 @@
       </c>
       <c r="M97" s="15"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" hidden="1">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -56113,7 +56117,7 @@
       </c>
       <c r="M98" s="15"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" hidden="1">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -56146,7 +56150,7 @@
       </c>
       <c r="M99" s="15"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" hidden="1">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -56179,7 +56183,7 @@
       </c>
       <c r="M100" s="15"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" hidden="1">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -56212,7 +56216,7 @@
       </c>
       <c r="M101" s="15"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" hidden="1">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -56245,7 +56249,7 @@
       </c>
       <c r="M102" s="15"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" hidden="1">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -56278,7 +56282,7 @@
       </c>
       <c r="M103" s="15"/>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" hidden="1">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -56307,7 +56311,7 @@
       </c>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" hidden="1">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -56336,7 +56340,7 @@
       </c>
       <c r="M105" s="15"/>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" hidden="1">
       <c r="A106" s="14">
         <v>105</v>
       </c>
@@ -56365,7 +56369,7 @@
       </c>
       <c r="M106" s="15"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" hidden="1">
       <c r="A107" s="14">
         <v>106</v>
       </c>
@@ -56394,7 +56398,7 @@
       </c>
       <c r="M107" s="15"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" hidden="1">
       <c r="A108" s="14">
         <v>107</v>
       </c>
@@ -56423,7 +56427,7 @@
       </c>
       <c r="M108" s="15"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" hidden="1">
       <c r="A109" s="14">
         <v>108</v>
       </c>
@@ -56452,7 +56456,7 @@
       </c>
       <c r="M109" s="15"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" hidden="1">
       <c r="A110" s="14">
         <v>109</v>
       </c>
@@ -56481,7 +56485,7 @@
       </c>
       <c r="M110" s="15"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" hidden="1">
       <c r="A111" s="14">
         <v>110</v>
       </c>
@@ -56510,7 +56514,7 @@
       </c>
       <c r="M111" s="15"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" hidden="1">
       <c r="A112" s="14">
         <v>111</v>
       </c>
@@ -56545,7 +56549,7 @@
       </c>
       <c r="M112" s="15"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" hidden="1">
       <c r="A113" s="14">
         <v>112</v>
       </c>
@@ -56580,7 +56584,7 @@
       </c>
       <c r="M113" s="15"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" hidden="1">
       <c r="A114" s="14">
         <v>113</v>
       </c>
@@ -56615,7 +56619,7 @@
       </c>
       <c r="M114" s="15"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" hidden="1">
       <c r="A115" s="14">
         <v>114</v>
       </c>
@@ -56648,7 +56652,7 @@
       </c>
       <c r="M115" s="15"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" hidden="1">
       <c r="A116" s="14">
         <v>115</v>
       </c>
@@ -56681,7 +56685,7 @@
       </c>
       <c r="M116" s="15"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" hidden="1">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -56716,7 +56720,7 @@
       </c>
       <c r="M117" s="15"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" hidden="1">
       <c r="A118" s="14">
         <v>126</v>
       </c>
@@ -56747,7 +56751,7 @@
       </c>
       <c r="M118" s="15"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" hidden="1">
       <c r="A119" s="14">
         <v>127</v>
       </c>
@@ -56778,7 +56782,7 @@
       </c>
       <c r="M119" s="15"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" hidden="1">
       <c r="A120" s="14">
         <v>128</v>
       </c>
@@ -56809,7 +56813,7 @@
       </c>
       <c r="M120" s="15"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" hidden="1">
       <c r="A121" s="14">
         <v>129</v>
       </c>
@@ -56840,7 +56844,7 @@
       </c>
       <c r="M121" s="15"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" hidden="1">
       <c r="A122" s="14">
         <v>130</v>
       </c>
@@ -56875,7 +56879,7 @@
       </c>
       <c r="M122" s="15"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" hidden="1">
       <c r="A123" s="14">
         <v>131</v>
       </c>
@@ -56906,7 +56910,7 @@
       </c>
       <c r="M123" s="15"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" hidden="1">
       <c r="A124" s="14">
         <v>132</v>
       </c>
@@ -56941,7 +56945,7 @@
       </c>
       <c r="M124" s="15"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" hidden="1">
       <c r="A125" s="14">
         <v>133</v>
       </c>
@@ -56976,7 +56980,7 @@
       </c>
       <c r="M125" s="15"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" hidden="1">
       <c r="A126" s="14">
         <v>134</v>
       </c>
@@ -57011,7 +57015,7 @@
       </c>
       <c r="M126" s="15"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" hidden="1">
       <c r="A127" s="14">
         <v>135</v>
       </c>
@@ -57042,7 +57046,7 @@
       </c>
       <c r="M127" s="15"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" hidden="1">
       <c r="A128" s="14">
         <v>136</v>
       </c>
@@ -57073,7 +57077,7 @@
       </c>
       <c r="M128" s="15"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" hidden="1">
       <c r="A129" s="14">
         <v>137</v>
       </c>
@@ -57104,7 +57108,7 @@
       </c>
       <c r="M129" s="15"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" hidden="1">
       <c r="A130" s="14">
         <v>138</v>
       </c>
@@ -57135,7 +57139,7 @@
       </c>
       <c r="M130" s="15"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" hidden="1">
       <c r="A131" s="14">
         <v>139</v>
       </c>
@@ -57166,7 +57170,7 @@
       </c>
       <c r="M131" s="15"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" hidden="1">
       <c r="A132" s="14">
         <v>140</v>
       </c>
@@ -57201,7 +57205,7 @@
       </c>
       <c r="M132" s="15"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" hidden="1">
       <c r="A133" s="14">
         <v>141</v>
       </c>
@@ -57236,7 +57240,7 @@
       </c>
       <c r="M133" s="15"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" hidden="1">
       <c r="A134" s="14">
         <v>142</v>
       </c>
@@ -57267,7 +57271,7 @@
       </c>
       <c r="M134" s="15"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" hidden="1">
       <c r="A135" s="14">
         <v>143</v>
       </c>
@@ -57298,7 +57302,7 @@
       </c>
       <c r="M135" s="15"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" hidden="1">
       <c r="A136" s="14">
         <v>144</v>
       </c>
@@ -57333,7 +57337,7 @@
       </c>
       <c r="M136" s="15"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" hidden="1">
       <c r="A137" s="14">
         <v>145</v>
       </c>
@@ -57364,7 +57368,7 @@
       </c>
       <c r="M137" s="15"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" hidden="1">
       <c r="A138" s="14">
         <v>146</v>
       </c>
@@ -57399,7 +57403,7 @@
       </c>
       <c r="M138" s="15"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" hidden="1">
       <c r="A139" s="14">
         <v>147</v>
       </c>
@@ -57437,7 +57441,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" hidden="1">
       <c r="A140" s="14">
         <v>148</v>
       </c>
@@ -57472,7 +57476,7 @@
       </c>
       <c r="M140" s="15"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" hidden="1">
       <c r="A141" s="14">
         <v>149</v>
       </c>
@@ -57507,7 +57511,7 @@
       </c>
       <c r="M141" s="15"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" hidden="1">
       <c r="A142" s="14">
         <v>150</v>
       </c>
@@ -57542,7 +57546,7 @@
       </c>
       <c r="M142" s="15"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" hidden="1">
       <c r="A143" s="14">
         <v>151</v>
       </c>
@@ -57573,7 +57577,7 @@
       </c>
       <c r="M143" s="15"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" hidden="1">
       <c r="A144" s="14">
         <v>152</v>
       </c>
@@ -57604,7 +57608,7 @@
       </c>
       <c r="M144" s="15"/>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" hidden="1">
       <c r="A145" s="14">
         <v>153</v>
       </c>
@@ -57639,7 +57643,7 @@
       </c>
       <c r="M145" s="15"/>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" hidden="1">
       <c r="A146" s="14">
         <v>154</v>
       </c>
@@ -57674,7 +57678,7 @@
       </c>
       <c r="M146" s="15"/>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" hidden="1">
       <c r="A147" s="14">
         <v>155</v>
       </c>
@@ -57709,7 +57713,7 @@
       </c>
       <c r="M147" s="15"/>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" hidden="1">
       <c r="A148" s="14">
         <v>156</v>
       </c>
@@ -57744,7 +57748,7 @@
       </c>
       <c r="M148" s="15"/>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" hidden="1">
       <c r="A149" s="14">
         <v>157</v>
       </c>
@@ -57779,7 +57783,7 @@
       </c>
       <c r="M149" s="15"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" hidden="1">
       <c r="A150" s="14">
         <v>158</v>
       </c>
@@ -57814,7 +57818,7 @@
       </c>
       <c r="M150" s="15"/>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" hidden="1">
       <c r="A151" s="14">
         <v>159</v>
       </c>
@@ -57849,7 +57853,7 @@
       </c>
       <c r="M151" s="15"/>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" hidden="1">
       <c r="A152" s="14">
         <v>160</v>
       </c>
@@ -57884,7 +57888,7 @@
       </c>
       <c r="M152" s="15"/>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" hidden="1">
       <c r="A153" s="14">
         <v>161</v>
       </c>
@@ -57919,7 +57923,7 @@
       </c>
       <c r="M153" s="15"/>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" hidden="1">
       <c r="A154" s="14">
         <v>162</v>
       </c>
@@ -57954,7 +57958,7 @@
       </c>
       <c r="M154" s="15"/>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" hidden="1">
       <c r="A155" s="14">
         <v>163</v>
       </c>
@@ -57989,7 +57993,7 @@
       </c>
       <c r="M155" s="15"/>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" hidden="1">
       <c r="A156" s="14">
         <v>164</v>
       </c>
@@ -58024,7 +58028,7 @@
       </c>
       <c r="M156" s="15"/>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" hidden="1">
       <c r="A157" s="14">
         <v>165</v>
       </c>
@@ -58053,7 +58057,7 @@
       </c>
       <c r="M157" s="15"/>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" hidden="1">
       <c r="A158" s="14">
         <v>166</v>
       </c>
@@ -58082,7 +58086,7 @@
       </c>
       <c r="M158" s="15"/>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" hidden="1">
       <c r="A159" s="14">
         <v>167</v>
       </c>
@@ -58111,7 +58115,7 @@
       </c>
       <c r="M159" s="15"/>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" hidden="1">
       <c r="A160" s="14">
         <v>168</v>
       </c>
@@ -58140,7 +58144,7 @@
       </c>
       <c r="M160" s="15"/>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" hidden="1">
       <c r="A161" s="14">
         <v>169</v>
       </c>
@@ -58169,7 +58173,7 @@
       </c>
       <c r="M161" s="15"/>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" hidden="1">
       <c r="A162" s="14">
         <v>170</v>
       </c>
@@ -58198,7 +58202,7 @@
       </c>
       <c r="M162" s="15"/>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" hidden="1">
       <c r="A163" s="14">
         <v>171</v>
       </c>
@@ -58227,7 +58231,7 @@
       </c>
       <c r="M163" s="15"/>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" hidden="1">
       <c r="A164" s="14">
         <v>172</v>
       </c>
@@ -58256,7 +58260,7 @@
       </c>
       <c r="M164" s="15"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="14">
         <v>173</v>
       </c>
@@ -58291,7 +58295,7 @@
       </c>
       <c r="M165" s="15"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="14">
         <v>174</v>
       </c>
@@ -58326,7 +58330,7 @@
       </c>
       <c r="M166" s="15"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="14">
         <v>175</v>
       </c>
@@ -58361,7 +58365,7 @@
       </c>
       <c r="M167" s="15"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="14">
         <v>176</v>
       </c>
@@ -58396,7 +58400,7 @@
       </c>
       <c r="M168" s="15"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="14">
         <v>177</v>
       </c>
@@ -58431,7 +58435,7 @@
       </c>
       <c r="M169" s="15"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="14">
         <v>178</v>
       </c>
@@ -58466,7 +58470,7 @@
       </c>
       <c r="M170" s="15"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="14">
         <v>179</v>
       </c>
@@ -58501,7 +58505,7 @@
       </c>
       <c r="M171" s="15"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="14">
         <v>180</v>
       </c>
@@ -58536,7 +58540,7 @@
       </c>
       <c r="M172" s="15"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="14">
         <v>181</v>
       </c>
@@ -58571,7 +58575,7 @@
       </c>
       <c r="M173" s="15"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="14">
         <v>182</v>
       </c>
@@ -58606,7 +58610,7 @@
       </c>
       <c r="M174" s="15"/>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" hidden="1">
       <c r="A175" s="14">
         <v>183</v>
       </c>
@@ -58639,7 +58643,7 @@
       </c>
       <c r="M175" s="15"/>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" hidden="1">
       <c r="A176" s="14">
         <v>184</v>
       </c>
@@ -58672,7 +58676,7 @@
       </c>
       <c r="M176" s="15"/>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" hidden="1">
       <c r="A177" s="14">
         <v>185</v>
       </c>
@@ -58705,7 +58709,7 @@
       </c>
       <c r="M177" s="15"/>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" hidden="1">
       <c r="A178" s="14">
         <v>186</v>
       </c>
@@ -58738,7 +58742,7 @@
       </c>
       <c r="M178" s="15"/>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" hidden="1">
       <c r="A179" s="14">
         <v>187</v>
       </c>
@@ -58771,7 +58775,7 @@
       </c>
       <c r="M179" s="15"/>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" hidden="1">
       <c r="A180" s="14">
         <v>188</v>
       </c>
@@ -58804,7 +58808,7 @@
       </c>
       <c r="M180" s="15"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="14">
         <v>189</v>
       </c>
@@ -58843,7 +58847,7 @@
       </c>
       <c r="M181" s="15"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="14">
         <v>190</v>
       </c>
@@ -58882,7 +58886,7 @@
       </c>
       <c r="M182" s="15"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="14">
         <v>191</v>
       </c>
@@ -58921,7 +58925,7 @@
       </c>
       <c r="M183" s="15"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="14">
         <v>192</v>
       </c>
@@ -58960,7 +58964,7 @@
       </c>
       <c r="M184" s="15"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="14">
         <v>193</v>
       </c>
@@ -58999,7 +59003,7 @@
       </c>
       <c r="M185" s="15"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="14">
         <v>194</v>
       </c>
@@ -59038,7 +59042,7 @@
       </c>
       <c r="M186" s="15"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="14">
         <v>195</v>
       </c>
@@ -59077,7 +59081,7 @@
       </c>
       <c r="M187" s="15"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="14">
         <v>196</v>
       </c>
@@ -59114,7 +59118,7 @@
       </c>
       <c r="M188" s="15"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="14">
         <v>197</v>
       </c>
@@ -59153,7 +59157,7 @@
       </c>
       <c r="M189" s="15"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="14">
         <v>198</v>
       </c>
@@ -59192,7 +59196,7 @@
       </c>
       <c r="M190" s="15"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="14">
         <v>199</v>
       </c>
@@ -59231,7 +59235,7 @@
       </c>
       <c r="M191" s="15"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="14">
         <v>200</v>
       </c>
@@ -59268,7 +59272,7 @@
       </c>
       <c r="M192" s="15"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="14">
         <v>201</v>
       </c>
@@ -59307,7 +59311,7 @@
       </c>
       <c r="M193" s="15"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="14">
         <v>202</v>
       </c>
@@ -59346,7 +59350,7 @@
       </c>
       <c r="M194" s="15"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="14">
         <v>203</v>
       </c>
@@ -59385,7 +59389,7 @@
       </c>
       <c r="M195" s="15"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="14">
         <v>204</v>
       </c>
@@ -59424,7 +59428,7 @@
       </c>
       <c r="M196" s="15"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="14">
         <v>205</v>
       </c>
@@ -59463,7 +59467,7 @@
       </c>
       <c r="M197" s="15"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="14">
         <v>206</v>
       </c>
@@ -59502,7 +59506,7 @@
       </c>
       <c r="M198" s="15"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="14">
         <v>207</v>
       </c>
@@ -59541,7 +59545,7 @@
       </c>
       <c r="M199" s="15"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="14">
         <v>208</v>
       </c>
@@ -59710,7 +59714,7 @@
       <c r="L204" s="15"/>
       <c r="M204" s="15"/>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" hidden="1">
       <c r="A205" s="14">
         <v>213</v>
       </c>
@@ -59747,7 +59751,7 @@
       </c>
       <c r="M205" s="15"/>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" hidden="1">
       <c r="A206" s="14">
         <v>214</v>
       </c>
@@ -59784,7 +59788,7 @@
       </c>
       <c r="M206" s="15"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="14">
         <v>215</v>
       </c>
@@ -59819,7 +59823,7 @@
       </c>
       <c r="M207" s="15"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="14">
         <v>216</v>
       </c>
@@ -59854,7 +59858,7 @@
       </c>
       <c r="M208" s="15"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="14">
         <v>217</v>
       </c>
@@ -59889,7 +59893,7 @@
       </c>
       <c r="M209" s="15"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="14">
         <v>218</v>
       </c>
@@ -59924,7 +59928,7 @@
       </c>
       <c r="M210" s="15"/>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" hidden="1">
       <c r="A211" s="14">
         <v>219</v>
       </c>
@@ -59953,7 +59957,7 @@
       </c>
       <c r="M211" s="15"/>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" hidden="1">
       <c r="A212" s="14">
         <v>220</v>
       </c>
@@ -59982,7 +59986,7 @@
       </c>
       <c r="M212" s="15"/>
     </row>
-    <row r="213" spans="1:13" ht="15.75">
+    <row r="213" spans="1:13" ht="15.75" hidden="1">
       <c r="A213" s="14">
         <v>221</v>
       </c>
@@ -60017,7 +60021,7 @@
       </c>
       <c r="M213" s="15"/>
     </row>
-    <row r="214" spans="1:13" ht="15.75">
+    <row r="214" spans="1:13" ht="15.75" hidden="1">
       <c r="A214" s="14">
         <v>222</v>
       </c>
@@ -60052,7 +60056,7 @@
       </c>
       <c r="M214" s="15"/>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" hidden="1">
       <c r="A215" s="14">
         <v>223</v>
       </c>
@@ -60087,7 +60091,7 @@
       </c>
       <c r="M215" s="15"/>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" hidden="1">
       <c r="A216" s="14">
         <v>224</v>
       </c>
@@ -60122,7 +60126,7 @@
       </c>
       <c r="M216" s="15"/>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" hidden="1">
       <c r="A217" s="14">
         <v>227</v>
       </c>
@@ -60159,7 +60163,7 @@
       </c>
       <c r="M217" s="15"/>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" hidden="1">
       <c r="A218" s="14">
         <v>228</v>
       </c>
@@ -60196,7 +60200,7 @@
       </c>
       <c r="M218" s="15"/>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" hidden="1">
       <c r="A219" s="14">
         <v>229</v>
       </c>
@@ -60233,7 +60237,7 @@
       </c>
       <c r="M219" s="15"/>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" hidden="1">
       <c r="A220" s="14">
         <v>230</v>
       </c>
@@ -60270,7 +60274,7 @@
       </c>
       <c r="M220" s="15"/>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" hidden="1">
       <c r="A221" s="14">
         <v>231</v>
       </c>
@@ -60307,7 +60311,7 @@
       </c>
       <c r="M221" s="15"/>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" hidden="1">
       <c r="A222" s="14">
         <v>232</v>
       </c>
@@ -60342,7 +60346,7 @@
       </c>
       <c r="M222" s="15"/>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" hidden="1">
       <c r="A223" s="14">
         <v>233</v>
       </c>
@@ -60377,7 +60381,7 @@
       </c>
       <c r="M223" s="15"/>
     </row>
-    <row r="224" spans="1:13" ht="14.25">
+    <row r="224" spans="1:13" ht="14.25" hidden="1">
       <c r="A224" s="14">
         <v>236</v>
       </c>
@@ -60412,7 +60416,7 @@
       </c>
       <c r="M224" s="15"/>
     </row>
-    <row r="225" spans="1:13" ht="14.25">
+    <row r="225" spans="1:13" ht="14.25" hidden="1">
       <c r="A225" s="14">
         <v>237</v>
       </c>
@@ -60447,7 +60451,7 @@
       </c>
       <c r="M225" s="15"/>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" hidden="1">
       <c r="A226" s="14">
         <v>241</v>
       </c>
@@ -60484,7 +60488,7 @@
       </c>
       <c r="M226" s="15"/>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" hidden="1">
       <c r="A227" s="14">
         <v>242</v>
       </c>
@@ -60521,7 +60525,7 @@
       </c>
       <c r="M227" s="15"/>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" hidden="1">
       <c r="A228" s="14">
         <v>243</v>
       </c>
@@ -60558,7 +60562,7 @@
       </c>
       <c r="M228" s="15"/>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" hidden="1">
       <c r="A229" s="14">
         <v>244</v>
       </c>
@@ -60595,7 +60599,7 @@
       </c>
       <c r="M229" s="15"/>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" hidden="1">
       <c r="A230" s="14">
         <v>245</v>
       </c>
@@ -60632,7 +60636,7 @@
       </c>
       <c r="M230" s="15"/>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" hidden="1">
       <c r="A231" s="14">
         <v>246</v>
       </c>
@@ -60669,7 +60673,7 @@
       </c>
       <c r="M231" s="15"/>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" hidden="1">
       <c r="A232" s="14">
         <v>247</v>
       </c>
@@ -60706,7 +60710,7 @@
       </c>
       <c r="M232" s="15"/>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" hidden="1">
       <c r="A233" s="14">
         <v>248</v>
       </c>
@@ -60743,7 +60747,7 @@
       </c>
       <c r="M233" s="15"/>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" hidden="1">
       <c r="A234" s="14">
         <v>249</v>
       </c>
@@ -60908,7 +60912,7 @@
         <v>306</v>
       </c>
       <c r="H238" s="13">
-        <v>0.78125</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="I238" s="26"/>
       <c r="J238" s="15" t="s">

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3266" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FECAF55-847F-4CE8-8716-9B1C23576122}"/>
+  <xr:revisionPtr revIDLastSave="3267" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2CBF48-A24D-4662-9730-6E4DA0895EC9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47822,71 +47822,528 @@
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
   <mergeCells count="611">
-    <mergeCell ref="B805:E805"/>
-    <mergeCell ref="B806:E806"/>
-    <mergeCell ref="B807:E807"/>
-    <mergeCell ref="B808:E808"/>
-    <mergeCell ref="B809:E809"/>
-    <mergeCell ref="B810:E810"/>
-    <mergeCell ref="B795:E795"/>
-    <mergeCell ref="B796:E796"/>
-    <mergeCell ref="B797:E797"/>
-    <mergeCell ref="B798:E798"/>
-    <mergeCell ref="B799:E799"/>
-    <mergeCell ref="B800:E800"/>
-    <mergeCell ref="B801:E801"/>
-    <mergeCell ref="B802:E802"/>
-    <mergeCell ref="B803:E803"/>
-    <mergeCell ref="B749:E749"/>
-    <mergeCell ref="B750:E750"/>
-    <mergeCell ref="B751:E751"/>
-    <mergeCell ref="B752:E752"/>
-    <mergeCell ref="B753:E753"/>
-    <mergeCell ref="B754:E754"/>
-    <mergeCell ref="B755:E755"/>
-    <mergeCell ref="B756:E756"/>
-    <mergeCell ref="B757:E757"/>
-    <mergeCell ref="B734:E734"/>
-    <mergeCell ref="B735:E735"/>
-    <mergeCell ref="B727:E727"/>
-    <mergeCell ref="B728:E728"/>
-    <mergeCell ref="B730:E730"/>
-    <mergeCell ref="B731:E731"/>
-    <mergeCell ref="B732:E732"/>
-    <mergeCell ref="B733:E733"/>
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B726:E726"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B837:E837"/>
+    <mergeCell ref="B839:E839"/>
+    <mergeCell ref="B840:E840"/>
+    <mergeCell ref="B842:E842"/>
+    <mergeCell ref="B843:E843"/>
+    <mergeCell ref="B844:E844"/>
+    <mergeCell ref="B845:E845"/>
+    <mergeCell ref="B846:E846"/>
+    <mergeCell ref="B847:E847"/>
+    <mergeCell ref="B828:E828"/>
+    <mergeCell ref="B829:E829"/>
+    <mergeCell ref="B830:E830"/>
+    <mergeCell ref="B831:E831"/>
+    <mergeCell ref="B832:E832"/>
+    <mergeCell ref="B833:E833"/>
+    <mergeCell ref="B834:E834"/>
+    <mergeCell ref="B835:E835"/>
+    <mergeCell ref="B836:E836"/>
+    <mergeCell ref="B819:E819"/>
+    <mergeCell ref="B820:E820"/>
+    <mergeCell ref="B821:E821"/>
+    <mergeCell ref="B822:E822"/>
+    <mergeCell ref="B823:E823"/>
+    <mergeCell ref="B824:E824"/>
+    <mergeCell ref="B825:E825"/>
+    <mergeCell ref="B826:E826"/>
+    <mergeCell ref="B827:E827"/>
+    <mergeCell ref="B779:E779"/>
+    <mergeCell ref="B811:E811"/>
+    <mergeCell ref="B812:E812"/>
+    <mergeCell ref="B813:E813"/>
+    <mergeCell ref="B814:E814"/>
+    <mergeCell ref="B815:E815"/>
+    <mergeCell ref="B816:E816"/>
+    <mergeCell ref="B817:E817"/>
+    <mergeCell ref="B818:E818"/>
+    <mergeCell ref="B780:E780"/>
+    <mergeCell ref="B781:E781"/>
+    <mergeCell ref="B782:E782"/>
+    <mergeCell ref="B783:E783"/>
+    <mergeCell ref="B784:E784"/>
+    <mergeCell ref="B786:E786"/>
+    <mergeCell ref="B787:E787"/>
+    <mergeCell ref="B788:E788"/>
+    <mergeCell ref="B794:E794"/>
+    <mergeCell ref="B790:E790"/>
+    <mergeCell ref="B791:E791"/>
+    <mergeCell ref="B792:E792"/>
+    <mergeCell ref="B793:E793"/>
+    <mergeCell ref="B789:E789"/>
+    <mergeCell ref="B804:E804"/>
+    <mergeCell ref="B769:E769"/>
+    <mergeCell ref="B770:E770"/>
+    <mergeCell ref="B771:E771"/>
+    <mergeCell ref="B773:E773"/>
+    <mergeCell ref="B774:E774"/>
+    <mergeCell ref="B775:E775"/>
+    <mergeCell ref="B776:E776"/>
+    <mergeCell ref="B777:E777"/>
+    <mergeCell ref="B778:E778"/>
+    <mergeCell ref="B759:E759"/>
+    <mergeCell ref="B760:E760"/>
+    <mergeCell ref="B761:E761"/>
+    <mergeCell ref="B762:E762"/>
+    <mergeCell ref="B763:E763"/>
+    <mergeCell ref="B765:E765"/>
+    <mergeCell ref="B766:E766"/>
+    <mergeCell ref="B767:E767"/>
+    <mergeCell ref="B768:E768"/>
+    <mergeCell ref="B747:E747"/>
+    <mergeCell ref="B748:E748"/>
+    <mergeCell ref="B736:E736"/>
+    <mergeCell ref="B737:E737"/>
+    <mergeCell ref="B740:E740"/>
+    <mergeCell ref="B741:E741"/>
+    <mergeCell ref="B742:E742"/>
+    <mergeCell ref="B743:E743"/>
+    <mergeCell ref="B744:E744"/>
+    <mergeCell ref="B745:E745"/>
+    <mergeCell ref="B746:E746"/>
+    <mergeCell ref="B651:E651"/>
+    <mergeCell ref="B695:E695"/>
+    <mergeCell ref="B696:E696"/>
+    <mergeCell ref="B697:E697"/>
+    <mergeCell ref="B698:E698"/>
+    <mergeCell ref="B699:E699"/>
+    <mergeCell ref="B701:E701"/>
+    <mergeCell ref="B657:E657"/>
+    <mergeCell ref="B658:E658"/>
+    <mergeCell ref="B659:E659"/>
+    <mergeCell ref="B660:E660"/>
+    <mergeCell ref="B667:E667"/>
+    <mergeCell ref="B668:E668"/>
+    <mergeCell ref="B669:E669"/>
+    <mergeCell ref="B670:E670"/>
+    <mergeCell ref="B671:E671"/>
+    <mergeCell ref="B672:E672"/>
+    <mergeCell ref="B673:E673"/>
+    <mergeCell ref="B674:E674"/>
+    <mergeCell ref="B675:E675"/>
+    <mergeCell ref="B687:E687"/>
+    <mergeCell ref="B688:E688"/>
+    <mergeCell ref="B691:E691"/>
+    <mergeCell ref="B692:E692"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
     <mergeCell ref="B594:E594"/>
     <mergeCell ref="B627:E627"/>
     <mergeCell ref="B647:E647"/>
@@ -47911,528 +48368,71 @@
     <mergeCell ref="B624:E624"/>
     <mergeCell ref="B625:E625"/>
     <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B651:E651"/>
-    <mergeCell ref="B695:E695"/>
-    <mergeCell ref="B696:E696"/>
-    <mergeCell ref="B697:E697"/>
-    <mergeCell ref="B698:E698"/>
-    <mergeCell ref="B699:E699"/>
-    <mergeCell ref="B701:E701"/>
-    <mergeCell ref="B657:E657"/>
-    <mergeCell ref="B658:E658"/>
-    <mergeCell ref="B659:E659"/>
-    <mergeCell ref="B660:E660"/>
-    <mergeCell ref="B667:E667"/>
-    <mergeCell ref="B668:E668"/>
-    <mergeCell ref="B669:E669"/>
-    <mergeCell ref="B670:E670"/>
-    <mergeCell ref="B671:E671"/>
-    <mergeCell ref="B672:E672"/>
-    <mergeCell ref="B673:E673"/>
-    <mergeCell ref="B674:E674"/>
-    <mergeCell ref="B675:E675"/>
-    <mergeCell ref="B687:E687"/>
-    <mergeCell ref="B688:E688"/>
-    <mergeCell ref="B691:E691"/>
-    <mergeCell ref="B692:E692"/>
-    <mergeCell ref="B747:E747"/>
-    <mergeCell ref="B748:E748"/>
-    <mergeCell ref="B736:E736"/>
-    <mergeCell ref="B737:E737"/>
-    <mergeCell ref="B740:E740"/>
-    <mergeCell ref="B741:E741"/>
-    <mergeCell ref="B742:E742"/>
-    <mergeCell ref="B743:E743"/>
-    <mergeCell ref="B744:E744"/>
-    <mergeCell ref="B745:E745"/>
-    <mergeCell ref="B746:E746"/>
-    <mergeCell ref="B759:E759"/>
-    <mergeCell ref="B760:E760"/>
-    <mergeCell ref="B761:E761"/>
-    <mergeCell ref="B762:E762"/>
-    <mergeCell ref="B763:E763"/>
-    <mergeCell ref="B765:E765"/>
-    <mergeCell ref="B766:E766"/>
-    <mergeCell ref="B767:E767"/>
-    <mergeCell ref="B768:E768"/>
-    <mergeCell ref="B769:E769"/>
-    <mergeCell ref="B770:E770"/>
-    <mergeCell ref="B771:E771"/>
-    <mergeCell ref="B773:E773"/>
-    <mergeCell ref="B774:E774"/>
-    <mergeCell ref="B775:E775"/>
-    <mergeCell ref="B776:E776"/>
-    <mergeCell ref="B777:E777"/>
-    <mergeCell ref="B778:E778"/>
-    <mergeCell ref="B779:E779"/>
-    <mergeCell ref="B811:E811"/>
-    <mergeCell ref="B812:E812"/>
-    <mergeCell ref="B813:E813"/>
-    <mergeCell ref="B814:E814"/>
-    <mergeCell ref="B815:E815"/>
-    <mergeCell ref="B816:E816"/>
-    <mergeCell ref="B817:E817"/>
-    <mergeCell ref="B818:E818"/>
-    <mergeCell ref="B780:E780"/>
-    <mergeCell ref="B781:E781"/>
-    <mergeCell ref="B782:E782"/>
-    <mergeCell ref="B783:E783"/>
-    <mergeCell ref="B784:E784"/>
-    <mergeCell ref="B786:E786"/>
-    <mergeCell ref="B787:E787"/>
-    <mergeCell ref="B788:E788"/>
-    <mergeCell ref="B794:E794"/>
-    <mergeCell ref="B790:E790"/>
-    <mergeCell ref="B791:E791"/>
-    <mergeCell ref="B792:E792"/>
-    <mergeCell ref="B793:E793"/>
-    <mergeCell ref="B789:E789"/>
-    <mergeCell ref="B804:E804"/>
-    <mergeCell ref="B819:E819"/>
-    <mergeCell ref="B820:E820"/>
-    <mergeCell ref="B821:E821"/>
-    <mergeCell ref="B822:E822"/>
-    <mergeCell ref="B823:E823"/>
-    <mergeCell ref="B824:E824"/>
-    <mergeCell ref="B825:E825"/>
-    <mergeCell ref="B826:E826"/>
-    <mergeCell ref="B827:E827"/>
-    <mergeCell ref="B828:E828"/>
-    <mergeCell ref="B829:E829"/>
-    <mergeCell ref="B830:E830"/>
-    <mergeCell ref="B831:E831"/>
-    <mergeCell ref="B832:E832"/>
-    <mergeCell ref="B833:E833"/>
-    <mergeCell ref="B834:E834"/>
-    <mergeCell ref="B835:E835"/>
-    <mergeCell ref="B836:E836"/>
-    <mergeCell ref="B837:E837"/>
-    <mergeCell ref="B839:E839"/>
-    <mergeCell ref="B840:E840"/>
-    <mergeCell ref="B842:E842"/>
-    <mergeCell ref="B843:E843"/>
-    <mergeCell ref="B844:E844"/>
-    <mergeCell ref="B845:E845"/>
-    <mergeCell ref="B846:E846"/>
-    <mergeCell ref="B847:E847"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
+    <mergeCell ref="B734:E734"/>
+    <mergeCell ref="B735:E735"/>
+    <mergeCell ref="B727:E727"/>
+    <mergeCell ref="B728:E728"/>
+    <mergeCell ref="B730:E730"/>
+    <mergeCell ref="B731:E731"/>
+    <mergeCell ref="B732:E732"/>
+    <mergeCell ref="B733:E733"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B749:E749"/>
+    <mergeCell ref="B750:E750"/>
+    <mergeCell ref="B751:E751"/>
+    <mergeCell ref="B752:E752"/>
+    <mergeCell ref="B753:E753"/>
+    <mergeCell ref="B754:E754"/>
+    <mergeCell ref="B755:E755"/>
+    <mergeCell ref="B756:E756"/>
+    <mergeCell ref="B757:E757"/>
+    <mergeCell ref="B805:E805"/>
+    <mergeCell ref="B806:E806"/>
+    <mergeCell ref="B807:E807"/>
+    <mergeCell ref="B808:E808"/>
+    <mergeCell ref="B809:E809"/>
+    <mergeCell ref="B810:E810"/>
+    <mergeCell ref="B795:E795"/>
+    <mergeCell ref="B796:E796"/>
+    <mergeCell ref="B797:E797"/>
+    <mergeCell ref="B798:E798"/>
+    <mergeCell ref="B799:E799"/>
+    <mergeCell ref="B800:E800"/>
+    <mergeCell ref="B801:E801"/>
+    <mergeCell ref="B802:E802"/>
+    <mergeCell ref="B803:E803"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -60859,7 +60859,7 @@
         <v>252</v>
       </c>
       <c r="B237" s="42">
-        <v>46281</v>
+        <v>46311</v>
       </c>
       <c r="C237" s="12" t="s">
         <v>305</v>

--- a/data/20251229_LSP管理.xlsx
+++ b/data/20251229_LSP管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiraizumitatsuya/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3267" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2CBF48-A24D-4662-9730-6E4DA0895EC9}"/>
+  <xr:revisionPtr revIDLastSave="3270" documentId="13_ncr:1_{118E22AB-A700-4546-AC50-A03A5FE8C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF755B94-D14E-441F-A01D-E44DA21C3398}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マイル管理" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3260" uniqueCount="415">
   <si>
     <t>日付</t>
   </si>
@@ -886,13 +886,16 @@
     <t>合計</t>
   </si>
   <si>
+    <t>ライフスタイルサービス</t>
+  </si>
+  <si>
+    <t>JALカード利用</t>
+  </si>
+  <si>
     <t>航空</t>
   </si>
   <si>
     <t>JAL国内線利用</t>
-  </si>
-  <si>
-    <t>ライフスタイルサービス</t>
   </si>
   <si>
     <t>JALマイレージパーク利用</t>
@@ -902,9 +905,6 @@
   </si>
   <si>
     <t>JAL Wellness &amp; Travel利用</t>
-  </si>
-  <si>
-    <t>JALカード利用</t>
   </si>
   <si>
     <t>2周年LSP会員（JALカード）</t>
@@ -8714,6 +8714,9 @@
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="191"/>
+                <c:pt idx="21">
+                  <c:v>46276</c:v>
+                </c:pt>
                 <c:pt idx="22">
                   <c:v>46268</c:v>
                 </c:pt>
@@ -9225,70 +9228,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="191"/>
                 <c:pt idx="0">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1737</c:v>
+                  <c:v>1747</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>1737</c:v>
@@ -10255,7 +10258,7 @@
                   <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>165</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>13</c:v>
@@ -15150,7 +15153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}">
-  <dimension ref="A1:O847"/>
+  <dimension ref="A1:O860"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -47819,36 +47822,1063 @@
         <v>140</v>
       </c>
     </row>
+    <row r="848" spans="1:13">
+      <c r="A848" s="27">
+        <v>46271</v>
+      </c>
+      <c r="B848" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C848" s="76"/>
+      <c r="D848" s="76"/>
+      <c r="E848" s="77"/>
+      <c r="F848" s="74">
+        <v>0</v>
+      </c>
+      <c r="G848" s="74">
+        <v>33</v>
+      </c>
+      <c r="H848" s="74">
+        <v>33</v>
+      </c>
+      <c r="I848" s="4">
+        <v>95829</v>
+      </c>
+      <c r="J848" s="74">
+        <v>0</v>
+      </c>
+      <c r="K848" s="74">
+        <v>0</v>
+      </c>
+      <c r="L848" s="74">
+        <f t="shared" ref="L848:L860" si="122">J848+L847</f>
+        <v>92630</v>
+      </c>
+      <c r="M848" s="74">
+        <f t="shared" ref="M848:M860" si="123">K848+M847</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="849" spans="1:13">
+      <c r="A849" s="27">
+        <v>46272</v>
+      </c>
+      <c r="B849" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C849" s="76"/>
+      <c r="D849" s="76"/>
+      <c r="E849" s="77"/>
+      <c r="F849" s="74">
+        <v>0</v>
+      </c>
+      <c r="G849" s="74">
+        <v>16</v>
+      </c>
+      <c r="H849" s="74">
+        <v>16</v>
+      </c>
+      <c r="I849" s="4">
+        <v>95845</v>
+      </c>
+      <c r="J849" s="74">
+        <v>0</v>
+      </c>
+      <c r="K849" s="74">
+        <v>0</v>
+      </c>
+      <c r="L849" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M849" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="850" spans="1:13">
+      <c r="A850" s="27">
+        <v>46273</v>
+      </c>
+      <c r="B850" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C850" s="76"/>
+      <c r="D850" s="76"/>
+      <c r="E850" s="77"/>
+      <c r="F850" s="74">
+        <v>0</v>
+      </c>
+      <c r="G850" s="74">
+        <v>6</v>
+      </c>
+      <c r="H850" s="74">
+        <v>6</v>
+      </c>
+      <c r="I850" s="4">
+        <v>95851</v>
+      </c>
+      <c r="J850" s="74">
+        <v>0</v>
+      </c>
+      <c r="K850" s="74">
+        <v>0</v>
+      </c>
+      <c r="L850" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M850" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="851" spans="1:13">
+      <c r="A851" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B851" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C851" s="76"/>
+      <c r="D851" s="76"/>
+      <c r="E851" s="77"/>
+      <c r="F851" s="74">
+        <v>0</v>
+      </c>
+      <c r="G851" s="74">
+        <v>1</v>
+      </c>
+      <c r="H851" s="74">
+        <v>1</v>
+      </c>
+      <c r="I851" s="4">
+        <v>95852</v>
+      </c>
+      <c r="J851" s="74">
+        <v>0</v>
+      </c>
+      <c r="K851" s="74">
+        <v>0</v>
+      </c>
+      <c r="L851" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M851" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="852" spans="1:13">
+      <c r="A852" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B852" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C852" s="76"/>
+      <c r="D852" s="76"/>
+      <c r="E852" s="77"/>
+      <c r="F852" s="74">
+        <v>0</v>
+      </c>
+      <c r="G852" s="74">
+        <v>10</v>
+      </c>
+      <c r="H852" s="74">
+        <v>10</v>
+      </c>
+      <c r="I852" s="4">
+        <v>95862</v>
+      </c>
+      <c r="J852" s="74">
+        <v>0</v>
+      </c>
+      <c r="K852" s="74">
+        <v>0</v>
+      </c>
+      <c r="L852" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M852" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="853" spans="1:13">
+      <c r="A853" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B853" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C853" s="76"/>
+      <c r="D853" s="76"/>
+      <c r="E853" s="77"/>
+      <c r="F853" s="74">
+        <v>0</v>
+      </c>
+      <c r="G853" s="74">
+        <v>1</v>
+      </c>
+      <c r="H853" s="74">
+        <v>1</v>
+      </c>
+      <c r="I853" s="4">
+        <v>95863</v>
+      </c>
+      <c r="J853" s="74">
+        <v>0</v>
+      </c>
+      <c r="K853" s="74">
+        <v>0</v>
+      </c>
+      <c r="L853" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M853" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="854" spans="1:13">
+      <c r="A854" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B854" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C854" s="76"/>
+      <c r="D854" s="76"/>
+      <c r="E854" s="77"/>
+      <c r="F854" s="74">
+        <v>0</v>
+      </c>
+      <c r="G854" s="74">
+        <v>1</v>
+      </c>
+      <c r="H854" s="74">
+        <v>1</v>
+      </c>
+      <c r="I854" s="4">
+        <v>95864</v>
+      </c>
+      <c r="J854" s="74">
+        <v>0</v>
+      </c>
+      <c r="K854" s="74">
+        <v>0</v>
+      </c>
+      <c r="L854" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M854" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="855" spans="1:13">
+      <c r="A855" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B855" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C855" s="76"/>
+      <c r="D855" s="76"/>
+      <c r="E855" s="77"/>
+      <c r="F855" s="74">
+        <v>0</v>
+      </c>
+      <c r="G855" s="74">
+        <v>1</v>
+      </c>
+      <c r="H855" s="74">
+        <v>1</v>
+      </c>
+      <c r="I855" s="4">
+        <v>95865</v>
+      </c>
+      <c r="J855" s="74">
+        <v>0</v>
+      </c>
+      <c r="K855" s="74">
+        <v>0</v>
+      </c>
+      <c r="L855" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M855" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="856" spans="1:13">
+      <c r="A856" s="27">
+        <v>46274</v>
+      </c>
+      <c r="B856" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C856" s="76"/>
+      <c r="D856" s="76"/>
+      <c r="E856" s="77"/>
+      <c r="F856" s="74">
+        <v>0</v>
+      </c>
+      <c r="G856" s="74">
+        <v>1</v>
+      </c>
+      <c r="H856" s="74">
+        <v>1</v>
+      </c>
+      <c r="I856" s="4">
+        <v>95866</v>
+      </c>
+      <c r="J856" s="74">
+        <v>0</v>
+      </c>
+      <c r="K856" s="74">
+        <v>0</v>
+      </c>
+      <c r="L856" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M856" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="857" spans="1:13">
+      <c r="A857" s="27">
+        <v>46275</v>
+      </c>
+      <c r="B857" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="C857" s="76"/>
+      <c r="D857" s="76"/>
+      <c r="E857" s="77"/>
+      <c r="F857" s="4">
+        <v>3327</v>
+      </c>
+      <c r="G857" s="74">
+        <v>0</v>
+      </c>
+      <c r="H857" s="4">
+        <v>3327</v>
+      </c>
+      <c r="I857" s="4">
+        <v>99193</v>
+      </c>
+      <c r="J857" s="74">
+        <v>0</v>
+      </c>
+      <c r="K857" s="74">
+        <v>0</v>
+      </c>
+      <c r="L857" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M857" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="858" spans="1:13">
+      <c r="A858" s="27">
+        <v>46275</v>
+      </c>
+      <c r="B858" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C858" s="76"/>
+      <c r="D858" s="76"/>
+      <c r="E858" s="77"/>
+      <c r="F858" s="74">
+        <v>0</v>
+      </c>
+      <c r="G858" s="74">
+        <v>16</v>
+      </c>
+      <c r="H858" s="74">
+        <v>16</v>
+      </c>
+      <c r="I858" s="4">
+        <v>99209</v>
+      </c>
+      <c r="J858" s="74">
+        <v>0</v>
+      </c>
+      <c r="K858" s="74">
+        <v>0</v>
+      </c>
+      <c r="L858" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M858" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="859" spans="1:13">
+      <c r="A859" s="27">
+        <v>46276</v>
+      </c>
+      <c r="B859" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="C859" s="76"/>
+      <c r="D859" s="76"/>
+      <c r="E859" s="77"/>
+      <c r="F859" s="74">
+        <v>0</v>
+      </c>
+      <c r="G859" s="74">
+        <v>8</v>
+      </c>
+      <c r="H859" s="74">
+        <v>8</v>
+      </c>
+      <c r="I859" s="4">
+        <v>99217</v>
+      </c>
+      <c r="J859" s="74">
+        <v>0</v>
+      </c>
+      <c r="K859" s="74">
+        <v>0</v>
+      </c>
+      <c r="L859" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M859" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="860" spans="1:13">
+      <c r="A860" s="29">
+        <v>46277</v>
+      </c>
+      <c r="B860" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C860" s="78"/>
+      <c r="D860" s="78"/>
+      <c r="E860" s="79"/>
+      <c r="F860" s="75">
+        <v>0</v>
+      </c>
+      <c r="G860" s="75">
+        <v>17</v>
+      </c>
+      <c r="H860" s="75">
+        <v>17</v>
+      </c>
+      <c r="I860" s="30">
+        <v>99234</v>
+      </c>
+      <c r="J860" s="75">
+        <v>0</v>
+      </c>
+      <c r="K860" s="75">
+        <v>0</v>
+      </c>
+      <c r="L860" s="74">
+        <f t="shared" si="122"/>
+        <v>92630</v>
+      </c>
+      <c r="M860" s="74">
+        <f t="shared" si="123"/>
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O523" xr:uid="{2A57836D-5153-486D-8B76-48FAFDDE1EA1}"/>
-  <mergeCells count="611">
-    <mergeCell ref="B837:E837"/>
-    <mergeCell ref="B839:E839"/>
-    <mergeCell ref="B840:E840"/>
-    <mergeCell ref="B842:E842"/>
-    <mergeCell ref="B843:E843"/>
-    <mergeCell ref="B844:E844"/>
-    <mergeCell ref="B845:E845"/>
-    <mergeCell ref="B846:E846"/>
-    <mergeCell ref="B847:E847"/>
-    <mergeCell ref="B828:E828"/>
-    <mergeCell ref="B829:E829"/>
-    <mergeCell ref="B830:E830"/>
-    <mergeCell ref="B831:E831"/>
-    <mergeCell ref="B832:E832"/>
-    <mergeCell ref="B833:E833"/>
-    <mergeCell ref="B834:E834"/>
-    <mergeCell ref="B835:E835"/>
-    <mergeCell ref="B836:E836"/>
-    <mergeCell ref="B819:E819"/>
-    <mergeCell ref="B820:E820"/>
-    <mergeCell ref="B821:E821"/>
-    <mergeCell ref="B822:E822"/>
-    <mergeCell ref="B823:E823"/>
-    <mergeCell ref="B824:E824"/>
-    <mergeCell ref="B825:E825"/>
-    <mergeCell ref="B826:E826"/>
-    <mergeCell ref="B827:E827"/>
+  <mergeCells count="624">
+    <mergeCell ref="B857:E857"/>
+    <mergeCell ref="B858:E858"/>
+    <mergeCell ref="B859:E859"/>
+    <mergeCell ref="B860:E860"/>
+    <mergeCell ref="B848:E848"/>
+    <mergeCell ref="B849:E849"/>
+    <mergeCell ref="B850:E850"/>
+    <mergeCell ref="B851:E851"/>
+    <mergeCell ref="B852:E852"/>
+    <mergeCell ref="B853:E853"/>
+    <mergeCell ref="B854:E854"/>
+    <mergeCell ref="B855:E855"/>
+    <mergeCell ref="B856:E856"/>
+    <mergeCell ref="B805:E805"/>
+    <mergeCell ref="B806:E806"/>
+    <mergeCell ref="B807:E807"/>
+    <mergeCell ref="B808:E808"/>
+    <mergeCell ref="B809:E809"/>
+    <mergeCell ref="B810:E810"/>
+    <mergeCell ref="B795:E795"/>
+    <mergeCell ref="B796:E796"/>
+    <mergeCell ref="B797:E797"/>
+    <mergeCell ref="B798:E798"/>
+    <mergeCell ref="B799:E799"/>
+    <mergeCell ref="B800:E800"/>
+    <mergeCell ref="B801:E801"/>
+    <mergeCell ref="B802:E802"/>
+    <mergeCell ref="B803:E803"/>
+    <mergeCell ref="B749:E749"/>
+    <mergeCell ref="B750:E750"/>
+    <mergeCell ref="B751:E751"/>
+    <mergeCell ref="B752:E752"/>
+    <mergeCell ref="B753:E753"/>
+    <mergeCell ref="B754:E754"/>
+    <mergeCell ref="B755:E755"/>
+    <mergeCell ref="B756:E756"/>
+    <mergeCell ref="B757:E757"/>
+    <mergeCell ref="B734:E734"/>
+    <mergeCell ref="B735:E735"/>
+    <mergeCell ref="B727:E727"/>
+    <mergeCell ref="B728:E728"/>
+    <mergeCell ref="B730:E730"/>
+    <mergeCell ref="B731:E731"/>
+    <mergeCell ref="B732:E732"/>
+    <mergeCell ref="B733:E733"/>
+    <mergeCell ref="B722:E722"/>
+    <mergeCell ref="B723:E723"/>
+    <mergeCell ref="B724:E724"/>
+    <mergeCell ref="B725:E725"/>
+    <mergeCell ref="B726:E726"/>
+    <mergeCell ref="B713:E713"/>
+    <mergeCell ref="B714:E714"/>
+    <mergeCell ref="B715:E715"/>
+    <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B717:E717"/>
+    <mergeCell ref="B718:E718"/>
+    <mergeCell ref="B719:E719"/>
+    <mergeCell ref="B720:E720"/>
+    <mergeCell ref="B721:E721"/>
+    <mergeCell ref="B703:E703"/>
+    <mergeCell ref="B706:E706"/>
+    <mergeCell ref="B707:E707"/>
+    <mergeCell ref="B708:E708"/>
+    <mergeCell ref="B709:E709"/>
+    <mergeCell ref="B710:E710"/>
+    <mergeCell ref="B711:E711"/>
+    <mergeCell ref="B712:E712"/>
+    <mergeCell ref="B693:E693"/>
+    <mergeCell ref="B704:E704"/>
+    <mergeCell ref="B677:E677"/>
+    <mergeCell ref="B678:E678"/>
+    <mergeCell ref="B680:E680"/>
+    <mergeCell ref="B681:E681"/>
+    <mergeCell ref="B682:E682"/>
+    <mergeCell ref="B683:E683"/>
+    <mergeCell ref="B684:E684"/>
+    <mergeCell ref="B685:E685"/>
+    <mergeCell ref="B686:E686"/>
+    <mergeCell ref="B594:E594"/>
+    <mergeCell ref="B627:E627"/>
+    <mergeCell ref="B647:E647"/>
+    <mergeCell ref="B661:E661"/>
+    <mergeCell ref="B662:E662"/>
+    <mergeCell ref="B663:E663"/>
+    <mergeCell ref="B664:E664"/>
+    <mergeCell ref="B665:E665"/>
+    <mergeCell ref="B666:E666"/>
+    <mergeCell ref="B633:E633"/>
+    <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B635:E635"/>
+    <mergeCell ref="B611:E611"/>
+    <mergeCell ref="B628:E628"/>
+    <mergeCell ref="B629:E629"/>
+    <mergeCell ref="B630:E630"/>
+    <mergeCell ref="B631:E631"/>
+    <mergeCell ref="B632:E632"/>
+    <mergeCell ref="B621:E621"/>
+    <mergeCell ref="B622:E622"/>
+    <mergeCell ref="B623:E623"/>
+    <mergeCell ref="B624:E624"/>
+    <mergeCell ref="B625:E625"/>
+    <mergeCell ref="B600:E600"/>
+    <mergeCell ref="B569:E569"/>
+    <mergeCell ref="B570:E570"/>
+    <mergeCell ref="B571:E571"/>
+    <mergeCell ref="B572:E572"/>
+    <mergeCell ref="B573:E573"/>
+    <mergeCell ref="B576:E576"/>
+    <mergeCell ref="B578:E578"/>
+    <mergeCell ref="B591:E591"/>
+    <mergeCell ref="B592:E592"/>
+    <mergeCell ref="B580:E580"/>
+    <mergeCell ref="B589:E589"/>
+    <mergeCell ref="B511:E511"/>
+    <mergeCell ref="B512:E512"/>
+    <mergeCell ref="B513:E513"/>
+    <mergeCell ref="B514:E514"/>
+    <mergeCell ref="B515:E515"/>
+    <mergeCell ref="B535:E535"/>
+    <mergeCell ref="B537:E537"/>
+    <mergeCell ref="B555:E555"/>
+    <mergeCell ref="B560:E560"/>
+    <mergeCell ref="B548:E548"/>
+    <mergeCell ref="B549:E549"/>
+    <mergeCell ref="B546:E546"/>
+    <mergeCell ref="B547:E547"/>
+    <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B534:E534"/>
+    <mergeCell ref="B536:E536"/>
+    <mergeCell ref="B538:E538"/>
+    <mergeCell ref="B539:E539"/>
+    <mergeCell ref="B540:E540"/>
+    <mergeCell ref="B541:E541"/>
+    <mergeCell ref="B543:E543"/>
+    <mergeCell ref="B544:E544"/>
+    <mergeCell ref="B526:E526"/>
+    <mergeCell ref="B527:E527"/>
+    <mergeCell ref="B505:E505"/>
+    <mergeCell ref="B480:E480"/>
+    <mergeCell ref="B469:E469"/>
+    <mergeCell ref="B481:E481"/>
+    <mergeCell ref="B490:E490"/>
+    <mergeCell ref="B491:E491"/>
+    <mergeCell ref="B492:E492"/>
+    <mergeCell ref="B493:E493"/>
+    <mergeCell ref="B494:E494"/>
+    <mergeCell ref="B498:E498"/>
+    <mergeCell ref="B499:E499"/>
+    <mergeCell ref="B500:E500"/>
+    <mergeCell ref="B501:E501"/>
+    <mergeCell ref="B502:E502"/>
+    <mergeCell ref="B503:E503"/>
+    <mergeCell ref="B504:E504"/>
+    <mergeCell ref="B482:E482"/>
+    <mergeCell ref="B495:E495"/>
+    <mergeCell ref="B377:E377"/>
+    <mergeCell ref="B378:E378"/>
+    <mergeCell ref="B379:E379"/>
+    <mergeCell ref="B388:E388"/>
+    <mergeCell ref="B395:E395"/>
+    <mergeCell ref="B400:E400"/>
+    <mergeCell ref="B402:E402"/>
+    <mergeCell ref="B393:E393"/>
+    <mergeCell ref="B396:E396"/>
+    <mergeCell ref="B398:E398"/>
+    <mergeCell ref="B399:E399"/>
+    <mergeCell ref="B401:E401"/>
+    <mergeCell ref="B386:E386"/>
+    <mergeCell ref="B292:E292"/>
+    <mergeCell ref="B458:E458"/>
+    <mergeCell ref="B466:E466"/>
+    <mergeCell ref="B467:E467"/>
+    <mergeCell ref="B468:E468"/>
+    <mergeCell ref="B426:E426"/>
+    <mergeCell ref="B438:E438"/>
+    <mergeCell ref="B439:E439"/>
+    <mergeCell ref="B453:E453"/>
+    <mergeCell ref="B454:E454"/>
+    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="B457:E457"/>
+    <mergeCell ref="B442:E442"/>
+    <mergeCell ref="B450:E450"/>
+    <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B387:E387"/>
+    <mergeCell ref="B389:E389"/>
+    <mergeCell ref="B390:E390"/>
+    <mergeCell ref="B392:E392"/>
+    <mergeCell ref="B403:E403"/>
+    <mergeCell ref="B404:E404"/>
+    <mergeCell ref="B406:E406"/>
+    <mergeCell ref="B409:E409"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="B412:E412"/>
+    <mergeCell ref="B419:E419"/>
+    <mergeCell ref="B425:E425"/>
+    <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="B279:E279"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="B290:E290"/>
+    <mergeCell ref="B291:E291"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B245:E245"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B229:E229"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="B236:E236"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B226:E226"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B203:E203"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="B167:E167"/>
+    <mergeCell ref="B168:E168"/>
+    <mergeCell ref="B169:E169"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="B174:E174"/>
+    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B187:E187"/>
+    <mergeCell ref="B188:E188"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="B207:E207"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="B189:E189"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B194:E194"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B301:E301"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B369:E369"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B324:E324"/>
+    <mergeCell ref="B360:E360"/>
+    <mergeCell ref="B362:E362"/>
+    <mergeCell ref="B364:E364"/>
+    <mergeCell ref="B365:E365"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="B332:E332"/>
+    <mergeCell ref="B356:E356"/>
+    <mergeCell ref="B357:E357"/>
+    <mergeCell ref="B358:E358"/>
+    <mergeCell ref="B359:E359"/>
+    <mergeCell ref="B375:E375"/>
+    <mergeCell ref="B376:E376"/>
+    <mergeCell ref="B319:E319"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="B309:E309"/>
+    <mergeCell ref="B311:E311"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B316:E316"/>
+    <mergeCell ref="B317:E317"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B329:E329"/>
+    <mergeCell ref="B333:E333"/>
+    <mergeCell ref="B342:E342"/>
+    <mergeCell ref="B347:E347"/>
+    <mergeCell ref="B361:E361"/>
+    <mergeCell ref="B368:E368"/>
+    <mergeCell ref="B528:E528"/>
+    <mergeCell ref="B529:E529"/>
+    <mergeCell ref="B530:E530"/>
+    <mergeCell ref="B531:E531"/>
+    <mergeCell ref="B532:E532"/>
+    <mergeCell ref="B367:E367"/>
+    <mergeCell ref="B370:E370"/>
+    <mergeCell ref="B506:E506"/>
+    <mergeCell ref="B507:E507"/>
+    <mergeCell ref="B508:E508"/>
+    <mergeCell ref="B509:E509"/>
+    <mergeCell ref="B510:E510"/>
+    <mergeCell ref="B371:E371"/>
+    <mergeCell ref="B410:E410"/>
+    <mergeCell ref="B408:E408"/>
+    <mergeCell ref="B374:E374"/>
+    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B449:E449"/>
+    <mergeCell ref="B459:E459"/>
+    <mergeCell ref="B460:E460"/>
+    <mergeCell ref="B461:E461"/>
+    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B478:E478"/>
+    <mergeCell ref="B479:E479"/>
+    <mergeCell ref="B551:E551"/>
+    <mergeCell ref="B552:E552"/>
+    <mergeCell ref="B553:E553"/>
+    <mergeCell ref="B557:E557"/>
+    <mergeCell ref="B561:E561"/>
+    <mergeCell ref="B562:E562"/>
+    <mergeCell ref="B563:E563"/>
+    <mergeCell ref="B606:E606"/>
+    <mergeCell ref="B599:E599"/>
+    <mergeCell ref="B595:E595"/>
+    <mergeCell ref="B596:E596"/>
+    <mergeCell ref="B597:E597"/>
+    <mergeCell ref="B598:E598"/>
+    <mergeCell ref="B558:E558"/>
+    <mergeCell ref="B559:E559"/>
+    <mergeCell ref="B556:E556"/>
+    <mergeCell ref="B605:E605"/>
+    <mergeCell ref="B567:E567"/>
+    <mergeCell ref="B564:E564"/>
+    <mergeCell ref="B565:E565"/>
+    <mergeCell ref="B566:E566"/>
+    <mergeCell ref="B575:E575"/>
+    <mergeCell ref="B577:E577"/>
+    <mergeCell ref="B579:E579"/>
+    <mergeCell ref="B601:E601"/>
+    <mergeCell ref="B602:E602"/>
+    <mergeCell ref="B603:E603"/>
+    <mergeCell ref="B604:E604"/>
+    <mergeCell ref="B620:E620"/>
+    <mergeCell ref="B626:E626"/>
+    <mergeCell ref="B653:E653"/>
+    <mergeCell ref="B654:E654"/>
+    <mergeCell ref="B655:E655"/>
+    <mergeCell ref="B636:E636"/>
+    <mergeCell ref="B637:E637"/>
+    <mergeCell ref="B638:E638"/>
+    <mergeCell ref="B639:E639"/>
+    <mergeCell ref="B640:E640"/>
+    <mergeCell ref="B641:E641"/>
+    <mergeCell ref="B652:E652"/>
+    <mergeCell ref="B642:E642"/>
+    <mergeCell ref="B643:E643"/>
+    <mergeCell ref="B644:E644"/>
+    <mergeCell ref="B645:E645"/>
+    <mergeCell ref="B646:E646"/>
+    <mergeCell ref="B648:E648"/>
+    <mergeCell ref="B649:E649"/>
+    <mergeCell ref="B650:E650"/>
+    <mergeCell ref="B651:E651"/>
+    <mergeCell ref="B695:E695"/>
+    <mergeCell ref="B696:E696"/>
+    <mergeCell ref="B697:E697"/>
+    <mergeCell ref="B698:E698"/>
+    <mergeCell ref="B699:E699"/>
+    <mergeCell ref="B701:E701"/>
+    <mergeCell ref="B657:E657"/>
+    <mergeCell ref="B658:E658"/>
+    <mergeCell ref="B659:E659"/>
+    <mergeCell ref="B660:E660"/>
+    <mergeCell ref="B667:E667"/>
+    <mergeCell ref="B668:E668"/>
+    <mergeCell ref="B669:E669"/>
+    <mergeCell ref="B670:E670"/>
+    <mergeCell ref="B671:E671"/>
+    <mergeCell ref="B672:E672"/>
+    <mergeCell ref="B673:E673"/>
+    <mergeCell ref="B674:E674"/>
+    <mergeCell ref="B675:E675"/>
+    <mergeCell ref="B687:E687"/>
+    <mergeCell ref="B688:E688"/>
+    <mergeCell ref="B691:E691"/>
+    <mergeCell ref="B692:E692"/>
+    <mergeCell ref="B747:E747"/>
+    <mergeCell ref="B748:E748"/>
+    <mergeCell ref="B736:E736"/>
+    <mergeCell ref="B737:E737"/>
+    <mergeCell ref="B740:E740"/>
+    <mergeCell ref="B741:E741"/>
+    <mergeCell ref="B742:E742"/>
+    <mergeCell ref="B743:E743"/>
+    <mergeCell ref="B744:E744"/>
+    <mergeCell ref="B745:E745"/>
+    <mergeCell ref="B746:E746"/>
+    <mergeCell ref="B759:E759"/>
+    <mergeCell ref="B760:E760"/>
+    <mergeCell ref="B761:E761"/>
+    <mergeCell ref="B762:E762"/>
+    <mergeCell ref="B763:E763"/>
+    <mergeCell ref="B765:E765"/>
+    <mergeCell ref="B766:E766"/>
+    <mergeCell ref="B767:E767"/>
+    <mergeCell ref="B768:E768"/>
+    <mergeCell ref="B769:E769"/>
+    <mergeCell ref="B770:E770"/>
+    <mergeCell ref="B771:E771"/>
+    <mergeCell ref="B773:E773"/>
+    <mergeCell ref="B774:E774"/>
+    <mergeCell ref="B775:E775"/>
+    <mergeCell ref="B776:E776"/>
+    <mergeCell ref="B777:E777"/>
+    <mergeCell ref="B778:E778"/>
     <mergeCell ref="B779:E779"/>
     <mergeCell ref="B811:E811"/>
     <mergeCell ref="B812:E812"/>
@@ -47873,566 +48903,33 @@
     <mergeCell ref="B793:E793"/>
     <mergeCell ref="B789:E789"/>
     <mergeCell ref="B804:E804"/>
-    <mergeCell ref="B769:E769"/>
-    <mergeCell ref="B770:E770"/>
-    <mergeCell ref="B771:E771"/>
-    <mergeCell ref="B773:E773"/>
-    <mergeCell ref="B774:E774"/>
-    <mergeCell ref="B775:E775"/>
-    <mergeCell ref="B776:E776"/>
-    <mergeCell ref="B777:E777"/>
-    <mergeCell ref="B778:E778"/>
-    <mergeCell ref="B759:E759"/>
-    <mergeCell ref="B760:E760"/>
-    <mergeCell ref="B761:E761"/>
-    <mergeCell ref="B762:E762"/>
-    <mergeCell ref="B763:E763"/>
-    <mergeCell ref="B765:E765"/>
-    <mergeCell ref="B766:E766"/>
-    <mergeCell ref="B767:E767"/>
-    <mergeCell ref="B768:E768"/>
-    <mergeCell ref="B747:E747"/>
-    <mergeCell ref="B748:E748"/>
-    <mergeCell ref="B736:E736"/>
-    <mergeCell ref="B737:E737"/>
-    <mergeCell ref="B740:E740"/>
-    <mergeCell ref="B741:E741"/>
-    <mergeCell ref="B742:E742"/>
-    <mergeCell ref="B743:E743"/>
-    <mergeCell ref="B744:E744"/>
-    <mergeCell ref="B745:E745"/>
-    <mergeCell ref="B746:E746"/>
-    <mergeCell ref="B651:E651"/>
-    <mergeCell ref="B695:E695"/>
-    <mergeCell ref="B696:E696"/>
-    <mergeCell ref="B697:E697"/>
-    <mergeCell ref="B698:E698"/>
-    <mergeCell ref="B699:E699"/>
-    <mergeCell ref="B701:E701"/>
-    <mergeCell ref="B657:E657"/>
-    <mergeCell ref="B658:E658"/>
-    <mergeCell ref="B659:E659"/>
-    <mergeCell ref="B660:E660"/>
-    <mergeCell ref="B667:E667"/>
-    <mergeCell ref="B668:E668"/>
-    <mergeCell ref="B669:E669"/>
-    <mergeCell ref="B670:E670"/>
-    <mergeCell ref="B671:E671"/>
-    <mergeCell ref="B672:E672"/>
-    <mergeCell ref="B673:E673"/>
-    <mergeCell ref="B674:E674"/>
-    <mergeCell ref="B675:E675"/>
-    <mergeCell ref="B687:E687"/>
-    <mergeCell ref="B688:E688"/>
-    <mergeCell ref="B691:E691"/>
-    <mergeCell ref="B692:E692"/>
-    <mergeCell ref="B601:E601"/>
-    <mergeCell ref="B602:E602"/>
-    <mergeCell ref="B603:E603"/>
-    <mergeCell ref="B604:E604"/>
-    <mergeCell ref="B620:E620"/>
-    <mergeCell ref="B626:E626"/>
-    <mergeCell ref="B653:E653"/>
-    <mergeCell ref="B654:E654"/>
-    <mergeCell ref="B655:E655"/>
-    <mergeCell ref="B636:E636"/>
-    <mergeCell ref="B637:E637"/>
-    <mergeCell ref="B638:E638"/>
-    <mergeCell ref="B639:E639"/>
-    <mergeCell ref="B640:E640"/>
-    <mergeCell ref="B641:E641"/>
-    <mergeCell ref="B652:E652"/>
-    <mergeCell ref="B642:E642"/>
-    <mergeCell ref="B643:E643"/>
-    <mergeCell ref="B644:E644"/>
-    <mergeCell ref="B645:E645"/>
-    <mergeCell ref="B646:E646"/>
-    <mergeCell ref="B648:E648"/>
-    <mergeCell ref="B649:E649"/>
-    <mergeCell ref="B650:E650"/>
-    <mergeCell ref="B551:E551"/>
-    <mergeCell ref="B552:E552"/>
-    <mergeCell ref="B553:E553"/>
-    <mergeCell ref="B557:E557"/>
-    <mergeCell ref="B561:E561"/>
-    <mergeCell ref="B562:E562"/>
-    <mergeCell ref="B563:E563"/>
-    <mergeCell ref="B606:E606"/>
-    <mergeCell ref="B599:E599"/>
-    <mergeCell ref="B595:E595"/>
-    <mergeCell ref="B596:E596"/>
-    <mergeCell ref="B597:E597"/>
-    <mergeCell ref="B598:E598"/>
-    <mergeCell ref="B558:E558"/>
-    <mergeCell ref="B559:E559"/>
-    <mergeCell ref="B556:E556"/>
-    <mergeCell ref="B605:E605"/>
-    <mergeCell ref="B567:E567"/>
-    <mergeCell ref="B564:E564"/>
-    <mergeCell ref="B565:E565"/>
-    <mergeCell ref="B566:E566"/>
-    <mergeCell ref="B575:E575"/>
-    <mergeCell ref="B577:E577"/>
-    <mergeCell ref="B579:E579"/>
-    <mergeCell ref="B528:E528"/>
-    <mergeCell ref="B529:E529"/>
-    <mergeCell ref="B530:E530"/>
-    <mergeCell ref="B531:E531"/>
-    <mergeCell ref="B532:E532"/>
-    <mergeCell ref="B367:E367"/>
-    <mergeCell ref="B370:E370"/>
-    <mergeCell ref="B506:E506"/>
-    <mergeCell ref="B507:E507"/>
-    <mergeCell ref="B508:E508"/>
-    <mergeCell ref="B509:E509"/>
-    <mergeCell ref="B510:E510"/>
-    <mergeCell ref="B371:E371"/>
-    <mergeCell ref="B410:E410"/>
-    <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B436:E436"/>
-    <mergeCell ref="B449:E449"/>
-    <mergeCell ref="B459:E459"/>
-    <mergeCell ref="B460:E460"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="B465:E465"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="B375:E375"/>
-    <mergeCell ref="B376:E376"/>
-    <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B303:E303"/>
-    <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B311:E311"/>
-    <mergeCell ref="B312:E312"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B314:E314"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B316:E316"/>
-    <mergeCell ref="B317:E317"/>
-    <mergeCell ref="B318:E318"/>
-    <mergeCell ref="B325:E325"/>
-    <mergeCell ref="B329:E329"/>
-    <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B342:E342"/>
-    <mergeCell ref="B347:E347"/>
-    <mergeCell ref="B361:E361"/>
-    <mergeCell ref="B368:E368"/>
-    <mergeCell ref="B369:E369"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B322:E322"/>
-    <mergeCell ref="B323:E323"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B360:E360"/>
-    <mergeCell ref="B362:E362"/>
-    <mergeCell ref="B364:E364"/>
-    <mergeCell ref="B365:E365"/>
-    <mergeCell ref="B327:E327"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B356:E356"/>
-    <mergeCell ref="B357:E357"/>
-    <mergeCell ref="B358:E358"/>
-    <mergeCell ref="B359:E359"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B294:E294"/>
-    <mergeCell ref="B295:E295"/>
-    <mergeCell ref="B296:E296"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B175:E175"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B187:E187"/>
-    <mergeCell ref="B188:E188"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B157:E157"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B170:E170"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B204:E204"/>
-    <mergeCell ref="B205:E205"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B225:E225"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B221:E221"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B242:E242"/>
-    <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B247:E247"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B229:E229"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B233:E233"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B235:E235"/>
-    <mergeCell ref="B236:E236"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B251:E251"/>
-    <mergeCell ref="B253:E253"/>
-    <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B259:E259"/>
-    <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B419:E419"/>
-    <mergeCell ref="B425:E425"/>
-    <mergeCell ref="B452:E452"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="B278:E278"/>
-    <mergeCell ref="B279:E279"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B289:E289"/>
-    <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B291:E291"/>
-    <mergeCell ref="B292:E292"/>
-    <mergeCell ref="B458:E458"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B468:E468"/>
-    <mergeCell ref="B426:E426"/>
-    <mergeCell ref="B438:E438"/>
-    <mergeCell ref="B439:E439"/>
-    <mergeCell ref="B453:E453"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="B455:E455"/>
-    <mergeCell ref="B456:E456"/>
-    <mergeCell ref="B457:E457"/>
-    <mergeCell ref="B442:E442"/>
-    <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B451:E451"/>
-    <mergeCell ref="B387:E387"/>
-    <mergeCell ref="B389:E389"/>
-    <mergeCell ref="B390:E390"/>
-    <mergeCell ref="B392:E392"/>
-    <mergeCell ref="B403:E403"/>
-    <mergeCell ref="B404:E404"/>
-    <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B409:E409"/>
-    <mergeCell ref="B377:E377"/>
-    <mergeCell ref="B378:E378"/>
-    <mergeCell ref="B379:E379"/>
-    <mergeCell ref="B388:E388"/>
-    <mergeCell ref="B395:E395"/>
-    <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B402:E402"/>
-    <mergeCell ref="B393:E393"/>
-    <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B398:E398"/>
-    <mergeCell ref="B399:E399"/>
-    <mergeCell ref="B401:E401"/>
-    <mergeCell ref="B386:E386"/>
-    <mergeCell ref="B505:E505"/>
-    <mergeCell ref="B480:E480"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B490:E490"/>
-    <mergeCell ref="B491:E491"/>
-    <mergeCell ref="B492:E492"/>
-    <mergeCell ref="B493:E493"/>
-    <mergeCell ref="B494:E494"/>
-    <mergeCell ref="B498:E498"/>
-    <mergeCell ref="B499:E499"/>
-    <mergeCell ref="B500:E500"/>
-    <mergeCell ref="B501:E501"/>
-    <mergeCell ref="B502:E502"/>
-    <mergeCell ref="B503:E503"/>
-    <mergeCell ref="B504:E504"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B495:E495"/>
-    <mergeCell ref="B511:E511"/>
-    <mergeCell ref="B512:E512"/>
-    <mergeCell ref="B513:E513"/>
-    <mergeCell ref="B514:E514"/>
-    <mergeCell ref="B515:E515"/>
-    <mergeCell ref="B535:E535"/>
-    <mergeCell ref="B537:E537"/>
-    <mergeCell ref="B555:E555"/>
-    <mergeCell ref="B560:E560"/>
-    <mergeCell ref="B548:E548"/>
-    <mergeCell ref="B549:E549"/>
-    <mergeCell ref="B546:E546"/>
-    <mergeCell ref="B547:E547"/>
-    <mergeCell ref="B533:E533"/>
-    <mergeCell ref="B534:E534"/>
-    <mergeCell ref="B536:E536"/>
-    <mergeCell ref="B538:E538"/>
-    <mergeCell ref="B539:E539"/>
-    <mergeCell ref="B540:E540"/>
-    <mergeCell ref="B541:E541"/>
-    <mergeCell ref="B543:E543"/>
-    <mergeCell ref="B544:E544"/>
-    <mergeCell ref="B526:E526"/>
-    <mergeCell ref="B527:E527"/>
-    <mergeCell ref="B569:E569"/>
-    <mergeCell ref="B570:E570"/>
-    <mergeCell ref="B571:E571"/>
-    <mergeCell ref="B572:E572"/>
-    <mergeCell ref="B573:E573"/>
-    <mergeCell ref="B576:E576"/>
-    <mergeCell ref="B578:E578"/>
-    <mergeCell ref="B591:E591"/>
-    <mergeCell ref="B592:E592"/>
-    <mergeCell ref="B580:E580"/>
-    <mergeCell ref="B589:E589"/>
-    <mergeCell ref="B594:E594"/>
-    <mergeCell ref="B627:E627"/>
-    <mergeCell ref="B647:E647"/>
-    <mergeCell ref="B661:E661"/>
-    <mergeCell ref="B662:E662"/>
-    <mergeCell ref="B663:E663"/>
-    <mergeCell ref="B664:E664"/>
-    <mergeCell ref="B665:E665"/>
-    <mergeCell ref="B666:E666"/>
-    <mergeCell ref="B633:E633"/>
-    <mergeCell ref="B634:E634"/>
-    <mergeCell ref="B635:E635"/>
-    <mergeCell ref="B611:E611"/>
-    <mergeCell ref="B628:E628"/>
-    <mergeCell ref="B629:E629"/>
-    <mergeCell ref="B630:E630"/>
-    <mergeCell ref="B631:E631"/>
-    <mergeCell ref="B632:E632"/>
-    <mergeCell ref="B621:E621"/>
-    <mergeCell ref="B622:E622"/>
-    <mergeCell ref="B623:E623"/>
-    <mergeCell ref="B624:E624"/>
-    <mergeCell ref="B625:E625"/>
-    <mergeCell ref="B600:E600"/>
-    <mergeCell ref="B677:E677"/>
-    <mergeCell ref="B678:E678"/>
-    <mergeCell ref="B680:E680"/>
-    <mergeCell ref="B681:E681"/>
-    <mergeCell ref="B682:E682"/>
-    <mergeCell ref="B683:E683"/>
-    <mergeCell ref="B684:E684"/>
-    <mergeCell ref="B685:E685"/>
-    <mergeCell ref="B686:E686"/>
-    <mergeCell ref="B703:E703"/>
-    <mergeCell ref="B706:E706"/>
-    <mergeCell ref="B707:E707"/>
-    <mergeCell ref="B708:E708"/>
-    <mergeCell ref="B709:E709"/>
-    <mergeCell ref="B710:E710"/>
-    <mergeCell ref="B711:E711"/>
-    <mergeCell ref="B712:E712"/>
-    <mergeCell ref="B693:E693"/>
-    <mergeCell ref="B704:E704"/>
-    <mergeCell ref="B713:E713"/>
-    <mergeCell ref="B714:E714"/>
-    <mergeCell ref="B715:E715"/>
-    <mergeCell ref="B716:E716"/>
-    <mergeCell ref="B717:E717"/>
-    <mergeCell ref="B718:E718"/>
-    <mergeCell ref="B719:E719"/>
-    <mergeCell ref="B720:E720"/>
-    <mergeCell ref="B721:E721"/>
-    <mergeCell ref="B734:E734"/>
-    <mergeCell ref="B735:E735"/>
-    <mergeCell ref="B727:E727"/>
-    <mergeCell ref="B728:E728"/>
-    <mergeCell ref="B730:E730"/>
-    <mergeCell ref="B731:E731"/>
-    <mergeCell ref="B732:E732"/>
-    <mergeCell ref="B733:E733"/>
-    <mergeCell ref="B722:E722"/>
-    <mergeCell ref="B723:E723"/>
-    <mergeCell ref="B724:E724"/>
-    <mergeCell ref="B725:E725"/>
-    <mergeCell ref="B726:E726"/>
-    <mergeCell ref="B749:E749"/>
-    <mergeCell ref="B750:E750"/>
-    <mergeCell ref="B751:E751"/>
-    <mergeCell ref="B752:E752"/>
-    <mergeCell ref="B753:E753"/>
-    <mergeCell ref="B754:E754"/>
-    <mergeCell ref="B755:E755"/>
-    <mergeCell ref="B756:E756"/>
-    <mergeCell ref="B757:E757"/>
-    <mergeCell ref="B805:E805"/>
-    <mergeCell ref="B806:E806"/>
-    <mergeCell ref="B807:E807"/>
-    <mergeCell ref="B808:E808"/>
-    <mergeCell ref="B809:E809"/>
-    <mergeCell ref="B810:E810"/>
-    <mergeCell ref="B795:E795"/>
-    <mergeCell ref="B796:E796"/>
-    <mergeCell ref="B797:E797"/>
-    <mergeCell ref="B798:E798"/>
-    <mergeCell ref="B799:E799"/>
-    <mergeCell ref="B800:E800"/>
-    <mergeCell ref="B801:E801"/>
-    <mergeCell ref="B802:E802"/>
-    <mergeCell ref="B803:E803"/>
+    <mergeCell ref="B819:E819"/>
+    <mergeCell ref="B820:E820"/>
+    <mergeCell ref="B821:E821"/>
+    <mergeCell ref="B822:E822"/>
+    <mergeCell ref="B823:E823"/>
+    <mergeCell ref="B824:E824"/>
+    <mergeCell ref="B825:E825"/>
+    <mergeCell ref="B826:E826"/>
+    <mergeCell ref="B827:E827"/>
+    <mergeCell ref="B828:E828"/>
+    <mergeCell ref="B829:E829"/>
+    <mergeCell ref="B830:E830"/>
+    <mergeCell ref="B831:E831"/>
+    <mergeCell ref="B832:E832"/>
+    <mergeCell ref="B833:E833"/>
+    <mergeCell ref="B834:E834"/>
+    <mergeCell ref="B835:E835"/>
+    <mergeCell ref="B836:E836"/>
+    <mergeCell ref="B837:E837"/>
+    <mergeCell ref="B839:E839"/>
+    <mergeCell ref="B840:E840"/>
+    <mergeCell ref="B842:E842"/>
+    <mergeCell ref="B843:E843"/>
+    <mergeCell ref="B844:E844"/>
+    <mergeCell ref="B845:E845"/>
+    <mergeCell ref="B846:E846"/>
+    <mergeCell ref="B847:E847"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G56" r:id="rId1" display="106" xr:uid="{91711D96-DEE6-4487-B096-595B3971FA7B}"/>
@@ -48686,7 +49183,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="34">
         <f t="shared" ref="G3:G189" si="0">G4+F3</f>
-        <v>1737</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15">
@@ -48697,7 +49194,7 @@
       <c r="F4" s="45"/>
       <c r="G4" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I4" t="s">
         <v>270</v>
@@ -48715,7 +49212,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I5" t="s">
         <v>271</v>
@@ -48733,14 +49230,14 @@
       <c r="F6" s="45"/>
       <c r="G6" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I6" t="s">
         <v>272</v>
       </c>
       <c r="J6">
         <f>SUMIFS(F3:F30143,D3:D30143, "*JALカード*")</f>
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15">
@@ -48751,7 +49248,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I7" t="s">
         <v>273</v>
@@ -48769,7 +49266,7 @@
       <c r="F8" s="45"/>
       <c r="G8" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>274</v>
@@ -48787,7 +49284,7 @@
       <c r="F9" s="45"/>
       <c r="G9" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>275</v>
@@ -48805,7 +49302,7 @@
       <c r="F10" s="45"/>
       <c r="G10" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>276</v>
@@ -48823,14 +49320,14 @@
       <c r="F11" s="45"/>
       <c r="G11" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>277</v>
       </c>
       <c r="J11">
         <f>SUM(J4:J10)</f>
-        <v>1737</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15">
@@ -48841,7 +49338,7 @@
       <c r="F12" s="45"/>
       <c r="G12" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -48853,7 +49350,7 @@
       <c r="F13" s="45"/>
       <c r="G13" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -48865,7 +49362,7 @@
       <c r="F14" s="45"/>
       <c r="G14" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -48877,7 +49374,7 @@
       <c r="F15" s="45"/>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I15" s="31"/>
     </row>
@@ -48889,7 +49386,7 @@
       <c r="F16" s="45"/>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I16" s="31"/>
     </row>
@@ -48901,7 +49398,7 @@
       <c r="F17" s="45"/>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I17" s="31"/>
     </row>
@@ -48913,7 +49410,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I18" s="31"/>
     </row>
@@ -48925,7 +49422,7 @@
       <c r="F19" s="45"/>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I19" s="31"/>
     </row>
@@ -48937,7 +49434,7 @@
       <c r="F20" s="45"/>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I20" s="31"/>
     </row>
@@ -48949,7 +49446,7 @@
       <c r="F21" s="45"/>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I21" s="31"/>
     </row>
@@ -48961,7 +49458,7 @@
       <c r="F22" s="45"/>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I22" s="31"/>
     </row>
@@ -48973,19 +49470,29 @@
       <c r="F23" s="45"/>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I23" s="31"/>
     </row>
-    <row r="24" spans="2:9" ht="15">
-      <c r="B24" s="44"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
+    <row r="24" spans="2:9" ht="17.25">
+      <c r="B24" s="44">
+        <v>46276</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="F24" s="45">
+        <v>10</v>
+      </c>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I24" s="31"/>
     </row>
@@ -48994,13 +49501,13 @@
         <v>46268</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F25" s="45">
         <v>5</v>
@@ -49016,13 +49523,13 @@
         <v>46266</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D26" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F26" s="45">
         <v>5</v>
@@ -49038,13 +49545,13 @@
         <v>46255</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D27" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F27" s="45">
         <v>1</v>
@@ -49060,13 +49567,13 @@
         <v>46250</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D28" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F28" s="45">
         <v>1</v>
@@ -49082,13 +49589,13 @@
         <v>46249</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D29" s="45" t="s">
         <v>273</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F29" s="45">
         <v>1</v>
@@ -49104,13 +49611,13 @@
         <v>46249</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D30" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F30" s="45">
         <v>1</v>
@@ -49126,13 +49633,13 @@
         <v>46245</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D31" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F31" s="45">
         <v>10</v>
@@ -49148,13 +49655,13 @@
         <v>46231</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D32" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F32" s="45">
         <v>5</v>
@@ -49170,7 +49677,7 @@
         <v>46226</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>273</v>
@@ -49192,13 +49699,13 @@
         <v>46225</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D34" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F34" s="45">
         <v>1</v>
@@ -49214,13 +49721,13 @@
         <v>46225</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D35" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F35" s="45">
         <v>5</v>
@@ -49236,13 +49743,13 @@
         <v>46222</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D36" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F36" s="45">
         <v>1</v>
@@ -49258,13 +49765,13 @@
         <v>46220</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D37" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F37" s="45">
         <v>5</v>
@@ -49280,13 +49787,13 @@
         <v>46218</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F38" s="45">
         <v>1</v>
@@ -49302,13 +49809,13 @@
         <v>46217</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D39" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F39" s="45">
         <v>5</v>
@@ -49324,13 +49831,13 @@
         <v>46214</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D40" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E40" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F40" s="45">
         <v>5</v>
@@ -49346,13 +49853,13 @@
         <v>46201</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D41" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F41" s="45">
         <v>5</v>
@@ -49368,13 +49875,13 @@
         <v>46194</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D42" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F42" s="45">
         <v>2</v>
@@ -49390,7 +49897,7 @@
         <v>46191</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D43" s="45" t="s">
         <v>273</v>
@@ -49412,13 +49919,13 @@
         <v>46188</v>
       </c>
       <c r="C44" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D44" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F44" s="45">
         <v>1</v>
@@ -49434,13 +49941,13 @@
         <v>46185</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D45" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F45" s="45">
         <v>5</v>
@@ -49456,13 +49963,13 @@
         <v>46184</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D46" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F46" s="45">
         <v>15</v>
@@ -49478,13 +49985,13 @@
         <v>46184</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D47" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F47" s="45">
         <v>5</v>
@@ -49500,13 +50007,13 @@
         <v>46183</v>
       </c>
       <c r="C48" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D48" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F48" s="45">
         <v>5</v>
@@ -49522,13 +50029,13 @@
         <v>46182</v>
       </c>
       <c r="C49" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D49" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F49" s="45">
         <v>5</v>
@@ -49544,13 +50051,13 @@
         <v>46173</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D50" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F50" s="45">
         <v>5</v>
@@ -49566,13 +50073,13 @@
         <v>46172</v>
       </c>
       <c r="C51" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D51" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F51" s="45">
         <v>5</v>
@@ -49610,13 +50117,13 @@
         <v>46164</v>
       </c>
       <c r="C53" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D53" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F53" s="45">
         <v>1</v>
@@ -49632,7 +50139,7 @@
         <v>46163</v>
       </c>
       <c r="C54" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D54" s="45" t="s">
         <v>273</v>
@@ -49654,13 +50161,13 @@
         <v>46159</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D55" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F55" s="45">
         <v>1</v>
@@ -49676,13 +50183,13 @@
         <v>46157</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D56" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F56" s="45">
         <v>1</v>
@@ -49698,13 +50205,13 @@
         <v>46157</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D57" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F57" s="45">
         <v>5</v>
@@ -49720,13 +50227,13 @@
         <v>46153</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D58" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F58" s="45">
         <v>5</v>
@@ -49742,13 +50249,13 @@
         <v>46140</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D59" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F59" s="45">
         <v>40</v>
@@ -49764,13 +50271,13 @@
         <v>46139</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D60" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F60" s="45">
         <v>20</v>
@@ -49786,13 +50293,13 @@
         <v>46134</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D61" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F61" s="45">
         <v>1</v>
@@ -49808,13 +50315,13 @@
         <v>46131</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D62" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F62" s="45">
         <v>1</v>
@@ -49830,13 +50337,13 @@
         <v>46130</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D63" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F63" s="45">
         <v>5</v>
@@ -49852,7 +50359,7 @@
         <v>46129</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D64" s="45" t="s">
         <v>273</v>
@@ -49874,13 +50381,13 @@
         <v>46129</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D65" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F65" s="45">
         <v>5</v>
@@ -49896,13 +50403,13 @@
         <v>46127</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D66" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F66" s="45">
         <v>1</v>
@@ -49918,13 +50425,13 @@
         <v>46127</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D67" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F67" s="45">
         <v>40</v>
@@ -49940,13 +50447,13 @@
         <v>46125</v>
       </c>
       <c r="C68" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D68" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F68" s="45">
         <v>5</v>
@@ -49962,13 +50469,13 @@
         <v>46124</v>
       </c>
       <c r="C69" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D69" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F69" s="45">
         <v>30</v>
@@ -49984,13 +50491,13 @@
         <v>46121</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D70" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F70" s="45">
         <v>5</v>
@@ -50006,13 +50513,13 @@
         <v>46113</v>
       </c>
       <c r="C71" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D71" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F71" s="45">
         <v>5</v>
@@ -50028,13 +50535,13 @@
         <v>46111</v>
       </c>
       <c r="C72" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D72" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F72" s="45">
         <v>5</v>
@@ -50050,13 +50557,13 @@
         <v>46110</v>
       </c>
       <c r="C73" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D73" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F73" s="45">
         <v>1</v>
@@ -50094,13 +50601,13 @@
         <v>46107</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D75" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F75" s="45">
         <v>5</v>
@@ -50116,13 +50623,13 @@
         <v>46106</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D76" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F76" s="45">
         <v>5</v>
@@ -50160,13 +50667,13 @@
         <v>46102</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D78" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F78" s="45">
         <v>1</v>
@@ -50182,7 +50689,7 @@
         <v>46099</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D79" s="45" t="s">
         <v>273</v>
@@ -50204,13 +50711,13 @@
         <v>46096</v>
       </c>
       <c r="C80" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D80" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F80" s="45">
         <v>1</v>
@@ -50226,13 +50733,13 @@
         <v>46093</v>
       </c>
       <c r="C81" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D81" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F81" s="45">
         <v>50</v>
@@ -50248,13 +50755,13 @@
         <v>46092</v>
       </c>
       <c r="C82" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D82" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F82" s="45">
         <v>10</v>
@@ -50270,13 +50777,13 @@
         <v>46083</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D83" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F83" s="45">
         <v>10</v>
@@ -50292,13 +50799,13 @@
         <v>46080</v>
       </c>
       <c r="C84" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D84" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F84" s="45">
         <v>35</v>
@@ -50314,13 +50821,13 @@
         <v>46077</v>
       </c>
       <c r="C85" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D85" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F85" s="45">
         <v>40</v>
@@ -50336,13 +50843,13 @@
         <v>46076</v>
       </c>
       <c r="C86" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D86" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F86" s="45">
         <v>15</v>
@@ -50358,13 +50865,13 @@
         <v>46074</v>
       </c>
       <c r="C87" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D87" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F87" s="45">
         <v>1</v>
@@ -50380,7 +50887,7 @@
         <v>46071</v>
       </c>
       <c r="C88" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D88" s="45" t="s">
         <v>273</v>
@@ -50402,13 +50909,13 @@
         <v>46068</v>
       </c>
       <c r="C89" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D89" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F89" s="45">
         <v>1</v>
@@ -50424,13 +50931,13 @@
         <v>46066</v>
       </c>
       <c r="C90" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D90" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E90" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F90" s="45">
         <v>30</v>
@@ -50446,13 +50953,13 @@
         <v>46065</v>
       </c>
       <c r="C91" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D91" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E91" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F91" s="45">
         <v>10</v>
@@ -50468,13 +50975,13 @@
         <v>46064</v>
       </c>
       <c r="C92" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D92" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F92" s="45">
         <v>10</v>
@@ -50490,13 +50997,13 @@
         <v>46064</v>
       </c>
       <c r="C93" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D93" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F93" s="45">
         <v>5</v>
@@ -50512,13 +51019,13 @@
         <v>46063</v>
       </c>
       <c r="C94" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D94" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F94" s="45">
         <v>45</v>
@@ -50534,13 +51041,13 @@
         <v>46062</v>
       </c>
       <c r="C95" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D95" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F95" s="45">
         <v>25</v>
@@ -50556,13 +51063,13 @@
         <v>46061</v>
       </c>
       <c r="C96" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D96" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F96" s="45">
         <v>30</v>
@@ -50578,13 +51085,13 @@
         <v>46059</v>
       </c>
       <c r="C97" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D97" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F97" s="45">
         <v>5</v>
@@ -50600,13 +51107,13 @@
         <v>46057</v>
       </c>
       <c r="C98" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D98" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F98" s="45">
         <v>5</v>
@@ -50622,13 +51129,13 @@
         <v>46056</v>
       </c>
       <c r="C99" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D99" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F99" s="45">
         <v>5</v>
@@ -50666,13 +51173,13 @@
         <v>46054</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D101" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F101" s="45">
         <v>5</v>
@@ -50688,13 +51195,13 @@
         <v>46052</v>
       </c>
       <c r="C102" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D102" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F102" s="45">
         <v>5</v>
@@ -50710,13 +51217,13 @@
         <v>46051</v>
       </c>
       <c r="C103" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D103" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F103" s="45">
         <v>5</v>
@@ -50732,13 +51239,13 @@
         <v>46048</v>
       </c>
       <c r="C104" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D104" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F104" s="45">
         <v>30</v>
@@ -50754,13 +51261,13 @@
         <v>46047</v>
       </c>
       <c r="C105" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D105" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F105" s="45">
         <v>2</v>
@@ -50776,13 +51283,13 @@
         <v>46044</v>
       </c>
       <c r="C106" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D106" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F106" s="45">
         <v>10</v>
@@ -50798,7 +51305,7 @@
         <v>46041</v>
       </c>
       <c r="C107" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D107" s="45" t="s">
         <v>273</v>
@@ -50820,13 +51327,13 @@
         <v>46040</v>
       </c>
       <c r="C108" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D108" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F108" s="45">
         <v>5</v>
@@ -50842,13 +51349,13 @@
         <v>46039</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D109" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F109" s="45">
         <v>5</v>
@@ -50864,13 +51371,13 @@
         <v>46037</v>
       </c>
       <c r="C110" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D110" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F110" s="45">
         <v>1</v>
@@ -50886,13 +51393,13 @@
         <v>46035</v>
       </c>
       <c r="C111" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D111" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F111" s="45">
         <v>40</v>
@@ -50908,13 +51415,13 @@
         <v>46034</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D112" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F112" s="45">
         <v>20</v>
@@ -50930,13 +51437,13 @@
         <v>46033</v>
       </c>
       <c r="C113" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D113" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F113" s="45">
         <v>30</v>
@@ -50947,7 +51454,7 @@
       </c>
       <c r="J113">
         <f>SUM(J4:J11)</f>
-        <v>3474</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="17.25">
@@ -50955,13 +51462,13 @@
         <v>46033</v>
       </c>
       <c r="C114" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D114" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F114" s="45">
         <v>40</v>
@@ -50976,13 +51483,13 @@
         <v>46032</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D115" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F115" s="45">
         <v>10</v>
@@ -50997,13 +51504,13 @@
         <v>46030</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D116" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F116" s="45">
         <v>5</v>
@@ -51018,13 +51525,13 @@
         <v>46016</v>
       </c>
       <c r="C117" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D117" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E117" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F117" s="45">
         <v>5</v>
@@ -51039,13 +51546,13 @@
         <v>46014</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D118" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E118" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F118" s="45">
         <v>5</v>
@@ -51060,13 +51567,13 @@
         <v>46012</v>
       </c>
       <c r="C119" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D119" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E119" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F119" s="45">
         <v>1</v>
@@ -51081,13 +51588,13 @@
         <v>46012</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D120" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E120" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F120" s="45">
         <v>5</v>
@@ -51102,13 +51609,13 @@
         <v>46011</v>
       </c>
       <c r="C121" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D121" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E121" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F121" s="45">
         <v>5</v>
@@ -51123,7 +51630,7 @@
         <v>46008</v>
       </c>
       <c r="C122" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D122" s="45" t="s">
         <v>273</v>
@@ -51144,13 +51651,13 @@
         <v>46006</v>
       </c>
       <c r="C123" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D123" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E123" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F123" s="45">
         <v>1</v>
@@ -51165,13 +51672,13 @@
         <v>46002</v>
       </c>
       <c r="C124" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D124" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E124" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F124" s="45">
         <v>10</v>
@@ -51186,13 +51693,13 @@
         <v>45996</v>
       </c>
       <c r="C125" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D125" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E125" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F125" s="45">
         <v>45</v>
@@ -51207,13 +51714,13 @@
         <v>45995</v>
       </c>
       <c r="C126" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D126" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E126" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F126" s="45">
         <v>5</v>
@@ -51228,13 +51735,13 @@
         <v>45994</v>
       </c>
       <c r="C127" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D127" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E127" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F127" s="45">
         <v>5</v>
@@ -51249,13 +51756,13 @@
         <v>45990</v>
       </c>
       <c r="C128" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D128" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E128" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F128" s="45">
         <v>5</v>
@@ -51270,13 +51777,13 @@
         <v>45989</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D129" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E129" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F129" s="45">
         <v>5</v>
@@ -51312,13 +51819,13 @@
         <v>45988</v>
       </c>
       <c r="C131" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D131" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E131" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F131" s="45">
         <v>5</v>
@@ -51333,13 +51840,13 @@
         <v>45987</v>
       </c>
       <c r="C132" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D132" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E132" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F132" s="45">
         <v>5</v>
@@ -51354,13 +51861,13 @@
         <v>45985</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D133" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E133" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F133" s="45">
         <v>5</v>
@@ -51375,13 +51882,13 @@
         <v>45983</v>
       </c>
       <c r="C134" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D134" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E134" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F134" s="45">
         <v>5</v>
@@ -51396,13 +51903,13 @@
         <v>45982</v>
       </c>
       <c r="C135" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D135" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E135" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F135" s="45">
         <v>1</v>
@@ -51417,7 +51924,7 @@
         <v>45978</v>
       </c>
       <c r="C136" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D136" s="45" t="s">
         <v>273</v>
@@ -51438,13 +51945,13 @@
         <v>45976</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D137" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E137" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F137" s="45">
         <v>1</v>
@@ -51459,13 +51966,13 @@
         <v>45972</v>
       </c>
       <c r="C138" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D138" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E138" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F138" s="45">
         <v>20</v>
@@ -51501,13 +52008,13 @@
         <v>45956</v>
       </c>
       <c r="C140" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D140" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E140" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F140" s="45">
         <v>5</v>
@@ -51522,13 +52029,13 @@
         <v>45955</v>
       </c>
       <c r="C141" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D141" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E141" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F141" s="45">
         <v>5</v>
@@ -51543,13 +52050,13 @@
         <v>45953</v>
       </c>
       <c r="C142" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D142" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E142" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F142" s="45">
         <v>5</v>
@@ -51564,13 +52071,13 @@
         <v>45952</v>
       </c>
       <c r="C143" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D143" s="45" t="s">
         <v>275</v>
       </c>
       <c r="E143" s="45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F143" s="45">
         <v>1</v>
@@ -51585,13 +52092,13 @@
         <v>45951</v>
       </c>
       <c r="C144" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D144" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E144" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F144" s="45">
         <v>10</v>
@@ -51606,7 +52113,7 @@
         <v>45947</v>
       </c>
       <c r="C145" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D145" s="45" t="s">
         <v>273</v>
@@ -51627,13 +52134,13 @@
         <v>45945</v>
       </c>
       <c r="C146" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D146" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E146" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F146" s="45">
         <v>1</v>
@@ -51648,13 +52155,13 @@
         <v>45943</v>
       </c>
       <c r="C147" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D147" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E147" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F147" s="45">
         <v>5</v>
@@ -51669,13 +52176,13 @@
         <v>45941</v>
       </c>
       <c r="C148" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D148" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E148" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F148" s="45">
         <v>15</v>
@@ -51690,13 +52197,13 @@
         <v>45941</v>
       </c>
       <c r="C149" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D149" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E149" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F149" s="45">
         <v>5</v>
@@ -51711,13 +52218,13 @@
         <v>45937</v>
       </c>
       <c r="C150" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D150" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E150" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F150" s="45">
         <v>35</v>
@@ -51732,13 +52239,13 @@
         <v>45936</v>
       </c>
       <c r="C151" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D151" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E151" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F151" s="45">
         <v>5</v>
@@ -51753,13 +52260,13 @@
         <v>45934</v>
       </c>
       <c r="C152" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D152" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E152" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F152" s="45">
         <v>5</v>
@@ -51774,13 +52281,13 @@
         <v>45930</v>
       </c>
       <c r="C153" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D153" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E153" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F153" s="45">
         <v>45</v>
@@ -51795,13 +52302,13 @@
         <v>45929</v>
       </c>
       <c r="C154" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D154" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E154" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F154" s="45">
         <v>45</v>
@@ -51816,13 +52323,13 @@
         <v>45928</v>
       </c>
       <c r="C155" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D155" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E155" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F155" s="45">
         <v>35</v>
@@ -51837,13 +52344,13 @@
         <v>45919</v>
       </c>
       <c r="C156" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D156" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E156" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F156" s="45">
         <v>5</v>
@@ -51858,13 +52365,13 @@
         <v>45917</v>
       </c>
       <c r="C157" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D157" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E157" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F157" s="45">
         <v>5</v>
@@ -51879,7 +52386,7 @@
         <v>45916</v>
       </c>
       <c r="C158" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D158" s="45" t="s">
         <v>273</v>
@@ -51900,13 +52407,13 @@
         <v>45915</v>
       </c>
       <c r="C159" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D159" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E159" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F159" s="45">
         <v>1</v>
@@ -51921,13 +52428,13 @@
         <v>45911</v>
       </c>
       <c r="C160" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D160" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E160" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F160" s="45">
         <v>5</v>
@@ -51942,13 +52449,13 @@
         <v>45905</v>
       </c>
       <c r="C161" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D161" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E161" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F161" s="45">
         <v>5</v>
@@ -51963,13 +52470,13 @@
         <v>45903</v>
       </c>
       <c r="C162" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D162" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E162" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F162" s="45">
         <v>5</v>
@@ -51984,13 +52491,13 @@
         <v>45893</v>
       </c>
       <c r="C163" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D163" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E163" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F163" s="45">
         <v>5</v>
@@ -52005,13 +52512,13 @@
         <v>45892</v>
       </c>
       <c r="C164" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D164" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F164" s="45">
         <v>5</v>
@@ -52026,7 +52533,7 @@
         <v>45888</v>
       </c>
       <c r="C165" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D165" s="45" t="s">
         <v>273</v>
@@ -52047,13 +52554,13 @@
         <v>45884</v>
       </c>
       <c r="C166" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D166" s="45" t="s">
         <v>274</v>
       </c>
       <c r="E166" s="45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F166" s="45">
         <v>1</v>
@@ -52068,13 +52575,13 @@
         <v>45877</v>
       </c>
       <c r="C167" s="45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D167" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E167" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F167" s="45">
         <v>10</v>
@@ -52089,13 +52596,13 @@
         <v>45874</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D168" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E168" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F168" s="33">
         <v>5</v>
@@ -52110,13 +52617,13 @@
         <v>45873</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D169" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E169" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F169" s="33">
         <v>5</v>
@@ -52131,13 +52638,13 @@
         <v>45867</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D170" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E170" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F170" s="33">
         <v>5</v>
@@ -52152,13 +52659,13 @@
         <v>45862</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D171" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E171" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F171" s="33">
         <v>5</v>
@@ -52173,13 +52680,13 @@
         <v>45838</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F172" s="33">
         <v>5</v>
@@ -52194,13 +52701,13 @@
         <v>45836</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F173" s="33">
         <v>5</v>
@@ -52215,13 +52722,13 @@
         <v>45789</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D174" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F174" s="33">
         <v>5</v>
@@ -52236,13 +52743,13 @@
         <v>45786</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D175" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E175" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F175" s="33">
         <v>5</v>
@@ -52257,13 +52764,13 @@
         <v>45729</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D176" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E176" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F176" s="33">
         <v>10</v>
@@ -52278,13 +52785,13 @@
         <v>45684</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D177" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E177" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F177" s="33">
         <v>5</v>
@@ -52299,13 +52806,13 @@
         <v>45682</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D178" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E178" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F178" s="33">
         <v>5</v>
@@ -52320,13 +52827,13 @@
         <v>45652</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D179" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E179" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F179" s="33">
         <v>5</v>
@@ -52341,13 +52848,13 @@
         <v>45649</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D180" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E180" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F180" s="33">
         <v>5</v>
@@ -52362,13 +52869,13 @@
         <v>45648</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D181" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E181" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F181" s="33">
         <v>5</v>
@@ -52383,13 +52890,13 @@
         <v>45614</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D182" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F182" s="33">
         <v>5</v>
@@ -52404,13 +52911,13 @@
         <v>45613</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E183" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F183" s="33">
         <v>5</v>
@@ -52425,13 +52932,13 @@
         <v>45592</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D184" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E184" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F184" s="33">
         <v>5</v>
@@ -52446,13 +52953,13 @@
         <v>45591</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D185" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E185" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F185" s="33">
         <v>5</v>
@@ -52467,13 +52974,13 @@
         <v>45514</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D186" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E186" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F186" s="33">
         <v>5</v>
@@ -52488,13 +52995,13 @@
         <v>45513</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>270</v>
       </c>
       <c r="E187" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F187" s="33">
         <v>5</v>
@@ -52509,7 +53016,7 @@
         <v>45335</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D188" s="33" t="s">
         <v>291</v>
@@ -52530,7 +53037,7 @@
         <v>45334</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D189" s="33" t="s">
         <v>291</v>
@@ -52551,7 +53058,7 @@
         <v>45291</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D190" s="33" t="s">
         <v>291</v>
@@ -52572,13 +53079,13 @@
         <v>45291</v>
       </c>
       <c r="C191" s="68" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D191" s="68" t="s">
         <v>270</v>
       </c>
       <c r="E191" s="68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F191" s="68">
         <v>10</v>
